--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="585">
   <si>
     <t xml:space="preserve">STM v2 (UCSD) - budget summary, lean scenario</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">1 Piezo scanner and coarse-approach actuator</t>
+    <t xml:space="preserve">1 Piezo scanner and stepper coarse approach</t>
   </si>
   <si>
     <t xml:space="preserve">2 Piezo driver (DIY, provisional)</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">4 Preamp specialty parts (Baird's changes)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 Printed head, sample plate and approach hardware</t>
+    <t xml:space="preserve">5 Printed head, sample plate and hardware</t>
   </si>
   <si>
     <t xml:space="preserve">Purchased components</t>
@@ -118,16 +118,7 @@
     <t xml:space="preserve">Options and their effect</t>
   </si>
   <si>
-    <t xml:space="preserve">Steel balls (ME-04) instead of sapphire contacts (merchandise)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keeps the stick-slip approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Total with that cut (tax and contingency scaled; shipping for Edmund removed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screw drive (B) instead of stick-slip (A), merchandise</t>
+    <t xml:space="preserve">Stick-slip approach instead of the stepper (not chosen), merchandise</t>
   </si>
   <si>
     <t xml:space="preserve">Piezo option P2: TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
@@ -238,1549 +229,1546 @@
     <t xml:space="preserve">PZ-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Piezo stack for the stick-slip coarse approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive SA050510 (5x5x10 mm, 150 V)</t>
+    <t xml:space="preserve">Coarse-approach stepper motor, NEMA-17, 200 steps/rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit 324 (12 V, 350 mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.adafruit.com/product/324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. Jacob's choice (2026-10-21): stay with a stepper-driven screw instead of stick-slip. Replaces v1's geared 28BYJ-48. Runs from a 12 V bench supply (campus).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stepper driver, microstepping (up to 1/256)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit 6121 (TMC2209 breakout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://adafruit.com/product/6121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. Replaces v1's ULN2003; step/dir from the Teensy. Fine microstepping gives about 6 nm of screw travel per microstep before any lever.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine-pitch adjuster screws, 1/4-80 (one motor-driven, two hand-set)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thorlabs FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thorlabs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical - v1 receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same screws as v1 (three bought 2026-06-24 at $8.78). Thorlabs pages do not load from here, so this is v1's price. 1/4-80 is 317.5 um per turn. v1 ran them in printed threads; matching brass bushings are not priced (U6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-voltage op-amp, one per channel (5 tube + 1 spare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TI OPA454AIDDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lcsc.com/product-detail/C50636.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, 241 in stock. The driver circuit is not designed yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer for the +/-45-50 V rails</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toroid, secondary not chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jameco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO EXACT PRODUCT PAGE: the secondary voltage is not chosen. The link is the nearest verified part (Hammond 182M18, 2 x 18 V, $67.85), which is NOT the right voltage; used as a price placeholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rectifier, filter caps, HV regulators, heatsinks, HV connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(no link - see notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO PRODUCT LINK: parts not chosen because the circuit is not drawn. Reference prices seen: GBU4J $1.25, Nichicon UVZ2A102 $2.28, TL783 $3.80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV driver bare PCB (rides the JLCPCB order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlcpcb.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min order 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link is JLCPCB's ordering site; a PCB has no product page until gerbers are uploaded. $2 for five is from a Hack Club guide (undated).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">each (2 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 invoice 2026-07-15 unit price. Re-quote not possible from here: JLCPCB prices only after gerber + BOM upload. Parts prices have moved since (e.g. LT1469 now $23.77 and out of stock at LCSC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preamp board, fully assembled (rev 2 gerbers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 unit price for the rev 1 preamp. Rev 2 adds 4.7 uF 50 V 1812 caps, a few cents each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare controller PCBs (as in the v1 order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 invoice line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare preamp PCBs (as in the v1 order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dual op-amp U21, bought separately in v1 alongside the JLCPCB order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 bought 2 at DigiKey ($16.35). DigiKey page blocked here; price is Mouser's via an aggregator. URL from search results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microcontroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teensy 4.1 (SparkFun DEV-16771)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SparkFun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sparkfun.com/teensy-4-1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page. Headers are campus stock. v1 paid $43.22 on Amazon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 GOhm feedback resistor, soldered across the op-amp pins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified - aggregator listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 + 1 spare (it is the part Baird's change depends on). URL from search results; DigiKey blocks this environment, price via aggregator (1,673 in stock).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTFE standoff terminal for the air-wired input node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/part/keystone/11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND (DigiKey 36-11301-ND); link is the Octopart listing (Mouser $2.03). v1 paid $2.09 at DigiKey.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 V lithium batteries for the analog supply (two give +/-9 V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energizer Ultimate Lithium L522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryMart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. Alkaline 4-pack at Battery Junction is $18.95 but was out of stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 V battery holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature sensor, +/-0.1 C (head and preamp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit 4821 (TI TMP117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://adafruit.com/product/4821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page. Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D-printing filament for head, sample plate and approach body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prusa Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 kg spool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. One spool covers the parts and reprints. Material is still open: PETG-CF is stiff and easy to print; nylon-CF is stiffer but needs a dried, hardened-nozzle printer. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice for this budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walmart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Components subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor and order totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales or use tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 Thorlabs order shipping, 2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships from the US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forum report Dec 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL ORDERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(should be 0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved out of the purchase list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference value if bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir tip wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind from a UCSD lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOPG sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D printer time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite base or optical breadboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield enclosures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise only. DIY driver = the 'Piezo driver' lines in the BOM. The total uses P1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver / dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change vs P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. XY (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. Z (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~13-16 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~3 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD250-INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 (spec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~8.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coarse approach and sample plate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Two hand-set 1/4-80 screws and the motor screw form the tripod, with steel-ball pivots (ME-04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not chosen, for the record: piezo stick-slip slider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive SA050510</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/</t>
   </si>
   <si>
-    <t xml:space="preserve">Direct product page. Same PiezoDrive shipment as PZ-01. Replaces v1's geared 28BYJ-48 approach.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High-voltage op-amp, one per channel (5 tube + 1 stick-slip + 1 spare)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TI OPA454AIDDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.lcsc.com/product-detail/C50636.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, 241 in stock. The driver circuit is not designed yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer for the +/-45-50 V rails</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toroid, secondary not chosen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jameco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO EXACT PRODUCT PAGE: the secondary voltage is not chosen. The link is the nearest verified part (Hammond 182M18, 2 x 18 V, $67.85), which is NOT the right voltage; used as a price placeholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rectifier, filter caps, HV regulators, heatsinks, HV connectors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(no link - see notes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO PRODUCT LINK: parts not chosen because the circuit is not drawn. Reference prices seen: GBU4J $1.25, Nichicon UVZ2A102 $2.28, TL783 $3.80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV driver bare PCB (rides the JLCPCB order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min order 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link is JLCPCB's ordering site; a PCB has no product page until gerbers are uploaded. $2 for five is from a Hack Club guide (undated).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">each (2 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Historical - v1 receipt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 invoice 2026-07-15 unit price. Re-quote not possible from here: JLCPCB prices only after gerber + BOM upload. Parts prices have moved since (e.g. LT1469 now $23.77 and out of stock at LCSC).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preamp board, fully assembled (rev 2 gerbers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 unit price for the rev 1 preamp. Rev 2 adds 4.7 uF 50 V 1812 caps, a few cents each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare controller PCBs (as in the v1 order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 invoice line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare preamp PCBs (as in the v1 order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual op-amp U21, bought separately in v1 alongside the JLCPCB order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Devices LT1469IN8#PBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DigiKey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 bought 2 at DigiKey ($16.35). DigiKey page blocked here; price is Mouser's via an aggregator. URL from search results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microcontroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SparkFun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sparkfun.com/teensy-4-1.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page. Headers are campus stock. v1 paid $43.22 on Amazon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 GOhm feedback resistor, soldered across the op-amp pins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified - aggregator listing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 + 1 spare (it is the part Baird's change depends on). URL from search results; DigiKey blocks this environment, price via aggregator (1,673 in stock).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTFE standoff terminal for the air-wired input node</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/part/keystone/11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND (DigiKey 36-11301-ND); link is the Octopart listing (Mouser $2.03). v1 paid $2.09 at DigiKey.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 V lithium batteries for the analog supply (two give +/-9 V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. Alkaline 4-pack at Battery Junction is $18.95 but was out of stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 V battery holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature sensor, +/-0.1 C (head and preamp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adafruit 4821 (TI TMP117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adafruit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://adafruit.com/product/4821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page. Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D-printing filament for head, sample plate and approach body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusa Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 kg spool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. One spool covers the parts and reprints. Material is still open: PETG-CF is stiff and easy to print; nylon-CF is stiffer but needs a dried, hardened-nozzle printer. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice for this budget.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sapphire balls as stick-slip contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edmund Optics 43-642, 2.0 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edmund Optics</t>
+    <t xml:space="preserve">Also needed a sawtooth HV channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapphire contacts, 2 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmund Optics 43-642</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/</t>
   </si>
   <si>
-    <t xml:space="preserve">Direct product page (20+ in stock). Count depends on slider design.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Precision-ground rod for slider guides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in x 36 in (#4653)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlineMetals</t>
+    <t xml:space="preserve">Ground guide rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1</t>
   </si>
   <si>
-    <t xml:space="preserve">36 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category page lists this size and price; select 1/8 in x 36 in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walmart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolate It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Components subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor and order totals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales or use tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum report Dec 2025.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL ORDERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(should be 0.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moved out of the purchase list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference value if bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir tip wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind from a UCSD lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOPG sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D printer time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite base or optical breadboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shield enclosures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise only. DIY driver = the 'Piezo driver' lines in the BOM. The total uses P1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver / dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change vs P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. XY (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. Z (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~13-16 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~3 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TD250-INV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 (spec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~8.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coarse approach and sample plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1's rubber-band/spring plate and geared stepper are retired. Body parts are printed (ME-01); only specialty hardware is bought.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A (baseline): stick-slip slider = PZ-02 + ME-02 + ME-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A with steel balls (ME-04, already bought) instead of sapphire contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B: spring-preloaded screw drive with stepper (Zahl's rules)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/4-80 fine screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thorlabs FAS-series (v1: FAS200 $8.78)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thorlabs page did not load here; v1 receipt price. Bushings/springs from campus stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stepper motor 0.9 deg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEPPERONLINE 17HM19-2004S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tindie.com/products/stepperonline/nema-17-stepper-motor-46ncm651ozin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stepper driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BigTreeTech TMC2209 V1.3</t>
+    <t xml:space="preserve">Stick-slip parts total (merchandise, plus one OPA454 channel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference vs the chosen stepper drive (positive = stick-slip costs more)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch). No springs or rubber bands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 purchases (historical prices)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer / part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / import tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. sales tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed line cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed unit cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-layer bare STM controller PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor invoice (kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approach scenario B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTL-28 (different part)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 11311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(not in v2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoiced orders total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total under $2,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See total vs ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind and campus tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered (assumed, unverified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No reuse of v1 parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vasquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; driver provisional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate replaced, not v1's springs; coarse approach stays a stepper (Jacob)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02..04, ME-04, ME-05, Approach options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detailed BOM 'Source link'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature monitoring; enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflicts with the printed structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN - flagged (U4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel balls at pivots; stiff screw drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04; PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope the preamp output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus, unverified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions and unresolved costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied to all merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% for price drift and breakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure is printed; kept for reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unresolved items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect on the total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What would resolve it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV driver design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04: $158.20 incl. transformer placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB price today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus items really free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed (Jacob's choice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filament choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick based on the campus printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screw bushings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping and duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate shown; DAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant price not displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$35 estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item or topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02 Adafruit 324 (12 V, 350 mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-03 Adafruit 6121 (TMC2209 breakout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-03 not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no link - see BOM note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02 Keystone 11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-03 Energizer Ultimate Lithium L522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04 Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-01 Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD MPL machine shop rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision access rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vetco MG 8331D-14G $167.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kozak Micro 1/4-80 screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMC2209 driver $4.25</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sold out at check.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change vs A if B replaces it (removes PZ-02, ME-02, ME-03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 purchases (historical prices)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturer / part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / import tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. sales tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed line cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed unit cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v2 line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-layer bare STM controller PCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor invoice (kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thorlabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thorlabs FAS200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approach scenario B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTL-28 (different part)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 11311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(not in v2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoiced orders total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where it is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total under $2,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See total vs ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind and campus tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered (assumed, unverified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No reuse of v1 parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; driver provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate and approach replaced, not v1's springs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02, ME-02..05, Approach options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detailed BOM 'Source link'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature monitoring; enclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conflicts with the printed structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN - flagged (U4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel balls at pivots; spring preload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04; Approach B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baird</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope the preamp output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus, unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions and unresolved costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied to all merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% for price drift and breakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure is printed; kept for reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob's requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unresolved items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect on the total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What would resolve it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV driver design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04: $164.92 incl. transformer placeholder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB price today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus items really free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed (Jacob's choice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filament choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick based on the campus printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approach choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stick-slip vs spring-preloaded screw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stick-slip (PZ-02, ME-02, ME-03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel balls instead of sapphire: -$84.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide with the advisers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping and duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate shown; DAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variant price not displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$35 estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item or topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02 PiezoDrive SA050510 (5x5x10 mm, 150 V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-03 not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no link - see BOM note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02 Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03 Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04 Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-01 Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-02 Edmund Optics 43-642, 2.0 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-03 OnlineMetals W1 drill rod 1/8 in x 36 in (#4653)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD MPL machine shop rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision access rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vetco MG 8331D-14G $167.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kozak Micro 1/4-80 screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMC2209 driver $4.25</t>
   </si>
   <si>
     <t xml:space="preserve">Prusament PETG Carbon Fiber 1 kg $54.99 (MatterHackers lists the same spool at $89.99)</t>
@@ -2273,7 +2261,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="64"/>
@@ -2313,7 +2301,7 @@
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A5,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>199</v>
+        <v>180.29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2322,7 +2310,7 @@
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A6,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>164.9229</v>
+        <v>158.1982</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2349,7 +2337,7 @@
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A9,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>219.55</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2358,7 +2346,7 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">SUM(B5:B9)</f>
-        <v>1227.0729</v>
+        <v>1112.0682</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
@@ -2370,7 +2358,7 @@
       </c>
       <c r="B11" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$27,"Verified*",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>546.4629</v>
+        <v>405.1182</v>
       </c>
       <c r="C11" s="7"/>
     </row>
@@ -2380,7 +2368,7 @@
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$27,"Historical*",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>491.24</v>
+        <v>517.58</v>
       </c>
       <c r="C12" s="7"/>
     </row>
@@ -2399,8 +2387,8 @@
         <v>16</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!C21</f>
-        <v>219</v>
+        <f aca="false">'Vendor-order totals'!C20</f>
+        <v>214.26</v>
       </c>
       <c r="C14" s="7"/>
     </row>
@@ -2409,8 +2397,8 @@
         <v>17</v>
       </c>
       <c r="B15" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!G21</f>
-        <v>228.997715</v>
+        <f aca="false">'Vendor-order totals'!G20</f>
+        <v>219.84407</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>18</v>
@@ -2421,7 +2409,7 @@
         <v>19</v>
       </c>
       <c r="B16" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!J19</f>
+        <f aca="false">'Vendor-order totals'!J18</f>
         <v>65</v>
       </c>
       <c r="C16" s="7"/>
@@ -2431,8 +2419,8 @@
         <v>20</v>
       </c>
       <c r="B17" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!I21</f>
-        <v>95.09814975</v>
+        <f aca="false">'Vendor-order totals'!I20</f>
+        <v>86.1852855</v>
       </c>
       <c r="C17" s="7"/>
     </row>
@@ -2442,7 +2430,7 @@
       </c>
       <c r="B18" s="5" t="n">
         <f aca="false">B10+B14+B15+B16+B17</f>
-        <v>1835.16876475</v>
+        <v>1697.3575555</v>
       </c>
       <c r="C18" s="6"/>
     </row>
@@ -2452,7 +2440,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">B18*Assumptions!B6</f>
-        <v>183.516876475</v>
+        <v>169.73575555</v>
       </c>
       <c r="C19" s="7"/>
     </row>
@@ -2462,7 +2450,7 @@
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">B18+B19</f>
-        <v>2018.685641225</v>
+        <v>1867.09331105</v>
       </c>
       <c r="C20" s="10"/>
     </row>
@@ -2482,7 +2470,7 @@
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">Assumptions!B9-B20</f>
-        <v>-18.6856412249999</v>
+        <v>132.90668895</v>
       </c>
       <c r="C22" s="7"/>
     </row>
@@ -2491,7 +2479,7 @@
         <v>26</v>
       </c>
       <c r="B23" s="3" t="n">
-        <f aca="false">B20-'Vendor-order totals'!J21*(1+Assumptions!B6)</f>
+        <f aca="false">B20-'Vendor-order totals'!J20*(1+Assumptions!B6)</f>
         <v>0</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2513,143 +2501,121 @@
         <v>29</v>
       </c>
       <c r="B26" s="3" t="n">
-        <f aca="false">-INDEX('Detailed BOM'!$K$5:$K$27,MATCH("ME-02",'Detailed BOM'!$A$5:$A$27,0))</f>
-        <v>-84.75</v>
-      </c>
-      <c r="C26" s="7" t="s">
+        <f aca="false">'Approach options'!F14</f>
+        <v>115.0047</v>
+      </c>
+      <c r="C26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="9" t="n">
-        <f aca="false">B20+(B26*(1+Assumptions!B5)-10)*(1+Assumptions!B6)</f>
-        <v>1907.235703725</v>
-      </c>
-      <c r="C27" s="10"/>
+      <c r="B27" s="3" t="n">
+        <f aca="false">'Piezo options'!I6</f>
+        <v>733.8018</v>
+      </c>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3" t="n">
-        <f aca="false">'Approach options'!F13</f>
-        <v>-104.99</v>
+        <f aca="false">'Piezo options'!I7</f>
+        <v>3013.8018</v>
       </c>
       <c r="C28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="3" t="n">
-        <f aca="false">'Piezo options'!I6</f>
-        <v>727.0771</v>
+        <f aca="false">'Piezo options'!I8</f>
+        <v>-20</v>
       </c>
       <c r="C29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="3" t="n">
-        <f aca="false">'Piezo options'!I7</f>
-        <v>3007.0771</v>
+        <f aca="false">'Piezo options'!I9</f>
+        <v>25</v>
       </c>
       <c r="C30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="3" t="n">
-        <f aca="false">'Piezo options'!I8</f>
-        <v>-20</v>
+        <f aca="false">'Piezo options'!I10</f>
+        <v>100</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <f aca="false">133.13</f>
+        <v>133.13</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="3" t="n">
-        <f aca="false">'Piezo options'!I9</f>
-        <v>25</v>
-      </c>
-      <c r="C32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>37</v>
       </c>
       <c r="B33" s="3" t="n">
-        <f aca="false">'Piezo options'!I10</f>
-        <v>100</v>
+        <f aca="false">42.74</f>
+        <v>42.74</v>
       </c>
       <c r="C33" s="7"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="3" t="n">
-        <f aca="false">133.13</f>
-        <v>133.13</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <f aca="false">42.74</f>
-        <v>42.74</v>
-      </c>
-      <c r="C35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>2</v>
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>3006.93</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="0" t="s">
         <v>41</v>
       </c>
+      <c r="B37" s="3" t="n">
+        <v>2626.74</v>
+      </c>
+      <c r="C37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>3006.93</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>2626.74</v>
-      </c>
-      <c r="C39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2677,7 +2643,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2687,34 +2653,34 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2724,417 +2690,417 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>528</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>529</v>
+        <v>523</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>96</v>
+        <v>525</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>330</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B9" r:id="rId1" display="https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/"/>
-    <hyperlink ref="B10" r:id="rId2" display="https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/"/>
-    <hyperlink ref="B11" r:id="rId3" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="B12" r:id="rId4" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="B14" r:id="rId5" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B15" r:id="rId6" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B10" r:id="rId2" display="https://www.adafruit.com/product/324"/>
+    <hyperlink ref="B11" r:id="rId3" display="https://adafruit.com/product/6121"/>
+    <hyperlink ref="B12" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
+    <hyperlink ref="B13" r:id="rId5" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="B14" r:id="rId6" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
     <hyperlink ref="B16" r:id="rId7" display="https://jlcpcb.com/"/>
     <hyperlink ref="B17" r:id="rId8" display="https://jlcpcb.com/"/>
     <hyperlink ref="B18" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B19" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="B20" r:id="rId11" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="B21" r:id="rId12" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="B22" r:id="rId13" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="B23" r:id="rId14" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
-    <hyperlink ref="B24" r:id="rId15" display="https://octopart.com/part/keystone/1294"/>
-    <hyperlink ref="B25" r:id="rId16" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="B26" r:id="rId17" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
-    <hyperlink ref="B27" r:id="rId18" display="https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/"/>
-    <hyperlink ref="B28" r:id="rId19" display="https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1"/>
+    <hyperlink ref="B19" r:id="rId10" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B20" r:id="rId11" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B21" r:id="rId12" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="B22" r:id="rId13" display="https://www.sparkfun.com/teensy-4-1.html"/>
+    <hyperlink ref="B23" r:id="rId14" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="B24" r:id="rId15" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="B25" r:id="rId16" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="B26" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="B27" r:id="rId18" display="https://adafruit.com/product/4821"/>
+    <hyperlink ref="B28" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
     <hyperlink ref="B29" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
     <hyperlink ref="B30" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
     <hyperlink ref="B31" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
@@ -3197,12 +3163,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3212,40 +3178,40 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>5</v>
@@ -3253,28 +3219,28 @@
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="15" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>64</v>
       </c>
       <c r="G5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>1</v>
@@ -3287,307 +3253,307 @@
         <v>131</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F6" s="15" t="s">
         <v>69</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>71</v>
       </c>
       <c r="G6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="K6" s="3" t="n">
         <f aca="false">I6*J6</f>
+        <v>14</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="F7" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>77</v>
-      </c>
       <c r="G7" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>6.7247</v>
+        <v>8.95</v>
       </c>
       <c r="K7" s="3" t="n">
         <f aca="false">I7*J7</f>
-        <v>47.0729</v>
+        <v>8.95</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E8" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="F8" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="G8" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>67.85</v>
+        <v>8.78</v>
       </c>
       <c r="K8" s="3" t="n">
         <f aca="false">I8*J8</f>
-        <v>67.85</v>
+        <v>26.34</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="G9" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>40</v>
+        <v>6.7247</v>
       </c>
       <c r="K9" s="3" t="n">
         <f aca="false">I9*J9</f>
-        <v>40</v>
+        <v>40.3482</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>93</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>96</v>
       </c>
       <c r="G10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2</v>
+        <v>67.85</v>
       </c>
       <c r="K10" s="3" t="n">
         <f aca="false">I10*J10</f>
-        <v>10</v>
+        <v>67.85</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M10" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="E11" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="G11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>102</v>
-      </c>
       <c r="I11" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>209.64</v>
+        <v>40</v>
       </c>
       <c r="K11" s="3" t="n">
         <f aca="false">I11*J11</f>
-        <v>419.28</v>
+        <v>40</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="F12" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="G12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G12" s="0" t="n">
+      <c r="I12" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>30.17</v>
       </c>
       <c r="K12" s="3" t="n">
         <f aca="false">I12*J12</f>
-        <v>60.34</v>
+        <v>10</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>109</v>
       </c>
@@ -3601,520 +3567,520 @@
         <v>111</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G13" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1.68</v>
+        <v>209.64</v>
       </c>
       <c r="K13" s="3" t="n">
         <f aca="false">I13*J13</f>
-        <v>5.04</v>
+        <v>419.28</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.8</v>
+        <v>30.17</v>
       </c>
       <c r="K14" s="3" t="n">
         <f aca="false">I14*J14</f>
-        <v>2.4</v>
+        <v>60.34</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="G15" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>18.26</v>
+        <v>1.68</v>
       </c>
       <c r="K15" s="3" t="n">
         <f aca="false">I15*J15</f>
-        <v>36.52</v>
+        <v>5.04</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>31.5</v>
+        <v>0.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <f aca="false">I16*J16</f>
-        <v>31.5</v>
+        <v>2.4</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="F17" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>130</v>
-      </c>
       <c r="G17" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I17" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.73</v>
+        <v>18.26</v>
       </c>
       <c r="K17" s="3" t="n">
         <f aca="false">I17*J17</f>
-        <v>11.46</v>
+        <v>36.52</v>
       </c>
       <c r="L17" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="D18" s="7" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="E18" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7" t="s">
+      <c r="F18" s="15" t="s">
         <v>134</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>136</v>
       </c>
       <c r="G18" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.09</v>
+        <v>31.5</v>
       </c>
       <c r="K18" s="3" t="n">
         <f aca="false">I18*J18</f>
-        <v>4.18</v>
+        <v>31.5</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>142</v>
-      </c>
       <c r="G19" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I19" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>21.95</v>
+        <v>5.73</v>
       </c>
       <c r="K19" s="3" t="n">
         <f aca="false">I19*J19</f>
-        <v>43.9</v>
+        <v>11.46</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>147</v>
-      </c>
       <c r="G20" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I20" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.99</v>
+        <v>2.09</v>
       </c>
       <c r="K20" s="3" t="n">
         <f aca="false">I20*J20</f>
-        <v>5.98</v>
+        <v>4.18</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="F21" s="15" t="s">
         <v>151</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>153</v>
       </c>
       <c r="G21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I21" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>11.5</v>
+        <v>21.95</v>
       </c>
       <c r="K21" s="3" t="n">
         <f aca="false">I21*J21</f>
-        <v>23</v>
+        <v>43.9</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M21" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="D22" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="E22" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F22" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="G22" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>54.99</v>
+        <v>2.99</v>
       </c>
       <c r="K22" s="3" t="n">
         <f aca="false">I22*J22</f>
-        <v>54.99</v>
+        <v>5.98</v>
       </c>
       <c r="L22" s="14" t="s">
-        <v>66</v>
+        <v>140</v>
       </c>
       <c r="M22" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>162</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>166</v>
-      </c>
       <c r="G23" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.25</v>
+        <v>11.5</v>
       </c>
       <c r="K23" s="3" t="n">
         <f aca="false">I23*J23</f>
-        <v>84.75</v>
+        <v>23</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>4.82</v>
+        <v>54.99</v>
       </c>
       <c r="K24" s="3" t="n">
         <f aca="false">I24*J24</f>
-        <v>4.82</v>
+        <v>54.99</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G25" s="0" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I25" s="0" t="n">
         <v>1</v>
@@ -4127,36 +4093,36 @@
         <v>9.99</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I26" s="0" t="n">
         <v>1</v>
@@ -4169,36 +4135,36 @@
         <v>30</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G27" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I27" s="0" t="n">
         <v>1</v>
@@ -4211,10 +4177,10 @@
         <v>35</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4224,34 +4190,34 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="K29" s="12" t="n">
         <f aca="false">SUM(K5:K27)</f>
-        <v>1227.0729</v>
+        <v>1112.0682</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F5" r:id="rId1" display="https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/"/>
-    <hyperlink ref="F6" r:id="rId2" display="https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="F10" r:id="rId5" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F11" r:id="rId6" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F6" r:id="rId2" display="https://www.adafruit.com/product/324"/>
+    <hyperlink ref="F7" r:id="rId3" display="https://adafruit.com/product/6121"/>
+    <hyperlink ref="F8" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
+    <hyperlink ref="F9" r:id="rId5" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="F10" r:id="rId6" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
     <hyperlink ref="F12" r:id="rId7" display="https://jlcpcb.com/"/>
     <hyperlink ref="F13" r:id="rId8" display="https://jlcpcb.com/"/>
     <hyperlink ref="F14" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F15" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="F16" r:id="rId11" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="F17" r:id="rId12" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="F18" r:id="rId13" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="F19" r:id="rId14" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
-    <hyperlink ref="F20" r:id="rId15" display="https://octopart.com/part/keystone/1294"/>
-    <hyperlink ref="F21" r:id="rId16" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="F22" r:id="rId17" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
-    <hyperlink ref="F23" r:id="rId18" display="https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/"/>
-    <hyperlink ref="F24" r:id="rId19" display="https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1"/>
+    <hyperlink ref="F15" r:id="rId10" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F16" r:id="rId11" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F17" r:id="rId12" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="F18" r:id="rId13" display="https://www.sparkfun.com/teensy-4-1.html"/>
+    <hyperlink ref="F19" r:id="rId14" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="F20" r:id="rId15" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="F21" r:id="rId16" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="F22" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="F23" r:id="rId18" display="https://adafruit.com/product/4821"/>
+    <hyperlink ref="F24" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
     <hyperlink ref="F25" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
     <hyperlink ref="F26" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
     <hyperlink ref="F27" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
@@ -4271,7 +4237,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -4287,12 +4253,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4302,121 +4268,118 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A5,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>199</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <f aca="false">B5*F5</f>
-        <v>19.9</v>
+        <v>13.1</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I5" s="3" t="n">
         <f aca="false">B5*Assumptions!$B$5</f>
-        <v>15.4225</v>
+        <v>10.1525</v>
       </c>
       <c r="J5" s="3" t="n">
         <f aca="false">B5+C5+G5+I5</f>
-        <v>294.3225</v>
+        <v>214.2525</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A6,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>87.0729</v>
+        <v>45.95</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>22.21</v>
+        <v>6</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>210</v>
+        <v>94</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <f aca="false">B6*F6</f>
-        <v>30.475515</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
         <f aca="false">B6*Assumptions!$B$5</f>
-        <v>6.74814975</v>
+        <v>3.561125</v>
       </c>
       <c r="J6" s="3" t="n">
         <f aca="false">B6+C6+G6+I6</f>
-        <v>146.50656475</v>
+        <v>55.511125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A7,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>67.85</v>
+        <v>26.34</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>15.26</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>205</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>0</v>
@@ -4425,160 +4388,169 @@
         <f aca="false">B7*F7</f>
         <v>0</v>
       </c>
+      <c r="H7" s="14" t="s">
+        <v>206</v>
+      </c>
       <c r="I7" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$5</f>
-        <v>5.258375</v>
+        <v>2.04135</v>
       </c>
       <c r="J7" s="3" t="n">
         <f aca="false">B7+C7+G7+I7</f>
-        <v>81.108375</v>
+        <v>43.64135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="B8" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A8,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>497.06</v>
+        <v>80.3482</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>50.3</v>
+        <v>22.21</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.35</v>
       </c>
       <c r="G8" s="3" t="n">
         <f aca="false">B8*F8</f>
-        <v>173.971</v>
+        <v>28.12187</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
-        <v>38.52215</v>
+        <v>6.2269855</v>
       </c>
       <c r="J8" s="3" t="n">
         <f aca="false">B8+C8+G8+I8</f>
-        <v>759.85315</v>
+        <v>136.9070555</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A9,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>58.14</v>
+        <v>67.85</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>8.49</v>
+        <v>8</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>214</v>
+        <v>94</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <f aca="false">B9*F9</f>
-        <v>4.6512</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">B9*Assumptions!$B$5</f>
-        <v>4.50585</v>
+        <v>5.258375</v>
       </c>
       <c r="J9" s="3" t="n">
         <f aca="false">B9+C9+G9+I9</f>
-        <v>75.78705</v>
+        <v>81.108375</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B10" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A10,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>31.5</v>
+        <v>497.06</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>50.3</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>209</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="G10" s="3" t="n">
         <f aca="false">B10*F10</f>
-        <v>0</v>
+        <v>173.971</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">B10*Assumptions!$B$5</f>
-        <v>2.44125</v>
+        <v>38.52215</v>
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">B10+C10+G10+I10</f>
-        <v>41.94125</v>
+        <v>759.85315</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A11,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>43.9</v>
+        <v>58.14</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6</v>
+        <v>8.49</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>211</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G11" s="3" t="n">
         <f aca="false">B11*F11</f>
-        <v>0</v>
+        <v>4.6512</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>212</v>
       </c>
       <c r="I11" s="3" t="n">
         <f aca="false">B11*Assumptions!$B$5</f>
-        <v>3.40225</v>
+        <v>4.50585</v>
       </c>
       <c r="J11" s="3" t="n">
         <f aca="false">B11+C11+G11+I11</f>
-        <v>53.30225</v>
+        <v>75.78705</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A12,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>23</v>
+        <v>31.5</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F12" s="16" t="n">
         <v>0</v>
@@ -4589,26 +4561,26 @@
       </c>
       <c r="I12" s="3" t="n">
         <f aca="false">B12*Assumptions!$B$5</f>
-        <v>1.7825</v>
+        <v>2.44125</v>
       </c>
       <c r="J12" s="3" t="n">
         <f aca="false">B12+C12+G12+I12</f>
-        <v>30.7825</v>
+        <v>41.94125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A13,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>54.99</v>
+        <v>43.9</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>0</v>
@@ -4619,26 +4591,26 @@
       </c>
       <c r="I13" s="3" t="n">
         <f aca="false">B13*Assumptions!$B$5</f>
-        <v>4.261725</v>
+        <v>3.40225</v>
       </c>
       <c r="J13" s="3" t="n">
         <f aca="false">B13+C13+G13+I13</f>
-        <v>69.251725</v>
+        <v>53.30225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A14,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>84.75</v>
+        <v>54.99</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>0</v>
@@ -4649,26 +4621,26 @@
       </c>
       <c r="I14" s="3" t="n">
         <f aca="false">B14*Assumptions!$B$5</f>
-        <v>6.568125</v>
+        <v>4.261725</v>
       </c>
       <c r="J14" s="3" t="n">
         <f aca="false">B14+C14+G14+I14</f>
-        <v>101.318125</v>
+        <v>69.251725</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A15,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>4.82</v>
+        <v>9.99</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0</v>
@@ -4679,26 +4651,26 @@
       </c>
       <c r="I15" s="3" t="n">
         <f aca="false">B15*Assumptions!$B$5</f>
-        <v>0.37355</v>
+        <v>0.774225</v>
       </c>
       <c r="J15" s="3" t="n">
         <f aca="false">B15+C15+G15+I15</f>
-        <v>15.19355</v>
+        <v>10.764225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A16,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>9.99</v>
+        <v>30</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F16" s="16" t="n">
         <v>0</v>
@@ -4709,26 +4681,26 @@
       </c>
       <c r="I16" s="3" t="n">
         <f aca="false">B16*Assumptions!$B$5</f>
-        <v>0.774225</v>
+        <v>2.325</v>
       </c>
       <c r="J16" s="3" t="n">
         <f aca="false">B16+C16+G16+I16</f>
-        <v>10.764225</v>
+        <v>44.325</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A17,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0</v>
@@ -4739,119 +4711,89 @@
       </c>
       <c r="I17" s="3" t="n">
         <f aca="false">B17*Assumptions!$B$5</f>
-        <v>2.325</v>
+        <v>2.7125</v>
       </c>
       <c r="J17" s="3" t="n">
         <f aca="false">B17+C17+G17+I17</f>
-        <v>44.325</v>
+        <v>45.7125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A18,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>35</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="16" t="n">
+        <v>213</v>
+      </c>
+      <c r="B18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <f aca="false">B18*F18</f>
+      <c r="C18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="3" t="n">
-        <f aca="false">B18*Assumptions!$B$5</f>
-        <v>2.7125</v>
+      <c r="D18" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="0" t="s">
+        <v>214</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <f aca="false">B18+C18+G18+I18</f>
-        <v>45.7125</v>
+        <f aca="false">Assumptions!$B$7</f>
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="I19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <f aca="false">Assumptions!$B$7</f>
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <f aca="false">SUM(B5:B17)</f>
+        <v>1112.0682</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <f aca="false">SUM(C5:C17)</f>
+        <v>214.26</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="9" t="n">
+        <f aca="false">SUM(G5:G17)</f>
+        <v>219.84407</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9" t="n">
+        <f aca="false">SUM(I5:I17)</f>
+        <v>86.1852855</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <f aca="false">SUM(J5:J18)</f>
+        <v>1697.3575555</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="B21" s="9" t="n">
-        <f aca="false">SUM(B5:B18)</f>
-        <v>1227.0729</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <f aca="false">SUM(C5:C18)</f>
-        <v>219</v>
-      </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9" t="n">
-        <f aca="false">SUM(G5:G18)</f>
-        <v>228.997715</v>
-      </c>
-      <c r="H21" s="8"/>
-      <c r="I21" s="9" t="n">
-        <f aca="false">SUM(I5:I18)</f>
-        <v>95.09814975</v>
-      </c>
-      <c r="J21" s="9" t="n">
-        <f aca="false">SUM(J5:J19)</f>
-        <v>1835.16876475</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <f aca="false">B21-'Detailed BOM'!K29</f>
+        <v>216</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <f aca="false">B20-'Detailed BOM'!K29</f>
         <v>0</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>220</v>
+      <c r="C22" s="14" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -4882,12 +4824,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4897,198 +4839,198 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>277.2</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>77</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>75.15</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>133.13</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5131,12 +5073,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5146,37 +5088,37 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>
@@ -5184,60 +5126,60 @@
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>164.9229</v>
+        <v>158.1982</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <f aca="false">D5+F5+G5</f>
-        <v>295.9229</v>
+        <v>289.1982</v>
       </c>
       <c r="I5" s="3" t="n">
         <f aca="false">H5-$H$5</f>
         <v>0</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>892</v>
@@ -5251,33 +5193,33 @@
       </c>
       <c r="I6" s="3" t="n">
         <f aca="false">H6-$H$5</f>
-        <v>727.0771</v>
+        <v>733.8018</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>3172</v>
@@ -5291,139 +5233,139 @@
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">H7-$H$5</f>
-        <v>3007.0771</v>
+        <v>3013.8018</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>111</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F8" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>164.9229</v>
+        <v>158.1982</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
         <f aca="false">D8+F8+G8</f>
-        <v>275.9229</v>
+        <v>269.1982</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">H8-$H$5</f>
         <v>-20</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>156</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F9" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>164.9229</v>
+        <v>158.1982</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
         <f aca="false">D9+F9+G9</f>
-        <v>320.9229</v>
+        <v>314.1982</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">H9-$H$5</f>
         <v>25</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>164.9229</v>
+        <v>158.1982</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>100</v>
       </c>
       <c r="H10" s="3" t="n">
         <f aca="false">D10+F10+G10</f>
-        <v>395.9229</v>
+        <v>389.1982</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">H10-$H$5</f>
         <v>100</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -5442,7 +5384,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="60"/>
@@ -5457,12 +5399,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5472,169 +5414,167 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B4" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("ME-02",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("ME-03",'Detailed BOM'!$A$5:$A$27,0))</f>
-        <v>157.57</v>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$27,0))</f>
+        <v>49.29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>313</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <f aca="false">B4-INDEX('Detailed BOM'!$K$5:$K$27,MATCH("ME-02",'Detailed BOM'!$A$5:$A$27,0))</f>
-        <v>72.82</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="18" t="s">
+      <c r="D9" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="G9" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="H8" s="18" t="s">
+      <c r="H9" s="18" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>321</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>322</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8.78</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <f aca="false">D9*E9</f>
-        <v>26.34</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>21.99</v>
+        <v>68</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">D10*E10</f>
-        <v>21.99</v>
+        <v>68</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4.25</v>
+        <v>28.25</v>
       </c>
       <c r="F11" s="3" t="n">
         <f aca="false">D11*E11</f>
-        <v>4.25</v>
+        <v>84.75</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>331</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>332</v>
+        <v>326</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4.82</v>
       </c>
       <c r="F12" s="3" t="n">
-        <f aca="false">SUM(F9:F11)</f>
-        <v>52.58</v>
+        <f aca="false">D12*E12</f>
+        <v>4.82</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F13" s="3" t="n">
-        <f aca="false">F12-B4</f>
-        <v>-104.99</v>
+        <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$27,MATCH("HV-01",'Detailed BOM'!$A$5:$A$27,0))</f>
+        <v>164.2947</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>2</v>
+        <v>330</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <f aca="false">F13-B4</f>
+        <v>115.0047</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>334</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125"/>
-    <hyperlink ref="C10" r:id="rId2" display="https://www.tindie.com/products/stepperonline/nema-17-stepper-motor-46ncm651ozin"/>
-    <hyperlink ref="C11" r:id="rId3" display="https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3"/>
+    <hyperlink ref="C10" r:id="rId1" display="https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/"/>
+    <hyperlink ref="C11" r:id="rId2" display="https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/"/>
+    <hyperlink ref="C12" r:id="rId3" display="https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5669,12 +5609,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5684,63 +5624,63 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>3</v>
@@ -5776,24 +5716,24 @@
         <v>2.44913335386511</v>
       </c>
       <c r="N5" s="14" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>352</v>
-      </c>
       <c r="D6" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>3</v>
@@ -5829,24 +5769,24 @@
         <v>1.166253978031</v>
       </c>
       <c r="N6" s="14" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>2</v>
@@ -5882,24 +5822,24 @@
         <v>305.609565855662</v>
       </c>
       <c r="N7" s="14" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="O7" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>2</v>
@@ -5935,24 +5875,24 @@
         <v>43.9823531464942</v>
       </c>
       <c r="N8" s="14" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="O8" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>3</v>
@@ -5988,24 +5928,24 @@
         <v>14.4166666666667</v>
       </c>
       <c r="N9" s="14" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2</v>
@@ -6040,24 +5980,24 @@
         <v>22.6647285954113</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="O10" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>4</v>
@@ -6092,24 +6032,24 @@
         <v>1.20513570229435</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="O11" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>2</v>
@@ -6144,24 +6084,24 @@
         <v>7.47</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="O12" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>2</v>
@@ -6196,15 +6136,15 @@
         <v>6.865</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="O13" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="G14" s="3" t="n">
         <f aca="false">SUM(G5:G13)</f>
@@ -6217,14 +6157,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">L14-832.1</f>
         <v>0</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6234,12 +6174,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>543.83</v>
@@ -6247,7 +6187,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="G19" s="3" t="n">
         <f aca="false">L14+G18</f>
@@ -6282,7 +6222,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6292,291 +6232,291 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>388</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C10" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>407</v>
-      </c>
       <c r="E10" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>414</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -6607,12 +6547,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6622,80 +6562,80 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B5" s="19" t="n">
         <v>0.0775</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>65</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>105</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6705,27 +6645,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="20" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6735,187 +6675,187 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="18" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>483</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>484</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="B23" s="7" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="B24" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>500</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>506</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>513</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="587">
   <si>
     <t xml:space="preserve">STM v2 (UCSD) - budget summary, lean scenario</t>
   </si>
@@ -49,19 +49,25 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">1 Piezo scanner and stepper coarse approach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 Piezo driver (DIY, provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 Electronics: repeat of v1's JLCPCB order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 Preamp specialty parts (Baird's changes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 Printed head, sample plate and hardware</t>
+    <t xml:space="preserve">1 Piezo scanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 Coarse approach (stepper on a fine screw)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 Circuit boards from JLCPCB (assembled and bare)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 Parts bought separately and hand-soldered onto the boards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Power: transformer and batteries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Modules wired in (microcontroller and sensors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 Printed structure, sample plate and isolation</t>
   </si>
   <si>
     <t xml:space="preserve">Purchased components</t>
@@ -280,10 +286,130 @@
     <t xml:space="preserve">Same screws as v1 (three bought 2026-06-24 at $8.78). Thorlabs pages do not load from here, so this is v1's price. 1/4-80 is 317.5 um per turn. v1 ran them in printed threads; matching brass bushings are not priced (U6).</t>
   </si>
   <si>
+    <t xml:space="preserve">EL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlcpcb.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">each (2 min)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 invoice 2026-07-15 unit price. Re-quote not possible from here: JLCPCB prices only after gerber + BOM upload. Parts prices have moved since (e.g. LT1469 now $23.77 and out of stock at LCSC).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preamp board, fully assembled (rev 2 gerbers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 unit price for the rev 1 preamp. Rev 2 adds 4.7 uF 50 V 1812 caps, a few cents each.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare controller PCBs (as in the v1 order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 invoice line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare preamp PCBs (as in the v1 order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV driver bare PCB (rides the JLCPCB order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">min order 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link is JLCPCB's ordering site; a PCB has no product page until gerbers are uploaded. $2 for five is from a Hack Club guide (undated).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U21 dual op-amp for the controller board (JLCPCB does not supply it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DigiKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 bought 2 at DigiKey ($16.35). DigiKey page blocked here; price is Mouser's via an aggregator. URL from search results.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 GOhm feedback resistor, soldered across the op-amp pins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified - aggregator listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 + 1 spare (it is the part Baird's change depends on). URL from search results; DigiKey blocks this environment, price via aggregator (1,673 in stock).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTFE standoff terminal for the air-wired input node</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/part/keystone/11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND (DigiKey 36-11301-ND); link is the Octopart listing (Mouser $2.03). v1 paid $2.09 at DigiKey.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HV-01</t>
   </si>
   <si>
-    <t xml:space="preserve">High-voltage op-amp, one per channel (5 tube + 1 spare)</t>
+    <t xml:space="preserve">High-voltage op-amp for the piezo driver board, one per channel (5 tube + 1 spare)</t>
   </si>
   <si>
     <t xml:space="preserve">TI OPA454AIDDAR</t>
@@ -298,6 +424,24 @@
     <t xml:space="preserve">Direct product page, 241 in stock. The driver circuit is not designed yet.</t>
   </si>
   <si>
+    <t xml:space="preserve">HV-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo driver board parts: rectifier, filter caps, HV regulators, heatsinks, HV connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(no link - see notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO PRODUCT LINK: parts not chosen because the circuit is not drawn. Reference prices seen: GBU4J $1.25, Nichicon UVZ2A102 $2.28, TL783 $3.80.</t>
+  </si>
+  <si>
     <t xml:space="preserve">HV-02</t>
   </si>
   <si>
@@ -313,112 +457,40 @@
     <t xml:space="preserve">https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimated</t>
-  </si>
-  <si>
     <t xml:space="preserve">NO EXACT PRODUCT PAGE: the secondary voltage is not chosen. The link is the nearest verified part (Hammond 182M18, 2 x 18 V, $67.85), which is NOT the right voltage; used as a price placeholder.</t>
   </si>
   <si>
-    <t xml:space="preserve">HV-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rectifier, filter caps, HV regulators, heatsinks, HV connectors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(no link - see notes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO PRODUCT LINK: parts not chosen because the circuit is not drawn. Reference prices seen: GBU4J $1.25, Nichicon UVZ2A102 $2.28, TL783 $3.80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV driver bare PCB (rides the JLCPCB order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min order 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link is JLCPCB's ordering site; a PCB has no product page until gerbers are uploaded. $2 for five is from a Hack Club guide (undated).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">each (2 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 invoice 2026-07-15 unit price. Re-quote not possible from here: JLCPCB prices only after gerber + BOM upload. Parts prices have moved since (e.g. LT1469 now $23.77 and out of stock at LCSC).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preamp board, fully assembled (rev 2 gerbers)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 unit price for the rev 1 preamp. Rev 2 adds 4.7 uF 50 V 1812 caps, a few cents each.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare controller PCBs (as in the v1 order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 invoice line.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare preamp PCBs (as in the v1 order)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dual op-amp U21, bought separately in v1 alongside the JLCPCB order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Devices LT1469IN8#PBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DigiKey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 bought 2 at DigiKey ($16.35). DigiKey page blocked here; price is Mouser's via an aggregator. URL from search results.</t>
+    <t xml:space="preserve">PA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 V lithium batteries for the analog supply (two give +/-9 V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energizer Ultimate Lithium L522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryMart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. Alkaline 4-pack at Battery Junction is $18.95 but was out of stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 V battery holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
   </si>
   <si>
     <t xml:space="preserve">EL-06</t>
@@ -439,72 +511,6 @@
     <t xml:space="preserve">Direct product page. Headers are campus stock. v1 paid $43.22 on Amazon.</t>
   </si>
   <si>
-    <t xml:space="preserve">PA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 GOhm feedback resistor, soldered across the op-amp pins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verified - aggregator listing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 + 1 spare (it is the part Baird's change depends on). URL from search results; DigiKey blocks this environment, price via aggregator (1,673 in stock).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTFE standoff terminal for the air-wired input node</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/part/keystone/11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND (DigiKey 36-11301-ND); link is the Octopart listing (Mouser $2.03). v1 paid $2.09 at DigiKey.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 V lithium batteries for the analog supply (two give +/-9 V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. Alkaline 4-pack at Battery Junction is $18.95 but was out of stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 V battery holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
-  </si>
-  <si>
     <t xml:space="preserve">PA-05</t>
   </si>
   <si>
@@ -652,24 +658,24 @@
     <t xml:space="preserve">Ships from the US</t>
   </si>
   <si>
+    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Forum report Dec 2025.</t>
   </si>
   <si>
     <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
   </si>
   <si>
-    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
   </si>
   <si>
@@ -811,7 +817,7 @@
     <t xml:space="preserve">Piezo purchasing options with dependencies</t>
   </si>
   <si>
-    <t xml:space="preserve">Merchandise only. DIY driver = the 'Piezo driver' lines in the BOM. The total uses P1.</t>
+    <t xml:space="preserve">Merchandise only. DIY driver = BOM lines HV-01 to HV-04. The total uses P1.</t>
   </si>
   <si>
     <t xml:space="preserve">Option</t>
@@ -1600,49 +1606,49 @@
     <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
   </si>
   <si>
+    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02 Keystone 11301</t>
+  </si>
+  <si>
     <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
   </si>
   <si>
+    <t xml:space="preserve">HV-03 not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no link - see BOM note</t>
+  </si>
+  <si>
     <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
   </si>
   <si>
-    <t xml:space="preserve">HV-03 not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no link - see BOM note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
+    <t xml:space="preserve">PA-03 Energizer Ultimate Lithium L522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04 Keystone 1294</t>
   </si>
   <si>
     <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02 Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03 Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04 Keystone 1294</t>
   </si>
   <si>
     <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
@@ -1924,7 +1930,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1978,6 +1984,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2261,7 +2271,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="64"/>
@@ -2300,8 +2310,8 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A5,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>180.29</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A5,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2309,8 +2319,8 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A6,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>158.1982</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A6,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>49.29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2318,8 +2328,8 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A7,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>555.08</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A7,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>497.06</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2327,8 +2337,8 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A8,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>88.52</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A8,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>132.5082</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2336,49 +2346,47 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,A9,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>129.98</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A9,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>117.73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <f aca="false">SUM(B5:B9)</f>
-        <v>1112.0682</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>12</v>
+      <c r="B10" s="3" t="n">
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A10,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>54.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A11,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>129.98</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$27,"Verified*",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>405.1182</v>
-      </c>
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="5" t="n">
+        <f aca="false">SUM(B5:B11)</f>
+        <v>1112.0682</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$27,"Historical*",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>517.58</v>
-      </c>
-      <c r="C12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>15</v>
       </c>
       <c r="B13" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$27,"Estimated",'Detailed BOM'!$K$5:$K$27)</f>
-        <v>189.37</v>
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Verified*",'Detailed BOM'!$K$5:$K$34)</f>
+        <v>405.1182</v>
       </c>
       <c r="C13" s="7"/>
     </row>
@@ -2387,8 +2395,8 @@
         <v>16</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!C20</f>
-        <v>214.26</v>
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Historical*",'Detailed BOM'!$K$5:$K$34)</f>
+        <v>517.58</v>
       </c>
       <c r="C14" s="7"/>
     </row>
@@ -2397,132 +2405,132 @@
         <v>17</v>
       </c>
       <c r="B15" s="3" t="n">
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Estimated",'Detailed BOM'!$K$5:$K$34)</f>
+        <v>189.37</v>
+      </c>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <f aca="false">'Vendor-order totals'!C20</f>
+        <v>214.26</v>
+      </c>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="3" t="n">
         <f aca="false">'Vendor-order totals'!G20</f>
         <v>219.84407</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="3" t="n">
+      <c r="C17" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="3" t="n">
         <f aca="false">'Vendor-order totals'!J18</f>
         <v>65</v>
       </c>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <f aca="false">'Vendor-order totals'!I20</f>
-        <v>86.1852855</v>
-      </c>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="5" t="n">
-        <f aca="false">B10+B14+B15+B16+B17</f>
-        <v>1697.3575555</v>
-      </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3" t="n">
-        <f aca="false">B18*Assumptions!B6</f>
-        <v>169.73575555</v>
+        <f aca="false">'Vendor-order totals'!I20</f>
+        <v>86.1852855</v>
       </c>
       <c r="C19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="9" t="n">
-        <f aca="false">B18+B19</f>
-        <v>1867.09331105</v>
-      </c>
-      <c r="C20" s="10"/>
+      <c r="B20" s="5" t="n">
+        <f aca="false">B12+B16+B17+B18+B19</f>
+        <v>1697.3575555</v>
+      </c>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3" t="n">
-        <f aca="false">Assumptions!B9</f>
-        <v>2000</v>
+        <f aca="false">B20*Assumptions!B6</f>
+        <v>169.73575555</v>
       </c>
       <c r="C21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="12" t="n">
-        <f aca="false">Assumptions!B9-B20</f>
-        <v>132.90668895</v>
-      </c>
-      <c r="C22" s="7"/>
+      <c r="B22" s="9" t="n">
+        <f aca="false">B20+B21</f>
+        <v>1867.09331105</v>
+      </c>
+      <c r="C22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3" t="n">
-        <f aca="false">B20-'Vendor-order totals'!J20*(1+Assumptions!B6)</f>
+        <f aca="false">Assumptions!B9</f>
+        <v>2000</v>
+      </c>
+      <c r="C23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="12" t="n">
+        <f aca="false">Assumptions!B9-B22</f>
+        <v>132.90668895</v>
+      </c>
+      <c r="C24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <f aca="false">B22-'Vendor-order totals'!J20*(1+Assumptions!B6)</f>
         <v>0</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>28</v>
+      <c r="C25" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <f aca="false">'Approach options'!F14</f>
-        <v>115.0047</v>
-      </c>
-      <c r="C26" s="7"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3" t="n">
-        <f aca="false">'Piezo options'!I6</f>
-        <v>733.8018</v>
-      </c>
-      <c r="C27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3" t="n">
-        <f aca="false">'Piezo options'!I7</f>
-        <v>3013.8018</v>
+        <f aca="false">'Approach options'!F14</f>
+        <v>115.0047</v>
       </c>
       <c r="C28" s="7"/>
     </row>
@@ -2531,8 +2539,8 @@
         <v>32</v>
       </c>
       <c r="B29" s="3" t="n">
-        <f aca="false">'Piezo options'!I8</f>
-        <v>-20</v>
+        <f aca="false">'Piezo options'!I6</f>
+        <v>733.8018</v>
       </c>
       <c r="C29" s="7"/>
     </row>
@@ -2541,8 +2549,8 @@
         <v>33</v>
       </c>
       <c r="B30" s="3" t="n">
-        <f aca="false">'Piezo options'!I9</f>
-        <v>25</v>
+        <f aca="false">'Piezo options'!I7</f>
+        <v>3013.8018</v>
       </c>
       <c r="C30" s="7"/>
     </row>
@@ -2551,8 +2559,8 @@
         <v>34</v>
       </c>
       <c r="B31" s="3" t="n">
-        <f aca="false">'Piezo options'!I10</f>
-        <v>100</v>
+        <f aca="false">'Piezo options'!I8</f>
+        <v>-20</v>
       </c>
       <c r="C31" s="7"/>
     </row>
@@ -2561,61 +2569,81 @@
         <v>35</v>
       </c>
       <c r="B32" s="3" t="n">
+        <f aca="false">'Piezo options'!I9</f>
+        <v>25</v>
+      </c>
+      <c r="C32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <f aca="false">'Piezo options'!I10</f>
+        <v>100</v>
+      </c>
+      <c r="C33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="n">
         <f aca="false">133.13</f>
         <v>133.13</v>
       </c>
-      <c r="C32" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="3" t="n">
+      <c r="C34" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="3" t="n">
         <f aca="false">42.74</f>
         <v>42.74</v>
       </c>
-      <c r="C33" s="7"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>38</v>
-      </c>
+      <c r="C35" s="7"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>3006.93</v>
-      </c>
-      <c r="C36" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>2626.74</v>
-      </c>
-      <c r="C37" s="7"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>3006.93</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2626.74</v>
+      </c>
+      <c r="C39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>42</v>
+    <row r="41" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2643,7 +2671,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2653,34 +2681,34 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>514</v>
+        <v>65</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>515</v>
+        <v>118</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>516</v>
+        <v>83</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>517</v>
+        <v>106</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2690,394 +2718,394 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>61</v>
+        <v>521</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>69</v>
+        <v>522</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>74</v>
+        <v>523</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>80</v>
+        <v>524</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>523</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>87</v>
+        <v>525</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>524</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>93</v>
+        <v>526</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>525</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>527</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>106</v>
+        <v>528</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>528</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>106</v>
+        <v>529</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>106</v>
+        <v>530</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>530</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>106</v>
+        <v>531</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>531</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>106</v>
+        <v>532</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>532</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>128</v>
+        <v>533</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>533</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>134</v>
+        <v>534</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>534</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>139</v>
+        <v>536</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>535</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>145</v>
+        <v>537</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>536</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>151</v>
+        <v>538</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>537</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>156</v>
+        <v>539</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>161</v>
+        <v>540</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>539</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>167</v>
+        <v>541</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>540</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>174</v>
+        <v>542</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>541</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>181</v>
+        <v>543</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>542</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>188</v>
+        <v>544</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>543</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>544</v>
+        <v>545</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>545</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>448</v>
+        <v>547</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>546</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>547</v>
+        <v>548</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>548</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>549</v>
+        <v>550</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>550</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>551</v>
+        <v>552</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>552</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>553</v>
+        <v>554</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>554</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>555</v>
+        <v>556</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>556</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>557</v>
+        <v>558</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>558</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>443</v>
+        <v>560</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>559</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>560</v>
+        <v>561</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>561</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>245</v>
+        <v>563</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>562</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>451</v>
+        <v>564</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>563</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>237</v>
+        <v>565</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>564</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>565</v>
+        <v>566</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>566</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>227</v>
+        <v>568</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>567</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>568</v>
+        <v>569</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>569</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>570</v>
+        <v>571</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>571</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>572</v>
+        <v>573</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>573</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>151</v>
+        <v>575</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>575</v>
+        <v>576</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>576</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>578</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>579</v>
+        <v>580</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>580</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>167</v>
+        <v>582</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>581</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>582</v>
+        <v>583</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -3086,19 +3114,19 @@
     <hyperlink ref="B10" r:id="rId2" display="https://www.adafruit.com/product/324"/>
     <hyperlink ref="B11" r:id="rId3" display="https://adafruit.com/product/6121"/>
     <hyperlink ref="B12" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
-    <hyperlink ref="B13" r:id="rId5" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="B14" r:id="rId6" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="B16" r:id="rId7" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B17" r:id="rId8" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B18" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B19" r:id="rId10" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B20" r:id="rId11" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B21" r:id="rId12" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="B22" r:id="rId13" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="B23" r:id="rId14" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="B24" r:id="rId15" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="B25" r:id="rId16" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
-    <hyperlink ref="B26" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="B13" r:id="rId5" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B14" r:id="rId6" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B15" r:id="rId7" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B16" r:id="rId8" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B17" r:id="rId9" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B18" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="B19" r:id="rId11" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="B20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="B21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="B23" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
+    <hyperlink ref="B24" r:id="rId15" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="B25" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="B26" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
     <hyperlink ref="B27" r:id="rId18" display="https://adafruit.com/product/4821"/>
     <hyperlink ref="B28" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
     <hyperlink ref="B29" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
@@ -3143,7 +3171,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3163,12 +3191,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3178,657 +3206,557 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>59</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <f aca="false">I5*J5</f>
-        <v>131</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>65</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>63</v>
       </c>
       <c r="G6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>62</v>
+      <c r="H6" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K6" s="3" t="n">
         <f aca="false">I6*J6</f>
-        <v>14</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>63</v>
+        <v>131</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>8.95</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <f aca="false">I7*J7</f>
-        <v>8.95</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>75</v>
-      </c>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>80</v>
+        <v>69</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>8.78</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="n">
         <f aca="false">I8*J8</f>
-        <v>26.34</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>81</v>
+        <v>14</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>87</v>
+        <v>75</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>6.7247</v>
+        <v>8.95</v>
       </c>
       <c r="K9" s="3" t="n">
         <f aca="false">I9*J9</f>
-        <v>40.3482</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>63</v>
+        <v>8.95</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>93</v>
+        <v>80</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>62</v>
+        <v>3</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>67.85</v>
+        <v>8.78</v>
       </c>
       <c r="K10" s="3" t="n">
         <f aca="false">I10*J10</f>
-        <v>67.85</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>94</v>
+        <v>26.34</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="14"/>
+    </row>
+    <row r="12" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <f aca="false">I11*J11</f>
-        <v>40</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>106</v>
+        <v>87</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>107</v>
+        <v>2</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>2</v>
+        <v>209.64</v>
       </c>
       <c r="K12" s="3" t="n">
         <f aca="false">I12*J12</f>
-        <v>10</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>94</v>
+        <v>419.28</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>106</v>
+        <v>94</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G13" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="14" t="s">
-        <v>112</v>
+      <c r="H13" s="15" t="s">
+        <v>90</v>
       </c>
       <c r="I13" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>209.64</v>
+        <v>30.17</v>
       </c>
       <c r="K13" s="3" t="n">
         <f aca="false">I13*J13</f>
-        <v>419.28</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>81</v>
+        <v>60.34</v>
+      </c>
+      <c r="L13" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>112</v>
+        <v>3</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>30.17</v>
+        <v>1.68</v>
       </c>
       <c r="K14" s="3" t="n">
         <f aca="false">I14*J14</f>
-        <v>60.34</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>81</v>
+        <v>5.04</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>106</v>
+        <v>98</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="14" t="s">
-        <v>62</v>
+      <c r="H15" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1.68</v>
+        <v>0.8</v>
       </c>
       <c r="K15" s="3" t="n">
         <f aca="false">I15*J15</f>
-        <v>5.04</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>81</v>
+        <v>2.4</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>62</v>
-      </c>
       <c r="I16" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="K16" s="3" t="n">
         <f aca="false">I16*J16</f>
-        <v>2.4</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>81</v>
+        <v>10</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G17" s="0" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I17" s="0" t="n">
+      <c r="H18" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I18" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>18.26</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <f aca="false">I17*J17</f>
-        <v>36.52</v>
-      </c>
-      <c r="L17" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>130</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>31.5</v>
       </c>
       <c r="K18" s="3" t="n">
         <f aca="false">I18*J18</f>
-        <v>31.5</v>
-      </c>
-      <c r="L18" s="14" t="s">
-        <v>63</v>
+        <v>36.52</v>
+      </c>
+      <c r="L18" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>139</v>
+        <v>116</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="G19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>62</v>
+      <c r="H19" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I19" s="0" t="n">
         <v>2</v>
@@ -3840,37 +3768,37 @@
         <f aca="false">I19*J19</f>
         <v>11.46</v>
       </c>
-      <c r="L19" s="14" t="s">
-        <v>140</v>
+      <c r="L19" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>145</v>
+        <v>122</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>123</v>
       </c>
       <c r="G20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="14" t="s">
-        <v>62</v>
+      <c r="H20" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I20" s="0" t="n">
         <v>2</v>
@@ -3882,345 +3810,564 @@
         <f aca="false">I20*J20</f>
         <v>4.18</v>
       </c>
-      <c r="L20" s="14" t="s">
-        <v>81</v>
+      <c r="L20" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>151</v>
+        <v>127</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>129</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>62</v>
+        <v>5</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>21.95</v>
+        <v>6.7247</v>
       </c>
       <c r="K21" s="3" t="n">
         <f aca="false">I21*J21</f>
-        <v>43.9</v>
-      </c>
-      <c r="L21" s="14" t="s">
-        <v>63</v>
+        <v>40.3482</v>
+      </c>
+      <c r="L21" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>156</v>
+        <v>133</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>134</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2.99</v>
+        <v>40</v>
       </c>
       <c r="K22" s="3" t="n">
         <f aca="false">I22*J22</f>
-        <v>5.98</v>
-      </c>
-      <c r="L22" s="14" t="s">
-        <v>140</v>
+        <v>40</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <f aca="false">I23*J23</f>
-        <v>23</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+    </row>
+    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>167</v>
+        <v>139</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>141</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="14" t="s">
-        <v>168</v>
+      <c r="H24" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I24" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>54.99</v>
+        <v>67.85</v>
       </c>
       <c r="K24" s="3" t="n">
         <f aca="false">I24*J24</f>
-        <v>54.99</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>63</v>
+        <v>67.85</v>
+      </c>
+      <c r="L24" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>174</v>
+        <v>145</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>147</v>
       </c>
       <c r="G25" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>175</v>
+        <v>2</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.99</v>
+        <v>21.95</v>
       </c>
       <c r="K25" s="3" t="n">
         <f aca="false">I25*J25</f>
-        <v>9.99</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>63</v>
+        <v>43.9</v>
+      </c>
+      <c r="L25" s="15" t="s">
+        <v>65</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>181</v>
+        <v>151</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>152</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="14" t="s">
-        <v>182</v>
+      <c r="H26" s="15" t="s">
+        <v>64</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>30</v>
+        <v>2.99</v>
       </c>
       <c r="K26" s="3" t="n">
         <f aca="false">I26*J26</f>
-        <v>30</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>63</v>
+        <v>5.98</v>
+      </c>
+      <c r="L26" s="15" t="s">
+        <v>118</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="G27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <f aca="false">I27*J27</f>
-        <v>35</v>
-      </c>
-      <c r="L27" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>190</v>
-      </c>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <f aca="false">I28*J28</f>
+        <v>31.5</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="0" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="11" t="s">
+      <c r="H29" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <f aca="false">I29*J29</f>
+        <v>23</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <f aca="false">I31*J31</f>
+        <v>54.99</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="I32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <f aca="false">I32*J32</f>
+        <v>9.99</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <f aca="false">I33*J33</f>
+        <v>30</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="K29" s="12" t="n">
-        <f aca="false">SUM(K5:K27)</f>
+      <c r="I34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <f aca="false">I34*J34</f>
+        <v>35</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <f aca="false">SUM(K5:K34)</f>
         <v>1112.0682</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" display="https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/"/>
-    <hyperlink ref="F6" r:id="rId2" display="https://www.adafruit.com/product/324"/>
-    <hyperlink ref="F7" r:id="rId3" display="https://adafruit.com/product/6121"/>
-    <hyperlink ref="F8" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
-    <hyperlink ref="F9" r:id="rId5" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="F10" r:id="rId6" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="F12" r:id="rId7" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F13" r:id="rId8" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F14" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F15" r:id="rId10" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F16" r:id="rId11" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F17" r:id="rId12" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="F18" r:id="rId13" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="F19" r:id="rId14" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="F20" r:id="rId15" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="F21" r:id="rId16" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
-    <hyperlink ref="F22" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
-    <hyperlink ref="F23" r:id="rId18" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="F24" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
-    <hyperlink ref="F25" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
-    <hyperlink ref="F26" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
-    <hyperlink ref="F27" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
+    <hyperlink ref="F6" r:id="rId1" display="https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/"/>
+    <hyperlink ref="F8" r:id="rId2" display="https://www.adafruit.com/product/324"/>
+    <hyperlink ref="F9" r:id="rId3" display="https://adafruit.com/product/6121"/>
+    <hyperlink ref="F10" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
+    <hyperlink ref="F12" r:id="rId5" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F13" r:id="rId6" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F14" r:id="rId7" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F15" r:id="rId8" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F16" r:id="rId9" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F18" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="F19" r:id="rId11" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="F20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="F21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="F24" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
+    <hyperlink ref="F25" r:id="rId15" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="F26" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="F28" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
+    <hyperlink ref="F29" r:id="rId18" display="https://adafruit.com/product/4821"/>
+    <hyperlink ref="F31" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
+    <hyperlink ref="F32" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
+    <hyperlink ref="F33" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
+    <hyperlink ref="F34" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4253,12 +4400,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4268,62 +4415,62 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A5,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A5,'Detailed BOM'!$K$5:$K$34)</f>
         <v>131</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="F5" s="16" t="n">
+      <c r="D5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" s="3" t="n">
         <f aca="false">B5*F5</f>
         <v>13.1</v>
       </c>
-      <c r="H5" s="14" t="s">
-        <v>204</v>
+      <c r="H5" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="I5" s="3" t="n">
         <f aca="false">B5*Assumptions!$B$5</f>
@@ -4336,19 +4483,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A6,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A6,'Detailed BOM'!$K$5:$K$34)</f>
         <v>45.95</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="16" t="n">
+      <c r="D6" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -4366,30 +4513,30 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A7,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A7,'Detailed BOM'!$K$5:$K$34)</f>
         <v>26.34</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>15.26</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="F7" s="16" t="n">
+      <c r="D7" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <f aca="false">B7*F7</f>
         <v>0</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>206</v>
+      <c r="H7" s="15" t="s">
+        <v>208</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$5</f>
@@ -4402,157 +4549,157 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A8,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>80.3482</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A8,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>497.06</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F8" s="16" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>0.35</v>
       </c>
       <c r="G8" s="3" t="n">
         <f aca="false">B8*F8</f>
-        <v>28.12187</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>208</v>
+        <v>173.971</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>210</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
-        <v>6.2269855</v>
+        <v>38.52215</v>
       </c>
       <c r="J8" s="3" t="n">
         <f aca="false">B8+C8+G8+I8</f>
-        <v>136.9070555</v>
+        <v>759.85315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A9,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>67.85</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A9,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>58.14</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
+        <v>8.49</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.08</v>
       </c>
       <c r="G9" s="3" t="n">
         <f aca="false">B9*F9</f>
-        <v>0</v>
+        <v>4.6512</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">B9*Assumptions!$B$5</f>
-        <v>5.258375</v>
+        <v>4.50585</v>
       </c>
       <c r="J9" s="3" t="n">
         <f aca="false">B9+C9+G9+I9</f>
-        <v>81.108375</v>
+        <v>75.78705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B10" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A10,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>497.06</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A10,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>80.3482</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="F10" s="16" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>0.35</v>
       </c>
       <c r="G10" s="3" t="n">
         <f aca="false">B10*F10</f>
-        <v>173.971</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>210</v>
+        <v>28.12187</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>214</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">B10*Assumptions!$B$5</f>
-        <v>38.52215</v>
+        <v>6.2269855</v>
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">B10+C10+G10+I10</f>
-        <v>759.85315</v>
+        <v>136.9070555</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A11,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>58.14</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A11,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>67.85</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.08</v>
+        <v>8</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
         <f aca="false">B11*F11</f>
-        <v>4.6512</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
         <f aca="false">B11*Assumptions!$B$5</f>
-        <v>4.50585</v>
+        <v>5.258375</v>
       </c>
       <c r="J11" s="3" t="n">
         <f aca="false">B11+C11+G11+I11</f>
-        <v>75.78705</v>
+        <v>81.108375</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B12" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A12,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>31.5</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A12,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>43.9</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -4561,28 +4708,28 @@
       </c>
       <c r="I12" s="3" t="n">
         <f aca="false">B12*Assumptions!$B$5</f>
-        <v>2.44125</v>
+        <v>3.40225</v>
       </c>
       <c r="J12" s="3" t="n">
         <f aca="false">B12+C12+G12+I12</f>
-        <v>41.94125</v>
+        <v>53.30225</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B13" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A13,'Detailed BOM'!$K$5:$K$27)</f>
-        <v>43.9</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A13,'Detailed BOM'!$K$5:$K$34)</f>
+        <v>31.5</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
@@ -4591,28 +4738,28 @@
       </c>
       <c r="I13" s="3" t="n">
         <f aca="false">B13*Assumptions!$B$5</f>
-        <v>3.40225</v>
+        <v>2.44125</v>
       </c>
       <c r="J13" s="3" t="n">
         <f aca="false">B13+C13+G13+I13</f>
-        <v>53.30225</v>
+        <v>41.94125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A14,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A14,'Detailed BOM'!$K$5:$K$34)</f>
         <v>54.99</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="16" t="n">
+      <c r="D14" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -4630,19 +4777,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B15" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A15,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A15,'Detailed BOM'!$K$5:$K$34)</f>
         <v>9.99</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="16" t="n">
+      <c r="D15" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
@@ -4660,19 +4807,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B16" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A16,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A16,'Detailed BOM'!$K$5:$K$34)</f>
         <v>30</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="16" t="n">
+      <c r="D16" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F16" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -4690,19 +4837,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B17" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$27,A17,'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A17,'Detailed BOM'!$K$5:$K$34)</f>
         <v>35</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="16" t="n">
+      <c r="D17" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="17" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -4720,7 +4867,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0</v>
@@ -4729,13 +4876,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="G18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>0</v>
@@ -4752,7 +4899,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">SUM(B5:B17)</f>
@@ -4786,14 +4933,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B22" s="3" t="n">
-        <f aca="false">B20-'Detailed BOM'!K29</f>
+        <f aca="false">B20-'Detailed BOM'!K36</f>
         <v>0</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>217</v>
+      <c r="C22" s="15" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4824,12 +4971,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4839,198 +4986,198 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>277.2</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>227</v>
+      <c r="D5" s="18" t="s">
+        <v>229</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>226</v>
+        <v>231</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>228</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>230</v>
+      <c r="D6" s="18" t="s">
+        <v>232</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>235</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="17" t="s">
         <v>237</v>
       </c>
+      <c r="B8" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>239</v>
+      </c>
       <c r="E8" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>236</v>
+        <v>241</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>75.15</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>240</v>
+      <c r="D9" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>236</v>
+        <v>244</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>247</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>236</v>
+        <v>249</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>133.13</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>236</v>
+        <v>251</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>236</v>
+        <v>253</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>236</v>
+        <v>255</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>236</v>
+        <v>256</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>236</v>
+        <v>258</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>236</v>
+        <v>259</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>238</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5073,12 +5220,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5088,37 +5235,37 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>
@@ -5126,22 +5273,22 @@
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F5" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -5155,31 +5302,31 @@
         <f aca="false">H5-$H$5</f>
         <v>0</v>
       </c>
-      <c r="J5" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>277</v>
+      <c r="J5" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>279</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>274</v>
+        <v>282</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>892</v>
@@ -5195,31 +5342,31 @@
         <f aca="false">H6-$H$5</f>
         <v>733.8018</v>
       </c>
-      <c r="J6" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>283</v>
+      <c r="J6" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>285</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>274</v>
+        <v>288</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>3172</v>
@@ -5235,34 +5382,34 @@
         <f aca="false">H7-$H$5</f>
         <v>3013.8018</v>
       </c>
-      <c r="J7" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>289</v>
+      <c r="J7" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>291</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>295</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>111</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F8" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -5276,34 +5423,34 @@
         <f aca="false">H8-$H$5</f>
         <v>-20</v>
       </c>
-      <c r="J8" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>296</v>
+      <c r="J8" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>298</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>302</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>156</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F9" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -5317,34 +5464,34 @@
         <f aca="false">H9-$H$5</f>
         <v>25</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>302</v>
+      <c r="J9" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>304</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>274</v>
+        <v>307</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>276</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F10" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$27,"2 Piezo driver (DIY, provisional)",'Detailed BOM'!$K$5:$K$27)</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -5358,14 +5505,14 @@
         <f aca="false">H10-$H$5</f>
         <v>100</v>
       </c>
-      <c r="J10" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>277</v>
+      <c r="J10" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>279</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -5399,12 +5546,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5414,21 +5561,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$27,0))+INDEX('Detailed BOM'!$K$5:$K$27,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$27,0))</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>49.29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5438,44 +5585,44 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="D9" s="18" t="s">
+      <c r="A9" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="F9" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>320</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>321</v>
+        <v>322</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>323</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
@@ -5487,22 +5634,22 @@
         <f aca="false">D10*E10</f>
         <v>68</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>322</v>
+      <c r="G10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>325</v>
+        <v>326</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>327</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -5514,19 +5661,19 @@
         <f aca="false">D11*E11</f>
         <v>84.75</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>63</v>
+      <c r="G11" s="15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>327</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>328</v>
+        <v>329</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>330</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>1</v>
@@ -5538,22 +5685,22 @@
         <f aca="false">D12*E12</f>
         <v>4.82</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>63</v>
+      <c r="G12" s="15" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F13" s="3" t="n">
-        <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$27,MATCH("HV-01",'Detailed BOM'!$A$5:$A$27,0))</f>
+        <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))</f>
         <v>164.2947</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F14" s="3" t="n">
         <f aca="false">F13-B4</f>
@@ -5567,7 +5714,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5609,12 +5756,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5624,63 +5771,63 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>3</v>
@@ -5715,25 +5862,25 @@
         <f aca="false">L5/E5</f>
         <v>2.44913335386511</v>
       </c>
-      <c r="N5" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="O5" s="14" t="s">
-        <v>348</v>
+      <c r="N5" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>3</v>
@@ -5768,25 +5915,25 @@
         <f aca="false">L6/E6</f>
         <v>1.166253978031</v>
       </c>
-      <c r="N6" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>348</v>
+      <c r="N6" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>2</v>
@@ -5821,25 +5968,25 @@
         <f aca="false">L7/E7</f>
         <v>305.609565855662</v>
       </c>
-      <c r="N7" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="O7" s="14" t="s">
-        <v>348</v>
+      <c r="N7" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>2</v>
@@ -5874,25 +6021,25 @@
         <f aca="false">L8/E8</f>
         <v>43.9823531464942</v>
       </c>
-      <c r="N8" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="O8" s="14" t="s">
-        <v>348</v>
+      <c r="N8" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>3</v>
@@ -5927,25 +6074,25 @@
         <f aca="false">L9/E9</f>
         <v>14.4166666666667</v>
       </c>
-      <c r="N9" s="14" t="s">
-        <v>354</v>
-      </c>
-      <c r="O9" s="14" t="s">
-        <v>348</v>
+      <c r="N9" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="O9" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2</v>
@@ -5979,25 +6126,25 @@
         <f aca="false">L10/E10</f>
         <v>22.6647285954113</v>
       </c>
-      <c r="N10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="O10" s="14" t="s">
-        <v>348</v>
+      <c r="N10" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>4</v>
@@ -6031,25 +6178,25 @@
         <f aca="false">L11/E11</f>
         <v>1.20513570229435</v>
       </c>
-      <c r="N11" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="O11" s="14" t="s">
-        <v>348</v>
+      <c r="N11" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>2</v>
@@ -6083,25 +6230,25 @@
         <f aca="false">L12/E12</f>
         <v>7.47</v>
       </c>
-      <c r="N12" s="14" t="s">
-        <v>364</v>
-      </c>
-      <c r="O12" s="14" t="s">
-        <v>348</v>
+      <c r="N12" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="O12" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B13" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="0" t="s">
         <v>365</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>363</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>2</v>
@@ -6135,16 +6282,16 @@
         <f aca="false">L13/E13</f>
         <v>6.865</v>
       </c>
-      <c r="N13" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>348</v>
+      <c r="N13" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G14" s="3" t="n">
         <f aca="false">SUM(G5:G13)</f>
@@ -6157,14 +6304,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">L14-832.1</f>
         <v>0</v>
       </c>
-      <c r="M15" s="14" t="s">
-        <v>217</v>
+      <c r="M15" s="15" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6174,12 +6321,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>543.83</v>
@@ -6187,7 +6334,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G19" s="3" t="n">
         <f aca="false">L14+G18</f>
@@ -6222,7 +6369,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6232,291 +6379,291 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>390</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>409</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>420</v>
-      </c>
       <c r="D16" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -6547,12 +6694,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6561,81 +6708,81 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>438</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>439</v>
-      </c>
-      <c r="C4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>440</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>374</v>
+      <c r="B4" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="B5" s="19" t="n">
+        <v>443</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <v>0.0775</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>442</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>443</v>
+      <c r="C5" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>444</v>
-      </c>
-      <c r="B6" s="16" t="n">
+        <v>446</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>445</v>
+      <c r="C6" s="15" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>448</v>
+      <c r="C7" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>450</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>451</v>
+      <c r="C8" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2000</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>453</v>
+      <c r="C9" s="15" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6644,28 +6791,28 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>454</v>
+      <c r="A11" s="21" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6674,188 +6821,188 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
-        <v>459</v>
+      <c r="A17" s="21" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>460</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="D18" s="18" t="s">
+      <c r="A18" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>462</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="C18" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="D18" s="19" t="s">
         <v>464</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="589">
   <si>
     <t xml:space="preserve">STM v2 (UCSD) - budget summary, lean scenario</t>
   </si>
@@ -463,1300 +463,1306 @@
     <t xml:space="preserve">PA-03</t>
   </si>
   <si>
-    <t xml:space="preserve">9 V lithium batteries for the analog supply (two give +/-9 V)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart</t>
+    <t xml:space="preserve">9 V alkaline batteries for the preamp supply (two give +/-9 V; two spares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energizer MAX 522BP-4, 4-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery Junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock (5 left at check). Any 9 V alkaline works: the OPA627 needs only +/-4.5 V and draws about 7 mA, so a pair lasts roughly 70 hours. Lithium (Energizer L522, $21.95 each at BatteryMart) lasts about twice as long with a flatter voltage, but is not needed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 V battery holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microcontroller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teensy 4.1 (SparkFun DEV-16771)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SparkFun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sparkfun.com/teensy-4-1.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page. Headers are campus stock. v1 paid $43.22 on Amazon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature sensor, +/-0.1 C (head and preamp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adafruit 4821 (TI TMP117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://adafruit.com/product/4821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page. Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D-printing filament for head, sample plate and approach body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prusa Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 kg spool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, in stock. One spool covers the parts and reprints. Material is still open: PETG-CF is stiff and easy to print; nylon-CF is stiffer but needs a dried, hardened-nozzle printer. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice for this budget.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walmart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Components subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor and order totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales or use tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 Thorlabs order shipping, 2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships from the US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forum report Dec 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL ORDERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(should be 0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved out of the purchase list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference value if bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir tip wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind from a UCSD lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOPG sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D printer time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite base or optical breadboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield enclosures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise only. DIY driver = BOM lines HV-01 to HV-04. The total uses P1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver / dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change vs P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. XY (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. Z (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~13-16 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~3 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD250-INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 (spec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~8.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coarse approach and sample plate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Two hand-set 1/4-80 screws and the motor screw form the tripod, with steel-ball pivots (ME-04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not chosen, for the record: piezo stick-slip slider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive SA050510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also needed a sawtooth HV channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapphire contacts, 2 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmund Optics 43-642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground guide rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stick-slip parts total (merchandise, plus one OPA454 channel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference vs the chosen stepper drive (positive = stick-slip costs more)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch). No springs or rubber bands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 purchases (historical prices)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer / part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / import tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. sales tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed line cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed unit cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-layer bare STM controller PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor invoice (kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approach scenario B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTL-28 (different part)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 11311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(not in v2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoiced orders total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total under $2,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See total vs ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind and campus tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered (assumed, unverified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No reuse of v1 parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vasquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; driver provisional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate replaced, not v1's springs; coarse approach stays a stepper (Jacob)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02..04, ME-04, ME-05, Approach options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detailed BOM 'Source link'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature monitoring; enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflicts with the printed structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN - flagged (U4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel balls at pivots; stiff screw drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04; PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope the preamp output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus, unverified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions and unresolved costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied to all merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% for price drift and breakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure is printed; kept for reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unresolved items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect on the total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What would resolve it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV driver design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04: $158.20 incl. transformer placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB price today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus items really free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed (Jacob's choice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filament choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick based on the campus printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screw bushings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping and duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate shown; DAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant price not displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$35 estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item or topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02 Adafruit 324 (12 V, 350 mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-03 Adafruit 6121 (TMC2209 breakout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02 Keystone 11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-03 not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no link - see BOM note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-03 Energizer MAX 522BP-4, 4-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04 Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-01 Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD MPL machine shop rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision access rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. Alkaline 4-pack at Battery Junction is $18.95 but was out of stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 V battery holder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://octopart.com/part/keystone/1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO DIRECT DIGIKEY URL FOUND; link is the Octopart listing (Newark $2.99, in stock). Bought in the DigiKey order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microcontroller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SparkFun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sparkfun.com/teensy-4-1.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page. Headers are campus stock. v1 paid $43.22 on Amazon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature sensor, +/-0.1 C (head and preamp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adafruit 4821 (TI TMP117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://adafruit.com/product/4821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page. Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D-printing filament for head, sample plate and approach body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusa Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 kg spool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. One spool covers the parts and reprints. Material is still open: PETG-CF is stiff and easy to print; nylon-CF is stiffer but needs a dried, hardened-nozzle printer. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice for this budget.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walmart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolate It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Components subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor and order totals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales or use tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 Thorlabs order shipping, 2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ships from the US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum report Dec 2025.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL ORDERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(should be 0.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moved out of the purchase list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference value if bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir tip wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind from a UCSD lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOPG sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D printer time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite base or optical breadboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shield enclosures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise only. DIY driver = BOM lines HV-01 to HV-04. The total uses P1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver / dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change vs P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. XY (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. Z (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~13-16 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~3 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TD250-INV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 (spec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~8.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coarse approach and sample plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Two hand-set 1/4-80 screws and the motor screw form the tripod, with steel-ball pivots (ME-04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not chosen, for the record: piezo stick-slip slider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive SA050510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also needed a sawtooth HV channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sapphire contacts, 2 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edmund Optics 43-642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground guide rod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stick-slip parts total (merchandise, plus one OPA454 channel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference vs the chosen stepper drive (positive = stick-slip costs more)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch). No springs or rubber bands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 purchases (historical prices)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturer / part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / import tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. sales tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed line cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed unit cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v2 line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-layer bare STM controller PCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor invoice (kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approach scenario B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTL-28 (different part)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 11311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(not in v2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoiced orders total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where it is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total under $2,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See total vs ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind and campus tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered (assumed, unverified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No reuse of v1 parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; driver provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate replaced, not v1's springs; coarse approach stays a stepper (Jacob)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02..04, ME-04, ME-05, Approach options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detailed BOM 'Source link'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature monitoring; enclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conflicts with the printed structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN - flagged (U4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel balls at pivots; stiff screw drive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04; PZ-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baird</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope the preamp output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus, unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions and unresolved costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied to all merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% for price drift and breakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure is printed; kept for reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob's requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unresolved items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect on the total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What would resolve it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV driver design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04: $158.20 incl. transformer placeholder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB price today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus items really free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed (Jacob's choice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filament choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick based on the campus printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screw bushings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None priced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping and duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate shown; DAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variant price not displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$35 estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item or topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02 Adafruit 324 (12 V, 350 mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-03 Adafruit 6121 (TMC2209 breakout)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02 Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-03 not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no link - see BOM note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03 Energizer Ultimate Lithium L522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04 Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-01 Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD MPL machine shop rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision access rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
   </si>
   <si>
     <t xml:space="preserve">Vetco MG 8331D-14G $167.95</t>
@@ -2347,7 +2353,7 @@
       </c>
       <c r="B9" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A9,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>117.73</v>
+        <v>94.68</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2374,7 +2380,7 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>1112.0682</v>
+        <v>1089.0182</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>14</v>
@@ -2386,7 +2392,7 @@
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Verified*",'Detailed BOM'!$K$5:$K$34)</f>
-        <v>405.1182</v>
+        <v>382.0682</v>
       </c>
       <c r="C13" s="7"/>
     </row>
@@ -2448,7 +2454,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">'Vendor-order totals'!I20</f>
-        <v>86.1852855</v>
+        <v>84.3989105</v>
       </c>
       <c r="C19" s="7"/>
     </row>
@@ -2458,7 +2464,7 @@
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">B12+B16+B17+B18+B19</f>
-        <v>1697.3575555</v>
+        <v>1672.5211805</v>
       </c>
       <c r="C20" s="6"/>
     </row>
@@ -2468,7 +2474,7 @@
       </c>
       <c r="B21" s="3" t="n">
         <f aca="false">B20*Assumptions!B6</f>
-        <v>169.73575555</v>
+        <v>167.25211805</v>
       </c>
       <c r="C21" s="7"/>
     </row>
@@ -2478,7 +2484,7 @@
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">B20+B21</f>
-        <v>1867.09331105</v>
+        <v>1839.77329855</v>
       </c>
       <c r="C22" s="10"/>
     </row>
@@ -2498,7 +2504,7 @@
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">Assumptions!B9-B22</f>
-        <v>132.90668895</v>
+        <v>160.22670145</v>
       </c>
       <c r="C24" s="7"/>
     </row>
@@ -2671,7 +2677,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2684,7 +2690,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2692,7 +2698,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,7 +2706,7 @@
         <v>83</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2708,7 +2714,7 @@
         <v>106</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2718,15 +2724,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>63</v>
@@ -2734,7 +2740,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>71</v>
@@ -2742,7 +2748,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>76</v>
@@ -2750,7 +2756,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>82</v>
@@ -2758,7 +2764,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>89</v>
@@ -2766,7 +2772,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>89</v>
@@ -2774,7 +2780,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>89</v>
@@ -2782,7 +2788,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>89</v>
@@ -2790,7 +2796,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>89</v>
@@ -2798,7 +2804,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>112</v>
@@ -2806,7 +2812,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>117</v>
@@ -2814,7 +2820,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>123</v>
@@ -2822,7 +2828,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>129</v>
@@ -2830,15 +2836,15 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>141</v>
@@ -2846,7 +2852,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>147</v>
@@ -2854,258 +2860,258 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>147</v>
+        <v>577</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -3124,7 +3130,7 @@
     <hyperlink ref="B20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
     <hyperlink ref="B21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
     <hyperlink ref="B23" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="B24" r:id="rId15" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="B24" r:id="rId15" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
     <hyperlink ref="B25" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
     <hyperlink ref="B26" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
     <hyperlink ref="B27" r:id="rId18" display="https://adafruit.com/product/4821"/>
@@ -3960,7 +3966,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>143</v>
       </c>
@@ -3983,43 +3989,43 @@
         <v>2</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="I25" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>21.95</v>
+        <v>20.85</v>
       </c>
       <c r="K25" s="3" t="n">
         <f aca="false">I25*J25</f>
-        <v>43.9</v>
+        <v>20.85</v>
       </c>
       <c r="L25" s="15" t="s">
         <v>65</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>111</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>2</v>
@@ -4041,7 +4047,7 @@
         <v>118</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4063,22 +4069,22 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G28" s="0" t="n">
         <v>1</v>
@@ -4100,27 +4106,27 @@
         <v>65</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>70</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G29" s="0" t="n">
         <v>2</v>
@@ -4142,7 +4148,7 @@
         <v>65</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4164,28 +4170,28 @@
     </row>
     <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G31" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I31" s="0" t="n">
         <v>1</v>
@@ -4201,33 +4207,33 @@
         <v>65</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G32" s="0" t="n">
         <v>3</v>
       </c>
       <c r="H32" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I32" s="0" t="n">
         <v>1</v>
@@ -4243,33 +4249,33 @@
         <v>65</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G33" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>1</v>
@@ -4285,33 +4291,33 @@
         <v>65</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G34" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I34" s="0" t="n">
         <v>1</v>
@@ -4327,7 +4333,7 @@
         <v>106</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4337,11 +4343,11 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C36" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K36" s="12" t="n">
         <f aca="false">SUM(K5:K34)</f>
-        <v>1112.0682</v>
+        <v>1089.0182</v>
       </c>
     </row>
   </sheetData>
@@ -4360,7 +4366,7 @@
     <hyperlink ref="F20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
     <hyperlink ref="F21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
     <hyperlink ref="F24" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="F25" r:id="rId15" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="F25" r:id="rId15" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
     <hyperlink ref="F26" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
     <hyperlink ref="F28" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
     <hyperlink ref="F29" r:id="rId18" display="https://adafruit.com/product/4821"/>
@@ -4400,12 +4406,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4418,31 +4424,31 @@
         <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4460,7 +4466,7 @@
         <v>106</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.1</v>
@@ -4470,7 +4476,7 @@
         <v>13.1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I5" s="3" t="n">
         <f aca="false">B5*Assumptions!$B$5</f>
@@ -4526,7 +4532,7 @@
         <v>83</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>0</v>
@@ -4536,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$5</f>
@@ -4562,7 +4568,7 @@
         <v>83</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>0.35</v>
@@ -4572,7 +4578,7 @@
         <v>173.971</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
@@ -4598,7 +4604,7 @@
         <v>83</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>0.08</v>
@@ -4608,7 +4614,7 @@
         <v>4.6512</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">B9*Assumptions!$B$5</f>
@@ -4634,7 +4640,7 @@
         <v>106</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>0.35</v>
@@ -4644,7 +4650,7 @@
         <v>28.12187</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">B10*Assumptions!$B$5</f>
@@ -4691,7 +4697,7 @@
       </c>
       <c r="B12" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A12,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>43.9</v>
+        <v>20.85</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
@@ -4708,16 +4714,16 @@
       </c>
       <c r="I12" s="3" t="n">
         <f aca="false">B12*Assumptions!$B$5</f>
-        <v>3.40225</v>
+        <v>1.615875</v>
       </c>
       <c r="J12" s="3" t="n">
         <f aca="false">B12+C12+G12+I12</f>
-        <v>53.30225</v>
+        <v>28.465875</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A13,'Detailed BOM'!$K$5:$K$34)</f>
@@ -4747,7 +4753,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A14,'Detailed BOM'!$K$5:$K$34)</f>
@@ -4777,7 +4783,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A15,'Detailed BOM'!$K$5:$K$34)</f>
@@ -4807,7 +4813,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A16,'Detailed BOM'!$K$5:$K$34)</f>
@@ -4837,7 +4843,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B17" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A17,'Detailed BOM'!$K$5:$K$34)</f>
@@ -4867,7 +4873,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0</v>
@@ -4882,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>0</v>
@@ -4899,11 +4905,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">SUM(B5:B17)</f>
-        <v>1112.0682</v>
+        <v>1089.0182</v>
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">SUM(C5:C17)</f>
@@ -4919,11 +4925,11 @@
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="n">
         <f aca="false">SUM(I5:I17)</f>
-        <v>86.1852855</v>
+        <v>84.3989105</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">SUM(J5:J18)</f>
-        <v>1697.3575555</v>
+        <v>1672.5211805</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4933,14 +4939,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" s="3" t="n">
         <f aca="false">B20-'Detailed BOM'!K36</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4971,12 +4977,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4986,198 +4992,198 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>277.2</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>77</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>75.15</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>133.13</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -5220,12 +5226,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5235,37 +5241,37 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>
@@ -5273,19 +5279,19 @@
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5303,30 +5309,30 @@
         <v>0</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>892</v>
@@ -5343,30 +5349,30 @@
         <v>733.8018</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>3172</v>
@@ -5383,30 +5389,30 @@
         <v>3013.8018</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>111</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F8" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5424,30 +5430,30 @@
         <v>-20</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>156</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F9" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5465,30 +5471,30 @@
         <v>25</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5506,13 +5512,13 @@
         <v>100</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5546,12 +5552,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,7 +5567,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5570,12 +5576,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5585,30 +5591,30 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>5</v>
@@ -5616,13 +5622,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
@@ -5638,18 +5644,18 @@
         <v>65</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -5667,13 +5673,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>1</v>
@@ -5691,7 +5697,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F13" s="3" t="n">
         <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5700,7 +5706,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F14" s="3" t="n">
         <f aca="false">F13-B4</f>
@@ -5714,7 +5720,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5756,12 +5762,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5771,49 +5777,49 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5821,10 +5827,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>88</v>
@@ -5866,7 +5872,7 @@
         <v>96</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5874,10 +5880,10 @@
         <v>88</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>88</v>
@@ -5919,7 +5925,7 @@
         <v>100</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5927,10 +5933,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>88</v>
@@ -5972,7 +5978,7 @@
         <v>85</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5980,10 +5986,10 @@
         <v>88</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>88</v>
@@ -6025,7 +6031,7 @@
         <v>92</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6033,10 +6039,10 @@
         <v>81</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>80</v>
@@ -6075,10 +6081,10 @@
         <v>14.4166666666667</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6086,13 +6092,13 @@
         <v>111</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2</v>
@@ -6130,7 +6136,7 @@
         <v>108</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6138,13 +6144,13 @@
         <v>111</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>4</v>
@@ -6179,10 +6185,10 @@
         <v>1.20513570229435</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,13 +6196,13 @@
         <v>111</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>2</v>
@@ -6231,10 +6237,10 @@
         <v>7.47</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6242,13 +6248,13 @@
         <v>111</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>122</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>2</v>
@@ -6286,12 +6292,12 @@
         <v>120</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G14" s="3" t="n">
         <f aca="false">SUM(G5:G13)</f>
@@ -6304,14 +6310,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">L14-832.1</f>
         <v>0</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6321,12 +6327,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>543.83</v>
@@ -6334,7 +6340,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G19" s="3" t="n">
         <f aca="false">L14+G18</f>
@@ -6369,7 +6375,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6379,291 +6385,291 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -6694,12 +6700,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6709,80 +6715,80 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B5" s="20" t="n">
         <v>0.0775</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>65</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>105</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6792,27 +6798,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6822,187 +6828,187 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -526,7 +526,7 @@
     <t xml:space="preserve">https://adafruit.com/product/4821</t>
   </si>
   <si>
-    <t xml:space="preserve">Direct product page. Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
+    <t xml:space="preserve">Direct product page, in stock. Checked 2026-10-21: resolution 0.0078 C per step, accuracy +/-0.1 C. Resolution is what matters, since this is for spotting changes, not absolute temperature. A printed loop expands roughly 1 nm per mK (assumes 30-70 ppm/K, about 30 mm of mismatched plastic, not measured), so one step is about 10 nm of drift. Good enough to tell whether drift of tens of nm follows temperature and when the head has settled; no affordable sensor resolves the ~0.1 mK that atom-scale drift corresponds to. Keep its I2C wiring away from the preamp input, or log it standalone (INVENTORY.md). Zahl: monitor temperature; Baird: steady amplifier temperature.</t>
   </si>
   <si>
     <t xml:space="preserve">ME-01</t>
@@ -4109,7 +4109,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
         <v>161</v>
       </c>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="591">
   <si>
     <t xml:space="preserve">STM v2 (UCSD) - budget summary, lean scenario</t>
   </si>
@@ -535,1255 +535,1261 @@
     <t xml:space="preserve">3D-printing filament for head, sample plate and approach body</t>
   </si>
   <si>
-    <t xml:space="preserve">Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusa Research</t>
+    <t xml:space="preserve">SUNLU PETG-CF (PETG carbon fiber), 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUNLU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 kg spool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page, sale price $19.99 (regular $22.99); free US shipping stated. Cheaper than v1's only recorded filament (SUNLU Easy PA nylon, $27.99, 2026-06-21). Carbon fiber is kept because it makes printed parts stiffer and more dimensionally stable than plain PETG; same brand's Easy PA nylon is $34.99. Prusament PETG-CF was $54.99 for the same material class. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walmart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ted Pella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isolate It</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Components subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor and order totals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales or use tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 Thorlabs order shipping, 2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ships from the US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forum report Dec 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store states free shipping to most of the US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL ORDERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(should be 0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moved out of the purchase list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference value if bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir tip wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind from a UCSD lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOPG sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D printer time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite base or optical breadboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield enclosures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Merchandise only. DIY driver = BOM lines HV-01 to HV-04. The total uses P1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tube price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver / dependencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Driver cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Option total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change vs P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. XY (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Est. Z (um)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~13-16 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~3 (est.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD250-INV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 (spec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB2006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY OPA454 driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~0.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB4006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~8.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coarse approach and sample plate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Two hand-set 1/4-80 screws and the motor screw form the tripod, with steel-ball pivots (ME-04)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not chosen, for the record: piezo stick-slip slider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive SA050510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also needed a sawtooth HV channel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sapphire contacts, 2 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edmund Optics 43-642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground guide rod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stick-slip parts total (merchandise, plus one OPA454 channel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference vs the chosen stepper drive (positive = stick-slip costs more)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch). No springs or rubber bands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 purchases (historical prices)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer / part</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tariff / import tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alloc. sales tax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed line cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Landed unit cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v2 line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-layer bare STM controller PCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor invoice (kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approach scenario B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Devices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTL-28 (different part)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone 11311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keystone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(not in v2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invoiced orders total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where it is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total under $2,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See total vs ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind and campus tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered (assumed, unverified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No reuse of v1 parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vasquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04, Piezo options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; driver provisional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample plate replaced, not v1's springs; coarse approach stays a stepper (Jacob)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02..04, ME-04, ME-05, Approach options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detailed BOM 'Source link'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature monitoring; enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conflicts with the printed structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN - flagged (U4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel balls at pivots; stiff screw drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04; PZ-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baird</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope the preamp output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus, unverified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions and unresolved costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied to all merchandise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contingency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10% for price drift and breakage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure is printed; kept for reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacob's requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unresolved items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect on the total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What would resolve it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV driver design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01..04: $158.20 incl. transformer placeholder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB price today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campus items really free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed (Jacob's choice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filament choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick based on the campus printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screw bushings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping and duty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No rate shown; DAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sorbothane price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant price not displayed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$35 estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+/- $10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check the cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item or topic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-02 Adafruit 324 (12 V, 350 mA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-03 Adafruit 6121 (TMC2209 breakout)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-02 Keystone 11301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-03 not designed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no link - see BOM note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-03 Energizer MAX 522BP-4, 4-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-04 Keystone 1294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-01 SUNLU PETG-CF (PETG carbon fiber), 1.75 mm, 1 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCSD MPL machine shop rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EnVision access rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vetco MG 8331D-14G $167.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kozak Micro 1/4-80 screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMC2209 driver $4.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prusament PETG Carbon Fiber 1 kg $54.99 (MatterHackers lists the same spool at $89.99)</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 kg spool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page, in stock. One spool covers the parts and reprints. Material is still open: PETG-CF is stiff and easy to print; nylon-CF is stiffer but needs a dried, hardened-nozzle printer. Zahl advised against plastics in the mechanical loop; printing is Jacob's choice for this budget.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardened steel balls for kinematic pivots</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walmart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.walmart.com/ip/533082272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magnetic stainless sample discs, 12 mm (HOPG carrier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ted Pella</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tedpella.com/AFM_html/AFM.aspx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catalogue page lists 16208 at $30.00 per 50. Replaces v1's rubber-band/spring plate.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane isolation pads, 0.5 in, 50 duro, 6x6 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolate It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct product page; this variant's price was not displayed (only the 0.08 in pad, $24.95).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Components subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor and order totals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One order per vendor; shipping, tariff and tax are per order, never assigned to one item.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales or use tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate on the site (DAP from Australia).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% provisional US tariff assumed; carrier fee in the Fees row.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 Thorlabs order shipping, 2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ships from the US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DHL shipping for the same order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC tariff page: 35% on PCB/SMT (v1 paid $163.48, about 32%).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 DigiKey standard shipping.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 receipts: ~8% tariff surcharge on ICs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forum report Dec 2025.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLC group's 35% PCB/SMT rate as proxy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive: carriers may charge USD 30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALL ORDERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check: merchandise equals the BOM subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(should be 0.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moved out of the purchase list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not in the total. Reference values show what each would cost if a lab can't provide it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference value if bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir tip wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind from a UCSD lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://store.bruker.com/products/dpt10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: Bruker DPT10 10 cut tips $277.20; Advent 0.25 mm x 0.2 m wire $297.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOPG sample</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference: NanoAndMore ZYH 10x10x1 mm $77.00. Jacob: sourced from UCSD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not needed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All structure is 3D printed; no machined parts, no shop fees.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3D printer time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jacobsschool.ucsd.edu/envision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision has 3D printers; fees not stated and Jacob's eligibility unconfirmed. Filament is purchased (ME-01).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite base or optical breadboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: Grizzly G9649 $75.15 + freight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench power supply (+/-15 V class)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 bought a $42.74 supply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oscilloscope, multimeter, soldering station, hot air</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision lists soldering stations and oscilloscopes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver epoxy or silver paint for mounting HOPG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference if bought: MG 8331D-14G $133.13 (DigiKey via aggregator).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wire (40 AWG magnet wire, 30 AWG Kynar), coax, hook-up wire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connectors, headers, DIP sockets, ribbon/USB/DB9 cables</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common lab stock; v1 spent about $50 on these on Amazon.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fasteners, springs, small magnets, BeCu or steel shim for clips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumables: IPA, acetone, flux, solder, wipes, gloves, tape, copper tape</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemistry stockroom sells against a project number; v1 lessons (99% IPA, RMA flux, copper tape) still apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tools: flush cutters, tweezers, ESD strap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shield enclosures</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die-cast box or copper tape from lab stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo purchasing options with dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Merchandise only. DIY driver = BOM lines HV-01 to HV-04. The total uses P1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tube price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver / dependencies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Driver cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extra services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Option total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change vs P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. XY (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Est. Z (um)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline: TB3006-N + DIY 5-channel OPA454 driver at +/-45 V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 linear driver (HVD-01..07, provisional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lowest cost. Range scales with voltage: about 29*(45/260)=5.0 um XY and 6.3*(45/260)=1.1 um Z if linear (estimate from PiezoDrive's spec at +/-260 V). Driver is an undesigned new circuit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + 2x PiezoDrive PDu150 + 2x PS1 supply</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2x PDu150 ($413) + 2x PS1 ($33)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~13-16 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~3 (est.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial, low noise (26 uV). Output is -30 to +150 V (unipolar), 3 channels per module, so 5 tube channels need two modules. PiezoDrive does not state how to wire it to a quartered tube. One PS1 per module assumed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB3006-N + PiezoDrive TD250-INV (vendor's recommended tube driver)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TD250-INV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29 (spec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3 (spec, half if Z shares)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive's own recommendation for tube scanners. Alone it exceeds the $2,000 ceiling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N (20 mm, stiffer) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB2006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIY OPA454 driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~0.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorter tube: less range (13 um XY spec), higher resonance. Saves $20.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N (40 mm, more range) + DIY driver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TB4006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~8.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">~1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">More XY range (51 um spec), lower resonance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline + PiezoDrive factory wiring service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horizontal Tube Wiring service $100 (vertical wiring price not loaded). Removes hand-soldering of electrode leads.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coarse approach and sample plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Two hand-set 1/4-80 screws and the motor screw form the tripod, with steel-ball pivots (ME-04)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not chosen, for the record: piezo stick-slip slider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive SA050510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/150v-5x5x10mm-piezo-stack-actuator-sa050510/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also needed a sawtooth HV channel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sapphire contacts, 2 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edmund Optics 43-642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.edmundoptics.com/p/20mm-diameter-sapphire-ball-lens/5174/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ground guide rod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnlineMetals W1 drill rod 1/8 in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.onlinemetals.com/en/buy/tool-steel-drill-rod-w1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stick-slip parts total (merchandise, plus one OPA454 channel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Difference vs the chosen stepper drive (positive = stick-slip costs more)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate: printed rigid plate + magnetic 12 mm steel disc (ME-05) on lab magnets; HOPG mounted with lab silver epoxy/paint (Baird) or clipped (Zahl's sketch). No springs or rubber bands.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 purchases (historical prices)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order-level shipping, discount and tax allocated by line merchandise; line-specific tariffs used where shown.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manufacturer / part</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Line merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. shipping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tariff / import tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alloc. sales tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed line cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Landed unit cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v2 line</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2-layer bare STM controller PCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor invoice (kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bare preamp PCB (OPA627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled controller board SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assembled preamp board SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAS200 2 in ultra-fine adjustment screw 1/4-80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approach scenario B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LT1469IN8#PBF dual op-amp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB9 receptacle A-DF 09 A/KG-T4S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTL-28 (different part)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone 11311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keystone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(not in v2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invoiced orders total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check vs invoice totals ($832.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon purchases (42 small orders: tools, consumables, hardware; line items kept private)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirements checklist (lean scenario)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where it is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total under $2,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See total vs ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Built at UCSD; campus items listed, not hidden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind and campus tab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered (assumed, unverified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No reuse of v1 parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All lines are new purchases; JLCPCB order is a new order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tip wire and HOPG from UCSD; printed structure; v1-style JLCPCB boards; filament bought</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind tab; ME-01; EL-01..04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Better piezo, possibly a tube (Vasquez), not a confirmed diagnosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vasquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piezo dependencies priced (driver, power, extra channels)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04, Piezo options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; driver provisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample plate replaced, not v1's springs; coarse approach stays a stepper (Jacob)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02..04, ME-04, ME-05, Approach options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every purchased line has a direct link or says why not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detailed BOM 'Source link'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Covered; 4 lines explain missing direct links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature monitoring; enclosure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05; enclosure from campus stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conflicts with the printed structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN - flagged (U4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steel balls at pivots; stiff screw drive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04; PZ-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 GOhm feedback + ~1.6 pF; batteries; ceramic caps; shielding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baird</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01, PA-03, PA-04; caps on rev 2 board; shield from campus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cut Pt/Ir tips; HOPG on conductive epoxy / steel disc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In-kind wire/HOPG/epoxy; ME-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scope the preamp output</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus oscilloscope (assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus, unverified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shipping, tariffs, tax, contingency, pack sizes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor-order totals; Budget summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earlier full-build scenario kept for comparison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget summary + STM_v2_budget_full_build.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions and unresolved costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cells B5-B9 drive formulas on other tabs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">California sales/use tax, City of San Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied to all merchandise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contingency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10% for price drift and breakage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carrier import processing fee (PiezoDrive, DAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Midpoint of PiezoDrive's stated $30-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/?p=991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(unused in this scenario) machining rate $/hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Structure is printed; kept for reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://mpl.ucsd.edu/machine-shop-info/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budget ceiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob's requirement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario assumptions (Jacob, 2026-10-21)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt/Ir wire and HOPG come from UCSD labs (in-kind).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Everything structural is 3D printed; nothing is machined. Filament is purchased.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electronics repeat v1's JLCPCB order: 2 controller boards and 2 preamps, fully placed. This is a new purchase, priced from the 2026-07-15 invoice.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchases are limited to what a lab doesn't readily have: batteries, the piezo and its driver, and other specialty parts. Commodity lab items are listed on 'In-kind and campus' as assumed campus stock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unresolved items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect on the total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What would resolve it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV driver design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not drawn; only the op-amps are priced exactly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01..04: $158.20 incl. transformer placeholder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Could move +/-$50; commercial PDu150 modules instead add about $734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draw the schematic, then itemize with links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB price today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Can't re-quote without uploading gerbers and BOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 unit prices + today's 35% tariff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part prices have moved; likely +/-10% on $497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload the v1 files to JLCPCB for a quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campus items really free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printers, supply, scope, epoxy, wire, stock not confirmed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bench supply ~$43+, epoxy $133 if a lab can't lend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm with Prof. Vasquez's lab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed structure vs Zahl's advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zahl: no plastics in the mechanical loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed (Jacob's choice)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal parts would bring back machining or stock cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decide with the advisers; ceramic/metal inserts at the tip-sample loop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filament choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF vs nylon-CF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETG-CF 1 kg $54.99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nylon-CF is similar or a bit more</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick based on the campus printer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screw bushings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None priced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping and duty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rate shown; DAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$60 + 10% + $65 carrier fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ask PiezoDrive for a delivered quote</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variant price not displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$35 estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+/- $10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check the cart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vendor's own page loaded on 2026-10-21 and showed the price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octopart/Findchips loaded and showed the distributor's price; distributor site blocked here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What v1 paid; used where no current price could be obtained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No price page, or part not chosen; note gives the basis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item or topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-01 PiezoDrive TB3006-N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-02 Adafruit 324 (12 V, 350 mA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-03 Adafruit 6121 (TMC2209 breakout)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-02 JLCPCB SMT assembly, v1 preamp rev 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-03 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-04 JLCPCB 2-layer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-04 JLCPCB 2-layer, 5 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-05 Analog Devices LT1469IN8#PBF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-01 Ohmite SM104031007FE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-02 Keystone 11301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-01 TI OPA454AIDDAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-03 not designed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no link - see BOM note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HV-02 toroid, secondary not chosen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-03 Energizer MAX 522BP-4, 4-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-04 Keystone 1294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-06 Teensy 4.1 (SparkFun DEV-16771)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PA-05 Adafruit 4821 (TI TMP117)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-01 Prusament PETG Carbon Fiber, 1.75 mm, 1 kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-04 uxcell 52100 G25, 0.18 in, 100 pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-05 Ted Pella 16208, pack of 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME-06 Sorbothane 0266050-50-10 (2 per pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB US tariff rates (35% PCB/SMT, 90% stencils, effective 2026-03-17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlc3dp.com/help/article/us-tariff-policy-faq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive shipping terms (DAP, duties extra, carrier fee $30-100)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube scanner specs and drive recommendation (TD250-INV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/piezoelectric-tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive tube price list (TB1006-N $63 .. TB10006-N $289)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product-category/tube-scanners/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PDu150 $413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive PS1 24 V supply $33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive TD250 $3,172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/td250-six-channel-250v/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiezoDrive horizontal tube wiring $100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.piezodrive.com/product/horizontal-tube-wiring/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Diego combined sales tax 7.75%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCSC Global Direct shipping/tariff experiences (forum, Dec 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD shop resources list (EnVision, Upper Campus shop, QI, stockroom)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCSD MPL machine shop rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EnVision access rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goodfellow Macor 3.2 mm x 100 mm $145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruker DPT10 Pt/Ir tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPI Pt/Ir 0.20 mm wire $206.64 / 2 ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.2spi.com/item/z01707/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigma Pt80Ir20 0.25 mm 1 m $1,730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite 12x18x3 G9651 $149.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BatteryMart Energizer L522 lithium $21.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vetco MG 8331D-14G $167.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kozak Micro 1/4-80 screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMC2209 driver $4.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prusament PETG Carbon Fiber 1 kg $54.99 (MatterHackers lists the same spool at $89.99)</t>
   </si>
   <si>
     <t xml:space="preserve">LCSC LT1469IN8#PBF now $23.77, out of stock</t>
@@ -2371,7 +2377,7 @@
       </c>
       <c r="B11" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A11,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>129.98</v>
+        <v>94.98</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2380,7 +2386,7 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>1089.0182</v>
+        <v>1054.0182</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>14</v>
@@ -2392,7 +2398,7 @@
       </c>
       <c r="B13" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Verified*",'Detailed BOM'!$K$5:$K$34)</f>
-        <v>382.0682</v>
+        <v>347.0682</v>
       </c>
       <c r="C13" s="7"/>
     </row>
@@ -2422,7 +2428,7 @@
       </c>
       <c r="B16" s="3" t="n">
         <f aca="false">'Vendor-order totals'!C20</f>
-        <v>214.26</v>
+        <v>204.26</v>
       </c>
       <c r="C16" s="7"/>
     </row>
@@ -2454,7 +2460,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">'Vendor-order totals'!I20</f>
-        <v>84.3989105</v>
+        <v>81.6864105</v>
       </c>
       <c r="C19" s="7"/>
     </row>
@@ -2464,7 +2470,7 @@
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">B12+B16+B17+B18+B19</f>
-        <v>1672.5211805</v>
+        <v>1624.8086805</v>
       </c>
       <c r="C20" s="6"/>
     </row>
@@ -2474,7 +2480,7 @@
       </c>
       <c r="B21" s="3" t="n">
         <f aca="false">B20*Assumptions!B6</f>
-        <v>167.25211805</v>
+        <v>162.48086805</v>
       </c>
       <c r="C21" s="7"/>
     </row>
@@ -2484,7 +2490,7 @@
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">B20+B21</f>
-        <v>1839.77329855</v>
+        <v>1787.28954855</v>
       </c>
       <c r="C22" s="10"/>
     </row>
@@ -2504,7 +2510,7 @@
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">Assumptions!B9-B22</f>
-        <v>160.22670145</v>
+        <v>212.71045145</v>
       </c>
       <c r="C24" s="7"/>
     </row>
@@ -2677,7 +2683,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2690,7 +2696,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2698,7 +2704,7 @@
         <v>118</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2706,7 +2712,7 @@
         <v>83</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2714,7 +2720,7 @@
         <v>106</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2724,15 +2730,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>63</v>
@@ -2740,7 +2746,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>71</v>
@@ -2748,7 +2754,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>76</v>
@@ -2756,7 +2762,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>82</v>
@@ -2764,7 +2770,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>89</v>
@@ -2772,7 +2778,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>89</v>
@@ -2780,7 +2786,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>89</v>
@@ -2788,7 +2794,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>89</v>
@@ -2796,7 +2802,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>89</v>
@@ -2804,7 +2810,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>112</v>
@@ -2812,7 +2818,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>117</v>
@@ -2820,7 +2826,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>123</v>
@@ -2828,7 +2834,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>129</v>
@@ -2836,15 +2842,15 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>141</v>
@@ -2852,7 +2858,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>147</v>
@@ -2860,7 +2866,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>153</v>
@@ -2868,7 +2874,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>159</v>
@@ -2876,7 +2882,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>164</v>
@@ -2884,7 +2890,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>170</v>
@@ -2892,7 +2898,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>177</v>
@@ -2900,7 +2906,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>184</v>
@@ -2908,7 +2914,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>191</v>
@@ -2916,202 +2922,202 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>170</v>
+        <v>586</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -3134,7 +3140,7 @@
     <hyperlink ref="B25" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
     <hyperlink ref="B26" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
     <hyperlink ref="B27" r:id="rId18" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="B28" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
+    <hyperlink ref="B28" r:id="rId19" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
     <hyperlink ref="B29" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
     <hyperlink ref="B30" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
     <hyperlink ref="B31" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
@@ -4168,7 +4174,7 @@
       <c r="L30" s="14"/>
       <c r="M30" s="14"/>
     </row>
-    <row r="31" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
         <v>166</v>
       </c>
@@ -4197,11 +4203,11 @@
         <v>1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>54.99</v>
+        <v>19.99</v>
       </c>
       <c r="K31" s="3" t="n">
         <f aca="false">I31*J31</f>
-        <v>54.99</v>
+        <v>19.99</v>
       </c>
       <c r="L31" s="15" t="s">
         <v>65</v>
@@ -4347,7 +4353,7 @@
       </c>
       <c r="K36" s="12" t="n">
         <f aca="false">SUM(K5:K34)</f>
-        <v>1089.0182</v>
+        <v>1054.0182</v>
       </c>
     </row>
   </sheetData>
@@ -4370,7 +4376,7 @@
     <hyperlink ref="F26" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
     <hyperlink ref="F28" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
     <hyperlink ref="F29" r:id="rId18" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="F31" r:id="rId19" display="https://www.prusa3d.com/product/prusament-petg-carbon-fiber-black-1kg/"/>
+    <hyperlink ref="F31" r:id="rId19" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
     <hyperlink ref="F32" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
     <hyperlink ref="F33" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
     <hyperlink ref="F34" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
@@ -4757,13 +4763,16 @@
       </c>
       <c r="B14" s="3" t="n">
         <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A14,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>54.99</v>
+        <v>19.99</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>106</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>216</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>0</v>
@@ -4774,11 +4783,11 @@
       </c>
       <c r="I14" s="3" t="n">
         <f aca="false">B14*Assumptions!$B$5</f>
-        <v>4.261725</v>
+        <v>1.549225</v>
       </c>
       <c r="J14" s="3" t="n">
         <f aca="false">B14+C14+G14+I14</f>
-        <v>69.251725</v>
+        <v>21.539225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4873,7 +4882,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0</v>
@@ -4888,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>0</v>
@@ -4905,15 +4914,15 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">SUM(B5:B17)</f>
-        <v>1089.0182</v>
+        <v>1054.0182</v>
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">SUM(C5:C17)</f>
-        <v>214.26</v>
+        <v>204.26</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
@@ -4925,11 +4934,11 @@
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="n">
         <f aca="false">SUM(I5:I17)</f>
-        <v>84.3989105</v>
+        <v>81.6864105</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">SUM(J5:J18)</f>
-        <v>1672.5211805</v>
+        <v>1624.8086805</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4939,14 +4948,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B22" s="3" t="n">
         <f aca="false">B20-'Detailed BOM'!K36</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4977,12 +4986,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4992,198 +5001,198 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>277.2</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>77</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>75.15</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>133.13</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -5226,12 +5235,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5241,37 +5250,37 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>
@@ -5279,19 +5288,19 @@
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F5" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5309,30 +5318,30 @@
         <v>0</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>892</v>
@@ -5349,30 +5358,30 @@
         <v>733.8018</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>3172</v>
@@ -5389,30 +5398,30 @@
         <v>3013.8018</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>111</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F8" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5430,30 +5439,30 @@
         <v>-20</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>156</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F9" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5471,30 +5480,30 @@
         <v>25</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F10" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5512,13 +5521,13 @@
         <v>100</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5552,12 +5561,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5567,7 +5576,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3" t="n">
         <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5576,12 +5585,12 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5591,30 +5600,30 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>5</v>
@@ -5622,13 +5631,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
@@ -5644,18 +5653,18 @@
         <v>65</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -5673,13 +5682,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>1</v>
@@ -5697,7 +5706,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F13" s="3" t="n">
         <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))</f>
@@ -5706,7 +5715,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F14" s="3" t="n">
         <f aca="false">F13-B4</f>
@@ -5720,7 +5729,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -5762,12 +5771,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5777,49 +5786,49 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5827,10 +5836,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>88</v>
@@ -5872,7 +5881,7 @@
         <v>96</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5880,10 +5889,10 @@
         <v>88</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>88</v>
@@ -5925,7 +5934,7 @@
         <v>100</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5933,10 +5942,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" s="0" t="s">
         <v>88</v>
@@ -5978,7 +5987,7 @@
         <v>85</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5986,10 +5995,10 @@
         <v>88</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>88</v>
@@ -6031,7 +6040,7 @@
         <v>92</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6039,10 +6048,10 @@
         <v>81</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>80</v>
@@ -6081,10 +6090,10 @@
         <v>14.4166666666667</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6092,13 +6101,13 @@
         <v>111</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2</v>
@@ -6136,7 +6145,7 @@
         <v>108</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6144,13 +6153,13 @@
         <v>111</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>4</v>
@@ -6185,10 +6194,10 @@
         <v>1.20513570229435</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6196,13 +6205,13 @@
         <v>111</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>2</v>
@@ -6237,10 +6246,10 @@
         <v>7.47</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,13 +6257,13 @@
         <v>111</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>122</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>2</v>
@@ -6292,12 +6301,12 @@
         <v>120</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G14" s="3" t="n">
         <f aca="false">SUM(G5:G13)</f>
@@ -6310,14 +6319,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">L14-832.1</f>
         <v>0</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6327,12 +6336,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>543.83</v>
@@ -6340,7 +6349,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G19" s="3" t="n">
         <f aca="false">L14+G18</f>
@@ -6375,7 +6384,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6385,291 +6394,291 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>392</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -6700,12 +6709,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6715,80 +6724,80 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B5" s="20" t="n">
         <v>0.0775</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>65</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>105</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6798,27 +6807,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6828,187 +6837,187 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="597">
   <si>
     <t xml:space="preserve">STM v2 (UCSD) - budget summary, lean scenario</t>
   </si>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">PZ-04</t>
   </si>
   <si>
-    <t xml:space="preserve">Fine-pitch adjuster screws, 1/4-80 (one motor-driven, two hand-set)</t>
+    <t xml:space="preserve">Ultra-fine adjustment screws, 1/4-80, 2 in long (one motor-driven, two hand-set)</t>
   </si>
   <si>
     <t xml:space="preserve">Thorlabs FAS200</t>
@@ -280,30 +280,45 @@
     <t xml:space="preserve">https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200</t>
   </si>
   <si>
+    <t xml:space="preserve">Jacob specified FAS200 (2 in, 1/4-80), the same screws v1 used (three bought 2026-06-24 at $8.78). $8.80 is the Thorlabs catalog page 521 price (PDF loaded; undated); the product page does not load from here. 1/4-80 is 317.5 um per turn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threaded bushings for the 1/4-80 screws (one per screw)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thorlabs F25SSN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4-80 threaded bushing, 0.63 in long, from the same Thorlabs catalog page ($8.60). Gives each screw a metal thread instead of a printed one, which wears. The printed part needs a hole sized to the bushing (take it from the Thorlabs drawing). v1's CAD names McMaster 98625A960 brass inserts instead; McMaster does not load here, so not priced.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EL-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jlcpcb.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">each (2 min)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Historical - v1 receipt</t>
   </si>
   <si>
-    <t xml:space="preserve">Same screws as v1 (three bought 2026-06-24 at $8.78). Thorlabs pages do not load from here, so this is v1's price. 1/4-80 is 317.5 um per turn. v1 ran them in printed threads; matching brass bushings are not priced (U6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EL-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controller board, fully assembled (v1 design)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB SMT assembly, v1 controller design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLCPCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jlcpcb.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">each (2 min)</t>
-  </si>
-  <si>
     <t xml:space="preserve">v1 invoice 2026-07-15 unit price. Re-quote not possible from here: JLCPCB prices only after gerber + BOM upload. Parts prices have moved since (e.g. LT1469 now $23.77 and out of stock at LCSC).</t>
   </si>
   <si>
@@ -970,7 +985,7 @@
     <t xml:space="preserve">Jacob's choice (2026-10-21): a stepper-driven fine screw, not stick-slip. v1's rubber-band/spring plate and geared 28BYJ-48 are retired.</t>
   </si>
   <si>
-    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 + PZ-03 + PZ-04</t>
+    <t xml:space="preserve">Chosen: stepper on a 1/4-80 screw = PZ-02 to PZ-05</t>
   </si>
   <si>
     <t xml:space="preserve">   Motor: NEMA-17 (Adafruit 324) with a TMC2209 driver at up to 1/256 microstepping, about 6 nm of screw travel per microstep before any lever</t>
@@ -1531,19 +1546,19 @@
     <t xml:space="preserve">U6</t>
   </si>
   <si>
-    <t xml:space="preserve">Screw bushings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v1 ran the 1/4-80 screws in printed threads, which wear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None priced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brass 1/4-80 bushings would add a few dollars each</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price Thorlabs or Newport bushings when their pages load</t>
+    <t xml:space="preserve">Bushing fit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F25SSN1 bushings are priced, but the printed hole for them is not drawn yet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bushings $25.80, priced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If the McMaster 98625A960 press-in inserts from v1's CAD are used instead, a few dollars different</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size the printed hole from the Thorlabs drawing, or price the McMaster insert</t>
   </si>
   <si>
     <t xml:space="preserve">U7</t>
@@ -1610,6 +1625,9 @@
   </si>
   <si>
     <t xml:space="preserve">PZ-04 Thorlabs FAS200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PZ-05 Thorlabs F25SSN1</t>
   </si>
   <si>
     <t xml:space="preserve">EL-01 JLCPCB SMT assembly, v1 controller design</t>
@@ -2322,7 +2340,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A5,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A5,'Detailed BOM'!$K$5:$K$35)</f>
         <v>131</v>
       </c>
     </row>
@@ -2331,8 +2349,8 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A6,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>49.29</v>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A6,'Detailed BOM'!$K$5:$K$35)</f>
+        <v>75.15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2340,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A7,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A7,'Detailed BOM'!$K$5:$K$35)</f>
         <v>497.06</v>
       </c>
     </row>
@@ -2349,7 +2367,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A8,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A8,'Detailed BOM'!$K$5:$K$35)</f>
         <v>132.5082</v>
       </c>
     </row>
@@ -2358,7 +2376,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A9,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A9,'Detailed BOM'!$K$5:$K$35)</f>
         <v>94.68</v>
       </c>
     </row>
@@ -2367,7 +2385,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A10,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A10,'Detailed BOM'!$K$5:$K$35)</f>
         <v>54.5</v>
       </c>
     </row>
@@ -2376,7 +2394,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$34,A11,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$B$5:$B$35,A11,'Detailed BOM'!$K$5:$K$35)</f>
         <v>94.98</v>
       </c>
     </row>
@@ -2386,7 +2404,7 @@
       </c>
       <c r="B12" s="5" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>1054.0182</v>
+        <v>1079.8782</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>14</v>
@@ -2397,8 +2415,8 @@
         <v>15</v>
       </c>
       <c r="B13" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Verified*",'Detailed BOM'!$K$5:$K$34)</f>
-        <v>347.0682</v>
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$35,"Verified*",'Detailed BOM'!$K$5:$K$35)</f>
+        <v>399.2682</v>
       </c>
       <c r="C13" s="7"/>
     </row>
@@ -2407,8 +2425,8 @@
         <v>16</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Historical*",'Detailed BOM'!$K$5:$K$34)</f>
-        <v>517.58</v>
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$35,"Historical*",'Detailed BOM'!$K$5:$K$35)</f>
+        <v>491.24</v>
       </c>
       <c r="C14" s="7"/>
     </row>
@@ -2417,7 +2435,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$34,"Estimated",'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$L$5:$L$35,"Estimated",'Detailed BOM'!$K$5:$K$35)</f>
         <v>189.37</v>
       </c>
       <c r="C15" s="7"/>
@@ -2460,7 +2478,7 @@
       </c>
       <c r="B19" s="3" t="n">
         <f aca="false">'Vendor-order totals'!I20</f>
-        <v>81.6864105</v>
+        <v>83.6905605</v>
       </c>
       <c r="C19" s="7"/>
     </row>
@@ -2470,7 +2488,7 @@
       </c>
       <c r="B20" s="5" t="n">
         <f aca="false">B12+B16+B17+B18+B19</f>
-        <v>1624.8086805</v>
+        <v>1652.6728305</v>
       </c>
       <c r="C20" s="6"/>
     </row>
@@ -2480,7 +2498,7 @@
       </c>
       <c r="B21" s="3" t="n">
         <f aca="false">B20*Assumptions!B6</f>
-        <v>162.48086805</v>
+        <v>165.26728305</v>
       </c>
       <c r="C21" s="7"/>
     </row>
@@ -2490,7 +2508,7 @@
       </c>
       <c r="B22" s="9" t="n">
         <f aca="false">B20+B21</f>
-        <v>1787.28954855</v>
+        <v>1817.94011355</v>
       </c>
       <c r="C22" s="10"/>
     </row>
@@ -2510,7 +2528,7 @@
       </c>
       <c r="B24" s="12" t="n">
         <f aca="false">Assumptions!B9-B22</f>
-        <v>212.71045145</v>
+        <v>182.05988645</v>
       </c>
       <c r="C24" s="7"/>
     </row>
@@ -2542,7 +2560,7 @@
       </c>
       <c r="B28" s="3" t="n">
         <f aca="false">'Approach options'!F14</f>
-        <v>115.0047</v>
+        <v>89.1447</v>
       </c>
       <c r="C28" s="7"/>
     </row>
@@ -2674,7 +2692,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -2683,7 +2701,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2696,31 +2714,31 @@
         <v>65</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2730,15 +2748,15 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>63</v>
@@ -2746,7 +2764,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>71</v>
@@ -2754,7 +2772,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>76</v>
@@ -2762,7 +2780,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>82</v>
@@ -2770,55 +2788,55 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>117</v>
@@ -2826,63 +2844,63 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>536</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>537</v>
+        <v>541</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>538</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>141</v>
+        <v>542</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>164</v>
@@ -2890,234 +2908,242 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>548</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>452</v>
+        <v>554</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>551</v>
+        <v>457</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>447</v>
+        <v>567</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>564</v>
+        <v>452</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>249</v>
+        <v>570</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>455</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>241</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>569</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>231</v>
+        <v>575</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>572</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>589</v>
-      </c>
-      <c r="B56" s="0" t="s">
-        <v>590</v>
+        <v>593</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -3126,47 +3152,48 @@
     <hyperlink ref="B10" r:id="rId2" display="https://www.adafruit.com/product/324"/>
     <hyperlink ref="B11" r:id="rId3" display="https://adafruit.com/product/6121"/>
     <hyperlink ref="B12" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
-    <hyperlink ref="B13" r:id="rId5" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B13" r:id="rId5" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1"/>
     <hyperlink ref="B14" r:id="rId6" display="https://jlcpcb.com/"/>
     <hyperlink ref="B15" r:id="rId7" display="https://jlcpcb.com/"/>
     <hyperlink ref="B16" r:id="rId8" display="https://jlcpcb.com/"/>
     <hyperlink ref="B17" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="B18" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="B19" r:id="rId11" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="B20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="B21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="B23" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="B24" r:id="rId15" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
-    <hyperlink ref="B25" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
-    <hyperlink ref="B26" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="B27" r:id="rId18" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="B28" r:id="rId19" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
-    <hyperlink ref="B29" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
-    <hyperlink ref="B30" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
-    <hyperlink ref="B31" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
-    <hyperlink ref="B32" r:id="rId23" display="https://jlc3dp.com/help/article/us-tariff-policy-faq"/>
-    <hyperlink ref="B33" r:id="rId24" display="https://www.piezodrive.com/?p=991"/>
-    <hyperlink ref="B34" r:id="rId25" display="https://www.piezodrive.com/piezoelectric-tube-scanners/"/>
-    <hyperlink ref="B35" r:id="rId26" display="https://www.piezodrive.com/product-category/tube-scanners/"/>
-    <hyperlink ref="B36" r:id="rId27" display="https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/"/>
-    <hyperlink ref="B37" r:id="rId28" display="https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/"/>
-    <hyperlink ref="B38" r:id="rId29" display="https://www.piezodrive.com/product/td250-six-channel-250v/"/>
-    <hyperlink ref="B39" r:id="rId30" display="https://www.piezodrive.com/product/horizontal-tube-wiring/"/>
-    <hyperlink ref="B40" r:id="rId31" display="https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md"/>
-    <hyperlink ref="B41" r:id="rId32" display="https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/"/>
-    <hyperlink ref="B42" r:id="rId33" display="https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae"/>
-    <hyperlink ref="B43" r:id="rId34" display="https://mpl.ucsd.edu/machine-shop-info/"/>
-    <hyperlink ref="B44" r:id="rId35" display="https://jacobsschool.ucsd.edu/envision"/>
-    <hyperlink ref="B45" r:id="rId36" display="https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916"/>
-    <hyperlink ref="B46" r:id="rId37" display="https://store.bruker.com/products/dpt10"/>
-    <hyperlink ref="B47" r:id="rId38" display="https://www.2spi.com/item/z01707/"/>
-    <hyperlink ref="B48" r:id="rId39" display="https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523"/>
-    <hyperlink ref="B49" r:id="rId40" display="https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651"/>
-    <hyperlink ref="B50" r:id="rId41" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
-    <hyperlink ref="B51" r:id="rId42" display="https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g"/>
-    <hyperlink ref="B52" r:id="rId43" display="https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws"/>
-    <hyperlink ref="B53" r:id="rId44" display="https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3"/>
-    <hyperlink ref="B56" r:id="rId45" display="DigiKey, Mouser, McMaster, Thorlabs and Amazon product pages could not be loaded from this environment; JLCPCB cannot quote without file upload."/>
+    <hyperlink ref="B18" r:id="rId10" display="https://jlcpcb.com/"/>
+    <hyperlink ref="B19" r:id="rId11" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="B20" r:id="rId12" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="B21" r:id="rId13" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="B22" r:id="rId14" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="B24" r:id="rId15" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
+    <hyperlink ref="B25" r:id="rId16" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
+    <hyperlink ref="B26" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="B27" r:id="rId18" display="https://www.sparkfun.com/teensy-4-1.html"/>
+    <hyperlink ref="B28" r:id="rId19" display="https://adafruit.com/product/4821"/>
+    <hyperlink ref="B29" r:id="rId20" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
+    <hyperlink ref="B30" r:id="rId21" display="https://www.walmart.com/ip/533082272"/>
+    <hyperlink ref="B31" r:id="rId22" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
+    <hyperlink ref="B32" r:id="rId23" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
+    <hyperlink ref="B33" r:id="rId24" display="https://jlc3dp.com/help/article/us-tariff-policy-faq"/>
+    <hyperlink ref="B34" r:id="rId25" display="https://www.piezodrive.com/?p=991"/>
+    <hyperlink ref="B35" r:id="rId26" display="https://www.piezodrive.com/piezoelectric-tube-scanners/"/>
+    <hyperlink ref="B36" r:id="rId27" display="https://www.piezodrive.com/product-category/tube-scanners/"/>
+    <hyperlink ref="B37" r:id="rId28" display="https://www.piezodrive.com/product/pdu150-three-channel-ultra-low-noise-150v-piezo-driver/"/>
+    <hyperlink ref="B38" r:id="rId29" display="https://www.piezodrive.com/product/ps1-24v-power-supply-for-modules/"/>
+    <hyperlink ref="B39" r:id="rId30" display="https://www.piezodrive.com/product/td250-six-channel-250v/"/>
+    <hyperlink ref="B40" r:id="rId31" display="https://www.piezodrive.com/product/horizontal-tube-wiring/"/>
+    <hyperlink ref="B41" r:id="rId32" display="https://trykintsugi.com/sales-tax-guides/usa/california/san-diego-county.md"/>
+    <hyperlink ref="B42" r:id="rId33" display="https://www.eevblog.com/forum/manufacture/lcscglobal-direct-shipping-to-usa-tariff-question/"/>
+    <hyperlink ref="B43" r:id="rId34" display="https://mae156b.eng.ucsd.edu/mae156-resources/mae-undergrad-lab-resources/lab-shops/ucsd-lab-shop-resources-outside-of-mae"/>
+    <hyperlink ref="B44" r:id="rId35" display="https://mpl.ucsd.edu/machine-shop-info/"/>
+    <hyperlink ref="B45" r:id="rId36" display="https://jacobsschool.ucsd.edu/envision"/>
+    <hyperlink ref="B46" r:id="rId37" display="https://www.goodfellow.com/usa/macor-glass-ceramic-rod-1000004916"/>
+    <hyperlink ref="B47" r:id="rId38" display="https://store.bruker.com/products/dpt10"/>
+    <hyperlink ref="B48" r:id="rId39" display="https://www.2spi.com/item/z01707/"/>
+    <hyperlink ref="B49" r:id="rId40" display="https://www.sigmaaldrich.com/US/en/product/aldrich/gf84004523"/>
+    <hyperlink ref="B50" r:id="rId41" display="https://www.penntoolco.com/grizzly-12-x-18-x-3-granite-surface-plate-no-ledge-g9651"/>
+    <hyperlink ref="B51" r:id="rId42" display="https://www.batterymart.com/p-energizer-la522-9volt-lithium-battery.html"/>
+    <hyperlink ref="B52" r:id="rId43" display="https://vetco.net/products/8331d-14g_silver_conductive_epoxy_adhesive_-_mg_chemicals_8331d-14g"/>
+    <hyperlink ref="B53" r:id="rId44" display="https://kozakmicro.com/collections/1-4-80-tpi-oem-alternative-screws"/>
+    <hyperlink ref="B54" r:id="rId45" display="https://www.tinymachines3d.com/products/bigtreetech-tmc2209-v1-3"/>
+    <hyperlink ref="B57" r:id="rId46" display="DigiKey, Mouser, McMaster, Thorlabs and Amazon product pages could not be loaded from this environment; JLCPCB cannot quote without file upload."/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3183,7 +3210,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3446,180 +3473,180 @@
         <v>3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>8.78</v>
+        <v>8.8</v>
       </c>
       <c r="K10" s="3" t="n">
         <f aca="false">I10*J10</f>
-        <v>26.34</v>
+        <v>26.4</v>
       </c>
       <c r="L10" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="M10" s="7" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <f aca="false">I11*J11</f>
+        <v>25.8</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="16" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>89</v>
-      </c>
-      <c r="G12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>209.64</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <f aca="false">I12*J12</f>
-        <v>419.28</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>92</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>93</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>89</v>
       </c>
       <c r="G13" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I13" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>30.17</v>
+        <v>209.64</v>
       </c>
       <c r="K13" s="3" t="n">
         <f aca="false">I13*J13</f>
-        <v>60.34</v>
+        <v>419.28</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1.68</v>
+        <v>30.17</v>
       </c>
       <c r="K14" s="3" t="n">
         <f aca="false">I14*J14</f>
-        <v>5.04</v>
+        <v>60.34</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>3</v>
@@ -3631,141 +3658,141 @@
         <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.8</v>
+        <v>1.68</v>
       </c>
       <c r="K15" s="3" t="n">
         <f aca="false">I15*J15</f>
-        <v>2.4</v>
+        <v>5.04</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>104</v>
-      </c>
       <c r="E16" s="15" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <f aca="false">I16*J16</f>
+        <v>2.4</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <f aca="false">I17*J17</f>
         <v>10</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="L17" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-    </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <f aca="false">I18*J18</f>
-        <v>36.52</v>
-      </c>
-      <c r="L18" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M18" s="7" t="s">
-        <v>113</v>
-      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="15" t="s">
         <v>116</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>111</v>
       </c>
       <c r="F19" s="16" t="s">
         <v>117</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="15" t="s">
         <v>64</v>
@@ -3774,37 +3801,37 @@
         <v>2</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.73</v>
+        <v>18.26</v>
       </c>
       <c r="K19" s="3" t="n">
         <f aca="false">I19*J19</f>
-        <v>11.46</v>
+        <v>36.52</v>
       </c>
       <c r="L19" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="M19" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" s="16" t="s">
         <v>122</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>123</v>
       </c>
       <c r="G20" s="0" t="n">
         <v>1</v>
@@ -3816,14 +3843,14 @@
         <v>2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.09</v>
+        <v>5.73</v>
       </c>
       <c r="K20" s="3" t="n">
         <f aca="false">I20*J20</f>
-        <v>4.18</v>
+        <v>11.46</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>124</v>
@@ -3843,312 +3870,312 @@
         <v>127</v>
       </c>
       <c r="E21" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F21" s="16" t="s">
-        <v>129</v>
-      </c>
       <c r="G21" s="0" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>64</v>
       </c>
       <c r="I21" s="0" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>6.7247</v>
+        <v>2.09</v>
       </c>
       <c r="K21" s="3" t="n">
         <f aca="false">I21*J21</f>
-        <v>40.3482</v>
+        <v>4.18</v>
       </c>
       <c r="L21" s="15" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E22" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="16" t="s">
         <v>134</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>40</v>
+        <v>6.7247</v>
       </c>
       <c r="K22" s="3" t="n">
         <f aca="false">I22*J22</f>
+        <v>40.3482</v>
+      </c>
+      <c r="L22" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="L22" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="K23" s="3" t="n">
+        <f aca="false">I23*J23</f>
+        <v>40</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-    </row>
-    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="G24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>67.85</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <f aca="false">I24*J24</f>
-        <v>67.85</v>
-      </c>
-      <c r="L24" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M24" s="7" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+    </row>
+    <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>142</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>143</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>147</v>
-      </c>
       <c r="G25" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="I25" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>20.85</v>
+        <v>67.85</v>
       </c>
       <c r="K25" s="3" t="n">
         <f aca="false">I25*J25</f>
-        <v>20.85</v>
+        <v>67.85</v>
       </c>
       <c r="L25" s="15" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="F26" s="16" t="s">
         <v>152</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="16" t="s">
-        <v>153</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>64</v>
+        <v>153</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2.99</v>
+        <v>20.85</v>
       </c>
       <c r="K26" s="3" t="n">
         <f aca="false">I26*J26</f>
-        <v>5.98</v>
+        <v>20.85</v>
       </c>
       <c r="L26" s="15" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <f aca="false">I27*J27</f>
+        <v>5.98</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="G28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="I28" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <f aca="false">I28*J28</f>
-        <v>31.5</v>
-      </c>
-      <c r="L28" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M28" s="7" t="s">
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>161</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>164</v>
       </c>
       <c r="G29" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>64</v>
       </c>
       <c r="I29" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>11.5</v>
+        <v>31.5</v>
       </c>
       <c r="K29" s="3" t="n">
         <f aca="false">I29*J29</f>
-        <v>23</v>
+        <v>31.5</v>
       </c>
       <c r="L29" s="15" t="s">
         <v>65</v>
@@ -4157,203 +4184,245 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+    <row r="30" customFormat="false" ht="122.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <f aca="false">I30*J30</f>
+        <v>23</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-    </row>
-    <row r="31" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="G31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+    </row>
+    <row r="32" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
         <v>171</v>
-      </c>
-      <c r="I31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <f aca="false">I31*J31</f>
-        <v>19.99</v>
-      </c>
-      <c r="L31" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>173</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="F32" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="G32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>176</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="G32" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="15" t="s">
-        <v>178</v>
       </c>
       <c r="I32" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="K32" s="3" t="n">
         <f aca="false">I32*J32</f>
-        <v>9.99</v>
+        <v>19.99</v>
       </c>
       <c r="L32" s="15" t="s">
         <v>65</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E33" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="F33" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="G33" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>183</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="G33" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>185</v>
       </c>
       <c r="I33" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>30</v>
+        <v>9.99</v>
       </c>
       <c r="K33" s="3" t="n">
         <f aca="false">I33*J33</f>
-        <v>30</v>
+        <v>9.99</v>
       </c>
       <c r="L33" s="15" t="s">
         <v>65</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="F34" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="G34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="G34" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="15" t="s">
-        <v>192</v>
       </c>
       <c r="I34" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K34" s="3" t="n">
         <f aca="false">I34*J34</f>
+        <v>30</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="I35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="L34" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="K35" s="3" t="n">
+        <f aca="false">I35*J35</f>
+        <v>35</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <f aca="false">SUM(K5:K34)</f>
-        <v>1054.0182</v>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <f aca="false">SUM(K5:K35)</f>
+        <v>1079.8782</v>
       </c>
     </row>
   </sheetData>
@@ -4362,24 +4431,25 @@
     <hyperlink ref="F8" r:id="rId2" display="https://www.adafruit.com/product/324"/>
     <hyperlink ref="F9" r:id="rId3" display="https://adafruit.com/product/6121"/>
     <hyperlink ref="F10" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS200"/>
-    <hyperlink ref="F12" r:id="rId5" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F11" r:id="rId5" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1"/>
     <hyperlink ref="F13" r:id="rId6" display="https://jlcpcb.com/"/>
     <hyperlink ref="F14" r:id="rId7" display="https://jlcpcb.com/"/>
     <hyperlink ref="F15" r:id="rId8" display="https://jlcpcb.com/"/>
     <hyperlink ref="F16" r:id="rId9" display="https://jlcpcb.com/"/>
-    <hyperlink ref="F18" r:id="rId10" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
-    <hyperlink ref="F19" r:id="rId11" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
-    <hyperlink ref="F20" r:id="rId12" display="https://octopart.com/part/keystone/11301"/>
-    <hyperlink ref="F21" r:id="rId13" display="https://www.lcsc.com/product-detail/C50636.html"/>
-    <hyperlink ref="F24" r:id="rId14" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
-    <hyperlink ref="F25" r:id="rId15" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
-    <hyperlink ref="F26" r:id="rId16" display="https://octopart.com/part/keystone/1294"/>
-    <hyperlink ref="F28" r:id="rId17" display="https://www.sparkfun.com/teensy-4-1.html"/>
-    <hyperlink ref="F29" r:id="rId18" display="https://adafruit.com/product/4821"/>
-    <hyperlink ref="F31" r:id="rId19" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
-    <hyperlink ref="F32" r:id="rId20" display="https://www.walmart.com/ip/533082272"/>
-    <hyperlink ref="F33" r:id="rId21" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
-    <hyperlink ref="F34" r:id="rId22" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
+    <hyperlink ref="F17" r:id="rId10" display="https://jlcpcb.com/"/>
+    <hyperlink ref="F19" r:id="rId11" display="https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892"/>
+    <hyperlink ref="F20" r:id="rId12" display="https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190"/>
+    <hyperlink ref="F21" r:id="rId13" display="https://octopart.com/part/keystone/11301"/>
+    <hyperlink ref="F22" r:id="rId14" display="https://www.lcsc.com/product-detail/C50636.html"/>
+    <hyperlink ref="F25" r:id="rId15" display="https://www.jameco.com/z/182M18-Hammond-Manufacturing-Toroidal-Transformer-120VA-50Hz-Dual-Secondary-36VCT-3-33A-Series-18V-6-66A-Parallel_2575671.html"/>
+    <hyperlink ref="F26" r:id="rId16" display="https://batteryjunction.com/batteries/shop-by-size/9v/energizer-522bp-4"/>
+    <hyperlink ref="F27" r:id="rId17" display="https://octopart.com/part/keystone/1294"/>
+    <hyperlink ref="F29" r:id="rId18" display="https://www.sparkfun.com/teensy-4-1.html"/>
+    <hyperlink ref="F30" r:id="rId19" display="https://adafruit.com/product/4821"/>
+    <hyperlink ref="F32" r:id="rId20" display="https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg"/>
+    <hyperlink ref="F33" r:id="rId21" display="https://www.walmart.com/ip/533082272"/>
+    <hyperlink ref="F34" r:id="rId22" display="https://www.tedpella.com/AFM_html/AFM.aspx"/>
+    <hyperlink ref="F35" r:id="rId23" display="https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4412,12 +4482,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,31 +4500,31 @@
         <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4462,17 +4532,17 @@
         <v>62</v>
       </c>
       <c r="B5" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A5,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A5,'Detailed BOM'!$K$5:$K$35)</f>
         <v>131</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>60</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>0.1</v>
@@ -4482,7 +4552,7 @@
         <v>13.1</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="I5" s="3" t="n">
         <f aca="false">B5*Assumptions!$B$5</f>
@@ -4498,14 +4568,14 @@
         <v>70</v>
       </c>
       <c r="B6" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A6,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A6,'Detailed BOM'!$K$5:$K$35)</f>
         <v>45.95</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>0</v>
@@ -4528,17 +4598,17 @@
         <v>81</v>
       </c>
       <c r="B7" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A7,'Detailed BOM'!$K$5:$K$34)</f>
-        <v>26.34</v>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A7,'Detailed BOM'!$K$5:$K$35)</f>
+        <v>52.2</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>15.26</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>0</v>
@@ -4548,33 +4618,33 @@
         <v>0</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">B7*Assumptions!$B$5</f>
-        <v>2.04135</v>
+        <v>4.0455</v>
       </c>
       <c r="J7" s="3" t="n">
         <f aca="false">B7+C7+G7+I7</f>
-        <v>43.64135</v>
+        <v>71.5055</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B8" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A8,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A8,'Detailed BOM'!$K$5:$K$35)</f>
         <v>497.06</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>0.35</v>
@@ -4584,7 +4654,7 @@
         <v>173.971</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I8" s="3" t="n">
         <f aca="false">B8*Assumptions!$B$5</f>
@@ -4597,20 +4667,20 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B9" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A9,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A9,'Detailed BOM'!$K$5:$K$35)</f>
         <v>58.14</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>8.49</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>0.08</v>
@@ -4620,7 +4690,7 @@
         <v>4.6512</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I9" s="3" t="n">
         <f aca="false">B9*Assumptions!$B$5</f>
@@ -4633,20 +4703,20 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B10" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A10,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A10,'Detailed BOM'!$K$5:$K$35)</f>
         <v>80.3482</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>22.21</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>0.35</v>
@@ -4656,7 +4726,7 @@
         <v>28.12187</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I10" s="3" t="n">
         <f aca="false">B10*Assumptions!$B$5</f>
@@ -4669,17 +4739,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A11,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A11,'Detailed BOM'!$K$5:$K$35)</f>
         <v>67.85</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>0</v>
@@ -4699,17 +4769,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B12" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A12,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A12,'Detailed BOM'!$K$5:$K$35)</f>
         <v>20.85</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F12" s="17" t="n">
         <v>0</v>
@@ -4729,17 +4799,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B13" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A13,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A13,'Detailed BOM'!$K$5:$K$35)</f>
         <v>31.5</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>0</v>
@@ -4759,20 +4829,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B14" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A14,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A14,'Detailed BOM'!$K$5:$K$35)</f>
         <v>19.99</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F14" s="17" t="n">
         <v>0</v>
@@ -4792,17 +4862,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B15" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A15,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A15,'Detailed BOM'!$K$5:$K$35)</f>
         <v>9.99</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>0</v>
@@ -4822,17 +4892,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B16" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A16,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A16,'Detailed BOM'!$K$5:$K$35)</f>
         <v>30</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F16" s="17" t="n">
         <v>0</v>
@@ -4852,17 +4922,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B17" s="3" t="n">
-        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$34,A17,'Detailed BOM'!$K$5:$K$34)</f>
+        <f aca="false">SUMIF('Detailed BOM'!$E$5:$E$35,A17,'Detailed BOM'!$K$5:$K$35)</f>
         <v>35</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>0</v>
@@ -4882,7 +4952,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0</v>
@@ -4891,13 +4961,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I18" s="0" t="n">
         <v>0</v>
@@ -4914,11 +4984,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B20" s="9" t="n">
         <f aca="false">SUM(B5:B17)</f>
-        <v>1054.0182</v>
+        <v>1079.8782</v>
       </c>
       <c r="C20" s="9" t="n">
         <f aca="false">SUM(C5:C17)</f>
@@ -4934,11 +5004,11 @@
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="n">
         <f aca="false">SUM(I5:I17)</f>
-        <v>81.6864105</v>
+        <v>83.6905605</v>
       </c>
       <c r="J20" s="9" t="n">
         <f aca="false">SUM(J5:J18)</f>
-        <v>1624.8086805</v>
+        <v>1652.6728305</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4948,14 +5018,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B22" s="3" t="n">
-        <f aca="false">B20-'Detailed BOM'!K36</f>
+        <f aca="false">B20-'Detailed BOM'!K37</f>
         <v>0</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -4986,12 +5056,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5001,198 +5071,198 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>277.2</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>77</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>75.15</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>133.13</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -5235,12 +5305,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5250,37 +5320,37 @@
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>
@@ -5288,22 +5358,22 @@
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F5" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-01",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-02",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-03",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-04",'Detailed BOM'!$A$5:$A$35,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G5" s="3" t="n">
@@ -5318,30 +5388,30 @@
         <v>0</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>283</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>278</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>892</v>
@@ -5358,30 +5428,30 @@
         <v>733.8018</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>3172</v>
@@ -5398,33 +5468,33 @@
         <v>3013.8018</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>111</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F8" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-01",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-02",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-03",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-04",'Detailed BOM'!$A$5:$A$35,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -5439,33 +5509,33 @@
         <v>-20</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>156</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F9" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-01",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-02",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-03",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-04",'Detailed BOM'!$A$5:$A$35,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G9" s="3" t="n">
@@ -5480,33 +5550,33 @@
         <v>25</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>131</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F10" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("HV-04",'Detailed BOM'!$A$5:$A$34,0))</f>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-01",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-02",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-03",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("HV-04",'Detailed BOM'!$A$5:$A$35,0))</f>
         <v>158.1982</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -5521,13 +5591,13 @@
         <v>100</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -5561,12 +5631,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5576,21 +5646,21 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B4" s="3" t="n">
-        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$34,0))+INDEX('Detailed BOM'!$K$5:$K$34,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$34,0))</f>
-        <v>49.29</v>
+        <f aca="false">INDEX('Detailed BOM'!$K$5:$K$35,MATCH("PZ-02",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("PZ-03",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("PZ-04",'Detailed BOM'!$A$5:$A$35,0))+INDEX('Detailed BOM'!$K$5:$K$35,MATCH("PZ-05",'Detailed BOM'!$A$5:$A$35,0))</f>
+        <v>75.15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5600,30 +5670,30 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>5</v>
@@ -5631,13 +5701,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>1</v>
@@ -5653,18 +5723,18 @@
         <v>65</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -5682,13 +5752,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>1</v>
@@ -5706,20 +5776,20 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F13" s="3" t="n">
-        <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$34,MATCH("HV-01",'Detailed BOM'!$A$5:$A$34,0))</f>
+        <f aca="false">SUM(F10:F12)+INDEX('Detailed BOM'!$J$5:$J$35,MATCH("HV-01",'Detailed BOM'!$A$5:$A$35,0))</f>
         <v>164.2947</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F14" s="3" t="n">
         <f aca="false">F13-B4</f>
-        <v>115.0047</v>
+        <v>89.1447</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5729,7 +5799,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -5771,12 +5841,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5786,63 +5856,63 @@
     </row>
     <row r="4" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>3</v>
@@ -5878,24 +5948,24 @@
         <v>2.44913335386511</v>
       </c>
       <c r="N5" s="15" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>3</v>
@@ -5931,24 +6001,24 @@
         <v>1.166253978031</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="O6" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>2</v>
@@ -5984,24 +6054,24 @@
         <v>305.609565855662</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>2</v>
@@ -6037,10 +6107,10 @@
         <v>43.9823531464942</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="O8" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6048,10 +6118,10 @@
         <v>81</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>80</v>
@@ -6090,24 +6160,24 @@
         <v>14.4166666666667</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E10" s="0" t="n">
         <v>2</v>
@@ -6142,24 +6212,24 @@
         <v>22.6647285954113</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E11" s="0" t="n">
         <v>4</v>
@@ -6194,24 +6264,24 @@
         <v>1.20513570229435</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="O11" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E12" s="0" t="n">
         <v>2</v>
@@ -6246,24 +6316,24 @@
         <v>7.47</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E13" s="0" t="n">
         <v>2</v>
@@ -6298,15 +6368,15 @@
         <v>6.865</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="O13" s="15" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="G14" s="3" t="n">
         <f aca="false">SUM(G5:G13)</f>
@@ -6319,14 +6389,14 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="L15" s="3" t="n">
         <f aca="false">L14-832.1</f>
         <v>0</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6336,12 +6406,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>543.83</v>
@@ -6349,7 +6419,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="G19" s="3" t="n">
         <f aca="false">L14+G18</f>
@@ -6384,7 +6454,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6394,291 +6464,291 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>424</v>
-      </c>
       <c r="D17" s="7" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6709,12 +6779,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6724,80 +6794,80 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B5" s="20" t="n">
         <v>0.0775</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>0.1</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>65</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>105</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>2000</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6807,27 +6877,27 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6837,187 +6907,187 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="294">
   <si>
     <t xml:space="preserve">STM v1: what it actually cost</t>
   </si>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">STM v2 at UCSD: budget</t>
   </si>
   <si>
-    <t xml:space="preserve">What this is: a scanning tunneling microscope (STM) images individual atoms by holding a sharp metal tip a few atoms above a sample and measuring the tiny electric current that flows across the gap. This sheet lists everything needed to build a second one (v2) at UCSD. Prices checked 21 October 2026, in US dollars. Sections 1 to 8 are parts we must buy. The microscope runs entirely on batteries (section 8), with no wall power. Section 9 lists items UCSD labs may already have; with nothing marked, the total assumes we buy all of them, which is why it starts above $2,000.</t>
+    <t xml:space="preserve">What this is: a scanning tunneling microscope (STM) images individual atoms by holding a sharp metal tip a few atoms above a sample and measuring the tiny electric current that flows across the gap. This sheet lists everything needed to build a second one (v2) at UCSD. Prices checked 21 October 2026, in US dollars. Sections 1 to 9 are parts we must buy. The microscope runs entirely on batteries (section 9), with no wall power. Section 10 lists items UCSD labs may already have; with nothing marked, the total assumes we buy all of them, which is why it starts above $2,000.</t>
   </si>
   <si>
     <t xml:space="preserve">Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Total request for v2 (updates as section 9 items are marked Yes)</t>
+    <t xml:space="preserve">Total request for v2 (updates as section 10 items are marked Yes)</t>
   </si>
   <si>
     <t xml:space="preserve">Room left under the $2,000 target</t>
   </si>
   <si>
-    <t xml:space="preserve">Total if UCSD supplies everything in section 9</t>
+    <t xml:space="preserve">Total if UCSD supplies everything in section 10</t>
   </si>
   <si>
     <t xml:space="preserve">What v1 actually cost, for comparison</t>
@@ -233,13 +233,136 @@
     <t xml:space="preserve">TB3006-N</t>
   </si>
   <si>
-    <t xml:space="preserve">2. High-voltage driver (powers the piezo tube)</t>
+    <t xml:space="preserve">2. Scanner mount and wiring (holds the tube and connects it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceramic mounting block</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A small block of machinable ceramic that the tube is glued to. It holds the tube rigidly and insulates it electrically. Estimate; it needs a few holes drilled. If drilling is not possible, an aluminium block with an insulating epoxy layer is the fallback.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Needed to mount the tube.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macor rod or plate offcut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural epoxy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong glue that bonds the tube to its mounting block. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1's parts were held with superglue, which gives off fumes that contaminate the electronics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loctite EA E-30CL or similar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conductive silver epoxy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glue that conducts electricity. It attaches the wires to the tube's contacts without soldering heat, which can damage the tube. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Needed to wire the tube.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CW2400 or similar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tip holder tubing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Short pieces of thin stainless steel tube that grip the scanning tip at the end of the piezo tube. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Replaces v1's glued tip holder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless hypodermic tubing, about 23 gauge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thin shielded tip cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very thin (about 1 mm) shielded cable that carries the tiny tip current to the preamp. 1 m. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. The tip now moves with the tube, so its cable must be thin and flexible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">micro-coax, about 1 mm, 1 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-voltage box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal box that holds the high-voltage driver board (section 3), keeping the 45 V away from fingers and blocking electrical noise. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. The driver sits in its own box, between the main board and the microscope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diecast aluminium, about 112 x 60 x 31 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9-pin connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plugs and sockets that connect the high-voltage box to the main board and to the microscope head. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Goes with the high-voltage box.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB9 plug and socket with covers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-voltage cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shielded cable with 5 wires, rated for at least 100 V, from the high-voltage box to the microscope head. 1 m. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Carries the 45 V signals to the tube.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-core shielded cable, 1 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test capacitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small capacitors that stand in for the tube when the high-voltage box is first tested, so a wiring mistake cannot crack the tube. 4 plus 4 spares. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Protects the tube during testing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2 nF 100 V film</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threaded inserts and screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small metal inserts melted into the printed plate, with screws, to fix the mounting block to the head. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M3 heat-set inserts and screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. High-voltage driver (powers the piezo tube)</t>
   </si>
   <si>
     <t xml:space="preserve">Amplifier chips</t>
   </si>
   <si>
-    <t xml:space="preserve">The tube has 5 electrical contacts. Each needs its own amplifier chip to raise the control signal to about 45 V. 5 chips plus 1 spare. Powered by batteries (section 8).</t>
+    <t xml:space="preserve">The tube has 4 outer electrical contacts that move it; the inner one is simply connected to ground. Each outer contact needs its own amplifier chip to raise the control signal to about 45 V. 4 chips plus 1 spare. Powered by batteries (section 9).</t>
   </si>
   <si>
     <t xml:space="preserve">New. The tube needs far more voltage than v1's electronics can supply.</t>
@@ -275,13 +398,13 @@
     <t xml:space="preserve">custom</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Coarse approach (brings the sample close to the tip)</t>
+    <t xml:space="preserve">4. Coarse approach (brings the sample close to the tip)</t>
   </si>
   <si>
     <t xml:space="preserve">Motor</t>
   </si>
   <si>
-    <t xml:space="preserve">A motor that turns in small, precise steps. It slowly turns one adjustment screw to bring the sample up to the tip, then the piezo tube takes over. Joined to the screw by a 3D-printed coupler and powered by AA batteries (section 8).</t>
+    <t xml:space="preserve">A motor that turns in small, precise steps. It slowly turns one adjustment screw to bring the sample up to the tip, then the piezo tube takes over. Joined to the screw by a 3D-printed coupler and powered by AA batteries (section 9).</t>
   </si>
   <si>
     <t xml:space="preserve">New. Replaces v1's small toy-grade motor. Finer steps lower the risk of crashing the tip into the sample.</t>
@@ -296,7 +419,7 @@
     <t xml:space="preserve">Motor controller</t>
   </si>
   <si>
-    <t xml:space="preserve">A small board that lets the microcontroller (section 4) move the motor in tiny fractions of a step.</t>
+    <t xml:space="preserve">A small board that lets the microcontroller (section 5) move the motor in tiny fractions of a step.</t>
   </si>
   <si>
     <t xml:space="preserve">New. Needed to run the new motor.</t>
@@ -332,7 +455,7 @@
     <t xml:space="preserve">F25SSN1</t>
   </si>
   <si>
-    <t xml:space="preserve">4. Control electronics (runs the microscope)</t>
+    <t xml:space="preserve">5. Control electronics (runs the microscope)</t>
   </si>
   <si>
     <t xml:space="preserve">Main circuit boards</t>
@@ -380,7 +503,7 @@
     <t xml:space="preserve">Teensy 4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Preamp (amplifies the tiny tip current)</t>
+    <t xml:space="preserve">6. Preamp (amplifies the tiny tip current)</t>
   </si>
   <si>
     <t xml:space="preserve">Preamp circuit boards</t>
@@ -428,13 +551,10 @@
     <t xml:space="preserve">Same kind as v1. Listed here because general labs rarely stock it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kirecoo copper foil tape, 2 in x 33 ft</t>
   </si>
   <si>
-    <t xml:space="preserve">6. Sample plate and frame</t>
+    <t xml:space="preserve">7. Sample plate and frame</t>
   </si>
   <si>
     <t xml:space="preserve">1 kg spool of carbon-fiber reinforced plastic for printing the head, sample plate and frame.</t>
@@ -500,7 +620,7 @@
     <t xml:space="preserve">Sorbothane 6x6 in, 2-pack</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Sensors</t>
+    <t xml:space="preserve">8. Sensors</t>
   </si>
   <si>
     <t xml:space="preserve">Temperature sensors</t>
@@ -515,7 +635,7 @@
     <t xml:space="preserve">4821 (TMP117)</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Power (batteries, no wall power)</t>
+    <t xml:space="preserve">9. Power (batteries, no wall power)</t>
   </si>
   <si>
     <t xml:space="preserve">9 V batteries</t>
@@ -572,13 +692,13 @@
     <t xml:space="preserve">All parts above</t>
   </si>
   <si>
-    <t xml:space="preserve">For sections 1 to 8 (section 9 prices do not include shipping). Estimates by seller: PiezoDrive $60.00, JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Isolate It $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon items ship free. Standard (not express) shipping everywhere, and the small electronic parts ship in the same box as the circuit boards.</t>
+    <t xml:space="preserve">For sections 1 to 9 (section 10 prices do not include shipping). Estimates by seller: PiezoDrive $60.00, JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Isolate It $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon items ship free. Standard (not express) shipping everywhere, and the small electronic parts ship in the same box as the circuit boards.</t>
   </si>
   <si>
     <t xml:space="preserve">Import tariff on circuit boards</t>
   </si>
   <si>
-    <t xml:space="preserve">The US charges a 35% import tariff on circuit boards and parts from China. Applied to the $577.41 of boards and parts from JLCPCB and LCSC. Cannot be avoided by changing shipping; only US-made boards would avoid it, and those cost more.</t>
+    <t xml:space="preserve">The US charges a 35% import tariff on circuit boards and parts from China. Applied to the $570.68 of boards and parts from JLCPCB and LCSC. Cannot be avoided by changing shipping; only US-made boards would avoid it, and those cost more.</t>
   </si>
   <si>
     <t xml:space="preserve">Other import fees</t>
@@ -593,7 +713,7 @@
     <t xml:space="preserve">UCSD purchasing may have its own shipping accounts or negotiated rates with these sellers, which could lower this. Not counted here.</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Things UCSD may already have: choose Yes in the last column if UCSD will provide it, and it comes off the total</t>
+    <t xml:space="preserve">10. Things UCSD may already have: choose Yes in the last column if UCSD will provide it, and it comes off the total</t>
   </si>
   <si>
     <t xml:space="preserve">Free from UCSD?</t>
@@ -668,6 +788,30 @@
     <t xml:space="preserve">FNIRSI DST-201</t>
   </si>
   <si>
+    <t xml:space="preserve">LCR meter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A handheld meter that measures capacitance. Used to check each of the tube's contacts before and after wiring. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Confirms the tube was not damaged during assembly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">handheld LCR meter, 1 kHz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interferometer parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A small laser, a beam splitter, two mirrors and a light sensor. Together they measure exactly how far the scanner moves per volt, which calibrates the images. Estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Calibrates the scanner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laser diode, beamsplitter cube, 2 mirrors, photodiode, mounts</t>
+  </si>
+  <si>
     <t xml:space="preserve">Soldering iron</t>
   </si>
   <si>
@@ -734,7 +878,7 @@
     <t xml:space="preserve">Parts</t>
   </si>
   <si>
-    <t xml:space="preserve">Sections 1 to 8, plus section 9 items not marked Yes</t>
+    <t xml:space="preserve">Sections 1 to 9, plus section 10 items not marked Yes</t>
   </si>
   <si>
     <t xml:space="preserve">Shipping and import fees</t>
@@ -758,10 +902,10 @@
     <t xml:space="preserve">For comparison</t>
   </si>
   <si>
-    <t xml:space="preserve">If UCSD provides everything in section 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If UCSD provides nothing in section 9</t>
+    <t xml:space="preserve">If UCSD provides everything in section 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If UCSD provides nothing in section 10</t>
   </si>
 </sst>
 </file>
@@ -1853,7 +1997,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -1898,8 +2042,8 @@
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="17" t="n">
-        <f aca="false">H91</f>
-        <v>2732.4</v>
+        <f aca="false">H106</f>
+        <v>2994.445</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1908,8 +2052,8 @@
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19" t="n">
-        <f aca="false">H92</f>
-        <v>-732.4</v>
+        <f aca="false">H107</f>
+        <v>-994.445</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1918,8 +2062,8 @@
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19" t="n">
-        <f aca="false">H95</f>
-        <v>1793.37</v>
+        <f aca="false">H110</f>
+        <v>1936.9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2034,7 +2178,7 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
         <v>70</v>
       </c>
@@ -2051,17 +2195,17 @@
         <v>74</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G16" s="23" t="n">
-        <v>6.725</v>
+        <v>35</v>
       </c>
       <c r="H16" s="23" t="n">
         <f aca="false">F16*G16</f>
-        <v>40.35</v>
+        <v>35</v>
       </c>
       <c r="I16" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
         <v>Open</v>
       </c>
     </row>
@@ -2085,14 +2229,14 @@
         <v>1</v>
       </c>
       <c r="G17" s="23" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H17" s="23" t="n">
         <f aca="false">F17*G17</f>
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I17" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
         <v>Open</v>
       </c>
     </row>
@@ -2104,179 +2248,243 @@
         <v>80</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E18" s="22" t="s">
         <v>82</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G18" s="23" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H18" s="23" t="n">
         <f aca="false">F18*G18</f>
+        <v>25</v>
+      </c>
+      <c r="I18" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="I18" s="24" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9" t="n">
-        <f aca="false">SUM(H16:H18)</f>
-        <v>90.35</v>
-      </c>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-    </row>
-    <row r="22" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="23" t="n">
+        <f aca="false">F19*G19</f>
+        <v>10</v>
+      </c>
+      <c r="I19" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <f aca="false">F20*G20</f>
+        <v>10</v>
+      </c>
+      <c r="I20" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" s="23" t="n">
+        <f aca="false">F21*G21</f>
+        <v>12</v>
+      </c>
+      <c r="I21" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="23" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H22" s="23" t="n">
         <f aca="false">F22*G22</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I22" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="F23" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="23" t="n">
-        <v>8.95</v>
+        <v>8</v>
       </c>
       <c r="H23" s="23" t="n">
         <f aca="false">F23*G23</f>
-        <v>8.95</v>
+        <v>8</v>
       </c>
       <c r="I23" s="24" t="str">
-        <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G24" s="23" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="H24" s="23" t="n">
         <f aca="false">F24*G24</f>
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I24" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
         <v>Open</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="23" t="n">
-        <v>8.6</v>
+        <v>5</v>
       </c>
       <c r="H25" s="23" t="n">
         <f aca="false">F25*G25</f>
-        <v>25.8</v>
+        <v>5</v>
       </c>
       <c r="I25" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
         <v>Open</v>
       </c>
     </row>
@@ -2291,14 +2499,14 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="9" t="n">
-        <f aca="false">SUM(H22:H25)</f>
-        <v>72.75</v>
+        <f aca="false">SUM(H16:H25)</f>
+        <v>130</v>
       </c>
       <c r="I26" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2309,730 +2517,776 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>209.64</v>
+        <v>6.725</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">F29*G29</f>
-        <v>419.28</v>
+        <v>33.625</v>
       </c>
       <c r="I29" s="24" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>1.68</v>
+        <v>40</v>
       </c>
       <c r="H30" s="23" t="n">
         <f aca="false">F30*G30</f>
-        <v>5.04</v>
+        <v>40</v>
       </c>
       <c r="I30" s="24" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="F31" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="23" t="n">
         <v>2</v>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>18.26</v>
       </c>
       <c r="H31" s="23" t="n">
         <f aca="false">F31*G31</f>
-        <v>36.52</v>
+        <v>10</v>
       </c>
       <c r="I31" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F32" s="21" t="n">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9" t="n">
+        <f aca="false">SUM(H29:H31)</f>
+        <v>83.625</v>
+      </c>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="23" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H32" s="23" t="n">
-        <f aca="false">F32*G32</f>
-        <v>31.5</v>
-      </c>
-      <c r="I32" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9" t="n">
-        <f aca="false">SUM(H29:H32)</f>
-        <v>492.34</v>
-      </c>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-    </row>
-    <row r="36" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G35" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <f aca="false">F35*G35</f>
+        <v>14</v>
+      </c>
+      <c r="I35" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="F36" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>30.17</v>
+        <v>8.95</v>
       </c>
       <c r="H36" s="23" t="n">
         <f aca="false">F36*G36</f>
-        <v>60.34</v>
+        <v>8.95</v>
       </c>
       <c r="I36" s="24" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="F37" s="21" t="n">
         <v>3</v>
       </c>
       <c r="G37" s="23" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="H37" s="23" t="n">
         <f aca="false">F37*G37</f>
-        <v>2.4</v>
+        <v>24</v>
       </c>
       <c r="I37" s="24" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F38" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>5.73</v>
+        <v>8.6</v>
       </c>
       <c r="H38" s="23" t="n">
         <f aca="false">F38*G38</f>
-        <v>11.46</v>
+        <v>25.8</v>
       </c>
       <c r="I38" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="F39" s="21" t="n">
+        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="9" t="n">
+        <f aca="false">SUM(H35:H38)</f>
+        <v>72.75</v>
+      </c>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="F42" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H39" s="23" t="n">
-        <f aca="false">F39*G39</f>
-        <v>4.18</v>
-      </c>
-      <c r="I39" s="24" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="F40" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="23" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H40" s="23" t="n">
-        <f aca="false">F40*G40</f>
-        <v>7.99</v>
-      </c>
-      <c r="I40" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="9" t="n">
-        <f aca="false">SUM(H36:H40)</f>
-        <v>86.37</v>
-      </c>
-      <c r="I41" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="G42" s="23" t="n">
+        <v>209.64</v>
+      </c>
+      <c r="H42" s="23" t="n">
+        <f aca="false">F42*G42</f>
+        <v>419.28</v>
+      </c>
+      <c r="I42" s="24" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H43" s="23" t="n">
+        <f aca="false">F43*G43</f>
+        <v>5.04</v>
+      </c>
+      <c r="I43" s="24" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="F44" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44" s="23" t="n">
-        <v>19.99</v>
+        <v>18.26</v>
       </c>
       <c r="H44" s="23" t="n">
         <f aca="false">F44*G44</f>
-        <v>19.99</v>
+        <v>36.52</v>
       </c>
       <c r="I44" s="24" t="str">
-        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F45" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="23" t="n">
-        <v>9.99</v>
+        <v>31.5</v>
       </c>
       <c r="H45" s="23" t="n">
         <f aca="false">F45*G45</f>
-        <v>9.99</v>
+        <v>31.5</v>
       </c>
       <c r="I45" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E46" s="22" t="s">
+        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="9" t="n">
+        <f aca="false">SUM(H42:H45)</f>
+        <v>492.34</v>
+      </c>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F49" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="H49" s="23" t="n">
+        <f aca="false">F49*G49</f>
+        <v>60.34</v>
+      </c>
+      <c r="I49" s="24" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="F46" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>30</v>
-      </c>
-      <c r="H46" s="23" t="n">
-        <f aca="false">F46*G46</f>
-        <v>30</v>
-      </c>
-      <c r="I46" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B47" s="22" t="s">
+      <c r="C50" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="C47" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E47" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="H47" s="23" t="n">
-        <f aca="false">F47*G47</f>
-        <v>9.49</v>
-      </c>
-      <c r="I47" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21" t="s">
+      <c r="D50" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H50" s="23" t="n">
+        <f aca="false">F50*G50</f>
+        <v>2.4</v>
+      </c>
+      <c r="I50" s="24" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B48" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="23" t="n">
-        <v>35</v>
-      </c>
-      <c r="H48" s="23" t="n">
-        <f aca="false">F48*G48</f>
-        <v>35</v>
-      </c>
-      <c r="I48" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="9" t="n">
-        <f aca="false">SUM(H44:H48)</f>
-        <v>104.47</v>
-      </c>
-      <c r="I49" s="8"/>
-    </row>
-    <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="E51" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="F51" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H51" s="23" t="n">
+        <f aca="false">F51*G51</f>
+        <v>11.46</v>
+      </c>
+      <c r="I51" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
+        <v>Open</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="21" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="F52" s="21" t="n">
         <v>2</v>
       </c>
       <c r="G52" s="23" t="n">
-        <v>11.5</v>
+        <v>2.09</v>
       </c>
       <c r="H52" s="23" t="n">
         <f aca="false">F52*G52</f>
-        <v>23</v>
+        <v>4.18</v>
       </c>
       <c r="I52" s="24" t="str">
-        <f aca="false">HYPERLINK("https://adafruit.com/product/4821","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F53" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H53" s="23" t="n">
+        <f aca="false">F53*G53</f>
+        <v>7.99</v>
+      </c>
+      <c r="I53" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="9" t="n">
-        <f aca="false">SUM(H52:H52)</f>
-        <v>23</v>
-      </c>
-      <c r="I53" s="8"/>
-    </row>
-    <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-    </row>
-    <row r="56" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="F56" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="23" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H56" s="23" t="n">
-        <f aca="false">F56*G56</f>
-        <v>64.17</v>
-      </c>
-      <c r="I56" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
-        <v>Open</v>
-      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="9" t="n">
+        <f aca="false">SUM(H49:H53)</f>
+        <v>86.37</v>
+      </c>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="21" t="s">
-        <v>169</v>
+        <v>36</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C57" s="22" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="E57" s="22" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F57" s="21" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G57" s="23" t="n">
-        <v>0.61</v>
+        <v>19.99</v>
       </c>
       <c r="H57" s="23" t="n">
         <f aca="false">F57*G57</f>
-        <v>12.2</v>
+        <v>19.99</v>
       </c>
       <c r="I57" s="24" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
         <v>Open</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="21" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="E58" s="22" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F58" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="23" t="n">
-        <v>10.95</v>
+        <v>9.99</v>
       </c>
       <c r="H58" s="23" t="n">
         <f aca="false">F58*G58</f>
-        <v>10.95</v>
+        <v>9.99</v>
       </c>
       <c r="I58" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="21" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="E59" s="22" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F59" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="23" t="n">
-        <v>2.95</v>
+        <v>30</v>
       </c>
       <c r="H59" s="23" t="n">
         <f aca="false">F59*G59</f>
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="I59" s="24" t="str">
-        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="9" t="n">
-        <f aca="false">SUM(H56:H59)</f>
-        <v>93.22</v>
-      </c>
-      <c r="I60" s="8"/>
+        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="F60" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="H60" s="23" t="n">
+        <f aca="false">F60*G60</f>
+        <v>9.49</v>
+      </c>
+      <c r="I60" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="F61" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="H61" s="23" t="n">
+        <f aca="false">F61*G61</f>
+        <v>35</v>
+      </c>
+      <c r="I61" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads","Open")</f>
+        <v>Open</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>181</v>
+        <v>15</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -3041,47 +3295,58 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
       <c r="H62" s="9" t="n">
-        <f aca="false">H13+H19+H26+H33+H41+H49+H53+H60</f>
-        <v>1093.5</v>
+        <f aca="false">SUM(H57:H61)</f>
+        <v>104.47</v>
       </c>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>166.75</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>183</v>
-      </c>
-      <c r="B64" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>202.09</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>185</v>
+    <row r="64" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+    </row>
+    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="s">
+        <v>199</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>83.25</v>
+        <v>200</v>
+      </c>
+      <c r="C65" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F65" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H65" s="23" t="n">
+        <f aca="false">F65*G65</f>
+        <v>23</v>
+      </c>
+      <c r="I65" s="24" t="str">
+        <f aca="false">HYPERLINK("https://adafruit.com/product/4821","Open")</f>
+        <v>Open</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>187</v>
+        <v>15</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -3090,636 +3355,918 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
       <c r="H66" s="9" t="n">
-        <f aca="false">SUM(H63:H65)</f>
-        <v>452.09</v>
+        <f aca="false">SUM(H65:H65)</f>
+        <v>23</v>
       </c>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="25" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-    </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B70" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C70" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="F70" s="28" t="s">
+    <row r="68" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+    </row>
+    <row r="69" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="F69" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="G70" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="H70" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="I70" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="J70" s="28" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G69" s="23" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="H69" s="23" t="n">
+        <f aca="false">F69*G69</f>
+        <v>64.17</v>
+      </c>
+      <c r="I69" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>212</v>
+      </c>
+      <c r="F70" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" s="23" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H70" s="23" t="n">
+        <f aca="false">F70*G70</f>
+        <v>12.2</v>
+      </c>
+      <c r="I70" s="24" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="21" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="E71" s="22" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="F71" s="21" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="23" t="n">
-        <v>277.2</v>
+        <v>10.95</v>
       </c>
       <c r="H71" s="23" t="n">
-        <f aca="false">IF(OR(J71="Yes",J71=TRUE()),0,F71*G71)</f>
-        <v>277.2</v>
+        <f aca="false">F71*G71</f>
+        <v>10.95</v>
       </c>
       <c r="I71" s="24" t="str">
-        <f aca="false">HYPERLINK("https://store.bruker.com/products/dpt10","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="J71" s="29"/>
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
+        <v>Open</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="21" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="E72" s="22" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F72" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" s="23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H72" s="23" t="n">
+        <f aca="false">F72*G72</f>
+        <v>5.9</v>
+      </c>
+      <c r="I72" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
+        <v>Open</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="9" t="n">
+        <f aca="false">SUM(H69:H72)</f>
+        <v>93.22</v>
+      </c>
+      <c r="I73" s="8"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="9" t="n">
+        <f aca="false">H13+H26+H32+H39+H46+H54+H62+H66+H73</f>
+        <v>1216.775</v>
+      </c>
+      <c r="I75" s="8"/>
+    </row>
+    <row r="76" customFormat="false" ht="108.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>166.75</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="0" t="s">
+        <v>223</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>199.74</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="0" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>83.25</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="9" t="n">
+        <f aca="false">SUM(H76:H78)</f>
+        <v>449.74</v>
+      </c>
+      <c r="I79" s="8"/>
+    </row>
+    <row r="80" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B82" s="27"/>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="27"/>
+    </row>
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H83" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="I83" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="J83" s="28" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F84" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G72" s="23" t="n">
+      <c r="G84" s="23" t="n">
+        <v>277.2</v>
+      </c>
+      <c r="H84" s="23" t="n">
+        <f aca="false">IF(OR(J84="Yes",J84=TRUE()),0,F84*G84)</f>
+        <v>277.2</v>
+      </c>
+      <c r="I84" s="24" t="str">
+        <f aca="false">HYPERLINK("https://store.bruker.com/products/dpt10","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="J84" s="29"/>
+    </row>
+    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="23" t="n">
         <v>77</v>
       </c>
-      <c r="H72" s="23" t="n">
-        <f aca="false">IF(OR(J72="Yes",J72=TRUE()),0,F72*G72)</f>
+      <c r="H85" s="23" t="n">
+        <f aca="false">IF(OR(J85="Yes",J85=TRUE()),0,F85*G85)</f>
         <v>77</v>
       </c>
-      <c r="I72" s="24" t="str">
+      <c r="I85" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J72" s="29"/>
-    </row>
-    <row r="73" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21" t="s">
-        <v>201</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="E73" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="F73" s="21" t="n">
+      <c r="J85" s="29"/>
+    </row>
+    <row r="86" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="E86" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="F86" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="23" t="n">
+      <c r="G86" s="23" t="n">
         <v>133.13</v>
       </c>
-      <c r="H73" s="23" t="n">
-        <f aca="false">IF(OR(J73="Yes",J73=TRUE()),0,F73*G73)</f>
+      <c r="H86" s="23" t="n">
+        <f aca="false">IF(OR(J86="Yes",J86=TRUE()),0,F86*G86)</f>
         <v>133.13</v>
       </c>
-      <c r="I73" s="24" t="str">
+      <c r="I86" s="24" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J73" s="29"/>
-    </row>
-    <row r="74" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21" t="s">
-        <v>206</v>
-      </c>
-      <c r="B74" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="F74" s="21" t="n">
+      <c r="J86" s="29"/>
+    </row>
+    <row r="87" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E87" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="F87" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G74" s="23" t="n">
+      <c r="G87" s="23" t="n">
         <v>75.15</v>
       </c>
-      <c r="H74" s="23" t="n">
-        <f aca="false">IF(OR(J74="Yes",J74=TRUE()),0,F74*G74)</f>
+      <c r="H87" s="23" t="n">
+        <f aca="false">IF(OR(J87="Yes",J87=TRUE()),0,F87*G87)</f>
         <v>75.15</v>
       </c>
-      <c r="I74" s="24" t="str">
+      <c r="I87" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J74" s="29"/>
-    </row>
-    <row r="75" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="21" t="s">
+      <c r="J87" s="29"/>
+    </row>
+    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B75" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E75" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="F75" s="21" t="n">
+      <c r="B88" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E88" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="F88" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="23" t="n">
+      <c r="G88" s="23" t="n">
         <v>57.99</v>
       </c>
-      <c r="H75" s="23" t="n">
-        <f aca="false">IF(OR(J75="Yes",J75=TRUE()),0,F75*G75)</f>
+      <c r="H88" s="23" t="n">
+        <f aca="false">IF(OR(J88="Yes",J88=TRUE()),0,F88*G88)</f>
         <v>57.99</v>
       </c>
-      <c r="I75" s="24" t="str">
+      <c r="I88" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J75" s="29"/>
-    </row>
-    <row r="76" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B76" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="C76" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>216</v>
-      </c>
-      <c r="E76" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="F76" s="21" t="n">
+      <c r="J88" s="29"/>
+    </row>
+    <row r="89" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E89" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="F89" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="23" t="n">
+      <c r="G89" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="H89" s="23" t="n">
+        <f aca="false">IF(OR(J89="Yes",J89=TRUE()),0,F89*G89)</f>
+        <v>40</v>
+      </c>
+      <c r="I89" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="J89" s="29"/>
+    </row>
+    <row r="90" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="D90" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="F90" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H90" s="23" t="n">
+        <f aca="false">IF(OR(J90="Yes",J90=TRUE()),0,F90*G90)</f>
+        <v>60</v>
+      </c>
+      <c r="I90" s="24" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="J90" s="29"/>
+    </row>
+    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="E91" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="F91" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="23" t="n">
         <v>25.99</v>
       </c>
-      <c r="H76" s="23" t="n">
-        <f aca="false">IF(OR(J76="Yes",J76=TRUE()),0,F76*G76)</f>
+      <c r="H91" s="23" t="n">
+        <f aca="false">IF(OR(J91="Yes",J91=TRUE()),0,F91*G91)</f>
         <v>25.99</v>
       </c>
-      <c r="I76" s="24" t="str">
+      <c r="I91" s="24" t="str">
         <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J76" s="29"/>
-    </row>
-    <row r="77" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="21" t="s">
-        <v>218</v>
-      </c>
-      <c r="B77" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C77" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E77" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F77" s="21" t="n">
+      <c r="J91" s="29"/>
+    </row>
+    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D92" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E92" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F92" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G77" s="23" t="n">
+      <c r="G92" s="23" t="n">
         <v>24.97</v>
       </c>
-      <c r="H77" s="23" t="n">
-        <f aca="false">IF(OR(J77="Yes",J77=TRUE()),0,F77*G77)</f>
+      <c r="H92" s="23" t="n">
+        <f aca="false">IF(OR(J92="Yes",J92=TRUE()),0,F92*G92)</f>
         <v>24.97</v>
       </c>
-      <c r="I77" s="24" t="str">
+      <c r="I92" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J77" s="29"/>
-    </row>
-    <row r="78" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="B78" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E78" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F78" s="21" t="n">
+      <c r="J92" s="29"/>
+    </row>
+    <row r="93" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="B93" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="C93" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E93" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F93" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G78" s="23" t="n">
+      <c r="G93" s="23" t="n">
         <v>11.99</v>
       </c>
-      <c r="H78" s="23" t="n">
-        <f aca="false">IF(OR(J78="Yes",J78=TRUE()),0,F78*G78)</f>
+      <c r="H93" s="23" t="n">
+        <f aca="false">IF(OR(J93="Yes",J93=TRUE()),0,F93*G93)</f>
         <v>11.99</v>
       </c>
-      <c r="I78" s="24" t="str">
+      <c r="I93" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J78" s="29"/>
-    </row>
-    <row r="79" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E79" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F79" s="21" t="n">
+      <c r="J93" s="29"/>
+    </row>
+    <row r="94" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="B94" s="22" t="s">
+        <v>272</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E94" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F94" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="23" t="n">
+      <c r="G94" s="23" t="n">
         <v>25.26</v>
       </c>
-      <c r="H79" s="23" t="n">
-        <f aca="false">IF(OR(J79="Yes",J79=TRUE()),0,F79*G79)</f>
+      <c r="H94" s="23" t="n">
+        <f aca="false">IF(OR(J94="Yes",J94=TRUE()),0,F94*G94)</f>
         <v>25.26</v>
       </c>
-      <c r="I79" s="24" t="str">
+      <c r="I94" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J79" s="29"/>
-    </row>
-    <row r="80" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="B80" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="C80" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E80" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F80" s="21" t="n">
+      <c r="J94" s="29"/>
+    </row>
+    <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="B95" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D95" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F95" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="23" t="n">
+      <c r="G95" s="23" t="n">
         <v>32.12</v>
       </c>
-      <c r="H80" s="23" t="n">
-        <f aca="false">IF(OR(J80="Yes",J80=TRUE()),0,F80*G80)</f>
+      <c r="H95" s="23" t="n">
+        <f aca="false">IF(OR(J95="Yes",J95=TRUE()),0,F95*G95)</f>
         <v>32.12</v>
       </c>
-      <c r="I80" s="24" t="str">
+      <c r="I95" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J80" s="29"/>
-    </row>
-    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B81" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="C81" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E81" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F81" s="21" t="n">
+      <c r="J95" s="29"/>
+    </row>
+    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="B96" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C96" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E96" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F96" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="23" t="n">
+      <c r="G96" s="23" t="n">
         <v>16.98</v>
       </c>
-      <c r="H81" s="23" t="n">
-        <f aca="false">IF(OR(J81="Yes",J81=TRUE()),0,F81*G81)</f>
+      <c r="H96" s="23" t="n">
+        <f aca="false">IF(OR(J96="Yes",J96=TRUE()),0,F96*G96)</f>
         <v>16.98</v>
       </c>
-      <c r="I81" s="24" t="str">
+      <c r="I96" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J81" s="29"/>
-    </row>
-    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="B82" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="C82" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D82" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E82" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F82" s="21" t="n">
+      <c r="J96" s="29"/>
+    </row>
+    <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D97" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E97" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F97" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="23" t="n">
+      <c r="G97" s="23" t="n">
         <v>22.31</v>
       </c>
-      <c r="H82" s="23" t="n">
-        <f aca="false">IF(OR(J82="Yes",J82=TRUE()),0,F82*G82)</f>
+      <c r="H97" s="23" t="n">
+        <f aca="false">IF(OR(J97="Yes",J97=TRUE()),0,F97*G97)</f>
         <v>22.31</v>
       </c>
-      <c r="I82" s="24" t="str">
+      <c r="I97" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J82" s="29"/>
-    </row>
-    <row r="83" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B83" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="C83" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E83" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F83" s="21" t="n">
+      <c r="J97" s="29"/>
+    </row>
+    <row r="98" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="B98" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="C98" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E98" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F98" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="23" t="n">
+      <c r="G98" s="23" t="n">
         <v>12.17</v>
       </c>
-      <c r="H83" s="23" t="n">
-        <f aca="false">IF(OR(J83="Yes",J83=TRUE()),0,F83*G83)</f>
+      <c r="H98" s="23" t="n">
+        <f aca="false">IF(OR(J98="Yes",J98=TRUE()),0,F98*G98)</f>
         <v>12.17</v>
       </c>
-      <c r="I83" s="24" t="str">
+      <c r="I98" s="24" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=precision+tweezers+set","Open")</f>
         <v>Open</v>
       </c>
-      <c r="J83" s="29"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="B84" s="31"/>
-      <c r="C84" s="31"/>
-      <c r="D84" s="31"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="31"/>
-      <c r="G84" s="31"/>
-      <c r="H84" s="32" t="n">
-        <f aca="false">SUM(H71:H83)</f>
-        <v>792.26</v>
-      </c>
-      <c r="I84" s="31"/>
-      <c r="J84" s="31"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B86" s="33"/>
-      <c r="C86" s="33"/>
-      <c r="D86" s="33"/>
-      <c r="E86" s="33"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="33"/>
-      <c r="J86" s="33"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="B87" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="C87" s="36"/>
-      <c r="D87" s="36"/>
-      <c r="E87" s="36"/>
-      <c r="F87" s="36"/>
-      <c r="G87" s="36"/>
-      <c r="H87" s="37" t="n">
-        <f aca="false">H62+H84</f>
-        <v>1885.76</v>
-      </c>
-      <c r="I87" s="36"/>
-      <c r="J87" s="36"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="B88" s="35"/>
-      <c r="C88" s="36"/>
-      <c r="D88" s="36"/>
-      <c r="E88" s="36"/>
-      <c r="F88" s="36"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="37" t="n">
-        <f aca="false">H66</f>
-        <v>452.09</v>
-      </c>
-      <c r="I88" s="36"/>
-      <c r="J88" s="36"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="B89" s="35"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="36"/>
-      <c r="E89" s="36"/>
-      <c r="F89" s="36"/>
-      <c r="G89" s="36"/>
-      <c r="H89" s="37" t="n">
-        <f aca="false">ROUND(H87*0.0775,2)</f>
-        <v>146.15</v>
-      </c>
-      <c r="I89" s="36"/>
-      <c r="J89" s="36"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="B90" s="35"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="36"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="36"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="37" t="n">
-        <f aca="false">ROUND((H87+H88+H89)*0.1,2)</f>
-        <v>248.4</v>
-      </c>
-      <c r="I90" s="36"/>
-      <c r="J90" s="36"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B91" s="38"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
-      <c r="F91" s="12"/>
-      <c r="G91" s="12"/>
-      <c r="H91" s="13" t="n">
-        <f aca="false">H87+H88+H89+H90</f>
-        <v>2732.4</v>
-      </c>
-      <c r="I91" s="12"/>
-      <c r="J91" s="12"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="B92" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="C92" s="36"/>
-      <c r="D92" s="36"/>
-      <c r="E92" s="36"/>
-      <c r="F92" s="36"/>
-      <c r="G92" s="36"/>
-      <c r="H92" s="37" t="n">
-        <f aca="false">2000-H91</f>
-        <v>-732.4</v>
-      </c>
-      <c r="I92" s="36"/>
-      <c r="J92" s="36"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="H95" s="39" t="n">
-        <f aca="false">ROUND((H62+ROUND(H62*0.0775,2)+H66)*1.1,2)</f>
-        <v>1793.37</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H96" s="39" t="n">
-        <f aca="false">ROUND((H62+SUMPRODUCT(F71:F83,G71:G83))*1.0775*1.1+H66*1.1,2)</f>
-        <v>2732.4</v>
+      <c r="J98" s="29"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B99" s="31"/>
+      <c r="C99" s="31"/>
+      <c r="D99" s="31"/>
+      <c r="E99" s="31"/>
+      <c r="F99" s="31"/>
+      <c r="G99" s="31"/>
+      <c r="H99" s="32" t="n">
+        <f aca="false">SUM(H84:H98)</f>
+        <v>892.26</v>
+      </c>
+      <c r="I99" s="31"/>
+      <c r="J99" s="31"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B101" s="33"/>
+      <c r="C101" s="33"/>
+      <c r="D101" s="33"/>
+      <c r="E101" s="33"/>
+      <c r="F101" s="33"/>
+      <c r="G101" s="33"/>
+      <c r="H101" s="33"/>
+      <c r="I101" s="33"/>
+      <c r="J101" s="33"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B102" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+      <c r="G102" s="36"/>
+      <c r="H102" s="37" t="n">
+        <f aca="false">H75+H99</f>
+        <v>2109.035</v>
+      </c>
+      <c r="I102" s="36"/>
+      <c r="J102" s="36"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="B103" s="35"/>
+      <c r="C103" s="36"/>
+      <c r="D103" s="36"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="36"/>
+      <c r="H103" s="37" t="n">
+        <f aca="false">H79</f>
+        <v>449.74</v>
+      </c>
+      <c r="I103" s="36"/>
+      <c r="J103" s="36"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="B104" s="35"/>
+      <c r="C104" s="36"/>
+      <c r="D104" s="36"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="36"/>
+      <c r="G104" s="36"/>
+      <c r="H104" s="37" t="n">
+        <f aca="false">ROUND(H102*0.0775,2)</f>
+        <v>163.45</v>
+      </c>
+      <c r="I104" s="36"/>
+      <c r="J104" s="36"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="B105" s="35"/>
+      <c r="C105" s="36"/>
+      <c r="D105" s="36"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="36"/>
+      <c r="G105" s="36"/>
+      <c r="H105" s="37" t="n">
+        <f aca="false">ROUND((H102+H103+H104)*0.1,2)</f>
+        <v>272.22</v>
+      </c>
+      <c r="I105" s="36"/>
+      <c r="J105" s="36"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B106" s="38"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="13" t="n">
+        <f aca="false">H102+H103+H104+H105</f>
+        <v>2994.445</v>
+      </c>
+      <c r="I106" s="12"/>
+      <c r="J106" s="12"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="B107" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="C107" s="36"/>
+      <c r="D107" s="36"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="36"/>
+      <c r="G107" s="36"/>
+      <c r="H107" s="37" t="n">
+        <f aca="false">2000-H106</f>
+        <v>-994.445</v>
+      </c>
+      <c r="I107" s="36"/>
+      <c r="J107" s="36"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H110" s="39" t="n">
+        <f aca="false">ROUND((H75+ROUND(H75*0.0775,2)+H79)*1.1,2)</f>
+        <v>1936.9</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H111" s="39" t="n">
+        <f aca="false">ROUND((H75+SUMPRODUCT(F84:F98,G84:G98))*1.0775*1.1+H79*1.1,2)</f>
+        <v>2994.45</v>
       </c>
     </row>
   </sheetData>
@@ -3731,7 +4278,7 @@
     <mergeCell ref="A8:B8"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J71:J83" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J84:J98" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="361">
   <si>
     <t xml:space="preserve">STM v1: what it actually cost</t>
   </si>
@@ -176,6 +176,9 @@
     <t xml:space="preserve">Parts and costs to build a second scanning tunneling microscope (v2) at UCSD, improving on the first one we built (v1). Prices checked 21 October 2026, in US dollars.</t>
   </si>
   <si>
+    <t xml:space="preserve">To choose what to fund, set the last column of any line to Yes or No. No takes that line out of every total. All lines start as Yes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Summary: total cost</t>
   </si>
   <si>
@@ -212,10 +215,16 @@
     <t xml:space="preserve">Everything needed for a complete, working microscope. It runs on batteries.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fund?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every purchase line in sections 1 to 8 has a Fund? choice in its last column. Yes keeps it in the budget, No removes it from every total, including shipping and fees that only that item needs.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Section 8</t>
   </si>
   <si>
-    <t xml:space="preserve">An optional upgrade to a better scanner. One Yes/No switch adds it to the total or removes it.</t>
+    <t xml:space="preserve">An optional upgrade to a better scanner. One Yes/No switch adds or removes the whole section; the Fund? choices inside it pick individual items.</t>
   </si>
   <si>
     <t xml:space="preserve">Section 9</t>
@@ -287,6 +296,9 @@
     <t xml:space="preserve">v1 receipt</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Sample approach: brings the sample up to the tip</t>
   </si>
   <si>
@@ -596,13 +608,13 @@
     <t xml:space="preserve">Shipping and import fees for sections 1 to 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Isolate It $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards.</t>
+    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Isolate It $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards. A seller's shipping drops out if nothing from that seller is funded.</t>
   </si>
   <si>
     <t xml:space="preserve">Import tariff on circuit boards</t>
   </si>
   <si>
-    <t xml:space="preserve">The US charges a 35% tariff on circuit boards and parts from China. Applied to the $487.06 of boards and parts from JLCPCB, the circuit board factory, and LCSC, its parts supplier. Only US-made boards avoid it, and they cost more.</t>
+    <t xml:space="preserve">The US charges a 35% tariff on circuit boards and parts from China. Applied to the funded boards and parts from JLCPCB, the circuit board factory, and LCSC, its parts supplier. Only US-made boards avoid it, and they cost more.</t>
   </si>
   <si>
     <t xml:space="preserve">Other import fees</t>
@@ -629,12 +641,6 @@
     <t xml:space="preserve">Switch:</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Include?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Piezo tube</t>
   </si>
   <si>
@@ -863,7 +869,7 @@
     <t xml:space="preserve">Shipping and import fees for the upgrade</t>
   </si>
   <si>
-    <t xml:space="preserve">Courier shipping for the tube from Australia (seller's estimate). The other upgrade parts ship with the section 1 to 7 orders.</t>
+    <t xml:space="preserve">Courier shipping for the tube from Australia (seller's estimate), only if a tube is funded. The other upgrade parts ship with the section 1 to 7 orders.</t>
   </si>
   <si>
     <t xml:space="preserve">35% US tariff on the driver's chips, parts and boards from China.</t>
@@ -1097,7 +1103,7 @@
     <t xml:space="preserve">With the upgrade, UCSD supplies everything</t>
   </si>
   <si>
-    <t xml:space="preserve">The upgrade cases include the optional extras as currently chosen in section 8 (spare tube and metal plate are No unless changed).</t>
+    <t xml:space="preserve">All four cases follow the Fund? choices made in the sheet. The upgrade cases include the optional extras as currently chosen in section 8 (spare tube and metal plate are No unless changed).</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1114,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1165,6 +1171,14 @@
     <font>
       <b val="true"/>
       <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1241,6 +1255,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
         <bgColor rgb="FF993366"/>
       </patternFill>
@@ -1249,12 +1269,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEDE3F5"/>
         <bgColor rgb="FFD9E2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1288,13 +1302,6 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -1307,6 +1314,13 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -1335,7 +1349,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1396,6 +1410,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1456,14 +1474,18 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1480,15 +1502,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1496,39 +1510,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1544,7 +1562,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1580,7 +1598,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1609,11 +1627,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <strike val="1"/>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1658,7 +1684,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF1F3864"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -2349,7 +2375,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -2375,3175 +2401,3323 @@
         <v>50</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="s">
-        <v>51</v>
+      <c r="A4" s="15" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="D5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19" t="n">
-        <f aca="false">H141</f>
+      <c r="A6" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20" t="n">
+        <f aca="false">H142</f>
         <v>2327.27</v>
       </c>
-      <c r="D6" s="20" t="n">
-        <f aca="false">H142</f>
+      <c r="D6" s="21" t="n">
+        <f aca="false">H143</f>
         <v>1317.13</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19" t="n">
-        <f aca="false">H143</f>
+      <c r="A7" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="20" t="n">
+        <f aca="false">H144</f>
         <v>3000.375</v>
       </c>
-      <c r="D7" s="20" t="n">
-        <f aca="false">H144</f>
+      <c r="D7" s="21" t="n">
+        <f aca="false">H145</f>
         <v>1942.825</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22" t="n">
-        <f aca="false">H136</f>
+      <c r="A8" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23" t="n">
+        <f aca="false">H137</f>
         <v>3000.375</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19" t="n">
+      <c r="A9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="n">
         <f aca="false">'v1 (what it cost)'!C55</f>
         <v>1375.93</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>58</v>
+      <c r="A11" s="15" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
+      <c r="B12" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="27"/>
+      <c r="K12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="s">
+      <c r="B13" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
+      <c r="B14" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="27"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
-      <c r="K15" s="26"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="s">
+      <c r="B15" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
+      <c r="B16" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="26"/>
-      <c r="I17" s="26"/>
-      <c r="J17" s="26"/>
-      <c r="K17" s="26"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="s">
+      <c r="B17" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25" t="s">
+      <c r="B18" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="B19" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" s="16" t="s">
+      <c r="B22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="G22" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
+      <c r="H22" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="I22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="K22" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="C24" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="29" t="n">
+      <c r="G24" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="29" t="n">
-        <f aca="false">F23*G23</f>
+      <c r="H24" s="30" t="n">
+        <f aca="false">IF(K24="No",0,F24*G24)</f>
         <v>5</v>
       </c>
-      <c r="I23" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="30" t="str">
+      <c r="I24" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=JESSINIE+18mm+piezo+disc","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+      <c r="K24" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="9" t="n">
-        <f aca="false">SUM(H23:H23)</f>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="9" t="n">
+        <f aca="false">SUM(H24:H24)</f>
         <v>5</v>
       </c>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-    </row>
-    <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="28" t="s">
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="F27" s="28" t="n">
+      <c r="B28" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G28" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="H27" s="29" t="n">
-        <f aca="false">F27*G27</f>
+      <c r="H28" s="30" t="n">
+        <f aca="false">IF(K28="No",0,F28*G28)</f>
         <v>14</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="30" t="str">
+      <c r="I28" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J28" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="27" t="s">
+      <c r="K28" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D29" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="27" t="s">
+      <c r="E29" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="30" t="n">
+        <v>8.95</v>
+      </c>
+      <c r="H29" s="30" t="n">
+        <f aca="false">IF(K29="No",0,F29*G29)</f>
+        <v>8.95</v>
+      </c>
+      <c r="I29" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>8.95</v>
-      </c>
-      <c r="H28" s="29" t="n">
-        <f aca="false">F28*G28</f>
-        <v>8.95</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J28" s="30" t="str">
+      <c r="J29" s="31" t="str">
         <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" s="27" t="s">
+      <c r="K29" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="F29" s="28" t="n">
+      <c r="B30" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G30" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H29" s="29" t="n">
-        <f aca="false">F29*G29</f>
+      <c r="H30" s="30" t="n">
+        <f aca="false">IF(K30="No",0,F30*G30)</f>
         <v>24</v>
       </c>
-      <c r="I29" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="30" t="str">
+      <c r="I30" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J30" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="27" t="s">
+      <c r="K30" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="F30" s="28" t="n">
+      <c r="E31" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G31" s="30" t="n">
         <v>8.6</v>
       </c>
-      <c r="H30" s="29" t="n">
-        <f aca="false">F30*G30</f>
+      <c r="H31" s="30" t="n">
+        <f aca="false">IF(K31="No",0,F31*G31)</f>
         <v>25.8</v>
       </c>
-      <c r="I30" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J30" s="30" t="str">
+      <c r="I31" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J31" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="K31" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9" t="n">
-        <f aca="false">SUM(H27:H30)</f>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9" t="n">
+        <f aca="false">SUM(H28:H31)</f>
         <v>72.75</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-    </row>
-    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" s="28" t="s">
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="B35" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="29" t="n">
+      <c r="G35" s="30" t="n">
         <v>209.64</v>
       </c>
-      <c r="H34" s="29" t="n">
-        <f aca="false">F34*G34</f>
+      <c r="H35" s="30" t="n">
+        <f aca="false">IF(K35="No",0,F35*G35)</f>
         <v>419.28</v>
       </c>
-      <c r="I34" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J34" s="30" t="str">
+      <c r="I35" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J35" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E35" s="27" t="s">
+      <c r="K35" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="F35" s="28" t="n">
+      <c r="E36" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="29" t="n">
+      <c r="G36" s="30" t="n">
         <v>1.68</v>
       </c>
-      <c r="H35" s="29" t="n">
-        <f aca="false">F35*G35</f>
+      <c r="H36" s="30" t="n">
+        <f aca="false">IF(K36="No",0,F36*G36)</f>
         <v>5.04</v>
       </c>
-      <c r="I35" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35" s="30" t="str">
+      <c r="I36" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J36" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="F36" s="28" t="n">
+      <c r="K36" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="29" t="n">
+      <c r="G37" s="30" t="n">
         <v>18.26</v>
       </c>
-      <c r="H36" s="29" t="n">
-        <f aca="false">F36*G36</f>
+      <c r="H37" s="30" t="n">
+        <f aca="false">IF(K37="No",0,F37*G37)</f>
         <v>36.52</v>
       </c>
-      <c r="I36" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="30" t="str">
+      <c r="I37" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J37" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="28" t="n">
+      <c r="K37" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="29" t="n">
+      <c r="G38" s="30" t="n">
         <v>31.5</v>
       </c>
-      <c r="H37" s="29" t="n">
-        <f aca="false">F37*G37</f>
+      <c r="H38" s="30" t="n">
+        <f aca="false">IF(K38="No",0,F38*G38)</f>
         <v>31.5</v>
       </c>
-      <c r="I37" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J37" s="30" t="str">
+      <c r="I38" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="K38" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="9" t="n">
-        <f aca="false">SUM(H34:H37)</f>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="9" t="n">
+        <f aca="false">SUM(H35:H38)</f>
         <v>492.34</v>
       </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-    </row>
-    <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-    </row>
-    <row r="41" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E41" s="27" t="s">
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+    </row>
+    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="28" t="n">
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+    </row>
+    <row r="42" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="F42" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="29" t="n">
+      <c r="G42" s="30" t="n">
         <v>30.17</v>
       </c>
-      <c r="H41" s="29" t="n">
-        <f aca="false">F41*G41</f>
+      <c r="H42" s="30" t="n">
+        <f aca="false">IF(K42="No",0,F42*G42)</f>
         <v>60.34</v>
       </c>
-      <c r="I41" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J41" s="30" t="str">
+      <c r="I42" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J42" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E42" s="27" t="s">
+      <c r="K42" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="E43" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="29" t="n">
+      <c r="G43" s="30" t="n">
         <v>0.8</v>
       </c>
-      <c r="H42" s="29" t="n">
-        <f aca="false">F42*G42</f>
+      <c r="H43" s="30" t="n">
+        <f aca="false">IF(K43="No",0,F43*G43)</f>
         <v>2.4</v>
       </c>
-      <c r="I42" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J42" s="30" t="str">
+      <c r="I43" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J43" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E43" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="F43" s="28" t="n">
+      <c r="K43" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C44" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F44" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="29" t="n">
+      <c r="G44" s="30" t="n">
         <v>5.73</v>
       </c>
-      <c r="H43" s="29" t="n">
-        <f aca="false">F43*G43</f>
+      <c r="H44" s="30" t="n">
+        <f aca="false">IF(K44="No",0,F44*G44)</f>
         <v>11.46</v>
       </c>
-      <c r="I43" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J43" s="30" t="str">
+      <c r="I44" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J44" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B44" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="F44" s="28" t="n">
+      <c r="K44" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="29" t="n">
+      <c r="G45" s="30" t="n">
         <v>2.09</v>
       </c>
-      <c r="H44" s="29" t="n">
-        <f aca="false">F44*G44</f>
+      <c r="H45" s="30" t="n">
+        <f aca="false">IF(K45="No",0,F45*G45)</f>
         <v>4.18</v>
       </c>
-      <c r="I44" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J44" s="30" t="str">
+      <c r="I45" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J45" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C45" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E45" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="F45" s="28" t="n">
+      <c r="K45" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F46" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="29" t="n">
+      <c r="G46" s="30" t="n">
         <v>7.99</v>
       </c>
-      <c r="H45" s="29" t="n">
-        <f aca="false">F45*G45</f>
+      <c r="H46" s="30" t="n">
+        <f aca="false">IF(K46="No",0,F46*G46)</f>
         <v>7.99</v>
       </c>
-      <c r="I45" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J45" s="30" t="str">
+      <c r="I46" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J46" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+      <c r="K46" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="9" t="n">
-        <f aca="false">SUM(H41:H45)</f>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="9" t="n">
+        <f aca="false">SUM(H42:H46)</f>
         <v>86.37</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-    </row>
-    <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="28" t="s">
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+    </row>
+    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E49" s="27" t="s">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="F49" s="28" t="n">
+      <c r="B50" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F50" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="29" t="n">
+      <c r="G50" s="30" t="n">
         <v>19.99</v>
       </c>
-      <c r="H49" s="29" t="n">
-        <f aca="false">F49*G49</f>
+      <c r="H50" s="30" t="n">
+        <f aca="false">IF(K50="No",0,F50*G50)</f>
         <v>19.99</v>
       </c>
-      <c r="I49" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J49" s="30" t="str">
+      <c r="I50" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J50" s="31" t="str">
         <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="F50" s="28" t="n">
+      <c r="K50" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="F51" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="29" t="n">
+      <c r="G51" s="30" t="n">
         <v>9.99</v>
       </c>
-      <c r="H50" s="29" t="n">
-        <f aca="false">F50*G50</f>
+      <c r="H51" s="30" t="n">
+        <f aca="false">IF(K51="No",0,F51*G51)</f>
         <v>9.99</v>
       </c>
-      <c r="I50" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J50" s="30" t="str">
+      <c r="I51" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J51" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="B51" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="C51" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E51" s="27" t="s">
+      <c r="K51" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="F51" s="28" t="n">
+      <c r="B52" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F52" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="29" t="n">
+      <c r="G52" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="H51" s="29" t="n">
-        <f aca="false">F51*G51</f>
+      <c r="H52" s="30" t="n">
+        <f aca="false">IF(K52="No",0,F52*G52)</f>
         <v>30</v>
       </c>
-      <c r="I51" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J51" s="30" t="str">
+      <c r="I52" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J52" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="27" t="s">
+      <c r="K52" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B52" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="F52" s="28" t="n">
+      <c r="B53" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="F53" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="29" t="n">
+      <c r="G53" s="30" t="n">
         <v>9.49</v>
       </c>
-      <c r="H52" s="29" t="n">
-        <f aca="false">F52*G52</f>
+      <c r="H53" s="30" t="n">
+        <f aca="false">IF(K53="No",0,F53*G53)</f>
         <v>9.49</v>
       </c>
-      <c r="I52" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J52" s="30" t="str">
+      <c r="I53" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J53" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C53" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="E53" s="27" t="s">
+      <c r="K53" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="F53" s="28" t="n">
+      <c r="B54" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="F54" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G53" s="29" t="n">
+      <c r="G54" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="H53" s="29" t="n">
-        <f aca="false">F53*G53</f>
+      <c r="H54" s="30" t="n">
+        <f aca="false">IF(K54="No",0,F54*G54)</f>
         <v>35</v>
       </c>
-      <c r="I53" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J53" s="30" t="str">
+      <c r="I54" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J54" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="K54" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="9" t="n">
-        <f aca="false">SUM(H49:H53)</f>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="9" t="n">
+        <f aca="false">SUM(H50:H54)</f>
         <v>104.47</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-    </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-    </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E57" s="27" t="s">
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+    </row>
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="F57" s="28" t="n">
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+    </row>
+    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="F58" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="29" t="n">
+      <c r="G58" s="30" t="n">
         <v>11.5</v>
       </c>
-      <c r="H57" s="29" t="n">
-        <f aca="false">F57*G57</f>
+      <c r="H58" s="30" t="n">
+        <f aca="false">IF(K58="No",0,F58*G58)</f>
         <v>23</v>
       </c>
-      <c r="I57" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J57" s="30" t="str">
+      <c r="I58" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J58" s="31" t="str">
         <f aca="false">HYPERLINK("https://adafruit.com/product/4821","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="7" t="s">
+      <c r="K58" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="9" t="n">
-        <f aca="false">SUM(H57:H57)</f>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="9" t="n">
+        <f aca="false">SUM(H58:H58)</f>
         <v>23</v>
       </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-    </row>
-    <row r="60" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-    </row>
-    <row r="61" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="D61" s="28" t="s">
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E61" s="27" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="F61" s="28" t="n">
+      <c r="B62" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F62" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G61" s="29" t="n">
+      <c r="G62" s="30" t="n">
         <v>21.39</v>
       </c>
-      <c r="H61" s="29" t="n">
-        <f aca="false">F61*G61</f>
+      <c r="H62" s="30" t="n">
+        <f aca="false">IF(K62="No",0,F62*G62)</f>
         <v>42.78</v>
       </c>
-      <c r="I61" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J61" s="30" t="str">
+      <c r="I62" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J62" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="F62" s="28" t="n">
+      <c r="K62" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F63" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="G62" s="29" t="n">
+      <c r="G63" s="30" t="n">
         <v>0.61</v>
       </c>
-      <c r="H62" s="29" t="n">
-        <f aca="false">F62*G62</f>
+      <c r="H63" s="30" t="n">
+        <f aca="false">IF(K63="No",0,F63*G63)</f>
         <v>6.1</v>
       </c>
-      <c r="I62" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J62" s="30" t="str">
+      <c r="I63" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J63" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="D63" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E63" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="F63" s="28" t="n">
+      <c r="K63" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="F64" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="29" t="n">
+      <c r="G64" s="30" t="n">
         <v>10.95</v>
       </c>
-      <c r="H63" s="29" t="n">
-        <f aca="false">F63*G63</f>
+      <c r="H64" s="30" t="n">
+        <f aca="false">IF(K64="No",0,F64*G64)</f>
         <v>10.95</v>
       </c>
-      <c r="I63" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J63" s="30" t="str">
+      <c r="I64" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J64" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="C64" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="F64" s="28" t="n">
+      <c r="K64" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F65" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G64" s="29" t="n">
+      <c r="G65" s="30" t="n">
         <v>2.95</v>
       </c>
-      <c r="H64" s="29" t="n">
-        <f aca="false">F64*G64</f>
+      <c r="H65" s="30" t="n">
+        <f aca="false">IF(K65="No",0,F65*G65)</f>
         <v>5.9</v>
       </c>
-      <c r="I64" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J64" s="30" t="str">
+      <c r="I65" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J65" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
+      <c r="K65" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="9" t="n">
-        <f aca="false">SUM(H61:H64)</f>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="9" t="n">
+        <f aca="false">SUM(H62:H65)</f>
         <v>65.73</v>
       </c>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="32" t="s">
-        <v>189</v>
-      </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="34" t="n">
-        <f aca="false">H24+H31+H38+H46+H54+H58+H65</f>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="36" t="n">
+        <f aca="false">H25+H32+H39+H47+H55+H59+H66</f>
         <v>849.66</v>
       </c>
-      <c r="I67" s="33"/>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-    </row>
-    <row r="69" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="5"/>
-    </row>
-    <row r="70" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="28" t="s">
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+    </row>
+    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+    </row>
+    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="C70" s="26"/>
-      <c r="D70" s="26"/>
-      <c r="E70" s="26"/>
-      <c r="H70" s="29" t="n">
+      <c r="B71" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="H71" s="30" t="n">
+        <f aca="false">IF(SUM(H28+H29+H58+H65)&gt;0,10,0)+IF(SUM(H30+H31)&gt;0,15.26,0)+IF(SUM(H35+H36+H42+H43)&gt;0,25,0)+IF(SUM(H37+H44+H45+H63)&gt;0,8.49,0)+IF(SUM(H38)&gt;0,8,0)+IF(SUM(H50)&gt;0,5,0)+IF(SUM(H52)&gt;0,15,0)+IF(SUM(H54)&gt;0,10,0)+IF(SUM(H62+H64)&gt;0,10,0)</f>
         <v>106.75</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B71" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="C71" s="26"/>
-      <c r="D71" s="26"/>
-      <c r="E71" s="26"/>
-      <c r="H71" s="29" t="n">
+    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="H72" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H35+H36+H42+H43),2)</f>
         <v>170.47</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="C72" s="26"/>
-      <c r="D72" s="26"/>
-      <c r="E72" s="26"/>
-      <c r="H72" s="29" t="n">
+    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B73" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="H73" s="30" t="n">
+        <f aca="false">ROUND(0.08*(H37+H44+H45+H63),2)</f>
         <v>4.66</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="33"/>
-      <c r="D73" s="33"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="34" t="n">
-        <f aca="false">SUM(H70:H72)</f>
-        <v>281.88</v>
-      </c>
-      <c r="I73" s="33"/>
-      <c r="J73" s="33"/>
-      <c r="K73" s="33"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B74" s="35" t="s">
-        <v>197</v>
-      </c>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="B74" s="35"/>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
       <c r="E74" s="35"/>
       <c r="F74" s="35"/>
       <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
+      <c r="H74" s="36" t="n">
+        <f aca="false">SUM(H71:H73)</f>
+        <v>281.88</v>
+      </c>
       <c r="I74" s="35"/>
       <c r="J74" s="35"/>
       <c r="K74" s="35"/>
     </row>
-    <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37"/>
-      <c r="I76" s="37"/>
-      <c r="J76" s="37"/>
-      <c r="K76" s="37"/>
-    </row>
-    <row r="77" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
-      <c r="D77" s="26"/>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26"/>
-      <c r="G77" s="26"/>
-      <c r="H77" s="26"/>
-      <c r="I77" s="26"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-    </row>
-    <row r="78" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="B78" s="39"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="39"/>
-      <c r="E78" s="39"/>
-      <c r="F78" s="39"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="39"/>
-      <c r="I78" s="40" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="J78" s="39"/>
-      <c r="K78" s="41" t="s">
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
+    </row>
+    <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="38" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="42" t="s">
+      <c r="B77" s="39"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39"/>
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="39"/>
+    </row>
+    <row r="78" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="27"/>
+      <c r="J78" s="27"/>
+      <c r="K78" s="27"/>
+    </row>
+    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="J79" s="41"/>
+      <c r="K79" s="43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B79" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="D79" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="E79" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="F79" s="42" t="s">
+      <c r="B80" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E80" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G79" s="42" t="s">
-        <v>78</v>
-      </c>
-      <c r="H79" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="I79" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="J79" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="K79" s="42" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="B80" s="39"/>
-      <c r="C80" s="39"/>
-      <c r="D80" s="39"/>
-      <c r="E80" s="39"/>
-      <c r="F80" s="39"/>
-      <c r="G80" s="39"/>
-      <c r="H80" s="39"/>
-      <c r="I80" s="39"/>
-      <c r="J80" s="39"/>
-      <c r="K80" s="39"/>
-    </row>
-    <row r="81" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="C81" s="27" t="s">
+      <c r="G80" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="H80" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="I80" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J80" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="K80" s="44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="D81" s="28" t="s">
+      <c r="B81" s="41"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
+      <c r="H81" s="41"/>
+      <c r="I81" s="41"/>
+      <c r="J81" s="41"/>
+      <c r="K81" s="41"/>
+    </row>
+    <row r="82" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="B82" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="E81" s="27" t="s">
+      <c r="C82" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="F81" s="28" t="n">
+      <c r="D82" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="E82" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F82" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="29" t="n">
+      <c r="G82" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="H81" s="29" t="n">
-        <f aca="false">F81*G81</f>
+      <c r="H82" s="30" t="n">
+        <f aca="false">IF(K82="No",0,F82*G82)</f>
         <v>131</v>
       </c>
-      <c r="I81" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J81" s="30" t="str">
+      <c r="I82" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J82" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="82" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="B82" s="39"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="39"/>
-      <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="39"/>
-    </row>
-    <row r="83" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="B83" s="27" t="s">
+      <c r="K82" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="C83" s="27" t="s">
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
+      <c r="J83" s="41"/>
+      <c r="K83" s="41"/>
+    </row>
+    <row r="84" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="D83" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E83" s="27" t="s">
+      <c r="B84" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="F83" s="28" t="n">
+      <c r="C84" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E84" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="F84" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="29" t="n">
+      <c r="G84" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="H83" s="29" t="n">
-        <f aca="false">F83*G83</f>
+      <c r="H84" s="30" t="n">
+        <f aca="false">IF(K84="No",0,F84*G84)</f>
         <v>35</v>
       </c>
-      <c r="I83" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J83" s="30" t="str">
+      <c r="I84" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J84" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="84" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="B84" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" s="27" t="s">
+      <c r="K84" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="D84" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E84" s="27" t="s">
+      <c r="B85" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="F84" s="28" t="n">
+      <c r="C85" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="D85" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E85" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="F85" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="29" t="n">
+      <c r="G85" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="H84" s="29" t="n">
-        <f aca="false">F84*G84</f>
+      <c r="H85" s="30" t="n">
+        <f aca="false">IF(K85="No",0,F85*G85)</f>
         <v>15</v>
       </c>
-      <c r="I84" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J84" s="30" t="str">
+      <c r="I85" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J85" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="B85" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C85" s="27" t="s">
+      <c r="K85" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="D85" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E85" s="27" t="s">
+      <c r="B86" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="F85" s="28" t="n">
+      <c r="C86" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="D86" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E86" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="F86" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="29" t="n">
+      <c r="G86" s="30" t="n">
         <v>25</v>
       </c>
-      <c r="H85" s="29" t="n">
-        <f aca="false">F85*G85</f>
+      <c r="H86" s="30" t="n">
+        <f aca="false">IF(K86="No",0,F86*G86)</f>
         <v>25</v>
       </c>
-      <c r="I85" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J85" s="30" t="str">
+      <c r="I86" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J86" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="B86" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C86" s="27" t="s">
+      <c r="K86" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="D86" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E86" s="27" t="s">
+      <c r="B87" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="F86" s="28" t="n">
+      <c r="C87" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="D87" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E87" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F87" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G86" s="29" t="n">
+      <c r="G87" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="H86" s="29" t="n">
-        <f aca="false">F86*G86</f>
+      <c r="H87" s="30" t="n">
+        <f aca="false">IF(K87="No",0,F87*G87)</f>
         <v>10</v>
       </c>
-      <c r="I86" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J86" s="30" t="str">
+      <c r="I87" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J87" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="87" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="B87" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C87" s="27" t="s">
+      <c r="K87" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="D87" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E87" s="27" t="s">
+      <c r="B88" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="F87" s="28" t="n">
+      <c r="C88" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D88" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E88" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="F88" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="29" t="n">
+      <c r="G88" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="H87" s="29" t="n">
-        <f aca="false">F87*G87</f>
+      <c r="H88" s="30" t="n">
+        <f aca="false">IF(K88="No",0,F88*G88)</f>
         <v>10</v>
       </c>
-      <c r="I87" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J87" s="30" t="str">
+      <c r="I88" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J88" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="88" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="B88" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C88" s="27" t="s">
+      <c r="K88" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="D88" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E88" s="27" t="s">
+      <c r="B89" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="F88" s="28" t="n">
+      <c r="C89" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="D89" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E89" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F89" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G88" s="29" t="n">
+      <c r="G89" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="H88" s="29" t="n">
-        <f aca="false">F88*G88</f>
+      <c r="H89" s="30" t="n">
+        <f aca="false">IF(K89="No",0,F89*G89)</f>
         <v>12</v>
       </c>
-      <c r="I88" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J88" s="30" t="str">
+      <c r="I89" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J89" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="89" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B89" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C89" s="27" t="s">
+      <c r="K89" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D89" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E89" s="27" t="s">
+      <c r="B90" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="F89" s="28" t="n">
+      <c r="C90" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D90" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E90" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F90" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G89" s="29" t="n">
+      <c r="G90" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="H89" s="29" t="n">
-        <f aca="false">F89*G89</f>
+      <c r="H90" s="30" t="n">
+        <f aca="false">IF(K90="No",0,F90*G90)</f>
         <v>6</v>
       </c>
-      <c r="I89" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J89" s="30" t="str">
+      <c r="I90" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J90" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C90" s="27" t="s">
+      <c r="K90" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="D90" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E90" s="27" t="s">
+      <c r="B91" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="F90" s="28" t="n">
+      <c r="C91" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D91" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="F91" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G90" s="29" t="n">
+      <c r="G91" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="H90" s="29" t="n">
-        <f aca="false">F90*G90</f>
+      <c r="H91" s="30" t="n">
+        <f aca="false">IF(K91="No",0,F91*G91)</f>
         <v>8</v>
       </c>
-      <c r="I90" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J90" s="30" t="str">
+      <c r="I91" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J91" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C91" s="27" t="s">
+      <c r="K91" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="D91" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E91" s="27" t="s">
+      <c r="B92" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="F91" s="28" t="n">
+      <c r="C92" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="D92" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E92" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="F92" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="G91" s="29" t="n">
+      <c r="G92" s="30" t="n">
         <v>0.5</v>
       </c>
-      <c r="H91" s="29" t="n">
-        <f aca="false">F91*G91</f>
+      <c r="H92" s="30" t="n">
+        <f aca="false">IF(K92="No",0,F92*G92)</f>
         <v>4</v>
       </c>
-      <c r="I91" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J91" s="30" t="str">
+      <c r="I92" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J92" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C92" s="27" t="s">
+      <c r="K92" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="D92" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" s="27" t="s">
+      <c r="B93" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="F92" s="28" t="n">
+      <c r="C93" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="D93" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E93" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="F93" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G92" s="29" t="n">
+      <c r="G93" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H92" s="29" t="n">
-        <f aca="false">F92*G92</f>
+      <c r="H93" s="30" t="n">
+        <f aca="false">IF(K93="No",0,F93*G93)</f>
         <v>5</v>
       </c>
-      <c r="I92" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J92" s="30" t="str">
+      <c r="I93" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J93" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="B93" s="39"/>
-      <c r="C93" s="39"/>
-      <c r="D93" s="39"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-      <c r="G93" s="39"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="39"/>
-      <c r="J93" s="39"/>
-      <c r="K93" s="39"/>
-    </row>
-    <row r="94" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="B94" s="27" t="s">
+      <c r="K93" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="C94" s="27" t="s">
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="41"/>
+      <c r="F94" s="41"/>
+      <c r="G94" s="41"/>
+      <c r="H94" s="41"/>
+      <c r="I94" s="41"/>
+      <c r="J94" s="41"/>
+      <c r="K94" s="41"/>
+    </row>
+    <row r="95" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="D94" s="28" t="s">
+      <c r="B95" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="E94" s="27" t="s">
+      <c r="C95" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="F94" s="28" t="n">
+      <c r="D95" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="E95" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F95" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="G94" s="29" t="n">
+      <c r="G95" s="30" t="n">
         <v>6.725</v>
       </c>
-      <c r="H94" s="29" t="n">
-        <f aca="false">F94*G94</f>
+      <c r="H95" s="30" t="n">
+        <f aca="false">IF(K95="No",0,F95*G95)</f>
         <v>33.625</v>
       </c>
-      <c r="I94" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J94" s="30" t="str">
+      <c r="I95" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J95" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="27" t="s">
+      <c r="K95" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B96" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="C96" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="D96" s="29" t="s">
         <v>256</v>
       </c>
-      <c r="B95" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C95" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="D95" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="E95" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="F95" s="28" t="n">
+      <c r="E96" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="F96" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G95" s="29" t="n">
+      <c r="G96" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="H95" s="29" t="n">
-        <f aca="false">F95*G95</f>
+      <c r="H96" s="30" t="n">
+        <f aca="false">IF(K96="No",0,F96*G96)</f>
         <v>40</v>
       </c>
-      <c r="I95" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J95" s="30" t="str">
+      <c r="I96" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J96" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="27" t="s">
+      <c r="K96" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B97" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C97" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="B96" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C96" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="D96" s="28" t="s">
-        <v>112</v>
-      </c>
-      <c r="E96" s="27" t="s">
+      <c r="D97" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="F96" s="28" t="n">
+      <c r="E97" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F97" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="G96" s="29" t="n">
+      <c r="G97" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="H96" s="29" t="n">
-        <f aca="false">F96*G96</f>
+      <c r="H97" s="30" t="n">
+        <f aca="false">IF(K97="No",0,F97*G97)</f>
         <v>10</v>
       </c>
-      <c r="I96" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J96" s="30" t="str">
+      <c r="I97" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J97" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="43" t="s">
-        <v>262</v>
-      </c>
-      <c r="B97" s="39"/>
-      <c r="C97" s="39"/>
-      <c r="D97" s="39"/>
-      <c r="E97" s="39"/>
-      <c r="F97" s="39"/>
-      <c r="G97" s="39"/>
-      <c r="H97" s="39"/>
-      <c r="I97" s="39"/>
-      <c r="J97" s="39"/>
-      <c r="K97" s="39"/>
-    </row>
-    <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="B98" s="27" t="s">
+      <c r="K97" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="45" t="s">
         <v>264</v>
       </c>
-      <c r="C98" s="27" t="s">
+      <c r="B98" s="41"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="41"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="41"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="41"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="41"/>
+      <c r="K98" s="41"/>
+    </row>
+    <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="D98" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="E98" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="F98" s="28" t="n">
+      <c r="B99" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C99" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="D99" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E99" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="F99" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G98" s="29" t="n">
+      <c r="G99" s="30" t="n">
         <v>21.39</v>
       </c>
-      <c r="H98" s="29" t="n">
-        <f aca="false">F98*G98</f>
+      <c r="H99" s="30" t="n">
+        <f aca="false">IF(K99="No",0,F99*G99)</f>
         <v>21.39</v>
       </c>
-      <c r="I98" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J98" s="30" t="str">
+      <c r="I99" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J99" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="27" t="s">
-        <v>266</v>
-      </c>
-      <c r="B99" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="D99" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="E99" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="F99" s="28" t="n">
+      <c r="K99" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="E100" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="F100" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="G99" s="29" t="n">
+      <c r="G100" s="30" t="n">
         <v>0.61</v>
       </c>
-      <c r="H99" s="29" t="n">
-        <f aca="false">F99*G99</f>
+      <c r="H100" s="30" t="n">
+        <f aca="false">IF(K100="No",0,F100*G100)</f>
         <v>6.1</v>
       </c>
-      <c r="I99" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J99" s="30" t="str">
+      <c r="I100" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J100" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
         <v>Open</v>
       </c>
-    </row>
-    <row r="100" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="43" t="s">
-        <v>268</v>
-      </c>
-      <c r="B100" s="39"/>
-      <c r="C100" s="39"/>
-      <c r="D100" s="39"/>
-      <c r="E100" s="39"/>
-      <c r="F100" s="39"/>
-      <c r="G100" s="39"/>
-      <c r="H100" s="39"/>
-      <c r="I100" s="39"/>
-      <c r="J100" s="39"/>
-      <c r="K100" s="39"/>
-    </row>
-    <row r="101" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="B101" s="27" t="s">
+      <c r="K100" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="45" t="s">
         <v>270</v>
       </c>
-      <c r="C101" s="27" t="s">
+      <c r="B101" s="41"/>
+      <c r="C101" s="41"/>
+      <c r="D101" s="41"/>
+      <c r="E101" s="41"/>
+      <c r="F101" s="41"/>
+      <c r="G101" s="41"/>
+      <c r="H101" s="41"/>
+      <c r="I101" s="41"/>
+      <c r="J101" s="41"/>
+      <c r="K101" s="41"/>
+    </row>
+    <row r="102" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="D101" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="F101" s="28" t="n">
+      <c r="B102" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C102" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="D102" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="E102" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F102" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G101" s="29" t="n">
+      <c r="G102" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="H101" s="29" t="n">
-        <f aca="false">IF(K101="Yes",F101*G101,0)</f>
+      <c r="H102" s="30" t="n">
+        <f aca="false">IF(K102="Yes",F102*G102,0)</f>
         <v>0</v>
       </c>
-      <c r="I101" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J101" s="30" t="str">
+      <c r="I102" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J102" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K101" s="44" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="B102" s="27" t="s">
+      <c r="K102" s="32" t="s">
         <v>274</v>
       </c>
-      <c r="C102" s="27" t="s">
+    </row>
+    <row r="103" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="D102" s="28" t="s">
+      <c r="B103" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="E102" s="27" t="s">
+      <c r="C103" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="F102" s="28" t="n">
+      <c r="D103" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="F103" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G102" s="29" t="n">
+      <c r="G103" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="H102" s="29" t="n">
-        <f aca="false">IF(K102="Yes",F102*G102,0)</f>
+      <c r="H103" s="30" t="n">
+        <f aca="false">IF(K103="Yes",F103*G103,0)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J102" s="30" t="str">
+      <c r="I103" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J103" s="31" t="str">
         <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K102" s="44" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="9" t="n">
-        <f aca="false">SUM(H80:H102)</f>
+      <c r="K103" s="32" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="9" t="n">
+        <f aca="false">SUM(H81:H103)</f>
         <v>372.115</v>
       </c>
-      <c r="I103" s="8"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-    </row>
-    <row r="105" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="43" t="s">
-        <v>279</v>
-      </c>
-      <c r="B105" s="39"/>
-      <c r="C105" s="39"/>
-      <c r="D105" s="39"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="39"/>
-      <c r="H105" s="39"/>
-      <c r="I105" s="39"/>
-      <c r="J105" s="39"/>
-      <c r="K105" s="39"/>
-    </row>
-    <row r="106" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="28" t="s">
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+    </row>
+    <row r="106" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B106" s="41"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="41"/>
+      <c r="E106" s="41"/>
+      <c r="F106" s="41"/>
+      <c r="G106" s="41"/>
+      <c r="H106" s="41"/>
+      <c r="I106" s="41"/>
+      <c r="J106" s="41"/>
+      <c r="K106" s="41"/>
+    </row>
+    <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B106" s="26" t="s">
-        <v>280</v>
-      </c>
-      <c r="C106" s="26"/>
-      <c r="D106" s="26"/>
-      <c r="E106" s="26"/>
-      <c r="H106" s="29" t="n">
+      <c r="B107" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="27"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="H107" s="30" t="n">
+        <f aca="false">IF(SUM(H82+H102)&gt;0,60,0)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="B107" s="26" t="s">
-        <v>281</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="26"/>
-      <c r="H107" s="29" t="n">
-        <f aca="false">ROUND(0.35*(H94+H95+H96),2)</f>
+    <row r="108" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="27"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
+      <c r="H108" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H95+H96+H97),2)</f>
         <v>29.27</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="B108" s="26" t="s">
-        <v>282</v>
-      </c>
-      <c r="C108" s="26"/>
-      <c r="D108" s="26"/>
-      <c r="E108" s="26"/>
-      <c r="H108" s="29" t="n">
-        <f aca="false">ROUND(0.1*(H81+H101)+0.08*(H99),2)+65</f>
+    <row r="109" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="C109" s="27"/>
+      <c r="D109" s="27"/>
+      <c r="E109" s="27"/>
+      <c r="H109" s="30" t="n">
+        <f aca="false">ROUND(0.1*(H82+H102)+0.08*(H100),2)+IF(SUM(H82+H102)&gt;0,65,0)</f>
         <v>78.59</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="9" t="n">
-        <f aca="false">SUM(H106:H108)</f>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="9" t="n">
+        <f aca="false">SUM(H107:H109)</f>
         <v>167.86</v>
       </c>
-      <c r="I109" s="8"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-    </row>
-    <row r="110" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B110" s="46" t="s">
-        <v>285</v>
-      </c>
-      <c r="C110" s="47"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="47"/>
-      <c r="G110" s="47"/>
-      <c r="H110" s="48" t="n">
-        <f aca="false">IF(K78="Yes",H103+H109,0)</f>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+    </row>
+    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="B111" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C111" s="48"/>
+      <c r="D111" s="48"/>
+      <c r="E111" s="48"/>
+      <c r="F111" s="48"/>
+      <c r="G111" s="48"/>
+      <c r="H111" s="49" t="n">
+        <f aca="false">IF(K79="Yes",H104+H110,0)</f>
         <v>539.975</v>
       </c>
-      <c r="I110" s="47"/>
-      <c r="J110" s="47"/>
-      <c r="K110" s="47"/>
-    </row>
-    <row r="112" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="49" t="s">
-        <v>286</v>
-      </c>
-      <c r="B112" s="50"/>
-      <c r="C112" s="50"/>
-      <c r="D112" s="50"/>
-      <c r="E112" s="50"/>
-      <c r="F112" s="50"/>
-      <c r="G112" s="50"/>
-      <c r="H112" s="50"/>
-      <c r="I112" s="50"/>
-      <c r="J112" s="50"/>
-      <c r="K112" s="50"/>
-    </row>
-    <row r="113" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="51" t="s">
+      <c r="I111" s="48"/>
+      <c r="J111" s="48"/>
+      <c r="K111" s="48"/>
+    </row>
+    <row r="113" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="50" t="s">
+        <v>288</v>
+      </c>
+      <c r="B113" s="51"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="51"/>
+      <c r="G113" s="51"/>
+      <c r="H113" s="51"/>
+      <c r="I113" s="51"/>
+      <c r="J113" s="51"/>
+      <c r="K113" s="51"/>
+    </row>
+    <row r="114" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B113" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113" s="51" t="s">
-        <v>67</v>
-      </c>
-      <c r="D113" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="E113" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="F113" s="51" t="s">
+      <c r="B114" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C114" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D114" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="E114" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="F114" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="G113" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="H113" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="I113" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="J113" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="K113" s="51" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="27" t="s">
-        <v>288</v>
-      </c>
-      <c r="B114" s="27" t="s">
+      <c r="G114" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H114" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I114" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J114" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="K114" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="C114" s="27" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="D114" s="28" t="s">
+      <c r="B115" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="E114" s="27" t="s">
+      <c r="C115" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="F114" s="28" t="n">
+      <c r="D115" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="E115" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="F115" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G114" s="29" t="n">
+      <c r="G115" s="30" t="n">
         <v>277.2</v>
       </c>
-      <c r="H114" s="29" t="n">
-        <f aca="false">IF(OR(K114="Yes",K114=TRUE()),0,F114*G114)</f>
+      <c r="H115" s="30" t="n">
+        <f aca="false">IF(OR(K115="Yes",K115=TRUE()),0,F115*G115)</f>
         <v>277.2</v>
       </c>
-      <c r="I114" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J114" s="30" t="str">
+      <c r="I115" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J115" s="31" t="str">
         <f aca="false">HYPERLINK("https://store.bruker.com/products/dpt10","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K114" s="52"/>
-    </row>
-    <row r="115" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="B115" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="C115" s="27" t="s">
+      <c r="K115" s="53"/>
+    </row>
+    <row r="116" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="D115" s="28" t="s">
+      <c r="B116" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="E115" s="27" t="s">
+      <c r="C116" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="F115" s="28" t="n">
+      <c r="D116" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="E116" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="F116" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G115" s="29" t="n">
+      <c r="G116" s="30" t="n">
         <v>77</v>
       </c>
-      <c r="H115" s="29" t="n">
-        <f aca="false">IF(OR(K115="Yes",K115=TRUE()),0,F115*G115)</f>
+      <c r="H116" s="30" t="n">
+        <f aca="false">IF(OR(K116="Yes",K116=TRUE()),0,F116*G116)</f>
         <v>77</v>
       </c>
-      <c r="I115" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J115" s="30" t="str">
+      <c r="I116" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J116" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K115" s="52"/>
-    </row>
-    <row r="116" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="C116" s="27" t="s">
+      <c r="K116" s="53"/>
+    </row>
+    <row r="117" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="D116" s="28" t="s">
+      <c r="B117" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="E116" s="27" t="s">
+      <c r="C117" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="F116" s="28" t="n">
+      <c r="D117" s="29" t="s">
+        <v>303</v>
+      </c>
+      <c r="E117" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F117" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G116" s="29" t="n">
+      <c r="G117" s="30" t="n">
         <v>133.13</v>
       </c>
-      <c r="H116" s="29" t="n">
-        <f aca="false">IF(OR(K116="Yes",K116=TRUE()),0,F116*G116)</f>
+      <c r="H117" s="30" t="n">
+        <f aca="false">IF(OR(K117="Yes",K117=TRUE()),0,F117*G117)</f>
         <v>133.13</v>
       </c>
-      <c r="I116" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J116" s="30" t="str">
+      <c r="I117" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J117" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K116" s="52"/>
-    </row>
-    <row r="117" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="B117" s="27" t="s">
-        <v>304</v>
-      </c>
-      <c r="C117" s="27" t="s">
+      <c r="K117" s="53"/>
+    </row>
+    <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="D117" s="28" t="s">
+      <c r="B118" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="E117" s="27" t="s">
+      <c r="C118" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="F117" s="28" t="n">
+      <c r="D118" s="29" t="s">
+        <v>308</v>
+      </c>
+      <c r="E118" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="F118" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G117" s="29" t="n">
+      <c r="G118" s="30" t="n">
         <v>75.15</v>
       </c>
-      <c r="H117" s="29" t="n">
-        <f aca="false">IF(OR(K117="Yes",K117=TRUE()),0,F117*G117)</f>
+      <c r="H118" s="30" t="n">
+        <f aca="false">IF(OR(K118="Yes",K118=TRUE()),0,F118*G118)</f>
         <v>75.15</v>
       </c>
-      <c r="I117" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J117" s="30" t="str">
+      <c r="I118" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J118" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K117" s="52"/>
-    </row>
-    <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="27" t="s">
+      <c r="K118" s="53"/>
+    </row>
+    <row r="119" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B118" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="C118" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D118" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E118" s="27" t="s">
+      <c r="B119" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="F118" s="28" t="n">
+      <c r="C119" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D119" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E119" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="F119" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G118" s="29" t="n">
+      <c r="G119" s="30" t="n">
         <v>57.99</v>
       </c>
-      <c r="H118" s="29" t="n">
-        <f aca="false">IF(OR(K118="Yes",K118=TRUE()),0,F118*G118)</f>
+      <c r="H119" s="30" t="n">
+        <f aca="false">IF(OR(K119="Yes",K119=TRUE()),0,F119*G119)</f>
         <v>57.99</v>
       </c>
-      <c r="I118" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J118" s="30" t="str">
+      <c r="I119" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J119" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K118" s="52"/>
-    </row>
-    <row r="119" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="27" t="s">
-        <v>311</v>
-      </c>
-      <c r="B119" s="27" t="s">
-        <v>312</v>
-      </c>
-      <c r="C119" s="27" t="s">
+      <c r="K119" s="53"/>
+    </row>
+    <row r="120" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="D119" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E119" s="27" t="s">
+      <c r="B120" s="28" t="s">
         <v>314</v>
       </c>
-      <c r="F119" s="28" t="n">
+      <c r="C120" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="D120" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E120" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="F120" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G119" s="29" t="n">
+      <c r="G120" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="H119" s="29" t="n">
-        <f aca="false">IF(OR(K119="Yes",K119=TRUE(),K78&lt;&gt;"Yes"),0,F119*G119)</f>
+      <c r="H120" s="30" t="n">
+        <f aca="false">IF(OR(K120="Yes",K120=TRUE(),K79&lt;&gt;"Yes"),0,F120*G120)</f>
         <v>40</v>
       </c>
-      <c r="I119" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J119" s="30" t="str">
+      <c r="I120" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J120" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K119" s="52"/>
-    </row>
-    <row r="120" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="27" t="s">
-        <v>315</v>
-      </c>
-      <c r="B120" s="27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C120" s="27" t="s">
+      <c r="K120" s="53"/>
+    </row>
+    <row r="121" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="28" t="s">
         <v>317</v>
       </c>
-      <c r="D120" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E120" s="27" t="s">
+      <c r="B121" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="F120" s="28" t="n">
+      <c r="C121" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="D121" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E121" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="F121" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G120" s="29" t="n">
+      <c r="G121" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="H120" s="29" t="n">
-        <f aca="false">IF(OR(K120="Yes",K120=TRUE()),0,F120*G120)</f>
+      <c r="H121" s="30" t="n">
+        <f aca="false">IF(OR(K121="Yes",K121=TRUE()),0,F121*G121)</f>
         <v>60</v>
       </c>
-      <c r="I120" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="J120" s="30" t="str">
+      <c r="I121" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="J121" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K120" s="52"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="27" t="s">
-        <v>319</v>
-      </c>
-      <c r="B121" s="27" t="s">
-        <v>320</v>
-      </c>
-      <c r="C121" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D121" s="28" t="s">
+      <c r="K121" s="53"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="28" t="s">
         <v>321</v>
       </c>
-      <c r="E121" s="27" t="s">
+      <c r="B122" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="F121" s="28" t="n">
+      <c r="C122" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D122" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="F122" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G121" s="29" t="n">
+      <c r="G122" s="30" t="n">
         <v>25.99</v>
       </c>
-      <c r="H121" s="29" t="n">
-        <f aca="false">IF(OR(K121="Yes",K121=TRUE()),0,F121*G121)</f>
+      <c r="H122" s="30" t="n">
+        <f aca="false">IF(OR(K122="Yes",K122=TRUE()),0,F122*G122)</f>
         <v>25.99</v>
       </c>
-      <c r="I121" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J121" s="30" t="str">
+      <c r="I122" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="J122" s="31" t="str">
         <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K121" s="52"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="27" t="s">
-        <v>323</v>
-      </c>
-      <c r="B122" s="27" t="s">
-        <v>324</v>
-      </c>
-      <c r="C122" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D122" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E122" s="27" t="s">
+      <c r="K122" s="53"/>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="F122" s="28" t="n">
+      <c r="B123" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C123" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D123" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E123" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F123" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="29" t="n">
+      <c r="G123" s="30" t="n">
         <v>24.97</v>
       </c>
-      <c r="H122" s="29" t="n">
-        <f aca="false">IF(OR(K122="Yes",K122=TRUE()),0,F122*G122)</f>
+      <c r="H123" s="30" t="n">
+        <f aca="false">IF(OR(K123="Yes",K123=TRUE()),0,F123*G123)</f>
         <v>24.97</v>
       </c>
-      <c r="I122" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J122" s="30" t="str">
+      <c r="I123" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J123" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K122" s="52"/>
-    </row>
-    <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="27" t="s">
-        <v>326</v>
-      </c>
-      <c r="B123" s="27" t="s">
+      <c r="K123" s="53"/>
+    </row>
+    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="B124" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="C124" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D124" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E124" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="C123" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D123" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E123" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F123" s="28" t="n">
+      <c r="F124" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G123" s="29" t="n">
+      <c r="G124" s="30" t="n">
         <v>11.99</v>
       </c>
-      <c r="H123" s="29" t="n">
-        <f aca="false">IF(OR(K123="Yes",K123=TRUE()),0,F123*G123)</f>
+      <c r="H124" s="30" t="n">
+        <f aca="false">IF(OR(K124="Yes",K124=TRUE()),0,F124*G124)</f>
         <v>11.99</v>
       </c>
-      <c r="I123" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J123" s="30" t="str">
+      <c r="I124" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J124" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K123" s="52"/>
-    </row>
-    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="B124" s="27" t="s">
-        <v>329</v>
-      </c>
-      <c r="C124" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D124" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E124" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F124" s="28" t="n">
+      <c r="K124" s="53"/>
+    </row>
+    <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B125" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C125" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D125" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E125" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F125" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G124" s="29" t="n">
+      <c r="G125" s="30" t="n">
         <v>25.26</v>
       </c>
-      <c r="H124" s="29" t="n">
-        <f aca="false">IF(OR(K124="Yes",K124=TRUE()),0,F124*G124)</f>
+      <c r="H125" s="30" t="n">
+        <f aca="false">IF(OR(K125="Yes",K125=TRUE()),0,F125*G125)</f>
         <v>25.26</v>
       </c>
-      <c r="I124" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J124" s="30" t="str">
+      <c r="I125" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J125" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K124" s="52"/>
-    </row>
-    <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="27" t="s">
-        <v>330</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>331</v>
-      </c>
-      <c r="C125" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D125" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E125" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F125" s="28" t="n">
+      <c r="K125" s="53"/>
+    </row>
+    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C126" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D126" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E126" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F126" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G125" s="29" t="n">
+      <c r="G126" s="30" t="n">
         <v>32.12</v>
       </c>
-      <c r="H125" s="29" t="n">
-        <f aca="false">IF(OR(K125="Yes",K125=TRUE()),0,F125*G125)</f>
+      <c r="H126" s="30" t="n">
+        <f aca="false">IF(OR(K126="Yes",K126=TRUE()),0,F126*G126)</f>
         <v>32.12</v>
       </c>
-      <c r="I125" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J125" s="30" t="str">
+      <c r="I126" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J126" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K125" s="52"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="27" t="s">
-        <v>332</v>
-      </c>
-      <c r="B126" s="27" t="s">
-        <v>333</v>
-      </c>
-      <c r="C126" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D126" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F126" s="28" t="n">
+      <c r="K126" s="53"/>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>335</v>
+      </c>
+      <c r="C127" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D127" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F127" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G126" s="29" t="n">
+      <c r="G127" s="30" t="n">
         <v>16.98</v>
       </c>
-      <c r="H126" s="29" t="n">
-        <f aca="false">IF(OR(K126="Yes",K126=TRUE()),0,F126*G126)</f>
+      <c r="H127" s="30" t="n">
+        <f aca="false">IF(OR(K127="Yes",K127=TRUE()),0,F127*G127)</f>
         <v>16.98</v>
       </c>
-      <c r="I126" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J126" s="30" t="str">
+      <c r="I127" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J127" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K126" s="52"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="27" t="s">
-        <v>334</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>335</v>
-      </c>
-      <c r="C127" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D127" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F127" s="28" t="n">
+      <c r="K127" s="53"/>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="B128" s="28" t="s">
+        <v>337</v>
+      </c>
+      <c r="C128" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D128" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E128" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F128" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="29" t="n">
+      <c r="G128" s="30" t="n">
         <v>22.31</v>
       </c>
-      <c r="H127" s="29" t="n">
-        <f aca="false">IF(OR(K127="Yes",K127=TRUE()),0,F127*G127)</f>
+      <c r="H128" s="30" t="n">
+        <f aca="false">IF(OR(K128="Yes",K128=TRUE()),0,F128*G128)</f>
         <v>22.31</v>
       </c>
-      <c r="I127" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J127" s="30" t="str">
+      <c r="I128" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J128" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K127" s="52"/>
-    </row>
-    <row r="128" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="27" t="s">
-        <v>336</v>
-      </c>
-      <c r="B128" s="27" t="s">
-        <v>337</v>
-      </c>
-      <c r="C128" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="D128" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="F128" s="28" t="n">
+      <c r="K128" s="53"/>
+    </row>
+    <row r="129" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B129" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="C129" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D129" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E129" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="F129" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G128" s="29" t="n">
+      <c r="G129" s="30" t="n">
         <v>12.17</v>
       </c>
-      <c r="H128" s="29" t="n">
-        <f aca="false">IF(OR(K128="Yes",K128=TRUE()),0,F128*G128)</f>
+      <c r="H129" s="30" t="n">
+        <f aca="false">IF(OR(K129="Yes",K129=TRUE()),0,F129*G129)</f>
         <v>12.17</v>
       </c>
-      <c r="I128" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="J128" s="30" t="str">
+      <c r="I129" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J129" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=precision+tweezers+set","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K128" s="52"/>
-    </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="53" t="s">
-        <v>338</v>
-      </c>
-      <c r="B129" s="54"/>
-      <c r="C129" s="54"/>
-      <c r="D129" s="54"/>
-      <c r="E129" s="54"/>
-      <c r="F129" s="54"/>
-      <c r="G129" s="54"/>
-      <c r="H129" s="55" t="n">
-        <f aca="false">SUM(H114:H128)</f>
+      <c r="K129" s="53"/>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="54" t="s">
+        <v>340</v>
+      </c>
+      <c r="B130" s="55"/>
+      <c r="C130" s="55"/>
+      <c r="D130" s="55"/>
+      <c r="E130" s="55"/>
+      <c r="F130" s="55"/>
+      <c r="G130" s="55"/>
+      <c r="H130" s="56" t="n">
+        <f aca="false">SUM(H115:H129)</f>
         <v>892.26</v>
       </c>
-      <c r="I129" s="54"/>
-      <c r="J129" s="54"/>
-      <c r="K129" s="54"/>
-    </row>
-    <row r="131" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="15"/>
-      <c r="K131" s="15"/>
-    </row>
-    <row r="132" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="B132" s="57" t="s">
+      <c r="I130" s="55"/>
+      <c r="J130" s="55"/>
+      <c r="K130" s="55"/>
+    </row>
+    <row r="132" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="C132" s="58"/>
-      <c r="D132" s="58"/>
-      <c r="E132" s="58"/>
-      <c r="F132" s="58"/>
-      <c r="G132" s="58"/>
-      <c r="H132" s="59" t="n">
-        <f aca="false">H67+IF((K78="Yes"),H103,0)+H129</f>
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="16"/>
+      <c r="I132" s="16"/>
+      <c r="J132" s="16"/>
+      <c r="K132" s="16"/>
+    </row>
+    <row r="133" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="57" t="s">
+        <v>342</v>
+      </c>
+      <c r="B133" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="C133" s="59"/>
+      <c r="D133" s="59"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="59"/>
+      <c r="G133" s="59"/>
+      <c r="H133" s="60" t="n">
+        <f aca="false">H68+IF((K79="Yes"),H104,0)+H130</f>
         <v>2114.035</v>
       </c>
-      <c r="I132" s="58"/>
-      <c r="J132" s="58"/>
-      <c r="K132" s="58"/>
-    </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="56" t="s">
-        <v>196</v>
-      </c>
-      <c r="B133" s="57"/>
-      <c r="C133" s="58"/>
-      <c r="D133" s="58"/>
-      <c r="E133" s="58"/>
-      <c r="F133" s="58"/>
-      <c r="G133" s="58"/>
-      <c r="H133" s="59" t="n">
-        <f aca="false">H73+IF((K78="Yes"),H109,0)</f>
+      <c r="I133" s="59"/>
+      <c r="J133" s="59"/>
+      <c r="K133" s="59"/>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B134" s="58"/>
+      <c r="C134" s="59"/>
+      <c r="D134" s="59"/>
+      <c r="E134" s="59"/>
+      <c r="F134" s="59"/>
+      <c r="G134" s="59"/>
+      <c r="H134" s="60" t="n">
+        <f aca="false">H74+IF((K79="Yes"),H110,0)</f>
         <v>449.74</v>
       </c>
-      <c r="I133" s="58"/>
-      <c r="J133" s="58"/>
-      <c r="K133" s="58"/>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="56" t="s">
+      <c r="I134" s="59"/>
+      <c r="J134" s="59"/>
+      <c r="K134" s="59"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="57" t="s">
+        <v>344</v>
+      </c>
+      <c r="B135" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="C135" s="59"/>
+      <c r="D135" s="59"/>
+      <c r="E135" s="59"/>
+      <c r="F135" s="59"/>
+      <c r="G135" s="59"/>
+      <c r="H135" s="60" t="n">
+        <f aca="false">ROUND(H133*0.0775,2)</f>
+        <v>163.84</v>
+      </c>
+      <c r="I135" s="59"/>
+      <c r="J135" s="59"/>
+      <c r="K135" s="59"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="57" t="s">
+        <v>346</v>
+      </c>
+      <c r="B136" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="C136" s="59"/>
+      <c r="D136" s="59"/>
+      <c r="E136" s="59"/>
+      <c r="F136" s="59"/>
+      <c r="G136" s="59"/>
+      <c r="H136" s="60" t="n">
+        <f aca="false">ROUND((H133+H134+H135)*0.1,2)</f>
+        <v>272.76</v>
+      </c>
+      <c r="I136" s="59"/>
+      <c r="J136" s="59"/>
+      <c r="K136" s="59"/>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B137" s="61"/>
+      <c r="C137" s="12"/>
+      <c r="D137" s="12"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
+      <c r="G137" s="12"/>
+      <c r="H137" s="13" t="n">
+        <f aca="false">H133+H134+H135+H136</f>
+        <v>3000.375</v>
+      </c>
+      <c r="I137" s="12"/>
+      <c r="J137" s="12"/>
+      <c r="K137" s="12"/>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="57" t="s">
+        <v>349</v>
+      </c>
+      <c r="B138" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="C138" s="59"/>
+      <c r="D138" s="59"/>
+      <c r="E138" s="59"/>
+      <c r="F138" s="59"/>
+      <c r="G138" s="59"/>
+      <c r="H138" s="60" t="n">
+        <f aca="false">2000-H137</f>
+        <v>-1000.375</v>
+      </c>
+      <c r="I138" s="59"/>
+      <c r="J138" s="59"/>
+      <c r="K138" s="59"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="62" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B141" s="16"/>
+      <c r="C141" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B134" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="C134" s="58"/>
-      <c r="D134" s="58"/>
-      <c r="E134" s="58"/>
-      <c r="F134" s="58"/>
-      <c r="G134" s="58"/>
-      <c r="H134" s="59" t="n">
-        <f aca="false">ROUND(H132*0.0775,2)</f>
-        <v>163.84</v>
-      </c>
-      <c r="I134" s="58"/>
-      <c r="J134" s="58"/>
-      <c r="K134" s="58"/>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="56" t="s">
-        <v>344</v>
-      </c>
-      <c r="B135" s="57" t="s">
-        <v>345</v>
-      </c>
-      <c r="C135" s="58"/>
-      <c r="D135" s="58"/>
-      <c r="E135" s="58"/>
-      <c r="F135" s="58"/>
-      <c r="G135" s="58"/>
-      <c r="H135" s="59" t="n">
-        <f aca="false">ROUND((H132+H133+H134)*0.1,2)</f>
-        <v>272.76</v>
-      </c>
-      <c r="I135" s="58"/>
-      <c r="J135" s="58"/>
-      <c r="K135" s="58"/>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B136" s="60"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="12"/>
-      <c r="F136" s="12"/>
-      <c r="G136" s="12"/>
-      <c r="H136" s="13" t="n">
-        <f aca="false">H132+H133+H134+H135</f>
-        <v>3000.375</v>
-      </c>
-      <c r="I136" s="12"/>
-      <c r="J136" s="12"/>
-      <c r="K136" s="12"/>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="56" t="s">
-        <v>347</v>
-      </c>
-      <c r="B137" s="57" t="s">
-        <v>348</v>
-      </c>
-      <c r="C137" s="58"/>
-      <c r="D137" s="58"/>
-      <c r="E137" s="58"/>
-      <c r="F137" s="58"/>
-      <c r="G137" s="58"/>
-      <c r="H137" s="59" t="n">
-        <f aca="false">2000-H136</f>
-        <v>-1000.375</v>
-      </c>
-      <c r="I137" s="58"/>
-      <c r="J137" s="58"/>
-      <c r="K137" s="58"/>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="61" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B140" s="15"/>
-      <c r="C140" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="E140" s="62" t="s">
-        <v>352</v>
-      </c>
-      <c r="F140" s="62"/>
-      <c r="G140" s="3" t="s">
+      <c r="D141" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="H140" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15"/>
-      <c r="K140" s="15"/>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="63" t="s">
+      <c r="E141" s="63" t="s">
         <v>354</v>
       </c>
-      <c r="B141" s="63"/>
-      <c r="C141" s="6" t="n">
-        <f aca="false">H67+SUMPRODUCT(F114:F128,G114:G128)-F119*G119</f>
+      <c r="F141" s="63"/>
+      <c r="G141" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I141" s="16"/>
+      <c r="J141" s="16"/>
+      <c r="K141" s="16"/>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="64" t="s">
+        <v>356</v>
+      </c>
+      <c r="B142" s="64"/>
+      <c r="C142" s="6" t="n">
+        <f aca="false">H68+SUMPRODUCT(F115:F129,G115:G129)-F120*G120</f>
         <v>1701.92</v>
       </c>
-      <c r="D141" s="6" t="n">
-        <f aca="false">H73</f>
+      <c r="D142" s="6" t="n">
+        <f aca="false">H74</f>
         <v>281.88</v>
       </c>
-      <c r="E141" s="64" t="n">
-        <f aca="false">ROUND(C141*0.0775,2)</f>
+      <c r="E142" s="65" t="n">
+        <f aca="false">ROUND(C142*0.0775,2)</f>
         <v>131.9</v>
       </c>
-      <c r="F141" s="64"/>
-      <c r="G141" s="6" t="n">
-        <f aca="false">ROUND((C141+D141+E141)*0.1,2)</f>
-        <v>211.57</v>
-      </c>
-      <c r="H141" s="65" t="n">
-        <f aca="false">C141+D141+E141+G141</f>
-        <v>2327.27</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="63" t="s">
-        <v>355</v>
-      </c>
-      <c r="B142" s="63"/>
-      <c r="C142" s="6" t="n">
-        <f aca="false">H67</f>
-        <v>849.66</v>
-      </c>
-      <c r="D142" s="6" t="n">
-        <f aca="false">H73</f>
-        <v>281.88</v>
-      </c>
-      <c r="E142" s="64" t="n">
-        <f aca="false">ROUND(C142*0.0775,2)</f>
-        <v>65.85</v>
-      </c>
-      <c r="F142" s="64"/>
+      <c r="F142" s="65"/>
       <c r="G142" s="6" t="n">
         <f aca="false">ROUND((C142+D142+E142)*0.1,2)</f>
-        <v>119.74</v>
-      </c>
-      <c r="H142" s="65" t="n">
+        <v>211.57</v>
+      </c>
+      <c r="H142" s="66" t="n">
         <f aca="false">C142+D142+E142+G142</f>
-        <v>1317.13</v>
+        <v>2327.27</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="63" t="s">
-        <v>356</v>
-      </c>
-      <c r="B143" s="63"/>
+      <c r="A143" s="64" t="s">
+        <v>357</v>
+      </c>
+      <c r="B143" s="64"/>
       <c r="C143" s="6" t="n">
-        <f aca="false">H67+H103+SUMPRODUCT(F114:F128,G114:G128)</f>
-        <v>2114.035</v>
+        <f aca="false">H68</f>
+        <v>849.66</v>
       </c>
       <c r="D143" s="6" t="n">
-        <f aca="false">H73+H109</f>
-        <v>449.74</v>
-      </c>
-      <c r="E143" s="64" t="n">
+        <f aca="false">H74</f>
+        <v>281.88</v>
+      </c>
+      <c r="E143" s="65" t="n">
         <f aca="false">ROUND(C143*0.0775,2)</f>
-        <v>163.84</v>
-      </c>
-      <c r="F143" s="64"/>
+        <v>65.85</v>
+      </c>
+      <c r="F143" s="65"/>
       <c r="G143" s="6" t="n">
         <f aca="false">ROUND((C143+D143+E143)*0.1,2)</f>
-        <v>272.76</v>
-      </c>
-      <c r="H143" s="65" t="n">
+        <v>119.74</v>
+      </c>
+      <c r="H143" s="66" t="n">
         <f aca="false">C143+D143+E143+G143</f>
-        <v>3000.375</v>
+        <v>1317.13</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="63" t="s">
-        <v>357</v>
-      </c>
-      <c r="B144" s="63"/>
+      <c r="A144" s="64" t="s">
+        <v>358</v>
+      </c>
+      <c r="B144" s="64"/>
       <c r="C144" s="6" t="n">
-        <f aca="false">H67+H103</f>
-        <v>1221.775</v>
+        <f aca="false">H68+H104+SUMPRODUCT(F115:F129,G115:G129)</f>
+        <v>2114.035</v>
       </c>
       <c r="D144" s="6" t="n">
-        <f aca="false">H73+H109</f>
+        <f aca="false">H74+H110</f>
         <v>449.74</v>
       </c>
-      <c r="E144" s="64" t="n">
+      <c r="E144" s="65" t="n">
         <f aca="false">ROUND(C144*0.0775,2)</f>
-        <v>94.69</v>
-      </c>
-      <c r="F144" s="64"/>
+        <v>163.84</v>
+      </c>
+      <c r="F144" s="65"/>
       <c r="G144" s="6" t="n">
         <f aca="false">ROUND((C144+D144+E144)*0.1,2)</f>
+        <v>272.76</v>
+      </c>
+      <c r="H144" s="66" t="n">
+        <f aca="false">C144+D144+E144+G144</f>
+        <v>3000.375</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="64" t="s">
+        <v>359</v>
+      </c>
+      <c r="B145" s="64"/>
+      <c r="C145" s="6" t="n">
+        <f aca="false">H68+H104</f>
+        <v>1221.775</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <f aca="false">H74+H110</f>
+        <v>449.74</v>
+      </c>
+      <c r="E145" s="65" t="n">
+        <f aca="false">ROUND(C145*0.0775,2)</f>
+        <v>94.69</v>
+      </c>
+      <c r="F145" s="65"/>
+      <c r="G145" s="6" t="n">
+        <f aca="false">ROUND((C145+D145+E145)*0.1,2)</f>
         <v>176.62</v>
       </c>
-      <c r="H144" s="65" t="n">
-        <f aca="false">C144+D144+E144+G144</f>
+      <c r="H145" s="66" t="n">
+        <f aca="false">C145+D145+E145+G145</f>
         <v>1942.825</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="35" t="s">
-        <v>358</v>
-      </c>
-      <c r="B145" s="35"/>
-      <c r="C145" s="35"/>
-      <c r="D145" s="35"/>
-      <c r="E145" s="35"/>
-      <c r="F145" s="35"/>
-      <c r="G145" s="35"/>
-      <c r="H145" s="35"/>
-      <c r="I145" s="35"/>
-      <c r="J145" s="35"/>
-      <c r="K145" s="35"/>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="B146" s="37"/>
+      <c r="C146" s="37"/>
+      <c r="D146" s="37"/>
+      <c r="E146" s="37"/>
+      <c r="F146" s="37"/>
+      <c r="G146" s="37"/>
+      <c r="H146" s="37"/>
+      <c r="I146" s="37"/>
+      <c r="J146" s="37"/>
+      <c r="K146" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="36">
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="D6:E6"/>
@@ -5561,16 +5735,15 @@
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B19:K19"/>
-    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B20:K20"/>
     <mergeCell ref="B71:E71"/>
     <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B74:K74"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B75:K75"/>
+    <mergeCell ref="A78:K78"/>
     <mergeCell ref="B107:E107"/>
     <mergeCell ref="B108:E108"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="B109:E109"/>
     <mergeCell ref="E141:F141"/>
     <mergeCell ref="A142:B142"/>
     <mergeCell ref="E142:F142"/>
@@ -5578,18 +5751,224 @@
     <mergeCell ref="E143:F143"/>
     <mergeCell ref="A144:B144"/>
     <mergeCell ref="E144:F144"/>
-    <mergeCell ref="A145:K145"/>
+    <mergeCell ref="A145:B145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="A146:K146"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K78" type="list">
+  <conditionalFormatting sqref="A24:J24">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K24="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28:J28">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K28="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:J29">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K29="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30:J30">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K30="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31:J31">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K31="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35:J35">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K35="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36:J36">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K36="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37:J37">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K37="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38:J38">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K38="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A42:J42">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K42="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A43:J43">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K43="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A44:J44">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K44="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45:J45">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K45="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46:J46">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K46="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50:J50">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K50="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51:J51">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K51="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52:J52">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K52="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53:J53">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K53="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54:J54">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K54="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58:J58">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K58="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62:J62">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K62="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A63:J63">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K63="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64:J64">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K64="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65:J65">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K65="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A82:J82">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K82="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A84:J84">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K84="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A85:J85">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K85="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A86:J86">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K86="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A87:J87">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K87="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A88:J88">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K88="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A89:J89">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K89="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A90:J90">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K90="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A91:J91">
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K91="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A92:J92">
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K92="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A93:J93">
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K93="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A95:J95">
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K95="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A96:J96">
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K96="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A97:J97">
+    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K97="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A99:J99">
+    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K99="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A100:J100">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K100="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K79" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K101:K102" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K102:K103" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K114:K128" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K115:K129" type="list">
+      <formula1>"Yes,No"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24 K28:K31 K35:K38 K42:K46 K50:K54 K58 K62:K65 K82 K84:K93 K95:K97 K99:K100" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="427">
   <si>
     <t xml:space="preserve">STM v1: what it actually cost</t>
   </si>
@@ -299,6 +299,21 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
+    <t xml:space="preserve">Small piezo discs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smaller (12 mm) version of the piezo disc above, to try in the scanner. Pack of 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Smaller discs move in finer steps and vibrate less; most successful home-built microscopes used discs this size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7BB-12-9 type, 12 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate</t>
+  </si>
+  <si>
     <t xml:space="preserve">2. Sample approach: brings the sample up to the tip</t>
   </si>
   <si>
@@ -359,6 +374,57 @@
     <t xml:space="preserve">F25SSN1</t>
   </si>
   <si>
+    <t xml:space="preserve">Approach springs and force gauge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel springs that press the sample holder onto its three screws, and a small gauge to set how hard they press.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Replace v1's rubber bands, which stretched and let the sample move.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel springs + small push-pull force gauge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flexible motor coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connects the motor to the adjustment screw while letting the screw float, so the motor does not push the sample sideways.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. A rigid link bends the screw as it turns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flexible shaft coupling, 5 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual sideways stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small hand-adjusted slide that moves the tip sideways onto a clean area of the sample, watched through the USB microscope (section 9).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 could only land the tip wherever it happened to be.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small manual XY linear stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backup approach parts (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parts for a different way of bringing the sample up (a piezo 'stick-slip' slider), only if the motor and screw do not work well enough. Starts as No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Backup recommended by our design review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">piezo stack + miniature slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
     <t xml:space="preserve">3. Main electronics: run the microscope and record the image</t>
   </si>
   <si>
@@ -410,6 +476,18 @@
     <t xml:space="preserve">Teensy 4.1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test resistors (dummy tip)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistors and capacitors that imitate the tip and sample, so the control software can be tuned before a real tip goes near the sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 tuned its control on the real tip, which risked crashing it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resistor and capacitor assortment</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. Signal amplifier: reads the tiny tip current</t>
   </si>
   <si>
@@ -461,7 +539,19 @@
     <t xml:space="preserve">Kirecoo copper foil tape, 2 in x 33 ft</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Frame and sample holder</t>
+    <t xml:space="preserve">Second high-value resistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 100 megaohm resistor so the signal amplifier can switch between two strengths: the stronger setting for the careful approach, this one for faster imaging. 1 plus 1 spare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Recommended by our design studies so scans are not limited to slow speeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 megaohm resistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Frame, sample holder and vibration isolation</t>
   </si>
   <si>
     <t xml:space="preserve">3D printer filament</t>
@@ -515,37 +605,166 @@
     <t xml:space="preserve">TRYMAG small neodymium magnets</t>
   </si>
   <si>
-    <t xml:space="preserve">Vibration pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rubber pads under the microscope that absorb building vibration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Replace v1's spring-hung platform.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isolate It</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorbothane 6x6 in, 2-pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Temperature sensors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Temperature sensors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Record the temperature at two points on the microscope. 2 sensors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Show whether slow drift in the image is caused by temperature changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4821 (TMP117)</t>
+    <t xml:space="preserve">Vibration springs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Three long steel springs hang the microscope's platform from its frame so building vibration does not reach the tip. Two packs of 2: 3 used plus 1 spare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed. v1 hung its platform the same way; v2 adjusts the load so the springs isolate better. Replaces the rubber pads in the earlier budget, which our vibration study found would make some vibrations worse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOCMKEAS 304 stainless, 0.5 x 3 x 300 mm, 2 packs of 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spring sleeves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thin tubing slipped over the hanging springs to stop them ringing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Damps the springs' own vibration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silicone tubing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damper magnets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong bar magnets fixed below the hanging platform. Together with the aluminium plate they stop the platform swinging after a bump, without touching it. Two packs of 12.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed. v1 had 12; v2 uses 24 for stronger damping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neodymium bar magnets 60 x 10 x 3 mm, pack of 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damper plate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminium disc on the underside of the platform that the magnets act on.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uxcell 6061 aluminium disc 150 x 6 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frame rods and nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Four stainless steel threaded rods and nuts that form the tower the platform hangs from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as v1. v1's rods stay with v1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M8 x 400 mm stainless rods (4) + M8 nuts (25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel weights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel plates bolted under the platform to bring the hanging weight to 1.5 to 2 kg, the load at which the springs isolate best.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 used loose coins, which can shift and cause small jumps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel plate or bar offcuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steel box lined with foam that covers the whole microscope. Blocks sound and electrical noise and keeps the temperature steady.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 had no cover, so sound, air currents and temperature changes all reached the tip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel box or tin with foam lining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aluminium shield can</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small aluminium can that fits over the scanning head inside the enclosure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. A second layer of shielding and temperature protection around the most sensitive part.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small aluminium enclosure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metal head and sample plates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stainless steel plates, laser cut by an online service from our drawings: one holds the tip and scanner, the other holds the sample. No machining needed by us. Price needs a quote once the drawings are uploaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Stiffer than v1's printed plastic and keeps its shape as the room warms and cools. Our studies found this the biggest single improvement for steady scans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SendCutSend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laser-cut stainless steel plates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ball seats and clamping hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened steel seats under the three steel balls, and small parts that let magnets clamp the sample holder down firmly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Stop the balls denting the plastic, so the sample holder stays put.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hardened seats and clamping hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Temperature and humidity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature and humidity logger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stand-alone recorder inside the enclosure that logs temperature and humidity during every scan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed. Replaces the two sensors wired to the microcontroller in the earlier budget; it works on its own and needs no wiring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">temperature and humidity data logger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silica gel and sealed box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drying beads and an airtight box, for testing whether damp air affects the tip current.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Moist air can leave a thin water film between tip and sample.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silica gel packs + airtight container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap sensor (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small chip that measures the tip-to-sample distance electrically, as an independent check on the scanner. Starts as No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional extra from our design review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDC1004 sensor board</t>
   </si>
   <si>
     <t xml:space="preserve">7. Batteries: the microscope runs on batteries, not wall power</t>
@@ -608,7 +827,7 @@
     <t xml:space="preserve">Shipping and import fees for sections 1 to 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Isolate It $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards. A seller's shipping drops out if nothing from that seller is funded.</t>
+    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards. A seller's shipping drops out if nothing from that seller is funded.</t>
   </si>
   <si>
     <t xml:space="preserve">Import tariff on circuit boards</t>
@@ -632,7 +851,7 @@
     <t xml:space="preserve">8. Optional upgrade: piezo tube scanner</t>
   </si>
   <si>
-    <t xml:space="preserve">Prof. Vasquez suggested replacing the flat piezo disc (section 1) with a piezo tube, which should give steadier scans. Our own study agrees, but recommends first fixing how the sample is held and checking temperature effects, because those cause most of v1's unsteadiness. The microscope works without this section. Set the switch to Yes to include it in the total, or No to leave it out.</t>
+    <t xml:space="preserve">Prof. Vasquez suggested replacing the flat piezo disc (section 1) with a piezo tube, which should give steadier scans. Our own study agrees, but recommends first fixing how the sample is held and checking temperature effects, because those cause most of v1's unsteadiness. The microscope works without this section. Our studies recommend building without it first, so it starts switched off. Set the switch to Yes to include it in the total, or No to leave it out.</t>
   </si>
   <si>
     <t xml:space="preserve">Include this upgrade in the total?</t>
@@ -779,6 +998,18 @@
     <t xml:space="preserve">M3 heat-set inserts and screws</t>
   </si>
   <si>
+    <t xml:space="preserve">Capacitance meter (LCR meter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handheld meter for checking the tube's electrical contacts before and after wiring.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Confirms the tube was not damaged during assembly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">handheld LCR meter, 1 kHz</t>
+  </si>
+  <si>
     <t xml:space="preserve">High-voltage driver: powers the tube</t>
   </si>
   <si>
@@ -845,24 +1076,6 @@
     <t xml:space="preserve">New. Recommended by our piezo study.</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metal head plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aluminium plate, cut and drilled by an outside shop, that holds the tube more rigidly than printed plastic. Needs machining, which the rest of v2 avoids; price needs a quote.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Metal keeps its shape better than plastic as the room warms and cools.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SendCutSend or similar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aluminium blank, cut and drilled</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upgrade parts</t>
   </si>
   <si>
@@ -893,19 +1106,19 @@
     <t xml:space="preserve">From UCSD?</t>
   </si>
   <si>
-    <t xml:space="preserve">Scanning tips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 ready-made platinum-iridium tips. The tip is the needle that scans the sample; this metal stays sharp in air.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changed. v1 made its own tips from tungsten wire, which corrodes in air.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bruker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPT10</t>
+    <t xml:space="preserve">Tip wire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platinum-iridium wire, 0.25 mm thick. Each tip is cut from it with scissors; this metal stays sharp in air. Enough for dozens of tips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed. v1 made its tips from tungsten wire, which corrodes in air. Replaces ready-made tips in the earlier budget at about the same price but many more tips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pt80/Ir20 wire, 0.25 mm, 0.2 m</t>
   </si>
   <si>
     <t xml:space="preserve">Graphite test sample</t>
@@ -938,19 +1151,16 @@
     <t xml:space="preserve">8331D-14G</t>
   </si>
   <si>
-    <t xml:space="preserve">Heavy stone base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granite slab, 9 x 12 in, under the microscope. Its weight damps vibration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Extra protection against vibration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penn Tool Co</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grizzly G9649</t>
+    <t xml:space="preserve">USB microscope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small camera-microscope with a calibration slide, for checking the tip's shape, aiming it at the sample, and measuring the scanner's lever arm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 had no way to inspect the tip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB microscope with calibration slide</t>
   </si>
   <si>
     <t xml:space="preserve">Handheld instrument for checking electrical signals while building and testing.</t>
@@ -962,18 +1172,6 @@
     <t xml:space="preserve">FNIRSI DST-201</t>
   </si>
   <si>
-    <t xml:space="preserve">Capacitance meter (LCR meter)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handheld meter for checking the tube's electrical contacts before and after wiring. Counted only when section 8 is switched on.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Confirms the tube was not damaged during assembly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">handheld LCR meter, 1 kHz</t>
-  </si>
-  <si>
     <t xml:space="preserve">Laser calibration parts</t>
   </si>
   <si>
@@ -1103,7 +1301,7 @@
     <t xml:space="preserve">With the upgrade, UCSD supplies everything</t>
   </si>
   <si>
-    <t xml:space="preserve">All four cases follow the Fund? choices made in the sheet. The upgrade cases include the optional extras as currently chosen in section 8 (spare tube and metal plate are No unless changed).</t>
+    <t xml:space="preserve">All four cases follow the Fund? choices made in the sheet. The upgrade cases include the optional extras as currently chosen in section 8 (the spare tube is No unless changed).</t>
   </si>
 </sst>
 </file>
@@ -2375,7 +2573,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -2428,12 +2626,12 @@
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="20" t="n">
-        <f aca="false">H142</f>
-        <v>2327.27</v>
+        <f aca="false">H159</f>
+        <v>2634.65</v>
       </c>
       <c r="D6" s="21" t="n">
-        <f aca="false">H143</f>
-        <v>1317.13</v>
+        <f aca="false">H160</f>
+        <v>1687.75</v>
       </c>
       <c r="E6" s="21"/>
     </row>
@@ -2443,12 +2641,12 @@
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="20" t="n">
-        <f aca="false">H144</f>
-        <v>3000.375</v>
+        <f aca="false">H161</f>
+        <v>3307.765</v>
       </c>
       <c r="D7" s="21" t="n">
-        <f aca="false">H145</f>
-        <v>1942.825</v>
+        <f aca="false">H162</f>
+        <v>2360.855</v>
       </c>
       <c r="E7" s="21"/>
     </row>
@@ -2458,8 +2656,8 @@
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="23" t="n">
-        <f aca="false">H137</f>
-        <v>3000.375</v>
+        <f aca="false">H154</f>
+        <v>2634.65</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
@@ -2721,88 +2919,88 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+    <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H25" s="30" t="n">
+        <f aca="false">IF(K25="No",0,F25*G25)</f>
+        <v>8</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=7BB-12-9+piezo+12mm","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K25" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9" t="n">
-        <f aca="false">SUM(H24:H24)</f>
-        <v>5</v>
-      </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="28" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="28" t="s">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9" t="n">
+        <f aca="false">SUM(H24:H25)</f>
+        <v>13</v>
+      </c>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="H28" s="30" t="n">
-        <f aca="false">IF(K28="No",0,F28*G28)</f>
-        <v>14</v>
-      </c>
-      <c r="I28" s="29" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="J28" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K28" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="s">
+      <c r="B29" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="C29" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="D29" s="29" t="s">
         <v>101</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>96</v>
       </c>
       <c r="E29" s="28" t="s">
         <v>102</v>
@@ -2811,61 +3009,61 @@
         <v>1</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>8.95</v>
+        <v>14</v>
       </c>
       <c r="H29" s="30" t="n">
         <f aca="false">IF(K29="No",0,F29*G29)</f>
-        <v>8.95</v>
+        <v>14</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J29" s="31" t="str">
-        <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
         <v>Open</v>
       </c>
       <c r="K29" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E30" s="28" t="s">
         <v>107</v>
       </c>
       <c r="F30" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>8</v>
+        <v>8.95</v>
       </c>
       <c r="H30" s="30" t="n">
         <f aca="false">IF(K30="No",0,F30*G30)</f>
-        <v>24</v>
+        <v>8.95</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J30" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
+        <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
         <v>Open</v>
       </c>
       <c r="K30" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
         <v>108</v>
       </c>
@@ -2876,96 +3074,174 @@
         <v>110</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="29" t="n">
         <v>3</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H31" s="30" t="n">
         <f aca="false">IF(K31="No",0,F31*G31)</f>
-        <v>25.8</v>
+        <v>24</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J31" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
+        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
         <v>Open</v>
       </c>
       <c r="K31" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <f aca="false">IF(K32="No",0,F32*G32)</f>
+        <v>25.8</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9" t="n">
-        <f aca="false">SUM(H28:H31)</f>
-        <v>72.75</v>
-      </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
+      <c r="H33" s="30" t="n">
+        <f aca="false">IF(K33="No",0,F33*G33)</f>
+        <v>15</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=push+pull+force+gauge+small","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K33" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" s="30" t="n">
+        <f aca="false">IF(K34="No",0,F34*G34)</f>
+        <v>12</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J34" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=flexible+shaft+coupling+5mm","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K34" s="32" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="28" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F35" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>209.64</v>
+        <v>40</v>
       </c>
       <c r="H35" s="30" t="n">
         <f aca="false">IF(K35="No",0,F35*G35)</f>
-        <v>419.28</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>90</v>
+        <v>40</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J35" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=manual+xy+linear+stage+40mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K35" s="32" t="s">
@@ -2974,397 +3250,397 @@
     </row>
     <row r="36" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F36" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>1.68</v>
+        <v>70</v>
       </c>
       <c r="H36" s="30" t="n">
         <f aca="false">IF(K36="No",0,F36*G36)</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=piezo+stack+actuator+5x5mm","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K36" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="9" t="n">
+        <f aca="false">SUM(H29:H36)</f>
+        <v>139.75</v>
+      </c>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+    </row>
+    <row r="40" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F40" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="30" t="n">
+        <v>209.64</v>
+      </c>
+      <c r="H40" s="30" t="n">
+        <f aca="false">IF(K40="No",0,F40*G40)</f>
+        <v>419.28</v>
+      </c>
+      <c r="I40" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J40" s="31" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K40" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H41" s="30" t="n">
+        <f aca="false">IF(K41="No",0,F41*G41)</f>
         <v>5.04</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I41" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J36" s="31" t="str">
+      <c r="J41" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K36" s="32" t="s">
+      <c r="K41" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="28" t="s">
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="F37" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="30" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="H37" s="30" t="n">
-        <f aca="false">IF(K37="No",0,F37*G37)</f>
-        <v>36.52</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J37" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K37" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="F38" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="30" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H38" s="30" t="n">
-        <f aca="false">IF(K38="No",0,F38*G38)</f>
-        <v>31.5</v>
-      </c>
-      <c r="I38" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J38" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K38" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="9" t="n">
-        <f aca="false">SUM(H35:H38)</f>
-        <v>492.34</v>
-      </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-    </row>
-    <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-    </row>
-    <row r="42" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>132</v>
-      </c>
       <c r="D42" s="29" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F42" s="29" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>30.17</v>
+        <v>18.26</v>
       </c>
       <c r="H42" s="30" t="n">
         <f aca="false">IF(K42="No",0,F42*G42)</f>
-        <v>60.34</v>
+        <v>36.52</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J42" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
         <v>Open</v>
       </c>
       <c r="K42" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="28" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="C43" s="28" t="s">
         <v>87</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="F43" s="29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>0.8</v>
+        <v>31.5</v>
       </c>
       <c r="H43" s="30" t="n">
         <f aca="false">IF(K43="No",0,F43*G43)</f>
-        <v>2.4</v>
+        <v>31.5</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="J43" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
         <v>Open</v>
       </c>
       <c r="K43" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="28" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E44" s="28" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>5.73</v>
+        <v>15</v>
       </c>
       <c r="H44" s="30" t="n">
         <f aca="false">IF(K44="No",0,F44*G44)</f>
-        <v>11.46</v>
-      </c>
-      <c r="I44" s="29" t="s">
-        <v>98</v>
+        <v>15</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J44" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=high+value+resistor+assortment+100M","Open")</f>
         <v>Open</v>
       </c>
       <c r="K44" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="C45" s="28" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="9" t="n">
+        <f aca="false">SUM(H40:H44)</f>
+        <v>507.34</v>
+      </c>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+    </row>
+    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>30.17</v>
+      </c>
+      <c r="H48" s="30" t="n">
+        <f aca="false">IF(K48="No",0,F48*G48)</f>
+        <v>60.34</v>
+      </c>
+      <c r="I48" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J48" s="31" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K48" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="D45" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="F45" s="29" t="n">
+      <c r="D49" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="F49" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" s="30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H49" s="30" t="n">
+        <f aca="false">IF(K49="No",0,F49*G49)</f>
+        <v>2.4</v>
+      </c>
+      <c r="I49" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J49" s="31" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F50" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="30" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H45" s="30" t="n">
-        <f aca="false">IF(K45="No",0,F45*G45)</f>
-        <v>4.18</v>
-      </c>
-      <c r="I45" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J45" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K45" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="30" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="H46" s="30" t="n">
-        <f aca="false">IF(K46="No",0,F46*G46)</f>
-        <v>7.99</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J46" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K46" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="9" t="n">
-        <f aca="false">SUM(H42:H46)</f>
-        <v>86.37</v>
-      </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-    </row>
-    <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="5"/>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="F50" s="29" t="n">
-        <v>1</v>
-      </c>
       <c r="G50" s="30" t="n">
-        <v>19.99</v>
+        <v>5.73</v>
       </c>
       <c r="H50" s="30" t="n">
         <f aca="false">IF(K50="No",0,F50*G50)</f>
-        <v>19.99</v>
+        <v>11.46</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J50" s="31" t="str">
-        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
         <v>Open</v>
       </c>
       <c r="K50" s="32" t="s">
@@ -3373,35 +3649,35 @@
     </row>
     <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="28" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F51" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="30" t="n">
-        <v>9.99</v>
+        <v>2.09</v>
       </c>
       <c r="H51" s="30" t="n">
         <f aca="false">IF(K51="No",0,F51*G51)</f>
-        <v>9.99</v>
+        <v>4.18</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J51" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
         <v>Open</v>
       </c>
       <c r="K51" s="32" t="s">
@@ -3410,1224 +3686,1212 @@
     </row>
     <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="28" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="E52" s="28" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F52" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>30</v>
+        <v>7.99</v>
       </c>
       <c r="H52" s="30" t="n">
         <f aca="false">IF(K52="No",0,F52*G52)</f>
-        <v>30</v>
+        <v>7.99</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J52" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
         <v>Open</v>
       </c>
       <c r="K52" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="28" t="s">
-        <v>33</v>
+        <v>172</v>
       </c>
       <c r="B53" s="28" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="F53" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>9.49</v>
+        <v>3</v>
       </c>
       <c r="H53" s="30" t="n">
         <f aca="false">IF(K53="No",0,F53*G53)</f>
-        <v>9.49</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>98</v>
+        <v>6</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J53" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/result?keywords=100M%20ohm%20resistor","Open")</f>
         <v>Open</v>
       </c>
       <c r="K53" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="C54" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="E54" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="F54" s="29" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="9" t="n">
+        <f aca="false">SUM(H48:H53)</f>
+        <v>92.37</v>
+      </c>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+    </row>
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+    </row>
+    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C57" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F57" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G54" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="H54" s="30" t="n">
-        <f aca="false">IF(K54="No",0,F54*G54)</f>
-        <v>35</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J54" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.isolateit.com/products/sorbothane-acoustic-and-vibration-isolation-square-6-x-6-pads","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K54" s="32" t="s">
+      <c r="G57" s="30" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H57" s="30" t="n">
+        <f aca="false">IF(K57="No",0,F57*G57)</f>
+        <v>19.99</v>
+      </c>
+      <c r="I57" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J57" s="31" t="str">
+        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K57" s="32" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="9" t="n">
-        <f aca="false">SUM(H50:H54)</f>
-        <v>104.47</v>
-      </c>
-      <c r="I55" s="8"/>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-    </row>
-    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
-      <c r="K57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="28" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B58" s="28" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F58" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>11.5</v>
+        <v>9.99</v>
       </c>
       <c r="H58" s="30" t="n">
         <f aca="false">IF(K58="No",0,F58*G58)</f>
-        <v>23</v>
+        <v>9.99</v>
       </c>
       <c r="I58" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J58" s="31" t="str">
-        <f aca="false">HYPERLINK("https://adafruit.com/product/4821","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
         <v>Open</v>
       </c>
       <c r="K58" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="9" t="n">
-        <f aca="false">SUM(H58:H58)</f>
-        <v>23</v>
-      </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-    </row>
-    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
-      <c r="K61" s="5"/>
-    </row>
-    <row r="62" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" s="30" t="n">
+        <f aca="false">IF(K59="No",0,F59*G59)</f>
+        <v>30</v>
+      </c>
+      <c r="I59" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J59" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K59" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="F60" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <f aca="false">IF(K60="No",0,F60*G60)</f>
+        <v>9.49</v>
+      </c>
+      <c r="I60" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J60" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K60" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="F61" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" s="30" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="H61" s="30" t="n">
+        <f aca="false">IF(K61="No",0,F61*G61)</f>
+        <v>27.98</v>
+      </c>
+      <c r="I61" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="J61" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/dp/B0F4CCYHL2","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K61" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="28" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="B62" s="28" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="F62" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="30" t="n">
-        <v>21.39</v>
+        <v>3</v>
       </c>
       <c r="H62" s="30" t="n">
         <f aca="false">IF(K62="No",0,F62*G62)</f>
-        <v>42.78</v>
-      </c>
-      <c r="I62" s="29" t="s">
-        <v>98</v>
+        <v>3</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J62" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silicone+tubing+small","Open")</f>
         <v>Open</v>
       </c>
       <c r="K62" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="28" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="B63" s="28" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="F63" s="29" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>0.61</v>
+        <v>8.99</v>
       </c>
       <c r="H63" s="30" t="n">
         <f aca="false">IF(K63="No",0,F63*G63)</f>
-        <v>6.1</v>
+        <v>17.98</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J63" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=neodymium+bar+magnets+60x10x3mm+12+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K63" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="28" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="B64" s="28" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="E64" s="28" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="F64" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="30" t="n">
-        <v>10.95</v>
+        <v>19.79</v>
       </c>
       <c r="H64" s="30" t="n">
         <f aca="false">IF(K64="No",0,F64*G64)</f>
-        <v>10.95</v>
+        <v>19.79</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J64" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+6061+aluminum+round+disc+150mm+6mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K64" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="28" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B65" s="28" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="F65" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>2.95</v>
+        <v>22.78</v>
       </c>
       <c r="H65" s="30" t="n">
         <f aca="false">IF(K65="No",0,F65*G65)</f>
-        <v>5.9</v>
+        <v>22.78</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="J65" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M8+x+400mm+stainless+steel+threaded+rod+4+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K65" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="7" t="s">
+    <row r="66" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="B66" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H66" s="30" t="n">
+        <f aca="false">IF(K66="No",0,F66*G66)</f>
+        <v>10</v>
+      </c>
+      <c r="I66" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J66" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.homedepot.com/s/steel%20plate","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K66" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="28" t="s">
+        <v>218</v>
+      </c>
+      <c r="B67" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="F67" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" s="30" t="n">
+        <f aca="false">IF(K67="No",0,F67*G67)</f>
+        <v>30</v>
+      </c>
+      <c r="I67" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J67" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=large+metal+storage+tin+with+lid","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K67" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="D68" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="F68" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="30" t="n">
+        <v>22</v>
+      </c>
+      <c r="H68" s="30" t="n">
+        <f aca="false">IF(K68="No",0,F68*G68)</f>
+        <v>22</v>
+      </c>
+      <c r="I68" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J68" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=aluminum+project+box+enclosure","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K68" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="B69" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C69" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="E69" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="F69" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="H69" s="30" t="n">
+        <f aca="false">IF(K69="No",0,F69*G69)</f>
+        <v>80</v>
+      </c>
+      <c r="I69" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J69" s="31" t="str">
+        <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K69" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="B70" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="C70" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E70" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="F70" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="9" t="n">
-        <f aca="false">SUM(H62:H65)</f>
-        <v>65.73</v>
-      </c>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="36" t="n">
-        <f aca="false">H25+H32+H39+H47+H55+H59+H66</f>
-        <v>849.66</v>
-      </c>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="35"/>
-    </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-    </row>
-    <row r="71" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="H71" s="30" t="n">
-        <f aca="false">IF(SUM(H28+H29+H58+H65)&gt;0,10,0)+IF(SUM(H30+H31)&gt;0,15.26,0)+IF(SUM(H35+H36+H42+H43)&gt;0,25,0)+IF(SUM(H37+H44+H45+H63)&gt;0,8.49,0)+IF(SUM(H38)&gt;0,8,0)+IF(SUM(H50)&gt;0,5,0)+IF(SUM(H52)&gt;0,15,0)+IF(SUM(H54)&gt;0,10,0)+IF(SUM(H62+H64)&gt;0,10,0)</f>
-        <v>106.75</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="B72" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="H72" s="30" t="n">
-        <f aca="false">ROUND(0.35*(H35+H36+H42+H43),2)</f>
-        <v>170.47</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B73" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="H73" s="30" t="n">
-        <f aca="false">ROUND(0.08*(H37+H44+H45+H63),2)</f>
-        <v>4.66</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="B74" s="35"/>
-      <c r="C74" s="35"/>
-      <c r="D74" s="35"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="36" t="n">
-        <f aca="false">SUM(H71:H73)</f>
-        <v>281.88</v>
-      </c>
-      <c r="I74" s="35"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="35"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B75" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37"/>
-      <c r="I75" s="37"/>
-      <c r="J75" s="37"/>
-      <c r="K75" s="37"/>
-    </row>
-    <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="B77" s="39"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
-      <c r="G77" s="39"/>
-      <c r="H77" s="39"/>
-      <c r="I77" s="39"/>
-      <c r="J77" s="39"/>
-      <c r="K77" s="39"/>
-    </row>
-    <row r="78" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
-    </row>
-    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="B79" s="41"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41"/>
-      <c r="I79" s="42" t="s">
-        <v>205</v>
-      </c>
-      <c r="J79" s="41"/>
-      <c r="K79" s="43" t="s">
+      <c r="H70" s="30" t="n">
+        <f aca="false">IF(K70="No",0,F70*G70)</f>
+        <v>15</v>
+      </c>
+      <c r="I70" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J70" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=hardened+steel+dowel+pin+assortment","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K70" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="44" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="9" t="n">
+        <f aca="false">SUM(H57:H70)</f>
+        <v>318</v>
+      </c>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+    </row>
+    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+    </row>
+    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B74" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="D74" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E74" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H74" s="30" t="n">
+        <f aca="false">IF(K74="No",0,F74*G74)</f>
+        <v>25</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J74" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=temperature+humidity+data+logger+USB","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K74" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="B75" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C75" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D75" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="F75" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" s="30" t="n">
+        <f aca="false">IF(K75="No",0,F75*G75)</f>
+        <v>10</v>
+      </c>
+      <c r="I75" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J75" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silica+gel+packets+airtight+container","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K75" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="B76" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="C76" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E76" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="F76" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H76" s="30" t="n">
+        <f aca="false">IF(K76="No",0,F76*G76)</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J76" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FDC1004+breakout+board","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K76" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="9" t="n">
+        <f aca="false">SUM(H74:H76)</f>
+        <v>35</v>
+      </c>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+    </row>
+    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+    </row>
+    <row r="80" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="B80" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="C80" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>252</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="F80" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B80" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="E80" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="F80" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="G80" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="H80" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="I80" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="J80" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="K80" s="44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="B81" s="41"/>
-      <c r="C81" s="41"/>
-      <c r="D81" s="41"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="41"/>
-      <c r="I81" s="41"/>
-      <c r="J81" s="41"/>
-      <c r="K81" s="41"/>
-    </row>
-    <row r="82" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G80" s="30" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="H80" s="30" t="n">
+        <f aca="false">IF(K80="No",0,F80*G80)</f>
+        <v>42.78</v>
+      </c>
+      <c r="I80" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J80" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K80" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="B81" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="C81" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="D81" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" s="30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H81" s="30" t="n">
+        <f aca="false">IF(K81="No",0,F81*G81)</f>
+        <v>6.1</v>
+      </c>
+      <c r="I81" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J81" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K81" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="28" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="B82" s="28" t="s">
-        <v>207</v>
+        <v>259</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="F82" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>131</v>
+        <v>10.95</v>
       </c>
       <c r="H82" s="30" t="n">
         <f aca="false">IF(K82="No",0,F82*G82)</f>
-        <v>131</v>
+        <v>10.95</v>
       </c>
       <c r="I82" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J82" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
         <v>Open</v>
       </c>
       <c r="K82" s="32" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="B83" s="41"/>
-      <c r="C83" s="41"/>
-      <c r="D83" s="41"/>
-      <c r="E83" s="41"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41"/>
-      <c r="I83" s="41"/>
-      <c r="J83" s="41"/>
-      <c r="K83" s="41"/>
-    </row>
-    <row r="84" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="B84" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="C84" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="D84" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="F84" s="29" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B83" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C83" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="D83" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="F83" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H83" s="30" t="n">
+        <f aca="false">IF(K83="No",0,F83*G83)</f>
+        <v>5.9</v>
+      </c>
+      <c r="I83" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J83" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K83" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="9" t="n">
+        <f aca="false">SUM(H80:H83)</f>
+        <v>65.73</v>
+      </c>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="B86" s="35"/>
+      <c r="C86" s="35"/>
+      <c r="D86" s="35"/>
+      <c r="E86" s="35"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="36" t="n">
+        <f aca="false">H26+H37+H45+H54+H71+H77+H84</f>
+        <v>1171.19</v>
+      </c>
+      <c r="I86" s="35"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="35"/>
+    </row>
+    <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="H89" s="30" t="n">
+        <f aca="false">IF(SUM(H29+H30+H83)&gt;0,10,0)+IF(SUM(H31+H32)&gt;0,15.26,0)+IF(SUM(H40+H41+H48+H49)&gt;0,25,0)+IF(SUM(H42+H50+H51+H53+H81)&gt;0,8.49,0)+IF(SUM(H43)&gt;0,8,0)+IF(SUM(H57)&gt;0,5,0)+IF(SUM(H59)&gt;0,15,0)+IF(SUM(H80+H82)&gt;0,10,0)</f>
+        <v>96.75</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="H90" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H40+H41+H48+H49),2)</f>
+        <v>170.47</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="H91" s="30" t="n">
+        <f aca="false">ROUND(0.08*(H42+H50+H51+H53+H81),2)</f>
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="36" t="n">
+        <f aca="false">SUM(H89:H91)</f>
+        <v>272.36</v>
+      </c>
+      <c r="I92" s="35"/>
+      <c r="J92" s="35"/>
+      <c r="K92" s="35"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B93" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="37"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="37"/>
+      <c r="H93" s="37"/>
+      <c r="I93" s="37"/>
+      <c r="J93" s="37"/>
+      <c r="K93" s="37"/>
+    </row>
+    <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="B95" s="39"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="39"/>
+      <c r="F95" s="39"/>
+      <c r="G95" s="39"/>
+      <c r="H95" s="39"/>
+      <c r="I95" s="39"/>
+      <c r="J95" s="39"/>
+      <c r="K95" s="39"/>
+    </row>
+    <row r="96" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="B96" s="27"/>
+      <c r="C96" s="27"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="27"/>
+      <c r="I96" s="27"/>
+      <c r="J96" s="27"/>
+      <c r="K96" s="27"/>
+    </row>
+    <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="B97" s="41"/>
+      <c r="C97" s="41"/>
+      <c r="D97" s="41"/>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+      <c r="H97" s="41"/>
+      <c r="I97" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="J97" s="41"/>
+      <c r="K97" s="43" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B98" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D98" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="E98" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F98" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="G98" s="44" t="s">
+        <v>81</v>
+      </c>
+      <c r="H98" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="I98" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="J98" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="K98" s="44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="45" t="s">
+        <v>279</v>
+      </c>
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="41"/>
+      <c r="H99" s="41"/>
+      <c r="I99" s="41"/>
+      <c r="J99" s="41"/>
+      <c r="K99" s="41"/>
+    </row>
+    <row r="100" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C100" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="D100" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="E100" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="F100" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="H84" s="30" t="n">
-        <f aca="false">IF(K84="No",0,F84*G84)</f>
-        <v>35</v>
-      </c>
-      <c r="I84" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J84" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K84" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="B85" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="C85" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="D85" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E85" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="F85" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="H85" s="30" t="n">
-        <f aca="false">IF(K85="No",0,F85*G85)</f>
-        <v>15</v>
-      </c>
-      <c r="I85" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J85" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K85" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="B86" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="C86" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="D86" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E86" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="F86" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="H86" s="30" t="n">
-        <f aca="false">IF(K86="No",0,F86*G86)</f>
-        <v>25</v>
-      </c>
-      <c r="I86" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J86" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K86" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="B87" s="28" t="s">
-        <v>225</v>
-      </c>
-      <c r="C87" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="D87" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E87" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="F87" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H87" s="30" t="n">
-        <f aca="false">IF(K87="No",0,F87*G87)</f>
-        <v>10</v>
-      </c>
-      <c r="I87" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J87" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K87" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="B88" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="C88" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="D88" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E88" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="F88" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H88" s="30" t="n">
-        <f aca="false">IF(K88="No",0,F88*G88)</f>
-        <v>10</v>
-      </c>
-      <c r="I88" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J88" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K88" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="B89" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="C89" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="D89" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E89" s="28" t="s">
-        <v>235</v>
-      </c>
-      <c r="F89" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H89" s="30" t="n">
-        <f aca="false">IF(K89="No",0,F89*G89)</f>
-        <v>12</v>
-      </c>
-      <c r="I89" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J89" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K89" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="B90" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="C90" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="D90" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E90" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="F90" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G90" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H90" s="30" t="n">
-        <f aca="false">IF(K90="No",0,F90*G90)</f>
-        <v>6</v>
-      </c>
-      <c r="I90" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J90" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K90" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="B91" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C91" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D91" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E91" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="F91" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H91" s="30" t="n">
-        <f aca="false">IF(K91="No",0,F91*G91)</f>
-        <v>8</v>
-      </c>
-      <c r="I91" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J91" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K91" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="B92" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="C92" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="D92" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E92" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="F92" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G92" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H92" s="30" t="n">
-        <f aca="false">IF(K92="No",0,F92*G92)</f>
-        <v>4</v>
-      </c>
-      <c r="I92" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J92" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K92" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="B93" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="C93" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="D93" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E93" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="F93" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="H93" s="30" t="n">
-        <f aca="false">IF(K93="No",0,F93*G93)</f>
-        <v>5</v>
-      </c>
-      <c r="I93" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J93" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K93" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="B94" s="41"/>
-      <c r="C94" s="41"/>
-      <c r="D94" s="41"/>
-      <c r="E94" s="41"/>
-      <c r="F94" s="41"/>
-      <c r="G94" s="41"/>
-      <c r="H94" s="41"/>
-      <c r="I94" s="41"/>
-      <c r="J94" s="41"/>
-      <c r="K94" s="41"/>
-    </row>
-    <row r="95" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="B95" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="C95" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="D95" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="E95" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F95" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" s="30" t="n">
-        <v>6.725</v>
-      </c>
-      <c r="H95" s="30" t="n">
-        <f aca="false">IF(K95="No",0,F95*G95)</f>
-        <v>33.625</v>
-      </c>
-      <c r="I95" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J95" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K95" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="B96" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="C96" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D96" s="29" t="s">
-        <v>256</v>
-      </c>
-      <c r="E96" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="F96" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="30" t="n">
-        <v>40</v>
-      </c>
-      <c r="H96" s="30" t="n">
-        <f aca="false">IF(K96="No",0,F96*G96)</f>
-        <v>40</v>
-      </c>
-      <c r="I96" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J96" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K96" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B97" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C97" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D97" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E97" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="F97" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G97" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H97" s="30" t="n">
-        <f aca="false">IF(K97="No",0,F97*G97)</f>
-        <v>10</v>
-      </c>
-      <c r="I97" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J97" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K97" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="B98" s="41"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="41"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="41"/>
-      <c r="I98" s="41"/>
-      <c r="J98" s="41"/>
-      <c r="K98" s="41"/>
-    </row>
-    <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B99" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="C99" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="D99" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="E99" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="F99" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="30" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H99" s="30" t="n">
-        <f aca="false">IF(K99="No",0,F99*G99)</f>
-        <v>21.39</v>
-      </c>
-      <c r="I99" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J99" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K99" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="B100" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="C100" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="D100" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="E100" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="F100" s="29" t="n">
-        <v>10</v>
-      </c>
       <c r="G100" s="30" t="n">
-        <v>0.61</v>
+        <v>131</v>
       </c>
       <c r="H100" s="30" t="n">
         <f aca="false">IF(K100="No",0,F100*G100)</f>
-        <v>6.1</v>
+        <v>131</v>
       </c>
       <c r="I100" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J100" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K100" s="32" t="s">
@@ -4636,7 +4900,7 @@
     </row>
     <row r="101" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="45" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B101" s="41"/>
       <c r="C101" s="41"/>
@@ -4651,1070 +4915,1635 @@
     </row>
     <row r="102" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="28" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B102" s="28" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="D102" s="29" t="s">
-        <v>209</v>
+        <v>88</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>210</v>
+        <v>288</v>
       </c>
       <c r="F102" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G102" s="30" t="n">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="H102" s="30" t="n">
-        <f aca="false">IF(K102="Yes",F102*G102,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I102" s="29" t="s">
-        <v>98</v>
+        <f aca="false">IF(K102="No",0,F102*G102)</f>
+        <v>35</v>
+      </c>
+      <c r="I102" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J102" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
         <v>Open</v>
       </c>
       <c r="K102" s="32" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="28" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B103" s="28" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="D103" s="29" t="s">
-        <v>278</v>
+        <v>88</v>
       </c>
       <c r="E103" s="28" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="F103" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H103" s="30" t="n">
+        <f aca="false">IF(K103="No",0,F103*G103)</f>
+        <v>15</v>
+      </c>
+      <c r="I103" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J103" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K103" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B104" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C104" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="D104" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E104" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="F104" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H104" s="30" t="n">
+        <f aca="false">IF(K104="No",0,F104*G104)</f>
+        <v>25</v>
+      </c>
+      <c r="I104" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J104" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K104" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C105" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="D105" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E105" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="F105" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H105" s="30" t="n">
+        <f aca="false">IF(K105="No",0,F105*G105)</f>
+        <v>10</v>
+      </c>
+      <c r="I105" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J105" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K105" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C106" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="D106" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="F106" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H106" s="30" t="n">
+        <f aca="false">IF(K106="No",0,F106*G106)</f>
+        <v>10</v>
+      </c>
+      <c r="I106" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J106" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K106" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C107" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="D107" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E107" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="F107" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H107" s="30" t="n">
+        <f aca="false">IF(K107="No",0,F107*G107)</f>
+        <v>12</v>
+      </c>
+      <c r="I107" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J107" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K107" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="B108" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="C108" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E108" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="F108" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" s="30" t="n">
+        <f aca="false">IF(K108="No",0,F108*G108)</f>
+        <v>6</v>
+      </c>
+      <c r="I108" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J108" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K108" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="C109" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="D109" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E109" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="F109" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H109" s="30" t="n">
+        <f aca="false">IF(K109="No",0,F109*G109)</f>
+        <v>8</v>
+      </c>
+      <c r="I109" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J109" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K109" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="C110" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="D110" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E110" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="F110" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G110" s="30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H110" s="30" t="n">
+        <f aca="false">IF(K110="No",0,F110*G110)</f>
+        <v>4</v>
+      </c>
+      <c r="I110" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J110" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K110" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="C111" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="D111" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E111" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="F111" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" s="30" t="n">
+        <f aca="false">IF(K111="No",0,F111*G111)</f>
+        <v>5</v>
+      </c>
+      <c r="I111" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J111" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K111" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>326</v>
+      </c>
+      <c r="C112" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="D112" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E112" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="F112" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="H103" s="30" t="n">
-        <f aca="false">IF(K103="Yes",F103*G103,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I103" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J103" s="31" t="str">
-        <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K103" s="32" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="9" t="n">
-        <f aca="false">SUM(H81:H103)</f>
-        <v>372.115</v>
-      </c>
-      <c r="I104" s="8"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-    </row>
-    <row r="106" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="B106" s="41"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="41"/>
-      <c r="E106" s="41"/>
-      <c r="F106" s="41"/>
-      <c r="G106" s="41"/>
-      <c r="H106" s="41"/>
-      <c r="I106" s="41"/>
-      <c r="J106" s="41"/>
-      <c r="K106" s="41"/>
-    </row>
-    <row r="107" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="C107" s="27"/>
-      <c r="D107" s="27"/>
-      <c r="E107" s="27"/>
-      <c r="H107" s="30" t="n">
-        <f aca="false">IF(SUM(H82+H102)&gt;0,60,0)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="27"/>
-      <c r="D108" s="27"/>
-      <c r="E108" s="27"/>
-      <c r="H108" s="30" t="n">
-        <f aca="false">ROUND(0.35*(H95+H96+H97),2)</f>
-        <v>29.27</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="B109" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="C109" s="27"/>
-      <c r="D109" s="27"/>
-      <c r="E109" s="27"/>
-      <c r="H109" s="30" t="n">
-        <f aca="false">ROUND(0.1*(H82+H102)+0.08*(H100),2)+IF(SUM(H82+H102)&gt;0,65,0)</f>
-        <v>78.59</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="8"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="9" t="n">
-        <f aca="false">SUM(H107:H109)</f>
-        <v>167.86</v>
-      </c>
-      <c r="I110" s="8"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-    </row>
-    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="B111" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C111" s="48"/>
-      <c r="D111" s="48"/>
-      <c r="E111" s="48"/>
-      <c r="F111" s="48"/>
-      <c r="G111" s="48"/>
-      <c r="H111" s="49" t="n">
-        <f aca="false">IF(K79="Yes",H104+H110,0)</f>
-        <v>539.975</v>
-      </c>
-      <c r="I111" s="48"/>
-      <c r="J111" s="48"/>
-      <c r="K111" s="48"/>
-    </row>
-    <row r="113" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="50" t="s">
-        <v>288</v>
-      </c>
-      <c r="B113" s="51"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="51"/>
-      <c r="G113" s="51"/>
-      <c r="H113" s="51"/>
-      <c r="I113" s="51"/>
-      <c r="J113" s="51"/>
-      <c r="K113" s="51"/>
-    </row>
-    <row r="114" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="B114" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C114" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="D114" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="E114" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="F114" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="G114" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="H114" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="I114" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="J114" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="K114" s="52" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H112" s="30" t="n">
+        <f aca="false">IF(K112="No",0,F112*G112)</f>
+        <v>40</v>
+      </c>
+      <c r="I112" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J112" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K112" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="45" t="s">
+        <v>329</v>
+      </c>
+      <c r="B113" s="41"/>
+      <c r="C113" s="41"/>
+      <c r="D113" s="41"/>
+      <c r="E113" s="41"/>
+      <c r="F113" s="41"/>
+      <c r="G113" s="41"/>
+      <c r="H113" s="41"/>
+      <c r="I113" s="41"/>
+      <c r="J113" s="41"/>
+      <c r="K113" s="41"/>
+    </row>
+    <row r="114" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B114" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C114" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="D114" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="E114" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="F114" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G114" s="30" t="n">
+        <v>6.725</v>
+      </c>
+      <c r="H114" s="30" t="n">
+        <f aca="false">IF(K114="No",0,F114*G114)</f>
+        <v>33.625</v>
+      </c>
+      <c r="I114" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J114" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K114" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="28" t="s">
-        <v>290</v>
+        <v>335</v>
       </c>
       <c r="B115" s="28" t="s">
-        <v>291</v>
+        <v>336</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="D115" s="29" t="s">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>294</v>
+        <v>338</v>
       </c>
       <c r="F115" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G115" s="30" t="n">
-        <v>277.2</v>
+        <v>40</v>
       </c>
       <c r="H115" s="30" t="n">
-        <f aca="false">IF(OR(K115="Yes",K115=TRUE()),0,F115*G115)</f>
-        <v>277.2</v>
-      </c>
-      <c r="I115" s="29" t="s">
-        <v>98</v>
+        <f aca="false">IF(K115="No",0,F115*G115)</f>
+        <v>40</v>
+      </c>
+      <c r="I115" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J115" s="31" t="str">
-        <f aca="false">HYPERLINK("https://store.bruker.com/products/dpt10","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K115" s="53"/>
+        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K115" s="32" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="28" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>296</v>
+        <v>340</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="D116" s="29" t="s">
-        <v>298</v>
+        <v>138</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
       <c r="F116" s="29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G116" s="30" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="H116" s="30" t="n">
-        <f aca="false">IF(OR(K116="Yes",K116=TRUE()),0,F116*G116)</f>
-        <v>77</v>
-      </c>
-      <c r="I116" s="29" t="s">
-        <v>98</v>
+        <f aca="false">IF(K116="No",0,F116*G116)</f>
+        <v>10</v>
+      </c>
+      <c r="I116" s="33" t="s">
+        <v>96</v>
       </c>
       <c r="J116" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K116" s="53"/>
-    </row>
-    <row r="117" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="B117" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="C117" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="D117" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="E117" s="28" t="s">
-        <v>304</v>
-      </c>
-      <c r="F117" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="30" t="n">
-        <v>133.13</v>
-      </c>
-      <c r="H117" s="30" t="n">
-        <f aca="false">IF(OR(K117="Yes",K117=TRUE()),0,F117*G117)</f>
-        <v>133.13</v>
-      </c>
-      <c r="I117" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J117" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K117" s="53"/>
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K116" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="45" t="s">
+        <v>341</v>
+      </c>
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="41"/>
+      <c r="I117" s="41"/>
+      <c r="J117" s="41"/>
+      <c r="K117" s="41"/>
     </row>
     <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="28" t="s">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="C118" s="28" t="s">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="D118" s="29" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="F118" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G118" s="30" t="n">
-        <v>75.15</v>
+        <v>21.39</v>
       </c>
       <c r="H118" s="30" t="n">
-        <f aca="false">IF(OR(K118="Yes",K118=TRUE()),0,F118*G118)</f>
-        <v>75.15</v>
+        <f aca="false">IF(K118="No",0,F118*G118)</f>
+        <v>21.39</v>
       </c>
       <c r="I118" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J118" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.penntoolco.com/grizzly-9-x-12-x-2-granite-surface-plate-no-ledge-g9649/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K118" s="53"/>
-    </row>
-    <row r="119" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K118" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="28" t="s">
-        <v>39</v>
+        <v>345</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>311</v>
+        <v>256</v>
       </c>
       <c r="D119" s="29" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E119" s="28" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="F119" s="29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G119" s="30" t="n">
-        <v>57.99</v>
+        <v>0.61</v>
       </c>
       <c r="H119" s="30" t="n">
-        <f aca="false">IF(OR(K119="Yes",K119=TRUE()),0,F119*G119)</f>
-        <v>57.99</v>
+        <f aca="false">IF(K119="No",0,F119*G119)</f>
+        <v>6.1</v>
       </c>
       <c r="I119" s="29" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J119" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K119" s="53"/>
-    </row>
-    <row r="120" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B120" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C120" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="D120" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E120" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="F120" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="30" t="n">
-        <v>40</v>
-      </c>
-      <c r="H120" s="30" t="n">
-        <f aca="false">IF(OR(K120="Yes",K120=TRUE(),K79&lt;&gt;"Yes"),0,F120*G120)</f>
-        <v>40</v>
-      </c>
-      <c r="I120" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J120" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K120" s="53"/>
-    </row>
-    <row r="121" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K119" s="32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="45" t="s">
+        <v>347</v>
+      </c>
+      <c r="B120" s="41"/>
+      <c r="C120" s="41"/>
+      <c r="D120" s="41"/>
+      <c r="E120" s="41"/>
+      <c r="F120" s="41"/>
+      <c r="G120" s="41"/>
+      <c r="H120" s="41"/>
+      <c r="I120" s="41"/>
+      <c r="J120" s="41"/>
+      <c r="K120" s="41"/>
+    </row>
+    <row r="121" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="28" t="s">
-        <v>317</v>
+        <v>348</v>
       </c>
       <c r="B121" s="28" t="s">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="D121" s="29" t="s">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="F121" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G121" s="30" t="n">
+        <v>131</v>
+      </c>
+      <c r="H121" s="30" t="n">
+        <f aca="false">IF(K121="Yes",F121*G121,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I121" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J121" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K121" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="8"/>
+      <c r="G122" s="8"/>
+      <c r="H122" s="9" t="n">
+        <f aca="false">SUM(H99:H121)</f>
+        <v>412.115</v>
+      </c>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="8"/>
+    </row>
+    <row r="124" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="45" t="s">
+        <v>352</v>
+      </c>
+      <c r="B124" s="41"/>
+      <c r="C124" s="41"/>
+      <c r="D124" s="41"/>
+      <c r="E124" s="41"/>
+      <c r="F124" s="41"/>
+      <c r="G124" s="41"/>
+      <c r="H124" s="41"/>
+      <c r="I124" s="41"/>
+      <c r="J124" s="41"/>
+      <c r="K124" s="41"/>
+    </row>
+    <row r="125" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" s="27" t="s">
+        <v>353</v>
+      </c>
+      <c r="C125" s="27"/>
+      <c r="D125" s="27"/>
+      <c r="E125" s="27"/>
+      <c r="H125" s="30" t="n">
+        <f aca="false">IF(SUM(H100+H121)&gt;0,60,0)</f>
         <v>60</v>
       </c>
-      <c r="H121" s="30" t="n">
-        <f aca="false">IF(OR(K121="Yes",K121=TRUE()),0,F121*G121)</f>
+    </row>
+    <row r="126" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="B126" s="27" t="s">
+        <v>354</v>
+      </c>
+      <c r="C126" s="27"/>
+      <c r="D126" s="27"/>
+      <c r="E126" s="27"/>
+      <c r="H126" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H114+H115+H116),2)</f>
+        <v>29.27</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>355</v>
+      </c>
+      <c r="C127" s="27"/>
+      <c r="D127" s="27"/>
+      <c r="E127" s="27"/>
+      <c r="H127" s="30" t="n">
+        <f aca="false">ROUND(0.1*(H100+H121)+0.08*(H119),2)+IF(SUM(H100+H121)&gt;0,65,0)</f>
+        <v>78.59</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B128" s="8"/>
+      <c r="C128" s="8"/>
+      <c r="D128" s="8"/>
+      <c r="E128" s="8"/>
+      <c r="F128" s="8"/>
+      <c r="G128" s="8"/>
+      <c r="H128" s="9" t="n">
+        <f aca="false">SUM(H125:H127)</f>
+        <v>167.86</v>
+      </c>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="8"/>
+    </row>
+    <row r="129" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="46" t="s">
+        <v>357</v>
+      </c>
+      <c r="B129" s="47" t="s">
+        <v>358</v>
+      </c>
+      <c r="C129" s="48"/>
+      <c r="D129" s="48"/>
+      <c r="E129" s="48"/>
+      <c r="F129" s="48"/>
+      <c r="G129" s="48"/>
+      <c r="H129" s="49" t="n">
+        <f aca="false">IF(K97="Yes",H122+H128,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I129" s="48"/>
+      <c r="J129" s="48"/>
+      <c r="K129" s="48"/>
+    </row>
+    <row r="131" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="50" t="s">
+        <v>359</v>
+      </c>
+      <c r="B131" s="51"/>
+      <c r="C131" s="51"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="51"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="51"/>
+      <c r="H131" s="51"/>
+      <c r="I131" s="51"/>
+      <c r="J131" s="51"/>
+      <c r="K131" s="51"/>
+    </row>
+    <row r="132" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B132" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C132" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="D132" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="E132" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="F132" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="G132" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="H132" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I132" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="J132" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="K132" s="52" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="B133" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="C133" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="D133" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="E133" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="F133" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="30" t="n">
+        <v>274</v>
+      </c>
+      <c r="H133" s="30" t="n">
+        <f aca="false">IF(OR(K133="Yes",K133=TRUE()),0,F133*G133)</f>
+        <v>274</v>
+      </c>
+      <c r="I133" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J133" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.advent-rm.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K133" s="53"/>
+    </row>
+    <row r="134" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B134" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="D134" s="29" t="s">
+        <v>369</v>
+      </c>
+      <c r="E134" s="28" t="s">
+        <v>370</v>
+      </c>
+      <c r="F134" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="30" t="n">
+        <v>77</v>
+      </c>
+      <c r="H134" s="30" t="n">
+        <f aca="false">IF(OR(K134="Yes",K134=TRUE()),0,F134*G134)</f>
+        <v>77</v>
+      </c>
+      <c r="I134" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J134" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K134" s="53"/>
+    </row>
+    <row r="135" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="B135" s="28" t="s">
+        <v>372</v>
+      </c>
+      <c r="C135" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="D135" s="29" t="s">
+        <v>374</v>
+      </c>
+      <c r="E135" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="F135" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="30" t="n">
+        <v>133.13</v>
+      </c>
+      <c r="H135" s="30" t="n">
+        <f aca="false">IF(OR(K135="Yes",K135=TRUE()),0,F135*G135)</f>
+        <v>133.13</v>
+      </c>
+      <c r="I135" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J135" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K135" s="53"/>
+    </row>
+    <row r="136" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="B136" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="C136" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="D136" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="F136" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="30" t="n">
+        <v>25</v>
+      </c>
+      <c r="H136" s="30" t="n">
+        <f aca="false">IF(OR(K136="Yes",K136=TRUE()),0,F136*G136)</f>
+        <v>25</v>
+      </c>
+      <c r="I136" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J136" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=USB+microscope+with+calibration+slide","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K136" s="53"/>
+    </row>
+    <row r="137" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B137" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="C137" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D137" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E137" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="F137" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="30" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="H137" s="30" t="n">
+        <f aca="false">IF(OR(K137="Yes",K137=TRUE()),0,F137*G137)</f>
+        <v>57.99</v>
+      </c>
+      <c r="I137" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J137" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K137" s="53"/>
+    </row>
+    <row r="138" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="B138" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="C138" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="D138" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="F138" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="I121" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="J121" s="31" t="str">
+      <c r="H138" s="30" t="n">
+        <f aca="false">IF(OR(K138="Yes",K138=TRUE()),0,F138*G138)</f>
+        <v>60</v>
+      </c>
+      <c r="I138" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J138" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K121" s="53"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B122" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="C122" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D122" s="29" t="s">
-        <v>323</v>
-      </c>
-      <c r="E122" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="F122" s="29" t="n">
+      <c r="K138" s="53"/>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="28" t="s">
+        <v>387</v>
+      </c>
+      <c r="B139" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="C139" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D139" s="29" t="s">
+        <v>389</v>
+      </c>
+      <c r="E139" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="F139" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="30" t="n">
+      <c r="G139" s="30" t="n">
         <v>25.99</v>
       </c>
-      <c r="H122" s="30" t="n">
-        <f aca="false">IF(OR(K122="Yes",K122=TRUE()),0,F122*G122)</f>
+      <c r="H139" s="30" t="n">
+        <f aca="false">IF(OR(K139="Yes",K139=TRUE()),0,F139*G139)</f>
         <v>25.99</v>
       </c>
-      <c r="I122" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="J122" s="31" t="str">
+      <c r="I139" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="J139" s="31" t="str">
         <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K122" s="53"/>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="B123" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="C123" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D123" s="29" t="s">
+      <c r="K139" s="53"/>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="B140" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="C140" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D140" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E123" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F123" s="29" t="n">
+      <c r="E140" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F140" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G123" s="30" t="n">
+      <c r="G140" s="30" t="n">
         <v>24.97</v>
       </c>
-      <c r="H123" s="30" t="n">
-        <f aca="false">IF(OR(K123="Yes",K123=TRUE()),0,F123*G123)</f>
+      <c r="H140" s="30" t="n">
+        <f aca="false">IF(OR(K140="Yes",K140=TRUE()),0,F140*G140)</f>
         <v>24.97</v>
       </c>
-      <c r="I123" s="29" t="s">
+      <c r="I140" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J123" s="31" t="str">
+      <c r="J140" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K123" s="53"/>
-    </row>
-    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="28" t="s">
-        <v>328</v>
-      </c>
-      <c r="B124" s="28" t="s">
-        <v>329</v>
-      </c>
-      <c r="C124" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D124" s="29" t="s">
+      <c r="K140" s="53"/>
+    </row>
+    <row r="141" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="B141" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="C141" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D141" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E124" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F124" s="29" t="n">
+      <c r="E141" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F141" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G124" s="30" t="n">
+      <c r="G141" s="30" t="n">
         <v>11.99</v>
       </c>
-      <c r="H124" s="30" t="n">
-        <f aca="false">IF(OR(K124="Yes",K124=TRUE()),0,F124*G124)</f>
+      <c r="H141" s="30" t="n">
+        <f aca="false">IF(OR(K141="Yes",K141=TRUE()),0,F141*G141)</f>
         <v>11.99</v>
       </c>
-      <c r="I124" s="29" t="s">
+      <c r="I141" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J124" s="31" t="str">
+      <c r="J141" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K124" s="53"/>
-    </row>
-    <row r="125" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="B125" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="C125" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D125" s="29" t="s">
+      <c r="K141" s="53"/>
+    </row>
+    <row r="142" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="B142" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="C142" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D142" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E125" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F125" s="29" t="n">
+      <c r="E142" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F142" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G125" s="30" t="n">
+      <c r="G142" s="30" t="n">
         <v>25.26</v>
       </c>
-      <c r="H125" s="30" t="n">
-        <f aca="false">IF(OR(K125="Yes",K125=TRUE()),0,F125*G125)</f>
+      <c r="H142" s="30" t="n">
+        <f aca="false">IF(OR(K142="Yes",K142=TRUE()),0,F142*G142)</f>
         <v>25.26</v>
       </c>
-      <c r="I125" s="29" t="s">
+      <c r="I142" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J125" s="31" t="str">
+      <c r="J142" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K125" s="53"/>
-    </row>
-    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="B126" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="C126" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D126" s="29" t="s">
+      <c r="K142" s="53"/>
+    </row>
+    <row r="143" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="28" t="s">
+        <v>398</v>
+      </c>
+      <c r="B143" s="28" t="s">
+        <v>399</v>
+      </c>
+      <c r="C143" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D143" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E126" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F126" s="29" t="n">
+      <c r="E143" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F143" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G126" s="30" t="n">
+      <c r="G143" s="30" t="n">
         <v>32.12</v>
       </c>
-      <c r="H126" s="30" t="n">
-        <f aca="false">IF(OR(K126="Yes",K126=TRUE()),0,F126*G126)</f>
+      <c r="H143" s="30" t="n">
+        <f aca="false">IF(OR(K143="Yes",K143=TRUE()),0,F143*G143)</f>
         <v>32.12</v>
       </c>
-      <c r="I126" s="29" t="s">
+      <c r="I143" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J126" s="31" t="str">
+      <c r="J143" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K126" s="53"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="B127" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="C127" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D127" s="29" t="s">
+      <c r="K143" s="53"/>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="B144" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="C144" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D144" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E127" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F127" s="29" t="n">
+      <c r="E144" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F144" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G127" s="30" t="n">
+      <c r="G144" s="30" t="n">
         <v>16.98</v>
       </c>
-      <c r="H127" s="30" t="n">
-        <f aca="false">IF(OR(K127="Yes",K127=TRUE()),0,F127*G127)</f>
+      <c r="H144" s="30" t="n">
+        <f aca="false">IF(OR(K144="Yes",K144=TRUE()),0,F144*G144)</f>
         <v>16.98</v>
       </c>
-      <c r="I127" s="29" t="s">
+      <c r="I144" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J127" s="31" t="str">
+      <c r="J144" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K127" s="53"/>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="B128" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="C128" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D128" s="29" t="s">
+      <c r="K144" s="53"/>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="B145" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="C145" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D145" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E128" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F128" s="29" t="n">
+      <c r="E145" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F145" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G128" s="30" t="n">
+      <c r="G145" s="30" t="n">
         <v>22.31</v>
       </c>
-      <c r="H128" s="30" t="n">
-        <f aca="false">IF(OR(K128="Yes",K128=TRUE()),0,F128*G128)</f>
+      <c r="H145" s="30" t="n">
+        <f aca="false">IF(OR(K145="Yes",K145=TRUE()),0,F145*G145)</f>
         <v>22.31</v>
       </c>
-      <c r="I128" s="29" t="s">
+      <c r="I145" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J128" s="31" t="str">
+      <c r="J145" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K128" s="53"/>
-    </row>
-    <row r="129" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B129" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="C129" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D129" s="29" t="s">
+      <c r="K145" s="53"/>
+    </row>
+    <row r="146" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="B146" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="C146" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="D146" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="E129" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="F129" s="29" t="n">
+      <c r="E146" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="F146" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G129" s="30" t="n">
+      <c r="G146" s="30" t="n">
         <v>12.17</v>
       </c>
-      <c r="H129" s="30" t="n">
-        <f aca="false">IF(OR(K129="Yes",K129=TRUE()),0,F129*G129)</f>
+      <c r="H146" s="30" t="n">
+        <f aca="false">IF(OR(K146="Yes",K146=TRUE()),0,F146*G146)</f>
         <v>12.17</v>
       </c>
-      <c r="I129" s="29" t="s">
+      <c r="I146" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J129" s="31" t="str">
+      <c r="J146" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=precision+tweezers+set","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K129" s="53"/>
-    </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="B130" s="55"/>
-      <c r="C130" s="55"/>
-      <c r="D130" s="55"/>
-      <c r="E130" s="55"/>
-      <c r="F130" s="55"/>
-      <c r="G130" s="55"/>
-      <c r="H130" s="56" t="n">
-        <f aca="false">SUM(H115:H129)</f>
-        <v>892.26</v>
-      </c>
-      <c r="I130" s="55"/>
-      <c r="J130" s="55"/>
-      <c r="K130" s="55"/>
-    </row>
-    <row r="132" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
-      <c r="D132" s="16"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="16"/>
-      <c r="G132" s="16"/>
-      <c r="H132" s="16"/>
-      <c r="I132" s="16"/>
-      <c r="J132" s="16"/>
-      <c r="K132" s="16"/>
-    </row>
-    <row r="133" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="B133" s="58" t="s">
-        <v>343</v>
-      </c>
-      <c r="C133" s="59"/>
-      <c r="D133" s="59"/>
-      <c r="E133" s="59"/>
-      <c r="F133" s="59"/>
-      <c r="G133" s="59"/>
-      <c r="H133" s="60" t="n">
-        <f aca="false">H68+IF((K79="Yes"),H104,0)+H130</f>
-        <v>2114.035</v>
-      </c>
-      <c r="I133" s="59"/>
-      <c r="J133" s="59"/>
-      <c r="K133" s="59"/>
-    </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="B134" s="58"/>
-      <c r="C134" s="59"/>
-      <c r="D134" s="59"/>
-      <c r="E134" s="59"/>
-      <c r="F134" s="59"/>
-      <c r="G134" s="59"/>
-      <c r="H134" s="60" t="n">
-        <f aca="false">H74+IF((K79="Yes"),H110,0)</f>
-        <v>449.74</v>
-      </c>
-      <c r="I134" s="59"/>
-      <c r="J134" s="59"/>
-      <c r="K134" s="59"/>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="B135" s="58" t="s">
-        <v>345</v>
-      </c>
-      <c r="C135" s="59"/>
-      <c r="D135" s="59"/>
-      <c r="E135" s="59"/>
-      <c r="F135" s="59"/>
-      <c r="G135" s="59"/>
-      <c r="H135" s="60" t="n">
-        <f aca="false">ROUND(H133*0.0775,2)</f>
-        <v>163.84</v>
-      </c>
-      <c r="I135" s="59"/>
-      <c r="J135" s="59"/>
-      <c r="K135" s="59"/>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="B136" s="58" t="s">
-        <v>347</v>
-      </c>
-      <c r="C136" s="59"/>
-      <c r="D136" s="59"/>
-      <c r="E136" s="59"/>
-      <c r="F136" s="59"/>
-      <c r="G136" s="59"/>
-      <c r="H136" s="60" t="n">
-        <f aca="false">ROUND((H133+H134+H135)*0.1,2)</f>
-        <v>272.76</v>
-      </c>
-      <c r="I136" s="59"/>
-      <c r="J136" s="59"/>
-      <c r="K136" s="59"/>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B137" s="61"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
-      <c r="E137" s="12"/>
-      <c r="F137" s="12"/>
-      <c r="G137" s="12"/>
-      <c r="H137" s="13" t="n">
-        <f aca="false">H133+H134+H135+H136</f>
-        <v>3000.375</v>
-      </c>
-      <c r="I137" s="12"/>
-      <c r="J137" s="12"/>
-      <c r="K137" s="12"/>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="57" t="s">
-        <v>349</v>
-      </c>
-      <c r="B138" s="58" t="s">
-        <v>350</v>
-      </c>
-      <c r="C138" s="59"/>
-      <c r="D138" s="59"/>
-      <c r="E138" s="59"/>
-      <c r="F138" s="59"/>
-      <c r="G138" s="59"/>
-      <c r="H138" s="60" t="n">
-        <f aca="false">2000-H137</f>
-        <v>-1000.375</v>
-      </c>
-      <c r="I138" s="59"/>
-      <c r="J138" s="59"/>
-      <c r="K138" s="59"/>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="62" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B141" s="16"/>
-      <c r="C141" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D141" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="E141" s="63" t="s">
-        <v>354</v>
-      </c>
-      <c r="F141" s="63"/>
-      <c r="G141" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="H141" s="3" t="s">
+      <c r="K146" s="53"/>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="54" t="s">
+        <v>406</v>
+      </c>
+      <c r="B147" s="55"/>
+      <c r="C147" s="55"/>
+      <c r="D147" s="55"/>
+      <c r="E147" s="55"/>
+      <c r="F147" s="55"/>
+      <c r="G147" s="55"/>
+      <c r="H147" s="56" t="n">
+        <f aca="false">SUM(H133:H146)</f>
+        <v>798.91</v>
+      </c>
+      <c r="I147" s="55"/>
+      <c r="J147" s="55"/>
+      <c r="K147" s="55"/>
+    </row>
+    <row r="149" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B149" s="16"/>
+      <c r="C149" s="16"/>
+      <c r="D149" s="16"/>
+      <c r="E149" s="16"/>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="16"/>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+    </row>
+    <row r="150" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="57" t="s">
+        <v>408</v>
+      </c>
+      <c r="B150" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="C150" s="59"/>
+      <c r="D150" s="59"/>
+      <c r="E150" s="59"/>
+      <c r="F150" s="59"/>
+      <c r="G150" s="59"/>
+      <c r="H150" s="60" t="n">
+        <f aca="false">H86+IF((K97="Yes"),H122,0)+H147</f>
+        <v>1970.1</v>
+      </c>
+      <c r="I150" s="59"/>
+      <c r="J150" s="59"/>
+      <c r="K150" s="59"/>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="B151" s="58"/>
+      <c r="C151" s="59"/>
+      <c r="D151" s="59"/>
+      <c r="E151" s="59"/>
+      <c r="F151" s="59"/>
+      <c r="G151" s="59"/>
+      <c r="H151" s="60" t="n">
+        <f aca="false">H92+IF((K97="Yes"),H128,0)</f>
+        <v>272.36</v>
+      </c>
+      <c r="I151" s="59"/>
+      <c r="J151" s="59"/>
+      <c r="K151" s="59"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="57" t="s">
+        <v>410</v>
+      </c>
+      <c r="B152" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="C152" s="59"/>
+      <c r="D152" s="59"/>
+      <c r="E152" s="59"/>
+      <c r="F152" s="59"/>
+      <c r="G152" s="59"/>
+      <c r="H152" s="60" t="n">
+        <f aca="false">ROUND(H150*0.0775,2)</f>
+        <v>152.68</v>
+      </c>
+      <c r="I152" s="59"/>
+      <c r="J152" s="59"/>
+      <c r="K152" s="59"/>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="57" t="s">
+        <v>412</v>
+      </c>
+      <c r="B153" s="58" t="s">
+        <v>413</v>
+      </c>
+      <c r="C153" s="59"/>
+      <c r="D153" s="59"/>
+      <c r="E153" s="59"/>
+      <c r="F153" s="59"/>
+      <c r="G153" s="59"/>
+      <c r="H153" s="60" t="n">
+        <f aca="false">ROUND((H150+H151+H152)*0.1,2)</f>
+        <v>239.51</v>
+      </c>
+      <c r="I153" s="59"/>
+      <c r="J153" s="59"/>
+      <c r="K153" s="59"/>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="B154" s="61"/>
+      <c r="C154" s="12"/>
+      <c r="D154" s="12"/>
+      <c r="E154" s="12"/>
+      <c r="F154" s="12"/>
+      <c r="G154" s="12"/>
+      <c r="H154" s="13" t="n">
+        <f aca="false">H150+H151+H152+H153</f>
+        <v>2634.65</v>
+      </c>
+      <c r="I154" s="12"/>
+      <c r="J154" s="12"/>
+      <c r="K154" s="12"/>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="57" t="s">
+        <v>415</v>
+      </c>
+      <c r="B155" s="58" t="s">
+        <v>416</v>
+      </c>
+      <c r="C155" s="59"/>
+      <c r="D155" s="59"/>
+      <c r="E155" s="59"/>
+      <c r="F155" s="59"/>
+      <c r="G155" s="59"/>
+      <c r="H155" s="60" t="n">
+        <f aca="false">2000-H154</f>
+        <v>-634.65</v>
+      </c>
+      <c r="I155" s="59"/>
+      <c r="J155" s="59"/>
+      <c r="K155" s="59"/>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="62" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B158" s="16"/>
+      <c r="C158" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E158" s="63" t="s">
+        <v>420</v>
+      </c>
+      <c r="F158" s="63"/>
+      <c r="G158" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H158" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="I141" s="16"/>
-      <c r="J141" s="16"/>
-      <c r="K141" s="16"/>
-    </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="64" t="s">
-        <v>356</v>
-      </c>
-      <c r="B142" s="64"/>
-      <c r="C142" s="6" t="n">
-        <f aca="false">H68+SUMPRODUCT(F115:F129,G115:G129)-F120*G120</f>
-        <v>1701.92</v>
-      </c>
-      <c r="D142" s="6" t="n">
-        <f aca="false">H74</f>
-        <v>281.88</v>
-      </c>
-      <c r="E142" s="65" t="n">
-        <f aca="false">ROUND(C142*0.0775,2)</f>
-        <v>131.9</v>
-      </c>
-      <c r="F142" s="65"/>
-      <c r="G142" s="6" t="n">
-        <f aca="false">ROUND((C142+D142+E142)*0.1,2)</f>
-        <v>211.57</v>
-      </c>
-      <c r="H142" s="66" t="n">
-        <f aca="false">C142+D142+E142+G142</f>
-        <v>2327.27</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="64" t="s">
-        <v>357</v>
-      </c>
-      <c r="B143" s="64"/>
-      <c r="C143" s="6" t="n">
-        <f aca="false">H68</f>
-        <v>849.66</v>
-      </c>
-      <c r="D143" s="6" t="n">
-        <f aca="false">H74</f>
-        <v>281.88</v>
-      </c>
-      <c r="E143" s="65" t="n">
-        <f aca="false">ROUND(C143*0.0775,2)</f>
-        <v>65.85</v>
-      </c>
-      <c r="F143" s="65"/>
-      <c r="G143" s="6" t="n">
-        <f aca="false">ROUND((C143+D143+E143)*0.1,2)</f>
-        <v>119.74</v>
-      </c>
-      <c r="H143" s="66" t="n">
-        <f aca="false">C143+D143+E143+G143</f>
-        <v>1317.13</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="64" t="s">
-        <v>358</v>
-      </c>
-      <c r="B144" s="64"/>
-      <c r="C144" s="6" t="n">
-        <f aca="false">H68+H104+SUMPRODUCT(F115:F129,G115:G129)</f>
-        <v>2114.035</v>
-      </c>
-      <c r="D144" s="6" t="n">
-        <f aca="false">H74+H110</f>
-        <v>449.74</v>
-      </c>
-      <c r="E144" s="65" t="n">
-        <f aca="false">ROUND(C144*0.0775,2)</f>
-        <v>163.84</v>
-      </c>
-      <c r="F144" s="65"/>
-      <c r="G144" s="6" t="n">
-        <f aca="false">ROUND((C144+D144+E144)*0.1,2)</f>
-        <v>272.76</v>
-      </c>
-      <c r="H144" s="66" t="n">
-        <f aca="false">C144+D144+E144+G144</f>
-        <v>3000.375</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="64" t="s">
-        <v>359</v>
-      </c>
-      <c r="B145" s="64"/>
-      <c r="C145" s="6" t="n">
-        <f aca="false">H68+H104</f>
-        <v>1221.775</v>
-      </c>
-      <c r="D145" s="6" t="n">
-        <f aca="false">H74+H110</f>
-        <v>449.74</v>
-      </c>
-      <c r="E145" s="65" t="n">
-        <f aca="false">ROUND(C145*0.0775,2)</f>
-        <v>94.69</v>
-      </c>
-      <c r="F145" s="65"/>
-      <c r="G145" s="6" t="n">
-        <f aca="false">ROUND((C145+D145+E145)*0.1,2)</f>
-        <v>176.62</v>
-      </c>
-      <c r="H145" s="66" t="n">
-        <f aca="false">C145+D145+E145+G145</f>
-        <v>1942.825</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="B146" s="37"/>
-      <c r="C146" s="37"/>
-      <c r="D146" s="37"/>
-      <c r="E146" s="37"/>
-      <c r="F146" s="37"/>
-      <c r="G146" s="37"/>
-      <c r="H146" s="37"/>
-      <c r="I146" s="37"/>
-      <c r="J146" s="37"/>
-      <c r="K146" s="37"/>
+      <c r="I158" s="16"/>
+      <c r="J158" s="16"/>
+      <c r="K158" s="16"/>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="64" t="s">
+        <v>422</v>
+      </c>
+      <c r="B159" s="64"/>
+      <c r="C159" s="6" t="n">
+        <f aca="false">H86+SUMPRODUCT(F133:F146,G133:G146)</f>
+        <v>1970.1</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <f aca="false">H92</f>
+        <v>272.36</v>
+      </c>
+      <c r="E159" s="65" t="n">
+        <f aca="false">ROUND(C159*0.0775,2)</f>
+        <v>152.68</v>
+      </c>
+      <c r="F159" s="65"/>
+      <c r="G159" s="6" t="n">
+        <f aca="false">ROUND((C159+D159+E159)*0.1,2)</f>
+        <v>239.51</v>
+      </c>
+      <c r="H159" s="66" t="n">
+        <f aca="false">C159+D159+E159+G159</f>
+        <v>2634.65</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="64" t="s">
+        <v>423</v>
+      </c>
+      <c r="B160" s="64"/>
+      <c r="C160" s="6" t="n">
+        <f aca="false">H86</f>
+        <v>1171.19</v>
+      </c>
+      <c r="D160" s="6" t="n">
+        <f aca="false">H92</f>
+        <v>272.36</v>
+      </c>
+      <c r="E160" s="65" t="n">
+        <f aca="false">ROUND(C160*0.0775,2)</f>
+        <v>90.77</v>
+      </c>
+      <c r="F160" s="65"/>
+      <c r="G160" s="6" t="n">
+        <f aca="false">ROUND((C160+D160+E160)*0.1,2)</f>
+        <v>153.43</v>
+      </c>
+      <c r="H160" s="66" t="n">
+        <f aca="false">C160+D160+E160+G160</f>
+        <v>1687.75</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="64" t="s">
+        <v>424</v>
+      </c>
+      <c r="B161" s="64"/>
+      <c r="C161" s="6" t="n">
+        <f aca="false">H86+H122+SUMPRODUCT(F133:F146,G133:G146)</f>
+        <v>2382.215</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <f aca="false">H92+H128</f>
+        <v>440.22</v>
+      </c>
+      <c r="E161" s="65" t="n">
+        <f aca="false">ROUND(C161*0.0775,2)</f>
+        <v>184.62</v>
+      </c>
+      <c r="F161" s="65"/>
+      <c r="G161" s="6" t="n">
+        <f aca="false">ROUND((C161+D161+E161)*0.1,2)</f>
+        <v>300.71</v>
+      </c>
+      <c r="H161" s="66" t="n">
+        <f aca="false">C161+D161+E161+G161</f>
+        <v>3307.765</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="64" t="s">
+        <v>425</v>
+      </c>
+      <c r="B162" s="64"/>
+      <c r="C162" s="6" t="n">
+        <f aca="false">H86+H122</f>
+        <v>1583.305</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <f aca="false">H92+H128</f>
+        <v>440.22</v>
+      </c>
+      <c r="E162" s="65" t="n">
+        <f aca="false">ROUND(C162*0.0775,2)</f>
+        <v>122.71</v>
+      </c>
+      <c r="F162" s="65"/>
+      <c r="G162" s="6" t="n">
+        <f aca="false">ROUND((C162+D162+E162)*0.1,2)</f>
+        <v>214.62</v>
+      </c>
+      <c r="H162" s="66" t="n">
+        <f aca="false">C162+D162+E162+G162</f>
+        <v>2360.855</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A163" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="B163" s="37"/>
+      <c r="C163" s="37"/>
+      <c r="D163" s="37"/>
+      <c r="E163" s="37"/>
+      <c r="F163" s="37"/>
+      <c r="G163" s="37"/>
+      <c r="H163" s="37"/>
+      <c r="I163" s="37"/>
+      <c r="J163" s="37"/>
+      <c r="K163" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -5736,33 +6565,33 @@
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="B75:K75"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="A142:B142"/>
-    <mergeCell ref="E142:F142"/>
-    <mergeCell ref="A143:B143"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="A145:B145"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B93:K93"/>
+    <mergeCell ref="A96:K96"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B126:E126"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="A160:B160"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="A161:B161"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="A162:B162"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="A163:K163"/>
   </mergeCells>
   <conditionalFormatting sqref="A24:J24">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K24="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A28:J28">
+  <conditionalFormatting sqref="A25:J25">
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K28="No"</formula>
+      <formula>$K25="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:J29">
@@ -5780,195 +6609,290 @@
       <formula>$K31="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A32:J32">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K32="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33:J33">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K33="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34:J34">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K34="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A35:J35">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K35="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36:J36">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K36="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A37:J37">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K37="No"</formula>
+  <conditionalFormatting sqref="A40:J40">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K40="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:J38">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K38="No"</formula>
+  <conditionalFormatting sqref="A41:J41">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K41="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42:J42">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K42="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:J43">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K43="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A44:J44">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K44="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45:J45">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K45="No"</formula>
+  <conditionalFormatting sqref="A48:J48">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K48="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46:J46">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K46="No"</formula>
+  <conditionalFormatting sqref="A49:J49">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K49="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50:J50">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K50="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51:J51">
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K51="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:J52">
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K52="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53:J53">
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K53="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A54:J54">
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K54="No"</formula>
+  <conditionalFormatting sqref="A57:J57">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K57="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:J58">
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K58="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A59:J59">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K59="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60:J60">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K60="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61:J61">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K61="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A62:J62">
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K62="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A63:J63">
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K63="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A64:J64">
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K64="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A65:J65">
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K65="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A66:J66">
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K66="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A67:J67">
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K67="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68:J68">
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K68="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A69:J69">
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K69="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70:J70">
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K70="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74:J74">
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K74="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75:J75">
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K75="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A76:J76">
+    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K76="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80:J80">
+    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K80="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A81:J81">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K81="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A82:J82">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K82="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A84:J84">
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K84="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A85:J85">
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K85="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A86:J86">
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K86="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A87:J87">
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K87="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A88:J88">
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K88="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A89:J89">
-    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K89="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A90:J90">
-    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K90="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A91:J91">
-    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K91="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A92:J92">
-    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K92="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A93:J93">
-    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K93="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A95:J95">
-    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K95="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A96:J96">
-    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K96="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A97:J97">
-    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K97="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A99:J99">
-    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K99="No"</formula>
+  <conditionalFormatting sqref="A83:J83">
+    <cfRule type="expression" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K83="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A100:J100">
-    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K100="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A102:J102">
+    <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K102="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A103:J103">
+    <cfRule type="expression" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K103="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A104:J104">
+    <cfRule type="expression" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K104="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A105:J105">
+    <cfRule type="expression" priority="48" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K105="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A106:J106">
+    <cfRule type="expression" priority="49" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K106="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A107:J107">
+    <cfRule type="expression" priority="50" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K107="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A108:J108">
+    <cfRule type="expression" priority="51" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K108="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A109:J109">
+    <cfRule type="expression" priority="52" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K109="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A110:J110">
+    <cfRule type="expression" priority="53" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K110="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A111:J111">
+    <cfRule type="expression" priority="54" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K111="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A112:J112">
+    <cfRule type="expression" priority="55" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K112="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A114:J114">
+    <cfRule type="expression" priority="56" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K114="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A115:J115">
+    <cfRule type="expression" priority="57" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K115="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A116:J116">
+    <cfRule type="expression" priority="58" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K116="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A118:J118">
+    <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K118="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A119:J119">
+    <cfRule type="expression" priority="60" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K119="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K79" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K97" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K102:K103" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K121" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K115:K129" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K133:K146" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24 K28:K31 K35:K38 K42:K46 K50:K54 K58 K62:K65 K82 K84:K93 K95:K97 K99:K100" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24:K25 K29:K36 K40:K44 K48:K53 K57:K70 K74:K76 K80:K83 K100 K102:K112 K114:K116 K118:K119" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -548,7 +548,7 @@
     <t xml:space="preserve">New. Recommended by our design studies so scans are not limited to slow speeds.</t>
   </si>
   <si>
-    <t xml:space="preserve">100 megaohm resistor</t>
+    <t xml:space="preserve">Ohmite SM104031006FE</t>
   </si>
   <si>
     <t xml:space="preserve">5. Frame, sample holder and vibration isolation</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">New. v1 used loose coins, which can shift and cause small jumps.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardware store</t>
+    <t xml:space="preserve">Home Depot</t>
   </si>
   <si>
     <t xml:space="preserve">steel plate or bar offcuts</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">Tip wire</t>
   </si>
   <si>
-    <t xml:space="preserve">Platinum-iridium wire, 0.25 mm thick. Each tip is cut from it with scissors; this metal stays sharp in air. Enough for dozens of tips.</t>
+    <t xml:space="preserve">Platinum-iridium wire, 0.25 mm thick, 20 cm long. Each tip is cut from it with scissors; this metal stays sharp in air. Enough for dozens of tips. Ships from the UK.</t>
   </si>
   <si>
     <t xml:space="preserve">Changed. v1 made its tips from tungsten wire, which corrodes in air. Replaces ready-made tips in the earlier budget at about the same price but many more tips.</t>
   </si>
   <si>
-    <t xml:space="preserve">Advent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt80/Ir20 wire, 0.25 mm, 0.2 m</t>
+    <t xml:space="preserve">Advent Research Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PT671004 (Pt80/Ir20, 0.25 mm, 0.2 m)</t>
   </si>
   <si>
     <t xml:space="preserve">Graphite test sample</t>
@@ -2627,11 +2627,11 @@
       <c r="B6" s="19"/>
       <c r="C6" s="20" t="n">
         <f aca="false">H159</f>
-        <v>2634.65</v>
+        <v>2668.88</v>
       </c>
       <c r="D6" s="21" t="n">
         <f aca="false">H160</f>
-        <v>1687.75</v>
+        <v>1694.7</v>
       </c>
       <c r="E6" s="21"/>
     </row>
@@ -2642,11 +2642,11 @@
       <c r="B7" s="19"/>
       <c r="C7" s="20" t="n">
         <f aca="false">H161</f>
-        <v>3307.765</v>
+        <v>3341.985</v>
       </c>
       <c r="D7" s="21" t="n">
         <f aca="false">H162</f>
-        <v>2360.855</v>
+        <v>2367.815</v>
       </c>
       <c r="E7" s="21"/>
     </row>
@@ -2657,7 +2657,7 @@
       <c r="B8" s="22"/>
       <c r="C8" s="23" t="n">
         <f aca="false">H154</f>
-        <v>2634.65</v>
+        <v>2668.88</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
@@ -3741,17 +3741,17 @@
         <v>2</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>3</v>
+        <v>5.73</v>
       </c>
       <c r="H53" s="30" t="n">
         <f aca="false">IF(K53="No",0,F53*G53)</f>
-        <v>6</v>
+        <v>11.46</v>
       </c>
       <c r="I53" s="33" t="s">
         <v>96</v>
       </c>
       <c r="J53" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/result?keywords=100M%20ohm%20resistor","Open")</f>
+        <f aca="false">HYPERLINK("https://octopart.com/search?q=SM104031006FE","Open")</f>
         <v>Open</v>
       </c>
       <c r="K53" s="32" t="s">
@@ -3770,7 +3770,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="9" t="n">
         <f aca="false">SUM(H48:H53)</f>
-        <v>92.37</v>
+        <v>97.83</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="8"/>
@@ -4172,7 +4172,7 @@
         <v>220</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
       <c r="E67" s="28" t="s">
         <v>221</v>
@@ -4283,7 +4283,7 @@
         <v>233</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>216</v>
+        <v>88</v>
       </c>
       <c r="E70" s="28" t="s">
         <v>234</v>
@@ -4664,7 +4664,7 @@
       <c r="G86" s="35"/>
       <c r="H86" s="36" t="n">
         <f aca="false">H26+H37+H45+H54+H71+H77+H84</f>
-        <v>1171.19</v>
+        <v>1176.65</v>
       </c>
       <c r="I86" s="35"/>
       <c r="J86" s="35"/>
@@ -4727,7 +4727,7 @@
       <c r="E91" s="27"/>
       <c r="H91" s="30" t="n">
         <f aca="false">ROUND(0.08*(H42+H50+H51+H53+H81),2)</f>
-        <v>5.14</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4742,7 +4742,7 @@
       <c r="G92" s="35"/>
       <c r="H92" s="36" t="n">
         <f aca="false">SUM(H89:H91)</f>
-        <v>272.36</v>
+        <v>272.8</v>
       </c>
       <c r="I92" s="35"/>
       <c r="J92" s="35"/>
@@ -5773,17 +5773,17 @@
         <v>1</v>
       </c>
       <c r="G133" s="30" t="n">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="H133" s="30" t="n">
         <f aca="false">IF(OR(K133="Yes",K133=TRUE()),0,F133*G133)</f>
-        <v>274</v>
-      </c>
-      <c r="I133" s="33" t="s">
-        <v>96</v>
+        <v>297</v>
+      </c>
+      <c r="I133" s="29" t="s">
+        <v>103</v>
       </c>
       <c r="J133" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.advent-rm.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.advent-rm.com/en-GB/Products/Alloys/Platinum-Iridium/Form/Wire/Line/PT6710","Open")</f>
         <v>Open</v>
       </c>
       <c r="K133" s="53"/>
@@ -6255,7 +6255,7 @@
       <c r="G147" s="55"/>
       <c r="H147" s="56" t="n">
         <f aca="false">SUM(H133:H146)</f>
-        <v>798.91</v>
+        <v>821.91</v>
       </c>
       <c r="I147" s="55"/>
       <c r="J147" s="55"/>
@@ -6290,7 +6290,7 @@
       <c r="G150" s="59"/>
       <c r="H150" s="60" t="n">
         <f aca="false">H86+IF((K97="Yes"),H122,0)+H147</f>
-        <v>1970.1</v>
+        <v>1998.56</v>
       </c>
       <c r="I150" s="59"/>
       <c r="J150" s="59"/>
@@ -6308,7 +6308,7 @@
       <c r="G151" s="59"/>
       <c r="H151" s="60" t="n">
         <f aca="false">H92+IF((K97="Yes"),H128,0)</f>
-        <v>272.36</v>
+        <v>272.8</v>
       </c>
       <c r="I151" s="59"/>
       <c r="J151" s="59"/>
@@ -6328,7 +6328,7 @@
       <c r="G152" s="59"/>
       <c r="H152" s="60" t="n">
         <f aca="false">ROUND(H150*0.0775,2)</f>
-        <v>152.68</v>
+        <v>154.89</v>
       </c>
       <c r="I152" s="59"/>
       <c r="J152" s="59"/>
@@ -6348,7 +6348,7 @@
       <c r="G153" s="59"/>
       <c r="H153" s="60" t="n">
         <f aca="false">ROUND((H150+H151+H152)*0.1,2)</f>
-        <v>239.51</v>
+        <v>242.63</v>
       </c>
       <c r="I153" s="59"/>
       <c r="J153" s="59"/>
@@ -6366,7 +6366,7 @@
       <c r="G154" s="12"/>
       <c r="H154" s="13" t="n">
         <f aca="false">H150+H151+H152+H153</f>
-        <v>2634.65</v>
+        <v>2668.88</v>
       </c>
       <c r="I154" s="12"/>
       <c r="J154" s="12"/>
@@ -6386,7 +6386,7 @@
       <c r="G155" s="59"/>
       <c r="H155" s="60" t="n">
         <f aca="false">2000-H154</f>
-        <v>-634.65</v>
+        <v>-668.88</v>
       </c>
       <c r="I155" s="59"/>
       <c r="J155" s="59"/>
@@ -6429,24 +6429,24 @@
       <c r="B159" s="64"/>
       <c r="C159" s="6" t="n">
         <f aca="false">H86+SUMPRODUCT(F133:F146,G133:G146)</f>
-        <v>1970.1</v>
+        <v>1998.56</v>
       </c>
       <c r="D159" s="6" t="n">
         <f aca="false">H92</f>
-        <v>272.36</v>
+        <v>272.8</v>
       </c>
       <c r="E159" s="65" t="n">
         <f aca="false">ROUND(C159*0.0775,2)</f>
-        <v>152.68</v>
+        <v>154.89</v>
       </c>
       <c r="F159" s="65"/>
       <c r="G159" s="6" t="n">
         <f aca="false">ROUND((C159+D159+E159)*0.1,2)</f>
-        <v>239.51</v>
+        <v>242.63</v>
       </c>
       <c r="H159" s="66" t="n">
         <f aca="false">C159+D159+E159+G159</f>
-        <v>2634.65</v>
+        <v>2668.88</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6456,24 +6456,24 @@
       <c r="B160" s="64"/>
       <c r="C160" s="6" t="n">
         <f aca="false">H86</f>
-        <v>1171.19</v>
+        <v>1176.65</v>
       </c>
       <c r="D160" s="6" t="n">
         <f aca="false">H92</f>
-        <v>272.36</v>
+        <v>272.8</v>
       </c>
       <c r="E160" s="65" t="n">
         <f aca="false">ROUND(C160*0.0775,2)</f>
-        <v>90.77</v>
+        <v>91.19</v>
       </c>
       <c r="F160" s="65"/>
       <c r="G160" s="6" t="n">
         <f aca="false">ROUND((C160+D160+E160)*0.1,2)</f>
-        <v>153.43</v>
+        <v>154.06</v>
       </c>
       <c r="H160" s="66" t="n">
         <f aca="false">C160+D160+E160+G160</f>
-        <v>1687.75</v>
+        <v>1694.7</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6483,24 +6483,24 @@
       <c r="B161" s="64"/>
       <c r="C161" s="6" t="n">
         <f aca="false">H86+H122+SUMPRODUCT(F133:F146,G133:G146)</f>
-        <v>2382.215</v>
+        <v>2410.675</v>
       </c>
       <c r="D161" s="6" t="n">
         <f aca="false">H92+H128</f>
-        <v>440.22</v>
+        <v>440.66</v>
       </c>
       <c r="E161" s="65" t="n">
         <f aca="false">ROUND(C161*0.0775,2)</f>
-        <v>184.62</v>
+        <v>186.83</v>
       </c>
       <c r="F161" s="65"/>
       <c r="G161" s="6" t="n">
         <f aca="false">ROUND((C161+D161+E161)*0.1,2)</f>
-        <v>300.71</v>
+        <v>303.82</v>
       </c>
       <c r="H161" s="66" t="n">
         <f aca="false">C161+D161+E161+G161</f>
-        <v>3307.765</v>
+        <v>3341.985</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6510,24 +6510,24 @@
       <c r="B162" s="64"/>
       <c r="C162" s="6" t="n">
         <f aca="false">H86+H122</f>
-        <v>1583.305</v>
+        <v>1588.765</v>
       </c>
       <c r="D162" s="6" t="n">
         <f aca="false">H92+H128</f>
-        <v>440.22</v>
+        <v>440.66</v>
       </c>
       <c r="E162" s="65" t="n">
         <f aca="false">ROUND(C162*0.0775,2)</f>
-        <v>122.71</v>
+        <v>123.13</v>
       </c>
       <c r="F162" s="65"/>
       <c r="G162" s="6" t="n">
         <f aca="false">ROUND((C162+D162+E162)*0.1,2)</f>
-        <v>214.62</v>
+        <v>215.26</v>
       </c>
       <c r="H162" s="66" t="n">
         <f aca="false">C162+D162+E162+G162</f>
-        <v>2360.855</v>
+        <v>2367.815</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="435">
   <si>
     <t xml:space="preserve">STM v1: what it actually cost</t>
   </si>
@@ -77,6 +77,12 @@
     <t xml:space="preserve">Adjustment screws (FAS200, 2 in long: longer than the design needs)</t>
   </si>
   <si>
+    <t xml:space="preserve">Brass bushings for the adjustment screws (Base Lab Tools, June)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/4-80 brass bushings (TB250-80-0438, 0.44 in long), pressed into the printed frame</t>
+  </si>
+  <si>
     <t xml:space="preserve">Electronic parts (DigiKey, three orders)</t>
   </si>
   <si>
@@ -176,7 +182,7 @@
     <t xml:space="preserve">Parts and costs to build a second scanning tunneling microscope (v2) at UCSD, improving on the first one we built (v1). Prices checked 21 October 2026, in US dollars.</t>
   </si>
   <si>
-    <t xml:space="preserve">To choose what to fund, set the last column of any line to Yes or No. No takes that line out of every total. All lines start as Yes.</t>
+    <t xml:space="preserve">To choose what to fund, set the last column of any line to Yes or No. No takes that line out of every total. Lines start as Yes, except the few marked optional, which start as No.</t>
   </si>
   <si>
     <t xml:space="preserve">Summary: total cost</t>
@@ -242,7 +248,7 @@
     <t xml:space="preserve">Price source</t>
   </si>
   <si>
-    <t xml:space="preserve">Catalog: the seller's listed price. v1 receipt: what we paid for the same item for v1 in 2026. Estimate: a typical price, to be confirmed by quote.</t>
+    <t xml:space="preserve">Catalog: the seller's listed price. v1 receipt: what we paid for the same item for v1 in 2026. Estimate: a typical price, to be confirmed by quote. Our design: printed by us, so it costs only plastic.</t>
   </si>
   <si>
     <t xml:space="preserve">What the totals include</t>
@@ -368,7 +374,7 @@
     <t xml:space="preserve">Metal sleeves set into the 3D-printed frame, so the screws turn in metal instead of plastic.</t>
   </si>
   <si>
-    <t xml:space="preserve">New. In v1 the screws turned directly in plastic, which wears and loosens.</t>
+    <t xml:space="preserve">Changed. v1 used 3 brass bushings for its 1/4-80 screws (Base Lab Tools, $19.68 plus shipping, see the v1 tab). v2 uses Thorlabs' matching bushings, made for the shorter FAS125 screws.</t>
   </si>
   <si>
     <t xml:space="preserve">F25SSN1</t>
@@ -389,25 +395,31 @@
     <t xml:space="preserve">Flexible motor coupling</t>
   </si>
   <si>
-    <t xml:space="preserve">Connects the motor to the adjustment screw while letting the screw float, so the motor does not push the sample sideways.</t>
+    <t xml:space="preserve">Printed flexible part that connects the motor to the adjustment screw while letting the screw float, so the motor does not push the sample sideways. Printed on our own printer from a redesigned v1 file; costs only plastic (the 3D printer filament line).</t>
   </si>
   <si>
     <t xml:space="preserve">New. A rigid link bends the screw as it turns.</t>
   </si>
   <si>
-    <t xml:space="preserve">flexible shaft coupling, 5 mm</t>
+    <t xml:space="preserve">Printed by us</t>
+  </si>
+  <si>
+    <t xml:space="preserve">printed flexure coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our design</t>
   </si>
   <si>
     <t xml:space="preserve">Manual sideways stage</t>
   </si>
   <si>
-    <t xml:space="preserve">Small hand-adjusted slide that moves the tip sideways onto a clean area of the sample, watched through the USB microscope (section 9).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. v1 could only land the tip wherever it happened to be.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">small manual XY linear stage</t>
+    <t xml:space="preserve">Printed slide, moved by hand with a fine screw, that shifts the tip sideways onto a clean area of the sample, watched through the USB microscope (section 9). Printed on our own printer from a redesigned v1 file; costs only plastic and a screw from the kits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 could only land the tip wherever it happened to be. Printed rather than bought: a little less precise than a metal stage, which is enough for picking a clean spot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">printed slide + fine screw</t>
   </si>
   <si>
     <t xml:space="preserve">Backup approach parts (optional)</t>
@@ -726,6 +738,18 @@
   </si>
   <si>
     <t xml:space="preserve">hardened seats and clamping hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brass heat-set inserts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small threaded brass inserts melted into the 3D-printed parts with a soldering iron, so ordinary small screws grip metal threads instead of plastic. Kit of assorted sizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as v1 (Nefuree kit, $9.99 on the v1 receipts). v1's kit is used up or stays with v1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nefuree M2/M3/M4 heat-set insert kit</t>
   </si>
   <si>
     <t xml:space="preserve">6. Temperature and humidity</t>
@@ -1308,9 +1332,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1547,7 +1572,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1570,6 +1595,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1660,11 +1689,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1672,7 +1697,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1694,6 +1719,10 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1730,6 +1759,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -2076,7 +2109,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -2118,91 +2151,91 @@
       <c r="D5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>419.27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>60.34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>5.04</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="7" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="7" t="n">
         <v>-20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>50.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>163.48</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="7" t="n">
         <v>29.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9" t="n">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10" t="n">
         <f aca="false">SUM(C6:C13)</f>
         <v>710.03</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
@@ -2212,43 +2245,43 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="7" t="n">
         <v>26.34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="7" t="n">
         <v>15.26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>1.65</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="9" t="n">
+      <c r="B20" s="9"/>
+      <c r="C20" s="10" t="n">
         <f aca="false">SUM(C17:C19)</f>
         <v>43.25</v>
       </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
@@ -2258,304 +2291,350 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>19.68</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>12.82</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10" t="n">
+        <f aca="false">SUM(C23:C25)</f>
+        <v>32.5</v>
+      </c>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C29" s="7" t="n">
         <v>32.7</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="0" t="n">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C30" s="7" t="n">
         <v>3.04</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B25" s="0" t="n">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C31" s="7" t="n">
         <v>5.62</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="0" t="n">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C32" s="7" t="n">
         <v>4.18</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C33" s="7" t="n">
         <v>25.47</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C34" s="7" t="n">
         <v>4.67</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C35" s="7" t="n">
         <v>3.14</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9" t="n">
-        <f aca="false">SUM(C23:C29)</f>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10" t="n">
+        <f aca="false">SUM(C29:C35)</f>
         <v>78.82</v>
       </c>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" s="6" t="n">
+      <c r="D36" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="7" t="n">
         <v>45.09</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="6" t="n">
+      <c r="D39" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="7" t="n">
         <v>57.38</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D40" s="11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>33.97</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>36.96</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>43.22</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>42.74</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>57.99</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>10.09</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="6" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>34.97</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>43.22</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="6" t="n">
-        <v>42.74</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>57.99</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>8.19</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>10.09</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>19.79</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>19.16</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>20.87</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="7" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9" t="n">
-        <f aca="false">SUM(C33:C52)</f>
+      <c r="B59" s="9"/>
+      <c r="C59" s="10" t="n">
+        <f aca="false">SUM(C39:C58)</f>
         <v>543.83</v>
       </c>
-      <c r="D53" s="8"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="13" t="n">
-        <f aca="false">C14+C20+C30+C53</f>
-        <v>1375.93</v>
-      </c>
-      <c r="D55" s="12"/>
+      <c r="D59" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="14" t="n">
+        <f aca="false">C14+C20+C26+C36+C59</f>
+        <v>1408.43</v>
+      </c>
+      <c r="D61" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2573,7 +2652,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -2591,285 +2670,285 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
-        <v>51</v>
+      <c r="A3" s="15" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
-        <v>52</v>
+      <c r="A4" s="16" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="18"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="20" t="n">
-        <f aca="false">H159</f>
-        <v>2668.88</v>
-      </c>
-      <c r="D6" s="21" t="n">
+      <c r="A6" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="20"/>
+      <c r="C6" s="21" t="n">
         <f aca="false">H160</f>
-        <v>1694.7</v>
-      </c>
-      <c r="E6" s="21"/>
+        <v>2619.08</v>
+      </c>
+      <c r="D6" s="22" t="n">
+        <f aca="false">H161</f>
+        <v>1644.91</v>
+      </c>
+      <c r="E6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="20" t="n">
-        <f aca="false">H161</f>
-        <v>3341.985</v>
-      </c>
-      <c r="D7" s="21" t="n">
+      <c r="A7" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21" t="n">
         <f aca="false">H162</f>
-        <v>2367.815</v>
-      </c>
-      <c r="E7" s="21"/>
+        <v>3292.185</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <f aca="false">H163</f>
+        <v>2318.015</v>
+      </c>
+      <c r="E7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="23" t="n">
-        <f aca="false">H154</f>
-        <v>2668.88</v>
-      </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
+      <c r="A8" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="24" t="n">
+        <f aca="false">H155</f>
+        <v>2619.08</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20" t="n">
-        <f aca="false">'v1 (what it cost)'!C55</f>
-        <v>1375.93</v>
-      </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="A9" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="n">
+        <f aca="false">'v1 (what it cost)'!C61</f>
+        <v>1408.43</v>
+      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>59</v>
+      <c r="A11" s="16" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
+      <c r="A12" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+      <c r="K12" s="28"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
+      <c r="A13" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
+      <c r="A14" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
+      <c r="A15" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="K22" s="18" t="s">
         <v>66</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-    </row>
-    <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="H22" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -2882,21 +2961,21 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="28" t="s">
+    <row r="24" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="B24" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="C24" s="6" t="s">
         <v>89</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F24" s="29" t="n">
         <v>1</v>
@@ -2909,31 +2988,31 @@
         <v>5</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J24" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=JESSINIE+18mm+piezo+disc","Open")</f>
         <v>Open</v>
       </c>
       <c r="K24" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="28" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="28" t="s">
+      <c r="B25" s="6" t="s">
         <v>95</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="F25" s="29" t="n">
         <v>1</v>
@@ -2946,37 +3025,37 @@
         <v>8</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J25" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=7BB-12-9+piezo+12mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K25" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="9" t="n">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="10" t="n">
         <f aca="false">SUM(H24:H25)</f>
         <v>13</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -2989,21 +3068,21 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="28" t="s">
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="B29" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="C29" s="6" t="s">
         <v>102</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="F29" s="29" t="n">
         <v>1</v>
@@ -3016,31 +3095,31 @@
         <v>14</v>
       </c>
       <c r="I29" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J29" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.adafruit.com/product/324","Open")</f>
         <v>Open</v>
       </c>
       <c r="K29" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D30" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="28" t="s">
+      <c r="B30" s="6" t="s">
         <v>107</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="F30" s="29" t="n">
         <v>1</v>
@@ -3053,31 +3132,31 @@
         <v>8.95</v>
       </c>
       <c r="I30" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J30" s="31" t="str">
         <f aca="false">HYPERLINK("https://adafruit.com/product/6121","Open")</f>
         <v>Open</v>
       </c>
       <c r="K30" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="B31" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="C31" s="6" t="s">
         <v>112</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="F31" s="29" t="n">
         <v>3</v>
@@ -3090,31 +3169,31 @@
         <v>24</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J31" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=FAS125","Open")</f>
         <v>Open</v>
       </c>
       <c r="K31" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="28" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" s="28" t="s">
-        <v>116</v>
+      <c r="E32" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="F32" s="29" t="n">
         <v>3</v>
@@ -3127,31 +3206,31 @@
         <v>25.8</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J32" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.thorlabs.com/thorproduct.cfm?partnumber=F25SSN1","Open")</f>
         <v>Open</v>
       </c>
       <c r="K32" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C33" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D33" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="28" t="s">
+      <c r="B33" s="6" t="s">
         <v>120</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="F33" s="29" t="n">
         <v>1</v>
@@ -3164,105 +3243,105 @@
         <v>15</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J33" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=push+pull+force+gauge+small","Open")</f>
         <v>Open</v>
       </c>
       <c r="K33" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="s">
-        <v>121</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="C34" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D34" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="28" t="s">
+      <c r="B34" s="6" t="s">
         <v>124</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="F34" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H34" s="30" t="n">
         <f aca="false">IF(K34="No",0,F34*G34)</f>
-        <v>12</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>96</v>
+        <v>0</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>128</v>
       </c>
       <c r="J34" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=flexible+shaft+coupling+5mm","Open")</f>
+        <f aca="false">HYPERLINK("https://github.com/jacobbkatz/We-Are-STMING/tree/main/CAD/prints","Open")</f>
         <v>Open</v>
       </c>
       <c r="K34" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>128</v>
+      <c r="E35" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="F35" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H35" s="30" t="n">
         <f aca="false">IF(K35="No",0,F35*G35)</f>
-        <v>40</v>
-      </c>
-      <c r="I35" s="33" t="s">
-        <v>96</v>
+        <v>0</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>128</v>
       </c>
       <c r="J35" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=manual+xy+linear+stage+40mm","Open")</f>
+        <f aca="false">HYPERLINK("https://github.com/jacobbkatz/We-Are-STMING/tree/main/CAD/prints","Open")</f>
         <v>Open</v>
       </c>
       <c r="K35" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="28" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="28" t="s">
-        <v>132</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="F36" s="29" t="n">
         <v>1</v>
@@ -3275,37 +3354,37 @@
         <v>0</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J36" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=piezo+stack+actuator+5x5mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K36" s="32" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="9" t="n">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10" t="n">
         <f aca="false">SUM(H29:H36)</f>
-        <v>139.75</v>
-      </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
+        <v>87.75</v>
+      </c>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3318,21 +3397,21 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E40" s="28" t="s">
+    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
         <v>139</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="F40" s="29" t="n">
         <v>2</v>
@@ -3345,31 +3424,31 @@
         <v>419.28</v>
       </c>
       <c r="I40" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J40" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K40" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>142</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="F41" s="29" t="n">
         <v>3</v>
@@ -3382,31 +3461,31 @@
         <v>5.04</v>
       </c>
       <c r="I41" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J41" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K41" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C42" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" s="28" t="s">
-        <v>146</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="F42" s="29" t="n">
         <v>2</v>
@@ -3419,31 +3498,31 @@
         <v>36.52</v>
       </c>
       <c r="I42" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J42" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
         <v>Open</v>
       </c>
       <c r="K42" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C43" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E43" s="28" t="s">
-        <v>150</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="F43" s="29" t="n">
         <v>1</v>
@@ -3456,31 +3535,31 @@
         <v>31.5</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J43" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
         <v>Open</v>
       </c>
       <c r="K43" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="C44" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="D44" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="28" t="s">
-        <v>154</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="F44" s="29" t="n">
         <v>1</v>
@@ -3493,37 +3572,37 @@
         <v>15</v>
       </c>
       <c r="I44" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J44" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=high+value+resistor+assortment+100M","Open")</f>
         <v>Open</v>
       </c>
       <c r="K44" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="9" t="n">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="10" t="n">
         <f aca="false">SUM(H40:H44)</f>
         <v>507.34</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -3536,21 +3615,21 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="28" t="s">
-        <v>159</v>
+    <row r="48" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="F48" s="29" t="n">
         <v>2</v>
@@ -3563,31 +3642,31 @@
         <v>60.34</v>
       </c>
       <c r="I48" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J48" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K48" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>142</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="F49" s="29" t="n">
         <v>3</v>
@@ -3600,31 +3679,31 @@
         <v>2.4</v>
       </c>
       <c r="I49" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J49" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>164</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="F50" s="29" t="n">
         <v>2</v>
@@ -3637,31 +3716,31 @@
         <v>11.46</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J50" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
         <v>Open</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>167</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="F51" s="29" t="n">
         <v>2</v>
@@ -3674,31 +3753,31 @@
         <v>4.18</v>
       </c>
       <c r="I51" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J51" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
         <v>Open</v>
       </c>
       <c r="K51" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E52" s="28" t="s">
-        <v>171</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="F52" s="29" t="n">
         <v>1</v>
@@ -3711,31 +3790,31 @@
         <v>7.99</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J52" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
         <v>Open</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C53" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E53" s="28" t="s">
-        <v>175</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="F53" s="29" t="n">
         <v>2</v>
@@ -3748,37 +3827,37 @@
         <v>11.46</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J53" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/search?q=SM104031006FE","Open")</f>
         <v>Open</v>
       </c>
       <c r="K53" s="32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="9" t="n">
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="10" t="n">
         <f aca="false">SUM(H48:H53)</f>
         <v>97.83</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -3791,21 +3870,21 @@
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
     </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="E57" s="28" t="s">
+    <row r="57" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="6" t="s">
         <v>181</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="F57" s="29" t="n">
         <v>1</v>
@@ -3818,31 +3897,31 @@
         <v>19.99</v>
       </c>
       <c r="I57" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J57" s="31" t="str">
         <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
         <v>Open</v>
       </c>
       <c r="K57" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="28" t="s">
-        <v>182</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="C58" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E58" s="28" t="s">
-        <v>185</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="F58" s="29" t="n">
         <v>1</v>
@@ -3855,31 +3934,31 @@
         <v>9.99</v>
       </c>
       <c r="I58" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J58" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
         <v>Open</v>
       </c>
       <c r="K58" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="E59" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="6" t="s">
         <v>190</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="F59" s="29" t="n">
         <v>1</v>
@@ -3892,31 +3971,31 @@
         <v>30</v>
       </c>
       <c r="I59" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J59" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
         <v>Open</v>
       </c>
       <c r="K59" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="28" t="s">
-        <v>33</v>
-      </c>
-      <c r="B60" s="28" t="s">
-        <v>191</v>
-      </c>
-      <c r="C60" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="28" t="s">
-        <v>193</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="F60" s="29" t="n">
         <v>1</v>
@@ -3929,31 +4008,31 @@
         <v>9.49</v>
       </c>
       <c r="I60" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J60" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
         <v>Open</v>
       </c>
       <c r="K60" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="B61" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="28" t="s">
-        <v>197</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="F61" s="29" t="n">
         <v>2</v>
@@ -3966,31 +4045,31 @@
         <v>27.98</v>
       </c>
       <c r="I61" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J61" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/dp/B0F4CCYHL2","Open")</f>
         <v>Open</v>
       </c>
       <c r="K61" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B62" s="28" t="s">
-        <v>199</v>
-      </c>
-      <c r="C62" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E62" s="28" t="s">
-        <v>201</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="F62" s="29" t="n">
         <v>1</v>
@@ -4003,31 +4082,31 @@
         <v>3</v>
       </c>
       <c r="I62" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J62" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silicone+tubing+small","Open")</f>
         <v>Open</v>
       </c>
       <c r="K62" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="B63" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="C63" s="28" t="s">
-        <v>204</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E63" s="28" t="s">
-        <v>205</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>209</v>
       </c>
       <c r="F63" s="29" t="n">
         <v>2</v>
@@ -4040,31 +4119,31 @@
         <v>17.98</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J63" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=neodymium+bar+magnets+60x10x3mm+12+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K63" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="28" t="s">
-        <v>206</v>
-      </c>
-      <c r="B64" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="C64" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E64" s="28" t="s">
-        <v>208</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="F64" s="29" t="n">
         <v>1</v>
@@ -4077,31 +4156,31 @@
         <v>19.79</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J64" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+6061+aluminum+round+disc+150mm+6mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K64" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="B65" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="C65" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="D65" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E65" s="28" t="s">
-        <v>212</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="F65" s="29" t="n">
         <v>1</v>
@@ -4114,31 +4193,31 @@
         <v>22.78</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J65" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M8+x+400mm+stainless+steel+threaded+rod+4+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K65" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="B66" s="28" t="s">
-        <v>214</v>
-      </c>
-      <c r="C66" s="28" t="s">
-        <v>215</v>
-      </c>
-      <c r="D66" s="29" t="s">
-        <v>216</v>
-      </c>
-      <c r="E66" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="6" t="s">
         <v>217</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="F66" s="29" t="n">
         <v>1</v>
@@ -4151,31 +4230,31 @@
         <v>10</v>
       </c>
       <c r="I66" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J66" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.homedepot.com/s/steel%20plate","Open")</f>
         <v>Open</v>
       </c>
       <c r="K66" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="B67" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="C67" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E67" s="28" t="s">
-        <v>221</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="F67" s="29" t="n">
         <v>1</v>
@@ -4188,31 +4267,31 @@
         <v>30</v>
       </c>
       <c r="I67" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J67" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=large+metal+storage+tin+with+lid","Open")</f>
         <v>Open</v>
       </c>
       <c r="K67" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="B68" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="C68" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="D68" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>225</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="F68" s="29" t="n">
         <v>1</v>
@@ -4225,31 +4304,31 @@
         <v>22</v>
       </c>
       <c r="I68" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J68" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=aluminum+project+box+enclosure","Open")</f>
         <v>Open</v>
       </c>
       <c r="K68" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="B69" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="C69" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="E69" s="28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="6" t="s">
         <v>230</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="F69" s="29" t="n">
         <v>1</v>
@@ -4262,31 +4341,31 @@
         <v>80</v>
       </c>
       <c r="I69" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J69" s="31" t="str">
         <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K69" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="B70" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="C70" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E70" s="28" t="s">
-        <v>234</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="F70" s="29" t="n">
         <v>1</v>
@@ -4299,783 +4378,783 @@
         <v>15</v>
       </c>
       <c r="I70" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J70" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=hardened+steel+dowel+pin+assortment","Open")</f>
         <v>Open</v>
       </c>
       <c r="K70" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="F71" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="30" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="H71" s="30" t="n">
+        <f aca="false">IF(K71="No",0,F71*G71)</f>
+        <v>9.99</v>
+      </c>
+      <c r="I71" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="J71" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Nefuree+heat+set+inserts+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K71" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="9" t="n">
-        <f aca="false">SUM(H57:H70)</f>
-        <v>318</v>
-      </c>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-    </row>
-    <row r="73" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
-    </row>
-    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="D74" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E74" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="F74" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="H74" s="30" t="n">
-        <f aca="false">IF(K74="No",0,F74*G74)</f>
-        <v>25</v>
-      </c>
-      <c r="I74" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J74" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=temperature+humidity+data+logger+USB","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K74" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="B75" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C75" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D75" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E75" s="28" t="s">
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="10" t="n">
+        <f aca="false">SUM(H57:H71)</f>
+        <v>327.99</v>
+      </c>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="s">
         <v>243</v>
+      </c>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="F75" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H75" s="30" t="n">
         <f aca="false">IF(K75="No",0,F75*G75)</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I75" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J75" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silica+gel+packets+airtight+container","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=temperature+humidity+data+logger+USB","Open")</f>
         <v>Open</v>
       </c>
       <c r="K75" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="B76" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="C76" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E76" s="28" t="s">
-        <v>247</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="F76" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H76" s="30" t="n">
         <f aca="false">IF(K76="No",0,F76*G76)</f>
+        <v>10</v>
+      </c>
+      <c r="I76" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J76" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silica+gel+packets+airtight+container","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K76" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="H77" s="30" t="n">
+        <f aca="false">IF(K77="No",0,F77*G77)</f>
         <v>0</v>
       </c>
-      <c r="I76" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J76" s="31" t="str">
+      <c r="I77" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J77" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FDC1004+breakout+board","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K76" s="32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+      <c r="K77" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="9" t="n">
-        <f aca="false">SUM(H74:H76)</f>
+      <c r="B78" s="9"/>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="10" t="n">
+        <f aca="false">SUM(H75:H77)</f>
         <v>35</v>
       </c>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-    </row>
-    <row r="79" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
-      <c r="K79" s="5"/>
-    </row>
-    <row r="80" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="B80" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="C80" s="28" t="s">
-        <v>251</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="E80" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F80" s="29" t="n">
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="5"/>
+      <c r="J80" s="5"/>
+      <c r="K80" s="5"/>
+    </row>
+    <row r="81" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F81" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G80" s="30" t="n">
+      <c r="G81" s="30" t="n">
         <v>21.39</v>
-      </c>
-      <c r="H80" s="30" t="n">
-        <f aca="false">IF(K80="No",0,F80*G80)</f>
-        <v>42.78</v>
-      </c>
-      <c r="I80" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J80" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K80" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="B81" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="C81" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D81" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E81" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F81" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G81" s="30" t="n">
-        <v>0.61</v>
       </c>
       <c r="H81" s="30" t="n">
         <f aca="false">IF(K81="No",0,F81*G81)</f>
-        <v>6.1</v>
+        <v>42.78</v>
       </c>
       <c r="I81" s="29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J81" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
         <v>Open</v>
       </c>
       <c r="K81" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="B82" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="C82" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D82" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="E82" s="28" t="s">
-        <v>261</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="F82" s="29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>10.95</v>
+        <v>0.61</v>
       </c>
       <c r="H82" s="30" t="n">
         <f aca="false">IF(K82="No",0,F82*G82)</f>
+        <v>6.1</v>
+      </c>
+      <c r="I82" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J82" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K82" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F83" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="30" t="n">
         <v>10.95</v>
-      </c>
-      <c r="I82" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J82" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K82" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="B83" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="C83" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="D83" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="E83" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="F83" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G83" s="30" t="n">
-        <v>2.95</v>
       </c>
       <c r="H83" s="30" t="n">
         <f aca="false">IF(K83="No",0,F83*G83)</f>
+        <v>10.95</v>
+      </c>
+      <c r="I83" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J83" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K83" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F84" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H84" s="30" t="n">
+        <f aca="false">IF(K84="No",0,F84*G84)</f>
         <v>5.9</v>
       </c>
-      <c r="I83" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J83" s="31" t="str">
+      <c r="I84" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J84" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K83" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="7" t="s">
+      <c r="K84" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="9" t="n">
-        <f aca="false">SUM(H80:H83)</f>
+      <c r="B85" s="9"/>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="10" t="n">
+        <f aca="false">SUM(H81:H84)</f>
         <v>65.73</v>
       </c>
-      <c r="I84" s="8"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="B86" s="35"/>
-      <c r="C86" s="35"/>
-      <c r="D86" s="35"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="36" t="n">
-        <f aca="false">H26+H37+H45+H54+H71+H77+H84</f>
-        <v>1176.65</v>
-      </c>
-      <c r="I86" s="35"/>
-      <c r="J86" s="35"/>
-      <c r="K86" s="35"/>
-    </row>
-    <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
-      <c r="J88" s="5"/>
-      <c r="K88" s="5"/>
-    </row>
-    <row r="89" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="29" t="s">
+      <c r="I85" s="9"/>
+      <c r="J85" s="9"/>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B87" s="35"/>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="36" t="n">
+        <f aca="false">H26+H37+H45+H54+H72+H78+H85</f>
+        <v>1134.64</v>
+      </c>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="35"/>
+    </row>
+    <row r="89" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+    </row>
+    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B89" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="H89" s="30" t="n">
-        <f aca="false">IF(SUM(H29+H30+H83)&gt;0,10,0)+IF(SUM(H31+H32)&gt;0,15.26,0)+IF(SUM(H40+H41+H48+H49)&gt;0,25,0)+IF(SUM(H42+H50+H51+H53+H81)&gt;0,8.49,0)+IF(SUM(H43)&gt;0,8,0)+IF(SUM(H57)&gt;0,5,0)+IF(SUM(H59)&gt;0,15,0)+IF(SUM(H80+H82)&gt;0,10,0)</f>
+      <c r="B90" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="H90" s="30" t="n">
+        <f aca="false">IF(SUM(H29+H30+H84)&gt;0,10,0)+IF(SUM(H31+H32)&gt;0,15.26,0)+IF(SUM(H40+H41+H48+H49)&gt;0,25,0)+IF(SUM(H42+H50+H51+H53+H82)&gt;0,8.49,0)+IF(SUM(H43)&gt;0,8,0)+IF(SUM(H57)&gt;0,5,0)+IF(SUM(H59)&gt;0,15,0)+IF(SUM(H81+H83)&gt;0,10,0)</f>
         <v>96.75</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="B90" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="H90" s="30" t="n">
+    <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B91" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="H91" s="30" t="n">
         <f aca="false">ROUND(0.35*(H40+H41+H48+H49),2)</f>
         <v>170.47</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="H91" s="30" t="n">
-        <f aca="false">ROUND(0.08*(H42+H50+H51+H53+H81),2)</f>
+    <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B92" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="H92" s="30" t="n">
+        <f aca="false">ROUND(0.08*(H42+H50+H51+H53+H82),2)</f>
         <v>5.58</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="B92" s="35"/>
-      <c r="C92" s="35"/>
-      <c r="D92" s="35"/>
-      <c r="E92" s="35"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="35"/>
-      <c r="H92" s="36" t="n">
-        <f aca="false">SUM(H89:H91)</f>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="36" t="n">
+        <f aca="false">SUM(H90:H92)</f>
         <v>272.8</v>
       </c>
-      <c r="I92" s="35"/>
-      <c r="J92" s="35"/>
-      <c r="K92" s="35"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B93" s="37" t="s">
-        <v>274</v>
-      </c>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="37"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="37"/>
-      <c r="H93" s="37"/>
-      <c r="I93" s="37"/>
-      <c r="J93" s="37"/>
-      <c r="K93" s="37"/>
-    </row>
-    <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="B95" s="39"/>
-      <c r="C95" s="39"/>
-      <c r="D95" s="39"/>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="39"/>
-      <c r="H95" s="39"/>
-      <c r="I95" s="39"/>
-      <c r="J95" s="39"/>
-      <c r="K95" s="39"/>
-    </row>
-    <row r="96" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="B96" s="27"/>
-      <c r="C96" s="27"/>
-      <c r="D96" s="27"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="27"/>
-      <c r="G96" s="27"/>
-      <c r="H96" s="27"/>
-      <c r="I96" s="27"/>
-      <c r="J96" s="27"/>
-      <c r="K96" s="27"/>
-    </row>
-    <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="B97" s="41"/>
-      <c r="C97" s="41"/>
-      <c r="D97" s="41"/>
-      <c r="E97" s="41"/>
-      <c r="F97" s="41"/>
-      <c r="G97" s="41"/>
-      <c r="H97" s="41"/>
-      <c r="I97" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="J97" s="41"/>
-      <c r="K97" s="43" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="B98" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="C98" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="D98" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="E98" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="F98" s="44" t="s">
-        <v>3</v>
-      </c>
-      <c r="G98" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="H98" s="44" t="s">
-        <v>82</v>
-      </c>
-      <c r="I98" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="J98" s="44" t="s">
-        <v>83</v>
-      </c>
+      <c r="I93" s="35"/>
+      <c r="J93" s="35"/>
+      <c r="K93" s="35"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B94" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="38"/>
+      <c r="F94" s="38"/>
+      <c r="G94" s="38"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="38"/>
+      <c r="J94" s="38"/>
+      <c r="K94" s="38"/>
+    </row>
+    <row r="96" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="B96" s="40"/>
+      <c r="C96" s="40"/>
+      <c r="D96" s="40"/>
+      <c r="E96" s="40"/>
+      <c r="F96" s="40"/>
+      <c r="G96" s="40"/>
+      <c r="H96" s="40"/>
+      <c r="I96" s="40"/>
+      <c r="J96" s="40"/>
+      <c r="K96" s="40"/>
+    </row>
+    <row r="97" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="B97" s="28"/>
+      <c r="C97" s="28"/>
+      <c r="D97" s="28"/>
+      <c r="E97" s="28"/>
+      <c r="F97" s="28"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="28"/>
+      <c r="I97" s="28"/>
+      <c r="J97" s="28"/>
+      <c r="K97" s="28"/>
+    </row>
+    <row r="98" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="B98" s="42"/>
+      <c r="C98" s="42"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="J98" s="42"/>
       <c r="K98" s="44" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="45" t="s">
-        <v>279</v>
-      </c>
-      <c r="B99" s="41"/>
-      <c r="C99" s="41"/>
-      <c r="D99" s="41"/>
-      <c r="E99" s="41"/>
-      <c r="F99" s="41"/>
-      <c r="G99" s="41"/>
-      <c r="H99" s="41"/>
-      <c r="I99" s="41"/>
-      <c r="J99" s="41"/>
-      <c r="K99" s="41"/>
-    </row>
-    <row r="100" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="B100" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="C100" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="D100" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="E100" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="F100" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B99" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="C99" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="D99" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E99" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="F99" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="G99" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="H99" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="I99" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="J99" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="K99" s="45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="B100" s="42"/>
+      <c r="C100" s="42"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="42"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="42"/>
+      <c r="H100" s="42"/>
+      <c r="I100" s="42"/>
+      <c r="J100" s="42"/>
+      <c r="K100" s="42"/>
+    </row>
+    <row r="101" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F101" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G100" s="30" t="n">
+      <c r="G101" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="H100" s="30" t="n">
-        <f aca="false">IF(K100="No",0,F100*G100)</f>
+      <c r="H101" s="30" t="n">
+        <f aca="false">IF(K101="No",0,F101*G101)</f>
         <v>131</v>
       </c>
-      <c r="I100" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J100" s="31" t="str">
+      <c r="I101" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J101" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K100" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="45" t="s">
-        <v>284</v>
-      </c>
-      <c r="B101" s="41"/>
-      <c r="C101" s="41"/>
-      <c r="D101" s="41"/>
-      <c r="E101" s="41"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="41"/>
-      <c r="H101" s="41"/>
-      <c r="I101" s="41"/>
-      <c r="J101" s="41"/>
-      <c r="K101" s="41"/>
-    </row>
-    <row r="102" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="B102" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="C102" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="D102" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>288</v>
-      </c>
-      <c r="F102" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="H102" s="30" t="n">
-        <f aca="false">IF(K102="No",0,F102*G102)</f>
-        <v>35</v>
-      </c>
-      <c r="I102" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J102" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K102" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="B103" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="C103" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="D103" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E103" s="28" t="s">
+      <c r="K101" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="46" t="s">
         <v>292</v>
+      </c>
+      <c r="B102" s="42"/>
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="42"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+      <c r="I102" s="42"/>
+      <c r="J102" s="42"/>
+      <c r="K102" s="42"/>
+    </row>
+    <row r="103" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="F103" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="30" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H103" s="30" t="n">
         <f aca="false">IF(K103="No",0,F103*G103)</f>
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I103" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J103" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
         <v>Open</v>
       </c>
       <c r="K103" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="28" t="s">
-        <v>293</v>
-      </c>
-      <c r="B104" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="D104" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E104" s="28" t="s">
-        <v>296</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>300</v>
       </c>
       <c r="F104" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G104" s="30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H104" s="30" t="n">
         <f aca="false">IF(K104="No",0,F104*G104)</f>
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I104" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J104" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
         <v>Open</v>
       </c>
       <c r="K104" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="28" t="s">
-        <v>297</v>
-      </c>
-      <c r="B105" s="28" t="s">
-        <v>298</v>
-      </c>
-      <c r="C105" s="28" t="s">
-        <v>299</v>
-      </c>
-      <c r="D105" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E105" s="28" t="s">
-        <v>300</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>304</v>
       </c>
       <c r="F105" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G105" s="30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H105" s="30" t="n">
         <f aca="false">IF(K105="No",0,F105*G105)</f>
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I105" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J105" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
         <v>Open</v>
       </c>
       <c r="K105" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="B106" s="28" t="s">
-        <v>302</v>
-      </c>
-      <c r="C106" s="28" t="s">
-        <v>303</v>
-      </c>
-      <c r="D106" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E106" s="28" t="s">
-        <v>304</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>308</v>
       </c>
       <c r="F106" s="29" t="n">
         <v>1</v>
@@ -5088,1462 +5167,1499 @@
         <v>10</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J106" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
         <v>Open</v>
       </c>
       <c r="K106" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="B107" s="28" t="s">
-        <v>306</v>
-      </c>
-      <c r="C107" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="D107" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E107" s="28" t="s">
-        <v>308</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="F107" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H107" s="30" t="n">
         <f aca="false">IF(K107="No",0,F107*G107)</f>
+        <v>10</v>
+      </c>
+      <c r="I107" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J107" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K107" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F108" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="30" t="n">
         <v>12</v>
-      </c>
-      <c r="I107" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J107" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K107" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="28" t="s">
-        <v>309</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>310</v>
-      </c>
-      <c r="C108" s="28" t="s">
-        <v>311</v>
-      </c>
-      <c r="D108" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E108" s="28" t="s">
-        <v>312</v>
-      </c>
-      <c r="F108" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G108" s="30" t="n">
-        <v>3</v>
       </c>
       <c r="H108" s="30" t="n">
         <f aca="false">IF(K108="No",0,F108*G108)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J108" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
         <v>Open</v>
       </c>
       <c r="K108" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="28" t="s">
-        <v>313</v>
-      </c>
-      <c r="B109" s="28" t="s">
-        <v>314</v>
-      </c>
-      <c r="C109" s="28" t="s">
-        <v>315</v>
-      </c>
-      <c r="D109" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E109" s="28" t="s">
-        <v>316</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="F109" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G109" s="30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H109" s="30" t="n">
         <f aca="false">IF(K109="No",0,F109*G109)</f>
+        <v>6</v>
+      </c>
+      <c r="I109" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J109" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K109" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F110" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="30" t="n">
         <v>8</v>
-      </c>
-      <c r="I109" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J109" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K109" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="28" t="s">
-        <v>317</v>
-      </c>
-      <c r="B110" s="28" t="s">
-        <v>318</v>
-      </c>
-      <c r="C110" s="28" t="s">
-        <v>319</v>
-      </c>
-      <c r="D110" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" s="28" t="s">
-        <v>320</v>
-      </c>
-      <c r="F110" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" s="30" t="n">
-        <v>0.5</v>
       </c>
       <c r="H110" s="30" t="n">
         <f aca="false">IF(K110="No",0,F110*G110)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I110" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J110" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
         <v>Open</v>
       </c>
       <c r="K110" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="28" t="s">
-        <v>321</v>
-      </c>
-      <c r="B111" s="28" t="s">
-        <v>322</v>
-      </c>
-      <c r="C111" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="D111" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E111" s="28" t="s">
-        <v>324</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="F111" s="29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G111" s="30" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H111" s="30" t="n">
         <f aca="false">IF(K111="No",0,F111*G111)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I111" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J111" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
         <v>Open</v>
       </c>
       <c r="K111" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="28" t="s">
-        <v>325</v>
-      </c>
-      <c r="B112" s="28" t="s">
-        <v>326</v>
-      </c>
-      <c r="C112" s="28" t="s">
-        <v>327</v>
-      </c>
-      <c r="D112" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E112" s="28" t="s">
-        <v>328</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>332</v>
       </c>
       <c r="F112" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="30" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="H112" s="30" t="n">
         <f aca="false">IF(K112="No",0,F112*G112)</f>
+        <v>5</v>
+      </c>
+      <c r="I112" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J112" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K112" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="F113" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="I112" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J112" s="31" t="str">
+      <c r="H113" s="30" t="n">
+        <f aca="false">IF(K113="No",0,F113*G113)</f>
+        <v>40</v>
+      </c>
+      <c r="I113" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J113" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K112" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="45" t="s">
-        <v>329</v>
-      </c>
-      <c r="B113" s="41"/>
-      <c r="C113" s="41"/>
-      <c r="D113" s="41"/>
-      <c r="E113" s="41"/>
-      <c r="F113" s="41"/>
-      <c r="G113" s="41"/>
-      <c r="H113" s="41"/>
-      <c r="I113" s="41"/>
-      <c r="J113" s="41"/>
-      <c r="K113" s="41"/>
-    </row>
-    <row r="114" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="28" t="s">
-        <v>330</v>
-      </c>
-      <c r="B114" s="28" t="s">
-        <v>331</v>
-      </c>
-      <c r="C114" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="D114" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="E114" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="F114" s="29" t="n">
+      <c r="K113" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="B114" s="42"/>
+      <c r="C114" s="42"/>
+      <c r="D114" s="42"/>
+      <c r="E114" s="42"/>
+      <c r="F114" s="42"/>
+      <c r="G114" s="42"/>
+      <c r="H114" s="42"/>
+      <c r="I114" s="42"/>
+      <c r="J114" s="42"/>
+      <c r="K114" s="42"/>
+    </row>
+    <row r="115" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F115" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="G114" s="30" t="n">
+      <c r="G115" s="30" t="n">
         <v>6.725</v>
-      </c>
-      <c r="H114" s="30" t="n">
-        <f aca="false">IF(K114="No",0,F114*G114)</f>
-        <v>33.625</v>
-      </c>
-      <c r="I114" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J114" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K114" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="B115" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="C115" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="D115" s="29" t="s">
-        <v>333</v>
-      </c>
-      <c r="E115" s="28" t="s">
-        <v>338</v>
-      </c>
-      <c r="F115" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="30" t="n">
-        <v>40</v>
       </c>
       <c r="H115" s="30" t="n">
         <f aca="false">IF(K115="No",0,F115*G115)</f>
+        <v>33.625</v>
+      </c>
+      <c r="I115" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J115" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K115" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="F116" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="30" t="n">
         <v>40</v>
-      </c>
-      <c r="I115" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J115" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K115" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="28" t="s">
-        <v>339</v>
-      </c>
-      <c r="B116" s="28" t="s">
-        <v>340</v>
-      </c>
-      <c r="C116" s="28" t="s">
-        <v>337</v>
-      </c>
-      <c r="D116" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E116" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="F116" s="29" t="n">
-        <v>5</v>
-      </c>
-      <c r="G116" s="30" t="n">
-        <v>2</v>
       </c>
       <c r="H116" s="30" t="n">
         <f aca="false">IF(K116="No",0,F116*G116)</f>
+        <v>40</v>
+      </c>
+      <c r="I116" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J116" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K116" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F117" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G117" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" s="30" t="n">
+        <f aca="false">IF(K117="No",0,F117*G117)</f>
         <v>10</v>
       </c>
-      <c r="I116" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J116" s="31" t="str">
+      <c r="I117" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J117" s="31" t="str">
         <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K116" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="45" t="s">
-        <v>341</v>
-      </c>
-      <c r="B117" s="41"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="41"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="41"/>
-      <c r="H117" s="41"/>
-      <c r="I117" s="41"/>
-      <c r="J117" s="41"/>
-      <c r="K117" s="41"/>
-    </row>
-    <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="28" t="s">
-        <v>342</v>
-      </c>
-      <c r="B118" s="28" t="s">
-        <v>343</v>
-      </c>
-      <c r="C118" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="D118" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="E118" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="F118" s="29" t="n">
+      <c r="K117" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="B118" s="42"/>
+      <c r="C118" s="42"/>
+      <c r="D118" s="42"/>
+      <c r="E118" s="42"/>
+      <c r="F118" s="42"/>
+      <c r="G118" s="42"/>
+      <c r="H118" s="42"/>
+      <c r="I118" s="42"/>
+      <c r="J118" s="42"/>
+      <c r="K118" s="42"/>
+    </row>
+    <row r="119" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F119" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G118" s="30" t="n">
+      <c r="G119" s="30" t="n">
         <v>21.39</v>
-      </c>
-      <c r="H118" s="30" t="n">
-        <f aca="false">IF(K118="No",0,F118*G118)</f>
-        <v>21.39</v>
-      </c>
-      <c r="I118" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J118" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K118" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="B119" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="C119" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D119" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="E119" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="F119" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="G119" s="30" t="n">
-        <v>0.61</v>
       </c>
       <c r="H119" s="30" t="n">
         <f aca="false">IF(K119="No",0,F119*G119)</f>
+        <v>21.39</v>
+      </c>
+      <c r="I119" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J119" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K119" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F120" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G120" s="30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H120" s="30" t="n">
+        <f aca="false">IF(K120="No",0,F120*G120)</f>
         <v>6.1</v>
       </c>
-      <c r="I119" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J119" s="31" t="str">
+      <c r="I120" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J120" s="31" t="str">
         <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K119" s="32" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="45" t="s">
-        <v>347</v>
-      </c>
-      <c r="B120" s="41"/>
-      <c r="C120" s="41"/>
-      <c r="D120" s="41"/>
-      <c r="E120" s="41"/>
-      <c r="F120" s="41"/>
-      <c r="G120" s="41"/>
-      <c r="H120" s="41"/>
-      <c r="I120" s="41"/>
-      <c r="J120" s="41"/>
-      <c r="K120" s="41"/>
-    </row>
-    <row r="121" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="28" t="s">
-        <v>348</v>
-      </c>
-      <c r="B121" s="28" t="s">
-        <v>349</v>
-      </c>
-      <c r="C121" s="28" t="s">
-        <v>350</v>
-      </c>
-      <c r="D121" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="E121" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="F121" s="29" t="n">
+      <c r="K120" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="46" t="s">
+        <v>355</v>
+      </c>
+      <c r="B121" s="42"/>
+      <c r="C121" s="42"/>
+      <c r="D121" s="42"/>
+      <c r="E121" s="42"/>
+      <c r="F121" s="42"/>
+      <c r="G121" s="42"/>
+      <c r="H121" s="42"/>
+      <c r="I121" s="42"/>
+      <c r="J121" s="42"/>
+      <c r="K121" s="42"/>
+    </row>
+    <row r="122" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="F122" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G121" s="30" t="n">
+      <c r="G122" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="H121" s="30" t="n">
-        <f aca="false">IF(K121="Yes",F121*G121,0)</f>
+      <c r="H122" s="30" t="n">
+        <f aca="false">IF(K122="Yes",F122*G122,0)</f>
         <v>0</v>
       </c>
-      <c r="I121" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J121" s="31" t="str">
+      <c r="I122" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J122" s="47" t="str">
         <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K121" s="32" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8"/>
-      <c r="D122" s="8"/>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="9" t="n">
-        <f aca="false">SUM(H99:H121)</f>
+      <c r="K122" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="10" t="n">
+        <f aca="false">SUM(H100:H122)</f>
         <v>412.115</v>
       </c>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
-    </row>
-    <row r="124" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="45" t="s">
-        <v>352</v>
-      </c>
-      <c r="B124" s="41"/>
-      <c r="C124" s="41"/>
-      <c r="D124" s="41"/>
-      <c r="E124" s="41"/>
-      <c r="F124" s="41"/>
-      <c r="G124" s="41"/>
-      <c r="H124" s="41"/>
-      <c r="I124" s="41"/>
-      <c r="J124" s="41"/>
-      <c r="K124" s="41"/>
-    </row>
-    <row r="125" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="29" t="s">
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+    </row>
+    <row r="125" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="46" t="s">
+        <v>360</v>
+      </c>
+      <c r="B125" s="42"/>
+      <c r="C125" s="42"/>
+      <c r="D125" s="42"/>
+      <c r="E125" s="42"/>
+      <c r="F125" s="42"/>
+      <c r="G125" s="42"/>
+      <c r="H125" s="42"/>
+      <c r="I125" s="42"/>
+      <c r="J125" s="42"/>
+      <c r="K125" s="42"/>
+    </row>
+    <row r="126" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B125" s="27" t="s">
-        <v>353</v>
-      </c>
-      <c r="C125" s="27"/>
-      <c r="D125" s="27"/>
-      <c r="E125" s="27"/>
-      <c r="H125" s="30" t="n">
-        <f aca="false">IF(SUM(H100+H121)&gt;0,60,0)</f>
+      <c r="B126" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="C126" s="28"/>
+      <c r="D126" s="28"/>
+      <c r="E126" s="28"/>
+      <c r="H126" s="30" t="n">
+        <f aca="false">IF(SUM(H101+H122)&gt;0,60,0)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="29" t="s">
-        <v>269</v>
-      </c>
-      <c r="B126" s="27" t="s">
-        <v>354</v>
-      </c>
-      <c r="C126" s="27"/>
-      <c r="D126" s="27"/>
-      <c r="E126" s="27"/>
-      <c r="H126" s="30" t="n">
-        <f aca="false">ROUND(0.35*(H114+H115+H116),2)</f>
+    <row r="127" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="C127" s="28"/>
+      <c r="D127" s="28"/>
+      <c r="E127" s="28"/>
+      <c r="H127" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H115+H116+H117),2)</f>
         <v>29.27</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="29" t="s">
-        <v>271</v>
-      </c>
-      <c r="B127" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="C127" s="27"/>
-      <c r="D127" s="27"/>
-      <c r="E127" s="27"/>
-      <c r="H127" s="30" t="n">
-        <f aca="false">ROUND(0.1*(H100+H121)+0.08*(H119),2)+IF(SUM(H100+H121)&gt;0,65,0)</f>
+    <row r="128" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B128" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="C128" s="28"/>
+      <c r="D128" s="28"/>
+      <c r="E128" s="28"/>
+      <c r="H128" s="30" t="n">
+        <f aca="false">ROUND(0.1*(H101+H122)+0.08*(H120),2)+IF(SUM(H101+H122)&gt;0,65,0)</f>
         <v>78.59</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B128" s="8"/>
-      <c r="C128" s="8"/>
-      <c r="D128" s="8"/>
-      <c r="E128" s="8"/>
-      <c r="F128" s="8"/>
-      <c r="G128" s="8"/>
-      <c r="H128" s="9" t="n">
-        <f aca="false">SUM(H125:H127)</f>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="B129" s="9"/>
+      <c r="C129" s="9"/>
+      <c r="D129" s="9"/>
+      <c r="E129" s="9"/>
+      <c r="F129" s="9"/>
+      <c r="G129" s="9"/>
+      <c r="H129" s="10" t="n">
+        <f aca="false">SUM(H126:H128)</f>
         <v>167.86</v>
       </c>
-      <c r="I128" s="8"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="8"/>
-    </row>
-    <row r="129" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="46" t="s">
-        <v>357</v>
-      </c>
-      <c r="B129" s="47" t="s">
-        <v>358</v>
-      </c>
-      <c r="C129" s="48"/>
-      <c r="D129" s="48"/>
-      <c r="E129" s="48"/>
-      <c r="F129" s="48"/>
-      <c r="G129" s="48"/>
-      <c r="H129" s="49" t="n">
-        <f aca="false">IF(K97="Yes",H122+H128,0)</f>
+      <c r="I129" s="9"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="9"/>
+    </row>
+    <row r="130" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="48" t="s">
+        <v>365</v>
+      </c>
+      <c r="B130" s="49" t="s">
+        <v>366</v>
+      </c>
+      <c r="C130" s="50"/>
+      <c r="D130" s="50"/>
+      <c r="E130" s="50"/>
+      <c r="F130" s="50"/>
+      <c r="G130" s="50"/>
+      <c r="H130" s="51" t="n">
+        <f aca="false">IF(K98="Yes",H123+H129,0)</f>
         <v>0</v>
       </c>
-      <c r="I129" s="48"/>
-      <c r="J129" s="48"/>
-      <c r="K129" s="48"/>
-    </row>
-    <row r="131" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="B131" s="51"/>
-      <c r="C131" s="51"/>
-      <c r="D131" s="51"/>
-      <c r="E131" s="51"/>
-      <c r="F131" s="51"/>
-      <c r="G131" s="51"/>
-      <c r="H131" s="51"/>
-      <c r="I131" s="51"/>
-      <c r="J131" s="51"/>
-      <c r="K131" s="51"/>
-    </row>
-    <row r="132" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I130" s="50"/>
+      <c r="J130" s="50"/>
+      <c r="K130" s="50"/>
+    </row>
+    <row r="132" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="52" t="s">
+        <v>367</v>
+      </c>
+      <c r="B132" s="53"/>
+      <c r="C132" s="53"/>
+      <c r="D132" s="53"/>
+      <c r="E132" s="53"/>
+      <c r="F132" s="53"/>
+      <c r="G132" s="53"/>
+      <c r="H132" s="53"/>
+      <c r="I132" s="53"/>
+      <c r="J132" s="53"/>
+      <c r="K132" s="53"/>
+    </row>
+    <row r="133" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B132" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C132" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="D132" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="E132" s="52" t="s">
+      <c r="B133" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="F132" s="52" t="s">
+      <c r="C133" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="D133" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="E133" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="F133" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G132" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="H132" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="I132" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="J132" s="52" t="s">
+      <c r="G133" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="K132" s="52" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="B133" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="C133" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="D133" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="E133" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="F133" s="29" t="n">
+      <c r="H133" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="I133" s="54" t="s">
+        <v>74</v>
+      </c>
+      <c r="J133" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="K133" s="54" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F134" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="G133" s="30" t="n">
+      <c r="G134" s="30" t="n">
         <v>297</v>
-      </c>
-      <c r="H133" s="30" t="n">
-        <f aca="false">IF(OR(K133="Yes",K133=TRUE()),0,F133*G133)</f>
-        <v>297</v>
-      </c>
-      <c r="I133" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J133" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.advent-rm.com/en-GB/Products/Alloys/Platinum-Iridium/Form/Wire/Line/PT6710","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K133" s="53"/>
-    </row>
-    <row r="134" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="28" t="s">
-        <v>366</v>
-      </c>
-      <c r="B134" s="28" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="28" t="s">
-        <v>368</v>
-      </c>
-      <c r="D134" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="E134" s="28" t="s">
-        <v>370</v>
-      </c>
-      <c r="F134" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="30" t="n">
-        <v>77</v>
       </c>
       <c r="H134" s="30" t="n">
         <f aca="false">IF(OR(K134="Yes",K134=TRUE()),0,F134*G134)</f>
+        <v>297</v>
+      </c>
+      <c r="I134" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J134" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.advent-rm.com/en-GB/Products/Alloys/Platinum-Iridium/Form/Wire/Line/PT6710","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K134" s="55"/>
+    </row>
+    <row r="135" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="F135" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="30" t="n">
         <v>77</v>
-      </c>
-      <c r="I134" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J134" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K134" s="53"/>
-    </row>
-    <row r="135" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="28" t="s">
-        <v>371</v>
-      </c>
-      <c r="B135" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="C135" s="28" t="s">
-        <v>373</v>
-      </c>
-      <c r="D135" s="29" t="s">
-        <v>374</v>
-      </c>
-      <c r="E135" s="28" t="s">
-        <v>375</v>
-      </c>
-      <c r="F135" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="30" t="n">
-        <v>133.13</v>
       </c>
       <c r="H135" s="30" t="n">
         <f aca="false">IF(OR(K135="Yes",K135=TRUE()),0,F135*G135)</f>
+        <v>77</v>
+      </c>
+      <c r="I135" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J135" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K135" s="55"/>
+    </row>
+    <row r="136" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F136" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="30" t="n">
         <v>133.13</v>
-      </c>
-      <c r="I135" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J135" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K135" s="53"/>
-    </row>
-    <row r="136" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="28" t="s">
-        <v>376</v>
-      </c>
-      <c r="B136" s="28" t="s">
-        <v>377</v>
-      </c>
-      <c r="C136" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="D136" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E136" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="F136" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="30" t="n">
-        <v>25</v>
       </c>
       <c r="H136" s="30" t="n">
         <f aca="false">IF(OR(K136="Yes",K136=TRUE()),0,F136*G136)</f>
+        <v>133.13</v>
+      </c>
+      <c r="I136" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J136" s="47" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K136" s="55"/>
+    </row>
+    <row r="137" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A137" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F137" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="30" t="n">
         <v>25</v>
-      </c>
-      <c r="I136" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J136" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=USB+microscope+with+calibration+slide","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K136" s="53"/>
-    </row>
-    <row r="137" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B137" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="C137" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D137" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E137" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="F137" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="30" t="n">
-        <v>57.99</v>
       </c>
       <c r="H137" s="30" t="n">
         <f aca="false">IF(OR(K137="Yes",K137=TRUE()),0,F137*G137)</f>
+        <v>25</v>
+      </c>
+      <c r="I137" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J137" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=USB+microscope+with+calibration+slide","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K137" s="55"/>
+    </row>
+    <row r="138" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A138" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F138" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="30" t="n">
         <v>57.99</v>
-      </c>
-      <c r="I137" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J137" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K137" s="53"/>
-    </row>
-    <row r="138" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="B138" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C138" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="D138" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E138" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="F138" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="30" t="n">
-        <v>60</v>
       </c>
       <c r="H138" s="30" t="n">
         <f aca="false">IF(OR(K138="Yes",K138=TRUE()),0,F138*G138)</f>
+        <v>57.99</v>
+      </c>
+      <c r="I138" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J138" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K138" s="55"/>
+    </row>
+    <row r="139" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A139" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F139" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="30" t="n">
         <v>60</v>
-      </c>
-      <c r="I138" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J138" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K138" s="53"/>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="B139" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="C139" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D139" s="29" t="s">
-        <v>389</v>
-      </c>
-      <c r="E139" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="F139" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="30" t="n">
-        <v>25.99</v>
       </c>
       <c r="H139" s="30" t="n">
         <f aca="false">IF(OR(K139="Yes",K139=TRUE()),0,F139*G139)</f>
+        <v>60</v>
+      </c>
+      <c r="I139" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J139" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K139" s="55"/>
+    </row>
+    <row r="140" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="F140" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="30" t="n">
         <v>25.99</v>
-      </c>
-      <c r="I139" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="J139" s="31" t="str">
-        <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K139" s="53"/>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="28" t="s">
-        <v>391</v>
-      </c>
-      <c r="B140" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="C140" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D140" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E140" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F140" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="30" t="n">
-        <v>24.97</v>
       </c>
       <c r="H140" s="30" t="n">
         <f aca="false">IF(OR(K140="Yes",K140=TRUE()),0,F140*G140)</f>
+        <v>25.99</v>
+      </c>
+      <c r="I140" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J140" s="47" t="str">
+        <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K140" s="55"/>
+    </row>
+    <row r="141" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F141" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="30" t="n">
         <v>24.97</v>
-      </c>
-      <c r="I140" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J140" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K140" s="53"/>
-    </row>
-    <row r="141" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="B141" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C141" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D141" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E141" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F141" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="30" t="n">
-        <v>11.99</v>
       </c>
       <c r="H141" s="30" t="n">
         <f aca="false">IF(OR(K141="Yes",K141=TRUE()),0,F141*G141)</f>
+        <v>24.97</v>
+      </c>
+      <c r="I141" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J141" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K141" s="55"/>
+    </row>
+    <row r="142" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F142" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="30" t="n">
         <v>11.99</v>
-      </c>
-      <c r="I141" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J141" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K141" s="53"/>
-    </row>
-    <row r="142" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="B142" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="C142" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D142" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E142" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F142" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" s="30" t="n">
-        <v>25.26</v>
       </c>
       <c r="H142" s="30" t="n">
         <f aca="false">IF(OR(K142="Yes",K142=TRUE()),0,F142*G142)</f>
+        <v>11.99</v>
+      </c>
+      <c r="I142" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J142" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K142" s="55"/>
+    </row>
+    <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F143" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="30" t="n">
         <v>25.26</v>
-      </c>
-      <c r="I142" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J142" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K142" s="53"/>
-    </row>
-    <row r="143" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="B143" s="28" t="s">
-        <v>399</v>
-      </c>
-      <c r="C143" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D143" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E143" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F143" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="30" t="n">
-        <v>32.12</v>
       </c>
       <c r="H143" s="30" t="n">
         <f aca="false">IF(OR(K143="Yes",K143=TRUE()),0,F143*G143)</f>
+        <v>25.26</v>
+      </c>
+      <c r="I143" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J143" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K143" s="55"/>
+    </row>
+    <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F144" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="30" t="n">
         <v>32.12</v>
-      </c>
-      <c r="I143" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J143" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K143" s="53"/>
-    </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="28" t="s">
-        <v>400</v>
-      </c>
-      <c r="B144" s="28" t="s">
-        <v>401</v>
-      </c>
-      <c r="C144" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D144" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E144" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F144" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" s="30" t="n">
-        <v>16.98</v>
       </c>
       <c r="H144" s="30" t="n">
         <f aca="false">IF(OR(K144="Yes",K144=TRUE()),0,F144*G144)</f>
+        <v>32.12</v>
+      </c>
+      <c r="I144" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J144" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K144" s="55"/>
+    </row>
+    <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F145" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="30" t="n">
         <v>16.98</v>
-      </c>
-      <c r="I144" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J144" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K144" s="53"/>
-    </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="28" t="s">
-        <v>402</v>
-      </c>
-      <c r="B145" s="28" t="s">
-        <v>403</v>
-      </c>
-      <c r="C145" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D145" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E145" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F145" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" s="30" t="n">
-        <v>22.31</v>
       </c>
       <c r="H145" s="30" t="n">
         <f aca="false">IF(OR(K145="Yes",K145=TRUE()),0,F145*G145)</f>
+        <v>16.98</v>
+      </c>
+      <c r="I145" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J145" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K145" s="55"/>
+    </row>
+    <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A146" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F146" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="30" t="n">
         <v>22.31</v>
-      </c>
-      <c r="I145" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J145" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K145" s="53"/>
-    </row>
-    <row r="146" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="B146" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="C146" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="D146" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E146" s="28" t="s">
-        <v>393</v>
-      </c>
-      <c r="F146" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="30" t="n">
-        <v>12.17</v>
       </c>
       <c r="H146" s="30" t="n">
         <f aca="false">IF(OR(K146="Yes",K146=TRUE()),0,F146*G146)</f>
+        <v>22.31</v>
+      </c>
+      <c r="I146" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J146" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K146" s="55"/>
+    </row>
+    <row r="147" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A147" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="F147" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="30" t="n">
         <v>12.17</v>
       </c>
-      <c r="I146" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J146" s="31" t="str">
+      <c r="H147" s="30" t="n">
+        <f aca="false">IF(OR(K147="Yes",K147=TRUE()),0,F147*G147)</f>
+        <v>12.17</v>
+      </c>
+      <c r="I147" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J147" s="47" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=precision+tweezers+set","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K146" s="53"/>
-    </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="54" t="s">
-        <v>406</v>
-      </c>
-      <c r="B147" s="55"/>
-      <c r="C147" s="55"/>
-      <c r="D147" s="55"/>
-      <c r="E147" s="55"/>
-      <c r="F147" s="55"/>
-      <c r="G147" s="55"/>
-      <c r="H147" s="56" t="n">
-        <f aca="false">SUM(H133:H146)</f>
+      <c r="K147" s="55"/>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="56" t="s">
+        <v>414</v>
+      </c>
+      <c r="B148" s="57"/>
+      <c r="C148" s="57"/>
+      <c r="D148" s="57"/>
+      <c r="E148" s="57"/>
+      <c r="F148" s="57"/>
+      <c r="G148" s="57"/>
+      <c r="H148" s="58" t="n">
+        <f aca="false">SUM(H134:H147)</f>
         <v>821.91</v>
       </c>
-      <c r="I147" s="55"/>
-      <c r="J147" s="55"/>
-      <c r="K147" s="55"/>
-    </row>
-    <row r="149" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
-      <c r="D149" s="16"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="16"/>
-      <c r="H149" s="16"/>
-      <c r="I149" s="16"/>
-      <c r="J149" s="16"/>
-      <c r="K149" s="16"/>
-    </row>
-    <row r="150" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="57" t="s">
-        <v>408</v>
-      </c>
-      <c r="B150" s="58" t="s">
-        <v>409</v>
-      </c>
-      <c r="C150" s="59"/>
-      <c r="D150" s="59"/>
-      <c r="E150" s="59"/>
-      <c r="F150" s="59"/>
-      <c r="G150" s="59"/>
-      <c r="H150" s="60" t="n">
-        <f aca="false">H86+IF((K97="Yes"),H122,0)+H147</f>
-        <v>1998.56</v>
-      </c>
-      <c r="I150" s="59"/>
-      <c r="J150" s="59"/>
-      <c r="K150" s="59"/>
-    </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="57" t="s">
-        <v>273</v>
-      </c>
-      <c r="B151" s="58"/>
-      <c r="C151" s="59"/>
-      <c r="D151" s="59"/>
-      <c r="E151" s="59"/>
-      <c r="F151" s="59"/>
-      <c r="G151" s="59"/>
-      <c r="H151" s="60" t="n">
-        <f aca="false">H92+IF((K97="Yes"),H128,0)</f>
+      <c r="I148" s="57"/>
+      <c r="J148" s="57"/>
+      <c r="K148" s="57"/>
+    </row>
+    <row r="150" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B150" s="17"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
+      <c r="G150" s="17"/>
+      <c r="H150" s="17"/>
+      <c r="I150" s="17"/>
+      <c r="J150" s="17"/>
+      <c r="K150" s="17"/>
+    </row>
+    <row r="151" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="59" t="s">
+        <v>416</v>
+      </c>
+      <c r="B151" s="60" t="s">
+        <v>417</v>
+      </c>
+      <c r="C151" s="61"/>
+      <c r="D151" s="61"/>
+      <c r="E151" s="61"/>
+      <c r="F151" s="61"/>
+      <c r="G151" s="61"/>
+      <c r="H151" s="62" t="n">
+        <f aca="false">H87+IF((K98="Yes"),H123,0)+H148</f>
+        <v>1956.55</v>
+      </c>
+      <c r="I151" s="61"/>
+      <c r="J151" s="61"/>
+      <c r="K151" s="61"/>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="59" t="s">
+        <v>281</v>
+      </c>
+      <c r="B152" s="60"/>
+      <c r="C152" s="61"/>
+      <c r="D152" s="61"/>
+      <c r="E152" s="61"/>
+      <c r="F152" s="61"/>
+      <c r="G152" s="61"/>
+      <c r="H152" s="62" t="n">
+        <f aca="false">H93+IF((K98="Yes"),H129,0)</f>
         <v>272.8</v>
       </c>
-      <c r="I151" s="59"/>
-      <c r="J151" s="59"/>
-      <c r="K151" s="59"/>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="57" t="s">
-        <v>410</v>
-      </c>
-      <c r="B152" s="58" t="s">
-        <v>411</v>
-      </c>
-      <c r="C152" s="59"/>
-      <c r="D152" s="59"/>
-      <c r="E152" s="59"/>
-      <c r="F152" s="59"/>
-      <c r="G152" s="59"/>
-      <c r="H152" s="60" t="n">
-        <f aca="false">ROUND(H150*0.0775,2)</f>
-        <v>154.89</v>
-      </c>
-      <c r="I152" s="59"/>
-      <c r="J152" s="59"/>
-      <c r="K152" s="59"/>
+      <c r="I152" s="61"/>
+      <c r="J152" s="61"/>
+      <c r="K152" s="61"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="57" t="s">
-        <v>412</v>
-      </c>
-      <c r="B153" s="58" t="s">
-        <v>413</v>
-      </c>
-      <c r="C153" s="59"/>
-      <c r="D153" s="59"/>
-      <c r="E153" s="59"/>
-      <c r="F153" s="59"/>
-      <c r="G153" s="59"/>
-      <c r="H153" s="60" t="n">
-        <f aca="false">ROUND((H150+H151+H152)*0.1,2)</f>
-        <v>242.63</v>
-      </c>
-      <c r="I153" s="59"/>
-      <c r="J153" s="59"/>
-      <c r="K153" s="59"/>
+      <c r="A153" s="59" t="s">
+        <v>418</v>
+      </c>
+      <c r="B153" s="60" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="61"/>
+      <c r="D153" s="61"/>
+      <c r="E153" s="61"/>
+      <c r="F153" s="61"/>
+      <c r="G153" s="61"/>
+      <c r="H153" s="62" t="n">
+        <f aca="false">ROUND(H151*0.0775,2)</f>
+        <v>151.63</v>
+      </c>
+      <c r="I153" s="61"/>
+      <c r="J153" s="61"/>
+      <c r="K153" s="61"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="11" t="s">
-        <v>414</v>
-      </c>
-      <c r="B154" s="61"/>
-      <c r="C154" s="12"/>
-      <c r="D154" s="12"/>
-      <c r="E154" s="12"/>
-      <c r="F154" s="12"/>
-      <c r="G154" s="12"/>
-      <c r="H154" s="13" t="n">
-        <f aca="false">H150+H151+H152+H153</f>
-        <v>2668.88</v>
-      </c>
-      <c r="I154" s="12"/>
-      <c r="J154" s="12"/>
-      <c r="K154" s="12"/>
+      <c r="A154" s="59" t="s">
+        <v>420</v>
+      </c>
+      <c r="B154" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="C154" s="61"/>
+      <c r="D154" s="61"/>
+      <c r="E154" s="61"/>
+      <c r="F154" s="61"/>
+      <c r="G154" s="61"/>
+      <c r="H154" s="62" t="n">
+        <f aca="false">ROUND((H151+H152+H153)*0.1,2)</f>
+        <v>238.1</v>
+      </c>
+      <c r="I154" s="61"/>
+      <c r="J154" s="61"/>
+      <c r="K154" s="61"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="57" t="s">
-        <v>415</v>
-      </c>
-      <c r="B155" s="58" t="s">
+      <c r="A155" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B155" s="63"/>
+      <c r="C155" s="13"/>
+      <c r="D155" s="13"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="13"/>
+      <c r="G155" s="13"/>
+      <c r="H155" s="14" t="n">
+        <f aca="false">H151+H152+H153+H154</f>
+        <v>2619.08</v>
+      </c>
+      <c r="I155" s="13"/>
+      <c r="J155" s="13"/>
+      <c r="K155" s="13"/>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="59" t="s">
+        <v>423</v>
+      </c>
+      <c r="B156" s="60" t="s">
+        <v>424</v>
+      </c>
+      <c r="C156" s="61"/>
+      <c r="D156" s="61"/>
+      <c r="E156" s="61"/>
+      <c r="F156" s="61"/>
+      <c r="G156" s="61"/>
+      <c r="H156" s="62" t="n">
+        <f aca="false">2000-H155</f>
+        <v>-619.08</v>
+      </c>
+      <c r="I156" s="61"/>
+      <c r="J156" s="61"/>
+      <c r="K156" s="61"/>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="64" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B159" s="17"/>
+      <c r="C159" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="C155" s="59"/>
-      <c r="D155" s="59"/>
-      <c r="E155" s="59"/>
-      <c r="F155" s="59"/>
-      <c r="G155" s="59"/>
-      <c r="H155" s="60" t="n">
-        <f aca="false">2000-H154</f>
-        <v>-668.88</v>
-      </c>
-      <c r="I155" s="59"/>
-      <c r="J155" s="59"/>
-      <c r="K155" s="59"/>
-    </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="62" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="B158" s="16"/>
-      <c r="C158" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="E158" s="63" t="s">
-        <v>420</v>
-      </c>
-      <c r="F158" s="63"/>
-      <c r="G158" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H158" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="I158" s="16"/>
-      <c r="J158" s="16"/>
-      <c r="K158" s="16"/>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="64" t="s">
-        <v>422</v>
-      </c>
-      <c r="B159" s="64"/>
-      <c r="C159" s="6" t="n">
-        <f aca="false">H86+SUMPRODUCT(F133:F146,G133:G146)</f>
-        <v>1998.56</v>
-      </c>
-      <c r="D159" s="6" t="n">
-        <f aca="false">H92</f>
+      <c r="D159" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E159" s="65" t="s">
+        <v>428</v>
+      </c>
+      <c r="F159" s="65"/>
+      <c r="G159" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I159" s="17"/>
+      <c r="J159" s="17"/>
+      <c r="K159" s="17"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="66" t="s">
+        <v>430</v>
+      </c>
+      <c r="B160" s="66"/>
+      <c r="C160" s="7" t="n">
+        <f aca="false">H87+SUMPRODUCT(F134:F147,G134:G147)</f>
+        <v>1956.55</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <f aca="false">H93</f>
         <v>272.8</v>
       </c>
-      <c r="E159" s="65" t="n">
-        <f aca="false">ROUND(C159*0.0775,2)</f>
-        <v>154.89</v>
-      </c>
-      <c r="F159" s="65"/>
-      <c r="G159" s="6" t="n">
-        <f aca="false">ROUND((C159+D159+E159)*0.1,2)</f>
-        <v>242.63</v>
-      </c>
-      <c r="H159" s="66" t="n">
-        <f aca="false">C159+D159+E159+G159</f>
-        <v>2668.88</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="64" t="s">
-        <v>423</v>
-      </c>
-      <c r="B160" s="64"/>
-      <c r="C160" s="6" t="n">
-        <f aca="false">H86</f>
-        <v>1176.65</v>
-      </c>
-      <c r="D160" s="6" t="n">
-        <f aca="false">H92</f>
+      <c r="E160" s="67" t="n">
+        <f aca="false">ROUND(C160*0.0775,2)</f>
+        <v>151.63</v>
+      </c>
+      <c r="F160" s="67"/>
+      <c r="G160" s="7" t="n">
+        <f aca="false">ROUND((C160+D160+E160)*0.1,2)</f>
+        <v>238.1</v>
+      </c>
+      <c r="H160" s="68" t="n">
+        <f aca="false">C160+D160+E160+G160</f>
+        <v>2619.08</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="66" t="s">
+        <v>431</v>
+      </c>
+      <c r="B161" s="66"/>
+      <c r="C161" s="7" t="n">
+        <f aca="false">H87</f>
+        <v>1134.64</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <f aca="false">H93</f>
         <v>272.8</v>
       </c>
-      <c r="E160" s="65" t="n">
-        <f aca="false">ROUND(C160*0.0775,2)</f>
-        <v>91.19</v>
-      </c>
-      <c r="F160" s="65"/>
-      <c r="G160" s="6" t="n">
-        <f aca="false">ROUND((C160+D160+E160)*0.1,2)</f>
-        <v>154.06</v>
-      </c>
-      <c r="H160" s="66" t="n">
-        <f aca="false">C160+D160+E160+G160</f>
-        <v>1694.7</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="64" t="s">
-        <v>424</v>
-      </c>
-      <c r="B161" s="64"/>
-      <c r="C161" s="6" t="n">
-        <f aca="false">H86+H122+SUMPRODUCT(F133:F146,G133:G146)</f>
-        <v>2410.675</v>
-      </c>
-      <c r="D161" s="6" t="n">
-        <f aca="false">H92+H128</f>
+      <c r="E161" s="67" t="n">
+        <f aca="false">ROUND(C161*0.0775,2)</f>
+        <v>87.93</v>
+      </c>
+      <c r="F161" s="67"/>
+      <c r="G161" s="7" t="n">
+        <f aca="false">ROUND((C161+D161+E161)*0.1,2)</f>
+        <v>149.54</v>
+      </c>
+      <c r="H161" s="68" t="n">
+        <f aca="false">C161+D161+E161+G161</f>
+        <v>1644.91</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="66" t="s">
+        <v>432</v>
+      </c>
+      <c r="B162" s="66"/>
+      <c r="C162" s="7" t="n">
+        <f aca="false">H87+H123+SUMPRODUCT(F134:F147,G134:G147)</f>
+        <v>2368.665</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <f aca="false">H93+H129</f>
         <v>440.66</v>
       </c>
-      <c r="E161" s="65" t="n">
-        <f aca="false">ROUND(C161*0.0775,2)</f>
-        <v>186.83</v>
-      </c>
-      <c r="F161" s="65"/>
-      <c r="G161" s="6" t="n">
-        <f aca="false">ROUND((C161+D161+E161)*0.1,2)</f>
-        <v>303.82</v>
-      </c>
-      <c r="H161" s="66" t="n">
-        <f aca="false">C161+D161+E161+G161</f>
-        <v>3341.985</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="64" t="s">
-        <v>425</v>
-      </c>
-      <c r="B162" s="64"/>
-      <c r="C162" s="6" t="n">
-        <f aca="false">H86+H122</f>
-        <v>1588.765</v>
-      </c>
-      <c r="D162" s="6" t="n">
-        <f aca="false">H92+H128</f>
+      <c r="E162" s="67" t="n">
+        <f aca="false">ROUND(C162*0.0775,2)</f>
+        <v>183.57</v>
+      </c>
+      <c r="F162" s="67"/>
+      <c r="G162" s="7" t="n">
+        <f aca="false">ROUND((C162+D162+E162)*0.1,2)</f>
+        <v>299.29</v>
+      </c>
+      <c r="H162" s="68" t="n">
+        <f aca="false">C162+D162+E162+G162</f>
+        <v>3292.185</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="66" t="s">
+        <v>433</v>
+      </c>
+      <c r="B163" s="66"/>
+      <c r="C163" s="7" t="n">
+        <f aca="false">H87+H123</f>
+        <v>1546.755</v>
+      </c>
+      <c r="D163" s="7" t="n">
+        <f aca="false">H93+H129</f>
         <v>440.66</v>
       </c>
-      <c r="E162" s="65" t="n">
-        <f aca="false">ROUND(C162*0.0775,2)</f>
-        <v>123.13</v>
-      </c>
-      <c r="F162" s="65"/>
-      <c r="G162" s="6" t="n">
-        <f aca="false">ROUND((C162+D162+E162)*0.1,2)</f>
-        <v>215.26</v>
-      </c>
-      <c r="H162" s="66" t="n">
-        <f aca="false">C162+D162+E162+G162</f>
-        <v>2367.815</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="37" t="s">
-        <v>426</v>
-      </c>
-      <c r="B163" s="37"/>
-      <c r="C163" s="37"/>
-      <c r="D163" s="37"/>
-      <c r="E163" s="37"/>
-      <c r="F163" s="37"/>
-      <c r="G163" s="37"/>
-      <c r="H163" s="37"/>
-      <c r="I163" s="37"/>
-      <c r="J163" s="37"/>
-      <c r="K163" s="37"/>
+      <c r="E163" s="67" t="n">
+        <f aca="false">ROUND(C163*0.0775,2)</f>
+        <v>119.87</v>
+      </c>
+      <c r="F163" s="67"/>
+      <c r="G163" s="7" t="n">
+        <f aca="false">ROUND((C163+D163+E163)*0.1,2)</f>
+        <v>210.73</v>
+      </c>
+      <c r="H163" s="68" t="n">
+        <f aca="false">C163+D163+E163+G163</f>
+        <v>2318.015</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A164" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="B164" s="38"/>
+      <c r="C164" s="38"/>
+      <c r="D164" s="38"/>
+      <c r="E164" s="38"/>
+      <c r="F164" s="38"/>
+      <c r="G164" s="38"/>
+      <c r="H164" s="38"/>
+      <c r="I164" s="38"/>
+      <c r="J164" s="38"/>
+      <c r="K164" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -6565,16 +6681,14 @@
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B89:E89"/>
     <mergeCell ref="B90:E90"/>
     <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B93:K93"/>
-    <mergeCell ref="A96:K96"/>
-    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B94:K94"/>
+    <mergeCell ref="A97:K97"/>
     <mergeCell ref="B126:E126"/>
     <mergeCell ref="B127:E127"/>
-    <mergeCell ref="E158:F158"/>
-    <mergeCell ref="A159:B159"/>
+    <mergeCell ref="B128:E128"/>
     <mergeCell ref="E159:F159"/>
     <mergeCell ref="A160:B160"/>
     <mergeCell ref="E160:F160"/>
@@ -6582,7 +6696,9 @@
     <mergeCell ref="E161:F161"/>
     <mergeCell ref="A162:B162"/>
     <mergeCell ref="E162:F162"/>
-    <mergeCell ref="A163:K163"/>
+    <mergeCell ref="A163:B163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="A164:K164"/>
   </mergeCells>
   <conditionalFormatting sqref="A24:J24">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6759,9 +6875,9 @@
       <formula>$K70="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A74:J74">
+  <conditionalFormatting sqref="A71:J71">
     <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K74="No"</formula>
+      <formula>$K71="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A75:J75">
@@ -6774,9 +6890,9 @@
       <formula>$K76="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80:J80">
+  <conditionalFormatting sqref="A77:J77">
     <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K80="No"</formula>
+      <formula>$K77="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A81:J81">
@@ -6794,14 +6910,14 @@
       <formula>$K83="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A100:J100">
+  <conditionalFormatting sqref="A84:J84">
     <cfRule type="expression" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K100="No"</formula>
+      <formula>$K84="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A102:J102">
+  <conditionalFormatting sqref="A101:J101">
     <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K102="No"</formula>
+      <formula>$K101="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A103:J103">
@@ -6854,9 +6970,9 @@
       <formula>$K112="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A114:J114">
+  <conditionalFormatting sqref="A113:J113">
     <cfRule type="expression" priority="56" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K114="No"</formula>
+      <formula>$K113="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A115:J115">
@@ -6869,9 +6985,9 @@
       <formula>$K116="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A118:J118">
+  <conditionalFormatting sqref="A117:J117">
     <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K118="No"</formula>
+      <formula>$K117="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A119:J119">
@@ -6879,20 +6995,25 @@
       <formula>$K119="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A120:J120">
+    <cfRule type="expression" priority="61" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K120="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K97" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K98" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K121" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K122" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K133:K146" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K134:K147" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24:K25 K29:K36 K40:K44 K48:K53 K57:K70 K74:K76 K80:K83 K100 K102:K112 K114:K116 K118:K119" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24:K25 K29:K36 K40:K44 K48:K53 K57:K71 K75:K77 K81:K84 K101 K103:K113 K115:K117 K119:K120" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/docs/v2-budget/STM_v2_budget.xlsx
+++ b/docs/v2-budget/STM_v2_budget.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="469">
   <si>
     <t xml:space="preserve">STM v1: what it actually cost</t>
   </si>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">Motor</t>
   </si>
   <si>
-    <t xml:space="preserve">Turns one adjustment screw to bring the sample slowly up to the tip. Once the sample is close, the scanner takes over.</t>
+    <t xml:space="preserve">Turns one adjustment screw to bring the sample slowly up to the tip. Once the sample is close, the scanner takes over. Run at low current (about 100 mA) and switched off while imaging, so its heat and electrical noise do not reach the tip.</t>
   </si>
   <si>
     <t xml:space="preserve">New. Replaces v1's low-precision hobby motor. Smaller steps make it less likely to crash the tip into the sample.</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">steel springs + small push-pull force gauge</t>
   </si>
   <si>
-    <t xml:space="preserve">Flexible motor coupling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Printed flexible part that connects the motor to the adjustment screw while letting the screw float, so the motor does not push the sample sideways. Printed on our own printer from a redesigned v1 file; costs only plastic (the 3D printer filament line).</t>
+    <t xml:space="preserve">Printed motor coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printed coupling that turns the adjustment screw but goes slack once the motor stops (a 'lost-motion' coupling), so the parked motor cannot push the screw or carry heat to it. Printed on our own printer from a redesigned v1 file; costs only plastic.</t>
   </si>
   <si>
     <t xml:space="preserve">New. A rigid link bends the screw as it turns.</t>
@@ -410,6 +410,45 @@
     <t xml:space="preserve">Our design</t>
   </si>
   <si>
+    <t xml:space="preserve">Metal motor coupling (optional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small metal coupling to use instead of the printed one if the printed one turns out too springy. Starts as No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optional. Our root-cause study found a soft printed coupling can store small tip movements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metal beam or Oldham coupling, 5 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor standoffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insulating fibreglass (G10) posts that mount the motor outside the enclosure, away from the scanning head.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Keeps the motor's heat away from the tip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G10 or PEEK standoffs, M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shielded motor cable and ferrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shielded twisted cable from the motor driver to the motor, with a clip-on ferrite, so the motor's switching noise does not reach the tip current.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Recommended by our solution study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shielded 4-core cable + clip-on ferrite</t>
+  </si>
+  <si>
     <t xml:space="preserve">Manual sideways stage</t>
   </si>
   <si>
@@ -434,9 +473,6 @@
     <t xml:space="preserve">piezo stack + miniature slide</t>
   </si>
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
     <t xml:space="preserve">3. Main electronics: run the microscope and record the image</t>
   </si>
   <si>
@@ -500,6 +536,15 @@
     <t xml:space="preserve">resistor and capacitor assortment</t>
   </si>
   <si>
+    <t xml:space="preserve">Signal filter parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A few resistors and capacitors that filter the tip signal just before it is digitised, so high-frequency noise does not fold into the image.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resistors + C0G capacitors</t>
+  </si>
+  <si>
     <t xml:space="preserve">4. Signal amplifier: reads the tiny tip current</t>
   </si>
   <si>
@@ -563,6 +608,18 @@
     <t xml:space="preserve">Ohmite SM104031006FE</t>
   </si>
   <si>
+    <t xml:space="preserve">Tiny feedback capacitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assortment of very small capacitors (0.2 to 1.5 pF) to try across the 100 megaohm resistor, which steadies the amplifier and lowers noise. For the 100 megaohm board only; the 1 gigaohm board gets none until it has been measured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Recommended by our design review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C0G capacitor assortment, 0.2 to 1.5 pF</t>
+  </si>
+  <si>
     <t xml:space="preserve">5. Frame, sample holder and vibration isolation</t>
   </si>
   <si>
@@ -692,13 +749,16 @@
     <t xml:space="preserve">Enclosure</t>
   </si>
   <si>
-    <t xml:space="preserve">Steel box lined with foam that covers the whole microscope. Blocks sound and electrical noise and keeps the temperature steady.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. v1 had no cover, so sound, air currents and temperature changes all reached the tip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel box or tin with foam lining</t>
+    <t xml:space="preserve">Box made from 1-inch insulating foam board, seams taped, over the whole microscope. Keeps the temperature steady and blocks air currents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. v1 had no cover, so air currents and temperature changes reached the tip.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owens Corning FOAMULAR 150, 1 in x 4 x 8 ft</t>
   </si>
   <si>
     <t xml:space="preserve">Aluminium shield can</t>
@@ -716,7 +776,7 @@
     <t xml:space="preserve">Metal head and sample plates</t>
   </si>
   <si>
-    <t xml:space="preserve">Stainless steel plates, laser cut by an online service from our drawings: one holds the tip and scanner, the other holds the sample. No machining needed by us. Price needs a quote once the drawings are uploaded.</t>
+    <t xml:space="preserve">Metal plates laser cut by an online service from our drawings: an aluminium plate that holds the tip and scanner, and a mild steel carrier for the sample (not stainless, which magnets do not grip). No machining needed by us. Price needs a quote once the drawings are uploaded.</t>
   </si>
   <si>
     <t xml:space="preserve">New. Stiffer than v1's printed plastic and keeps its shape as the room warms and cools. Our studies found this the biggest single improvement for steady scans.</t>
@@ -728,16 +788,19 @@
     <t xml:space="preserve">laser-cut stainless steel plates</t>
   </si>
   <si>
-    <t xml:space="preserve">Ball seats and clamping hardware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardened steel seats under the three steel balls, and small parts that let magnets clamp the sample holder down firmly.</t>
+    <t xml:space="preserve">Hardened ball seats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardened steel dowel pins, glued into the carrier in pairs, that the three steel balls sit in. Pack of 100.</t>
   </si>
   <si>
     <t xml:space="preserve">New. Stop the balls denting the plastic, so the sample holder stays put.</t>
   </si>
   <si>
-    <t xml:space="preserve">hardened seats and clamping hardware</t>
+    <t xml:space="preserve">AFT Fasteners</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/16 x 15/16 in dowel pins, 100 pack</t>
   </si>
   <si>
     <t xml:space="preserve">Brass heat-set inserts</t>
@@ -752,19 +815,55 @@
     <t xml:space="preserve">Nefuree M2/M3/M4 heat-set insert kit</t>
   </si>
   <si>
+    <t xml:space="preserve">Frame bracing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra braces for the tower and a stiffer frame for the hanging springs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Our design review found the v1 frame flexes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aluminium angle, brackets, screws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine wire and anchors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very thin (36 to 40 gauge) wire for every connection to the hanging platform, with anchor points, so cables do not carry vibration onto it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36-40 AWG wire + adhesive anchors</t>
+  </si>
+  <si>
     <t xml:space="preserve">6. Temperature and humidity</t>
   </si>
   <si>
     <t xml:space="preserve">Temperature and humidity logger</t>
   </si>
   <si>
-    <t xml:space="preserve">Stand-alone recorder inside the enclosure that logs temperature and humidity during every scan.</t>
+    <t xml:space="preserve">Two stand-alone recorders, one inside the enclosure and one in the room, that log temperature and humidity during every scan.</t>
   </si>
   <si>
     <t xml:space="preserve">Changed. Replaces the two sensors wired to the microcontroller in the earlier budget; it works on its own and needs no wiring.</t>
   </si>
   <si>
-    <t xml:space="preserve">temperature and humidity data logger</t>
+    <t xml:space="preserve">Govee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5075, 2-pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature sensors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two precise sensors read by the microcontroller: one on the head plate, one on the motor. Imaging waits until the motor has cooled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Temperature drift is a main cause of v1's unsteady scans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMP117 (4821)</t>
   </si>
   <si>
     <t xml:space="preserve">Silica gel and sealed box</t>
@@ -851,7 +950,7 @@
     <t xml:space="preserve">Shipping and import fees for sections 1 to 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards. A seller's shipping drops out if nothing from that seller is funded.</t>
+    <t xml:space="preserve">Standard shipping, estimated per seller: JLCPCB $25.00, Thorlabs $15.26, Ted Pella $15.00, Adafruit $10.00, Battery Junction $10.00, DigiKey $8.49, SparkFun $8.00, AFT Fasteners $8.00, SUNLU $5.00. Amazon ships free, and the small electronic parts ship with the circuit boards. A seller's shipping drops out if nothing from that seller is funded.</t>
   </si>
   <si>
     <t xml:space="preserve">Import tariff on circuit boards</t>
@@ -875,7 +974,7 @@
     <t xml:space="preserve">8. Optional upgrade: piezo tube scanner</t>
   </si>
   <si>
-    <t xml:space="preserve">Prof. Vasquez suggested replacing the flat piezo disc (section 1) with a piezo tube, which should give steadier scans. Our own study agrees, but recommends first fixing how the sample is held and checking temperature effects, because those cause most of v1's unsteadiness. The microscope works without this section. Our studies recommend building without it first, so it starts switched off. Set the switch to Yes to include it in the total, or No to leave it out.</t>
+    <t xml:space="preserve">Prof. Vazquez-Mena suggested replacing the flat piezo disc (section 1) with a piezo tube, which should give steadier scans. Our studies found that how the sample is held and temperature changes cause most of v1's unsteadiness, so those are fixed first. The microscope works without this section. Our studies recommend building without it first, so it starts switched off. Set the switch to Yes to include it in the total, or No to leave it out.</t>
   </si>
   <si>
     <t xml:space="preserve">Include this upgrade in the total?</t>
@@ -890,7 +989,7 @@
     <t xml:space="preserve">Replaces the disc in section 1. A ceramic tube that bends and stretches slightly when voltage is applied, moving the tip by less than the width of an atom.</t>
   </si>
   <si>
-    <t xml:space="preserve">New. Prof. Vasquez's suggestion, for steadier scanning.</t>
+    <t xml:space="preserve">New. Prof. Vazquez-Mena's suggestion, for steadier scanning.</t>
   </si>
   <si>
     <t xml:space="preserve">PiezoDrive</t>
@@ -1163,28 +1262,43 @@
     <t xml:space="preserve">Silver glue</t>
   </si>
   <si>
-    <t xml:space="preserve">Glue that conducts electricity. Fixes the graphite sample to its disc so current can flow through it.</t>
+    <t xml:space="preserve">Glue that conducts electricity. Fixes the graphite sample to its disc so current can flow through it. Small pack.</t>
   </si>
   <si>
     <t xml:space="preserve">New. Goes with the graphite sample.</t>
   </si>
   <si>
-    <t xml:space="preserve">MG Chemicals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8331D-14G</t>
+    <t xml:space="preserve">Chemtronics CW2400 or similar small silver epoxy</t>
   </si>
   <si>
     <t xml:space="preserve">USB microscope</t>
   </si>
   <si>
-    <t xml:space="preserve">Small camera-microscope with a calibration slide, for checking the tip's shape, aiming it at the sample, and measuring the scanner's lever arm.</t>
+    <t xml:space="preserve">Small camera-microscope (60 to 250 times), for checking the tip's shape, aiming it at the sample, and measuring the scanner's lever arm.</t>
   </si>
   <si>
     <t xml:space="preserve">New. v1 had no way to inspect the tip.</t>
   </si>
   <si>
-    <t xml:space="preserve">USB microscope with calibration slide</t>
+    <t xml:space="preserve">Plugable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB2-MICRO-250X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibration slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glass slide with a printed 0.01 mm scale, for measuring with the USB microscope (it does not come with one).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New. Goes with the USB microscope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eBay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage micrometer, 0.01 mm</t>
   </si>
   <si>
     <t xml:space="preserve">Handheld instrument for checking electrical signals while building and testing.</t>
@@ -1194,18 +1308,6 @@
   </si>
   <si>
     <t xml:space="preserve">FNIRSI DST-201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laser calibration parts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small laser, beam splitter, two mirrors and a light sensor. Together they measure exactly how far the scanner moves, which sets the scale of the images.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New. Calibrates the scanner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laser diode, beamsplitter cube, 2 mirrors, photodiode, mounts</t>
   </si>
   <si>
     <t xml:space="preserve">Soldering iron</t>
@@ -2652,7 +2754,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -2705,12 +2807,12 @@
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21" t="n">
-        <f aca="false">H160</f>
-        <v>2619.08</v>
+        <f aca="false">H168</f>
+        <v>2588.42</v>
       </c>
       <c r="D6" s="22" t="n">
-        <f aca="false">H161</f>
-        <v>1644.91</v>
+        <f aca="false">H169</f>
+        <v>1753.19</v>
       </c>
       <c r="E6" s="22"/>
     </row>
@@ -2720,12 +2822,12 @@
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="21" t="n">
-        <f aca="false">H162</f>
-        <v>3292.185</v>
+        <f aca="false">H170</f>
+        <v>3261.525</v>
       </c>
       <c r="D7" s="22" t="n">
-        <f aca="false">H163</f>
-        <v>2318.015</v>
+        <f aca="false">H171</f>
+        <v>2426.285</v>
       </c>
       <c r="E7" s="22"/>
     </row>
@@ -2735,8 +2837,8 @@
       </c>
       <c r="B8" s="23"/>
       <c r="C8" s="24" t="n">
-        <f aca="false">H155</f>
-        <v>2619.08</v>
+        <f aca="false">H163</f>
+        <v>2588.42</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -3068,7 +3170,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
         <v>100</v>
       </c>
@@ -3290,7 +3392,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
         <v>129</v>
       </c>
@@ -3301,7 +3403,7 @@
         <v>131</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>132</v>
@@ -3310,205 +3412,205 @@
         <v>1</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H35" s="30" t="n">
         <f aca="false">IF(K35="No",0,F35*G35)</f>
         <v>0</v>
       </c>
-      <c r="I35" s="29" t="s">
-        <v>128</v>
+      <c r="I35" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J35" s="31" t="str">
-        <f aca="false">HYPERLINK("https://github.com/jacobbkatz/We-Are-STMING/tree/main/CAD/prints","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=oldham+coupling+5mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K35" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="H36" s="30" t="n">
         <f aca="false">IF(K36="No",0,F36*G36)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I36" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J36" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=G10+fr4+standoff+M3","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K36" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H37" s="30" t="n">
+        <f aca="false">IF(K37="No",0,F37*G37)</f>
+        <v>8</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J37" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=shielded+4+core+cable+clip+on+ferrite","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K37" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="30" t="n">
+        <f aca="false">IF(K38="No",0,F38*G38)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="J38" s="31" t="str">
+        <f aca="false">HYPERLINK("https://github.com/jacobbkatz/We-Are-STMING/tree/main/CAD/prints","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K38" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <f aca="false">IF(K39="No",0,F39*G39)</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J39" s="31" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=piezo+stack+actuator+5x5mm","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K36" s="32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
+      <c r="K39" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10" t="n">
-        <f aca="false">SUM(H29:H36)</f>
-        <v>87.75</v>
-      </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-    </row>
-    <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-    </row>
-    <row r="40" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="30" t="n">
-        <v>209.64</v>
-      </c>
-      <c r="H40" s="30" t="n">
-        <f aca="false">IF(K40="No",0,F40*G40)</f>
-        <v>419.28</v>
-      </c>
-      <c r="I40" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J40" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K40" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" s="30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="H41" s="30" t="n">
-        <f aca="false">IF(K41="No",0,F41*G41)</f>
-        <v>5.04</v>
-      </c>
-      <c r="I41" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J41" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K41" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10" t="n">
+        <f aca="false">SUM(H29:H39)</f>
+        <v>103.75</v>
+      </c>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="F42" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="30" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="H42" s="30" t="n">
-        <f aca="false">IF(K42="No",0,F42*G42)</f>
-        <v>36.52</v>
-      </c>
-      <c r="I42" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K42" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+    </row>
+    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
         <v>151</v>
       </c>
@@ -3516,29 +3618,29 @@
         <v>152</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>31.5</v>
+        <v>209.64</v>
       </c>
       <c r="H43" s="30" t="n">
         <f aca="false">IF(K43="No",0,F43*G43)</f>
-        <v>31.5</v>
+        <v>419.28</v>
       </c>
       <c r="I43" s="29" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J43" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K43" s="32" t="s">
@@ -3547,582 +3649,582 @@
     </row>
     <row r="44" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
       </c>
       <c r="F44" s="29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>15</v>
+        <v>1.68</v>
       </c>
       <c r="H44" s="30" t="n">
         <f aca="false">IF(K44="No",0,F44*G44)</f>
-        <v>15</v>
-      </c>
-      <c r="I44" s="33" t="s">
-        <v>98</v>
+        <v>5.04</v>
+      </c>
+      <c r="I44" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J44" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=high+value+resistor+assortment+100M","Open")</f>
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K44" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
+    <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="30" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="H45" s="30" t="n">
+        <f aca="false">IF(K45="No",0,F45*G45)</f>
+        <v>36.52</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-devices-inc/LT1469IN8-PBF/962892","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K45" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F46" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="H46" s="30" t="n">
+        <f aca="false">IF(K46="No",0,F46*G46)</f>
+        <v>31.5</v>
+      </c>
+      <c r="I46" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.sparkfun.com/teensy-4-1.html","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K46" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="10" t="n">
-        <f aca="false">SUM(H40:H44)</f>
-        <v>507.34</v>
-      </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-    </row>
-    <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-    </row>
-    <row r="48" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H47" s="30" t="n">
+        <f aca="false">IF(K47="No",0,F47*G47)</f>
+        <v>15</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J47" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=high+value+resistor+assortment+100M","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K47" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="E48" s="6" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F48" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="30" t="n">
-        <v>30.17</v>
+        <v>3</v>
       </c>
       <c r="H48" s="30" t="n">
         <f aca="false">IF(K48="No",0,F48*G48)</f>
-        <v>60.34</v>
-      </c>
-      <c r="I48" s="29" t="s">
-        <v>92</v>
+        <v>3</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J48" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/filter/ceramic-capacitors/60","Open")</f>
         <v>Open</v>
       </c>
       <c r="K48" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" s="30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H49" s="30" t="n">
-        <f aca="false">IF(K49="No",0,F49*G49)</f>
-        <v>2.4</v>
-      </c>
-      <c r="I49" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J49" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K49" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F50" s="29" t="n">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="10" t="n">
+        <f aca="false">SUM(H43:H48)</f>
+        <v>510.34</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F52" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="30" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="H50" s="30" t="n">
-        <f aca="false">IF(K50="No",0,F50*G50)</f>
-        <v>11.46</v>
-      </c>
-      <c r="I50" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J50" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K50" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="F51" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" s="30" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="H51" s="30" t="n">
-        <f aca="false">IF(K51="No",0,F51*G51)</f>
-        <v>4.18</v>
-      </c>
-      <c r="I51" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J51" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K51" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="F52" s="29" t="n">
-        <v>1</v>
-      </c>
       <c r="G52" s="30" t="n">
-        <v>7.99</v>
+        <v>30.17</v>
       </c>
       <c r="H52" s="30" t="n">
         <f aca="false">IF(K52="No",0,F52*G52)</f>
-        <v>7.99</v>
+        <v>60.34</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="J52" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K52" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="F53" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>5.73</v>
+        <v>0.8</v>
       </c>
       <c r="H53" s="30" t="n">
         <f aca="false">IF(K53="No",0,F53*G53)</f>
-        <v>11.46</v>
-      </c>
-      <c r="I53" s="33" t="s">
-        <v>98</v>
+        <v>2.4</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J53" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/search?q=SM104031006FE","Open")</f>
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K53" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="10" t="n">
-        <f aca="false">SUM(H48:H53)</f>
-        <v>97.83</v>
-      </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-    </row>
-    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+    <row r="54" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="5"/>
-    </row>
-    <row r="57" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="30" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H54" s="30" t="n">
+        <f aca="false">IF(K54="No",0,F54*G54)</f>
+        <v>11.46</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J54" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/ohmite/SM104031007FE/824190","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K54" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F55" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="H55" s="30" t="n">
+        <f aca="false">IF(K55="No",0,F55*G55)</f>
+        <v>4.18</v>
+      </c>
+      <c r="I55" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J55" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/11301","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K55" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="30" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H56" s="30" t="n">
+        <f aca="false">IF(K56="No",0,F56*G56)</f>
+        <v>7.99</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J56" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Kirecoo+copper+foil+tape+2+inch","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K56" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="F57" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>19.99</v>
+        <v>5.73</v>
       </c>
       <c r="H57" s="30" t="n">
         <f aca="false">IF(K57="No",0,F57*G57)</f>
-        <v>19.99</v>
-      </c>
-      <c r="I57" s="29" t="s">
-        <v>105</v>
+        <v>11.46</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J57" s="31" t="str">
-        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
+        <f aca="false">HYPERLINK("https://octopart.com/search?q=SM104031006FE","Open")</f>
         <v>Open</v>
       </c>
       <c r="K57" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F58" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>9.99</v>
+        <v>8</v>
       </c>
       <c r="H58" s="30" t="n">
         <f aca="false">IF(K58="No",0,F58*G58)</f>
-        <v>9.99</v>
-      </c>
-      <c r="I58" s="29" t="s">
-        <v>105</v>
+        <v>8</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J58" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
+        <f aca="false">HYPERLINK("https://www.digikey.com/en/products/detail/analog-technologies/Capacitor-kit-C04-50/18833616","Open")</f>
         <v>Open</v>
       </c>
       <c r="K58" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F59" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="30" t="n">
-        <v>30</v>
-      </c>
-      <c r="H59" s="30" t="n">
-        <f aca="false">IF(K59="No",0,F59*G59)</f>
-        <v>30</v>
-      </c>
-      <c r="I59" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J59" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K59" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F60" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="30" t="n">
-        <v>9.49</v>
-      </c>
-      <c r="H60" s="30" t="n">
-        <f aca="false">IF(K60="No",0,F60*G60)</f>
-        <v>9.49</v>
-      </c>
-      <c r="I60" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J60" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K60" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B61" s="6" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="10" t="n">
+        <f aca="false">SUM(H52:H58)</f>
+        <v>105.83</v>
+      </c>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="6" t="s">
+      <c r="B62" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F61" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G61" s="30" t="n">
-        <v>13.99</v>
-      </c>
-      <c r="H61" s="30" t="n">
-        <f aca="false">IF(K61="No",0,F61*G61)</f>
-        <v>27.98</v>
-      </c>
-      <c r="I61" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="J61" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/dp/B0F4CCYHL2","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K61" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
+      <c r="C62" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="D62" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="E62" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="F62" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="30" t="n">
-        <v>3</v>
+        <v>19.99</v>
       </c>
       <c r="H62" s="30" t="n">
         <f aca="false">IF(K62="No",0,F62*G62)</f>
-        <v>3</v>
-      </c>
-      <c r="I62" s="33" t="s">
-        <v>98</v>
+        <v>19.99</v>
+      </c>
+      <c r="I62" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="J62" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silicone+tubing+small","Open")</f>
+        <f aca="false">HYPERLINK("https://store.sunlu.com/products/petg-cfpetg-carbon-fiber-3d-printer-filament-1kg","Open")</f>
         <v>Open</v>
       </c>
       <c r="K62" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="C63" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F63" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
       <c r="H63" s="30" t="n">
         <f aca="false">IF(K63="No",0,F63*G63)</f>
-        <v>17.98</v>
+        <v>9.99</v>
       </c>
       <c r="I63" s="29" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J63" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=neodymium+bar+magnets+60x10x3mm+12+pack","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+4.6mm+steel+balls+100","Open")</f>
         <v>Open</v>
       </c>
       <c r="K63" s="32" t="s">
@@ -4131,44 +4233,44 @@
     </row>
     <row r="64" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="D64" s="6" t="s">
-        <v>90</v>
+        <v>212</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F64" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="30" t="n">
-        <v>19.79</v>
+        <v>30</v>
       </c>
       <c r="H64" s="30" t="n">
         <f aca="false">IF(K64="No",0,F64*G64)</f>
-        <v>19.79</v>
+        <v>30</v>
       </c>
       <c r="I64" s="29" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J64" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+6061+aluminum+round+disc+150mm+6mm","Open")</f>
+        <f aca="false">HYPERLINK("https://www.tedpella.com/AFM_html/AFM.aspx","Open")</f>
         <v>Open</v>
       </c>
       <c r="K64" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="s">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>214</v>
@@ -4186,24 +4288,24 @@
         <v>1</v>
       </c>
       <c r="G65" s="30" t="n">
-        <v>22.78</v>
+        <v>9.49</v>
       </c>
       <c r="H65" s="30" t="n">
         <f aca="false">IF(K65="No",0,F65*G65)</f>
-        <v>22.78</v>
+        <v>9.49</v>
       </c>
       <c r="I65" s="29" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J65" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M8+x+400mm+stainless+steel+threaded+rod+4+pack","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=TRYMAG+small+neodymium+magnets","Open")</f>
         <v>Open</v>
       </c>
       <c r="K65" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
         <v>217</v>
       </c>
@@ -4214,137 +4316,137 @@
         <v>219</v>
       </c>
       <c r="D66" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="F66" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>10</v>
+        <v>13.99</v>
       </c>
       <c r="H66" s="30" t="n">
         <f aca="false">IF(K66="No",0,F66*G66)</f>
-        <v>10</v>
-      </c>
-      <c r="I66" s="33" t="s">
-        <v>98</v>
+        <v>27.98</v>
+      </c>
+      <c r="I66" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J66" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.homedepot.com/s/steel%20plate","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/dp/B0F4CCYHL2","Open")</f>
         <v>Open</v>
       </c>
       <c r="K66" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="C67" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F67" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="30" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="H67" s="30" t="n">
         <f aca="false">IF(K67="No",0,F67*G67)</f>
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I67" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J67" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=large+metal+storage+tin+with+lid","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silicone+tubing+small","Open")</f>
         <v>Open</v>
       </c>
       <c r="K67" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="C68" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F68" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" s="30" t="n">
-        <v>22</v>
+        <v>8.99</v>
       </c>
       <c r="H68" s="30" t="n">
         <f aca="false">IF(K68="No",0,F68*G68)</f>
-        <v>22</v>
-      </c>
-      <c r="I68" s="33" t="s">
-        <v>98</v>
+        <v>17.98</v>
+      </c>
+      <c r="I68" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J68" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=aluminum+project+box+enclosure","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=neodymium+bar+magnets+60x10x3mm+12+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K68" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="C69" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="F69" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="30" t="n">
-        <v>80</v>
+        <v>19.79</v>
       </c>
       <c r="H69" s="30" t="n">
         <f aca="false">IF(K69="No",0,F69*G69)</f>
-        <v>80</v>
-      </c>
-      <c r="I69" s="33" t="s">
-        <v>98</v>
+        <v>19.79</v>
+      </c>
+      <c r="I69" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J69" s="31" t="str">
-        <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=uxcell+6061+aluminum+round+disc+150mm+6mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K69" s="32" t="s">
@@ -4353,179 +4455,257 @@
     </row>
     <row r="70" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F70" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="30" t="n">
-        <v>15</v>
+        <v>22.78</v>
       </c>
       <c r="H70" s="30" t="n">
         <f aca="false">IF(K70="No",0,F70*G70)</f>
-        <v>15</v>
-      </c>
-      <c r="I70" s="33" t="s">
-        <v>98</v>
+        <v>22.78</v>
+      </c>
+      <c r="I70" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J70" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=hardened+steel+dowel+pin+assortment","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M8+x+400mm+stainless+steel+threaded+rod+4+pack","Open")</f>
         <v>Open</v>
       </c>
       <c r="K70" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="E71" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="F71" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G71" s="30" t="n">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="H71" s="30" t="n">
         <f aca="false">IF(K71="No",0,F71*G71)</f>
-        <v>9.99</v>
-      </c>
-      <c r="I71" s="29" t="s">
-        <v>92</v>
+        <v>10</v>
+      </c>
+      <c r="I71" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J71" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Nefuree+heat+set+inserts+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://www.homedepot.com/s/steel%20plate","Open")</f>
         <v>Open</v>
       </c>
       <c r="K71" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="10" t="n">
-        <f aca="false">SUM(H57:H71)</f>
-        <v>327.99</v>
-      </c>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-    </row>
-    <row r="74" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+    <row r="72" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
-      <c r="J74" s="5"/>
-      <c r="K74" s="5"/>
-    </row>
-    <row r="75" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D72" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F72" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="30" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="H72" s="30" t="n">
+        <f aca="false">IF(K72="No",0,F72*G72)</f>
+        <v>26.16</v>
+      </c>
+      <c r="I72" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J72" s="31" t="str">
+        <f aca="false">HYPERLINK("https://kkhardware.com/p/foamular-4x8x1-r-5-748232100012","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K72" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F73" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="30" t="n">
+        <v>22</v>
+      </c>
+      <c r="H73" s="30" t="n">
+        <f aca="false">IF(K73="No",0,F73*G73)</f>
+        <v>22</v>
+      </c>
+      <c r="I73" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J73" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=aluminum+project+box+enclosure","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K73" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="H74" s="30" t="n">
+        <f aca="false">IF(K74="No",0,F74*G74)</f>
+        <v>80</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J74" s="31" t="str">
+        <f aca="false">HYPERLINK("https://sendcutsend.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K74" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F75" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="30" t="n">
-        <v>25</v>
+        <v>16.17</v>
       </c>
       <c r="H75" s="30" t="n">
         <f aca="false">IF(K75="No",0,F75*G75)</f>
-        <v>25</v>
-      </c>
-      <c r="I75" s="33" t="s">
-        <v>98</v>
+        <v>16.17</v>
+      </c>
+      <c r="I75" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="J75" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=temperature+humidity+data+logger+USB","Open")</f>
+        <f aca="false">HYPERLINK("https://aftfasteners.com/3-16-x-15-16-dowel-pins-alloy-steel-bright-finish-100-pkg","Open")</f>
         <v>Open</v>
       </c>
       <c r="K75" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="F76" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="30" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="H76" s="30" t="n">
         <f aca="false">IF(K76="No",0,F76*G76)</f>
-        <v>10</v>
-      </c>
-      <c r="I76" s="33" t="s">
-        <v>98</v>
+        <v>9.99</v>
+      </c>
+      <c r="I76" s="29" t="s">
+        <v>92</v>
       </c>
       <c r="J76" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silica+gel+packets+airtight+container","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Nefuree+heat+set+inserts+kit","Open")</f>
         <v>Open</v>
       </c>
       <c r="K76" s="32" t="s">
@@ -4534,142 +4714,142 @@
     </row>
     <row r="77" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="F77" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G77" s="30" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H77" s="30" t="n">
         <f aca="false">IF(K77="No",0,F77*G77)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I77" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J77" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FDC1004+breakout+board","Open")</f>
+        <f aca="false">HYPERLINK("https://www.homedepot.com/s/aluminum%20angle","Open")</f>
         <v>Open</v>
       </c>
       <c r="K77" s="32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F78" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H78" s="30" t="n">
+        <f aca="false">IF(K78="No",0,F78*G78)</f>
+        <v>12</v>
+      </c>
+      <c r="I78" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J78" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=40+AWG+magnet+wire","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K78" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="10" t="n">
-        <f aca="false">SUM(H75:H77)</f>
-        <v>35</v>
-      </c>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
-    </row>
-    <row r="80" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
-      <c r="J80" s="5"/>
-      <c r="K80" s="5"/>
-    </row>
-    <row r="81" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="F81" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G81" s="30" t="n">
-        <v>21.39</v>
-      </c>
-      <c r="H81" s="30" t="n">
-        <f aca="false">IF(K81="No",0,F81*G81)</f>
-        <v>42.78</v>
-      </c>
-      <c r="I81" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J81" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K81" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="10" t="n">
+        <f aca="false">SUM(H62:H78)</f>
+        <v>365.32</v>
+      </c>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+    </row>
+    <row r="81" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5"/>
+      <c r="K81" s="5"/>
+    </row>
+    <row r="82" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>149</v>
+        <v>275</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F82" s="29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G82" s="30" t="n">
-        <v>0.61</v>
+        <v>20.78</v>
       </c>
       <c r="H82" s="30" t="n">
         <f aca="false">IF(K82="No",0,F82*G82)</f>
-        <v>6.1</v>
+        <v>20.78</v>
       </c>
       <c r="I82" s="29" t="s">
         <v>105</v>
       </c>
       <c r="J82" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://us.govee.com/collections/smart-thermo-hygrometers/products/govee-bluetooth-hygrometer-thermometer-h5075","Open")</f>
         <v>Open</v>
       </c>
       <c r="K82" s="32" t="s">
@@ -4678,684 +4858,606 @@
     </row>
     <row r="83" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>260</v>
+        <v>103</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="F83" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="30" t="n">
-        <v>10.95</v>
+        <v>11.5</v>
       </c>
       <c r="H83" s="30" t="n">
         <f aca="false">IF(K83="No",0,F83*G83)</f>
-        <v>10.95</v>
+        <v>23</v>
       </c>
       <c r="I83" s="29" t="s">
         <v>105</v>
       </c>
       <c r="J83" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/4821","Open")</f>
         <v>Open</v>
       </c>
       <c r="K83" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="F84" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G84" s="30" t="n">
-        <v>2.95</v>
+        <v>10</v>
       </c>
       <c r="H84" s="30" t="n">
         <f aca="false">IF(K84="No",0,F84*G84)</f>
-        <v>5.9</v>
-      </c>
-      <c r="I84" s="29" t="s">
-        <v>105</v>
+        <v>10</v>
+      </c>
+      <c r="I84" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J84" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=silica+gel+packets+airtight+container","Open")</f>
         <v>Open</v>
       </c>
       <c r="K84" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8" t="s">
+    <row r="85" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F85" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="B85" s="9"/>
-      <c r="C85" s="9"/>
-      <c r="D85" s="9"/>
-      <c r="E85" s="9"/>
-      <c r="F85" s="9"/>
-      <c r="G85" s="9"/>
-      <c r="H85" s="10" t="n">
-        <f aca="false">SUM(H81:H84)</f>
+      <c r="H85" s="30" t="n">
+        <f aca="false">IF(K85="No",0,F85*G85)</f>
+        <v>0</v>
+      </c>
+      <c r="I85" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J85" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FDC1004+breakout+board","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K85" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="9"/>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="10" t="n">
+        <f aca="false">SUM(H82:H85)</f>
+        <v>53.78</v>
+      </c>
+      <c r="I86" s="9"/>
+      <c r="J86" s="9"/>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="88" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5"/>
+      <c r="K88" s="5"/>
+    </row>
+    <row r="89" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F89" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="30" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="H89" s="30" t="n">
+        <f aca="false">IF(K89="No",0,F89*G89)</f>
+        <v>42.78</v>
+      </c>
+      <c r="I89" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J89" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K89" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F90" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H90" s="30" t="n">
+        <f aca="false">IF(K90="No",0,F90*G90)</f>
+        <v>6.1</v>
+      </c>
+      <c r="I90" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J90" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K90" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="F91" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="30" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="H91" s="30" t="n">
+        <f aca="false">IF(K91="No",0,F91*G91)</f>
+        <v>10.95</v>
+      </c>
+      <c r="I91" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J91" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-aa-en91-24pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K91" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F92" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H92" s="30" t="n">
+        <f aca="false">IF(K92="No",0,F92*G92)</f>
+        <v>5.9</v>
+      </c>
+      <c r="I92" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J92" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.adafruit.com/product/449","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K92" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="9"/>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="10" t="n">
+        <f aca="false">SUM(H89:H92)</f>
         <v>65.73</v>
       </c>
-      <c r="I85" s="9"/>
-      <c r="J85" s="9"/>
-      <c r="K85" s="9"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="34" t="s">
-        <v>274</v>
-      </c>
-      <c r="B87" s="35"/>
-      <c r="C87" s="35"/>
-      <c r="D87" s="35"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="36" t="n">
-        <f aca="false">H26+H37+H45+H54+H72+H78+H85</f>
-        <v>1134.64</v>
-      </c>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="35"/>
-    </row>
-    <row r="89" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="5"/>
-      <c r="K89" s="5"/>
-    </row>
-    <row r="90" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="37" t="s">
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="B95" s="35"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="35"/>
+      <c r="E95" s="35"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="35"/>
+      <c r="H95" s="36" t="n">
+        <f aca="false">H26+H40+H49+H59+H79+H86+H93</f>
+        <v>1217.75</v>
+      </c>
+      <c r="I95" s="35"/>
+      <c r="J95" s="35"/>
+      <c r="K95" s="35"/>
+    </row>
+    <row r="97" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5"/>
+      <c r="K97" s="5"/>
+    </row>
+    <row r="98" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B90" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="H90" s="30" t="n">
-        <f aca="false">IF(SUM(H29+H30+H84)&gt;0,10,0)+IF(SUM(H31+H32)&gt;0,15.26,0)+IF(SUM(H40+H41+H48+H49)&gt;0,25,0)+IF(SUM(H42+H50+H51+H53+H82)&gt;0,8.49,0)+IF(SUM(H43)&gt;0,8,0)+IF(SUM(H57)&gt;0,5,0)+IF(SUM(H59)&gt;0,15,0)+IF(SUM(H81+H83)&gt;0,10,0)</f>
-        <v>96.75</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="B91" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="H91" s="30" t="n">
-        <f aca="false">ROUND(0.35*(H40+H41+H48+H49),2)</f>
+      <c r="B98" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="H98" s="30" t="n">
+        <f aca="false">IF(SUM(H29+H30+H83+H92)&gt;0,10,0)+IF(SUM(H31+H32)&gt;0,15.26,0)+IF(SUM(H43+H44+H52+H53)&gt;0,25,0)+IF(SUM(H45+H48+H54+H55+H57+H58+H90)&gt;0,8.49,0)+IF(SUM(H46)&gt;0,8,0)+IF(SUM(H62)&gt;0,5,0)+IF(SUM(H64)&gt;0,15,0)+IF(SUM(H75)&gt;0,8,0)+IF(SUM(H89+H91)&gt;0,10,0)</f>
+        <v>104.75</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="B99" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="C99" s="28"/>
+      <c r="D99" s="28"/>
+      <c r="E99" s="28"/>
+      <c r="H99" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H43+H44+H52+H53),2)</f>
         <v>170.47</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B92" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="C92" s="28"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="H92" s="30" t="n">
-        <f aca="false">ROUND(0.08*(H42+H50+H51+H53+H82),2)</f>
-        <v>5.58</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="B93" s="35"/>
-      <c r="C93" s="35"/>
-      <c r="D93" s="35"/>
-      <c r="E93" s="35"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="36" t="n">
-        <f aca="false">SUM(H90:H92)</f>
-        <v>272.8</v>
-      </c>
-      <c r="I93" s="35"/>
-      <c r="J93" s="35"/>
-      <c r="K93" s="35"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B94" s="38" t="s">
-        <v>282</v>
-      </c>
-      <c r="C94" s="38"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="38"/>
-      <c r="F94" s="38"/>
-      <c r="G94" s="38"/>
-      <c r="H94" s="38"/>
-      <c r="I94" s="38"/>
-      <c r="J94" s="38"/>
-      <c r="K94" s="38"/>
-    </row>
-    <row r="96" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="B96" s="40"/>
-      <c r="C96" s="40"/>
-      <c r="D96" s="40"/>
-      <c r="E96" s="40"/>
-      <c r="F96" s="40"/>
-      <c r="G96" s="40"/>
-      <c r="H96" s="40"/>
-      <c r="I96" s="40"/>
-      <c r="J96" s="40"/>
-      <c r="K96" s="40"/>
-    </row>
-    <row r="97" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="B97" s="28"/>
-      <c r="C97" s="28"/>
-      <c r="D97" s="28"/>
-      <c r="E97" s="28"/>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="28"/>
-      <c r="I97" s="28"/>
-      <c r="J97" s="28"/>
-      <c r="K97" s="28"/>
-    </row>
-    <row r="98" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="B98" s="42"/>
-      <c r="C98" s="42"/>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="42"/>
-      <c r="G98" s="42"/>
-      <c r="H98" s="42"/>
-      <c r="I98" s="43" t="s">
-        <v>286</v>
-      </c>
-      <c r="J98" s="42"/>
-      <c r="K98" s="44" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="45" t="s">
+    <row r="100" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B100" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C100" s="28"/>
+      <c r="D100" s="28"/>
+      <c r="E100" s="28"/>
+      <c r="H100" s="30" t="n">
+        <f aca="false">ROUND(0.08*(H45+H48+H54+H55+H57+H58+H90),2)</f>
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35"/>
+      <c r="D101" s="35"/>
+      <c r="E101" s="35"/>
+      <c r="F101" s="35"/>
+      <c r="G101" s="35"/>
+      <c r="H101" s="36" t="n">
+        <f aca="false">SUM(H98:H100)</f>
+        <v>281.68</v>
+      </c>
+      <c r="I101" s="35"/>
+      <c r="J101" s="35"/>
+      <c r="K101" s="35"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B102" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="38"/>
+      <c r="F102" s="38"/>
+      <c r="G102" s="38"/>
+      <c r="H102" s="38"/>
+      <c r="I102" s="38"/>
+      <c r="J102" s="38"/>
+      <c r="K102" s="38"/>
+    </row>
+    <row r="104" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="B104" s="40"/>
+      <c r="C104" s="40"/>
+      <c r="D104" s="40"/>
+      <c r="E104" s="40"/>
+      <c r="F104" s="40"/>
+      <c r="G104" s="40"/>
+      <c r="H104" s="40"/>
+      <c r="I104" s="40"/>
+      <c r="J104" s="40"/>
+      <c r="K104" s="40"/>
+    </row>
+    <row r="105" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B105" s="28"/>
+      <c r="C105" s="28"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="28"/>
+      <c r="F105" s="28"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="28"/>
+      <c r="I105" s="28"/>
+      <c r="J105" s="28"/>
+      <c r="K105" s="28"/>
+    </row>
+    <row r="106" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B106" s="42"/>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="J106" s="42"/>
+      <c r="K106" s="44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B99" s="45" t="s">
+      <c r="B107" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="C99" s="45" t="s">
+      <c r="C107" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="D99" s="45" t="s">
+      <c r="D107" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="E99" s="45" t="s">
+      <c r="E107" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="F99" s="45" t="s">
+      <c r="F107" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G99" s="45" t="s">
+      <c r="G107" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="H99" s="45" t="s">
+      <c r="H107" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="I99" s="45" t="s">
+      <c r="I107" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="J99" s="45" t="s">
+      <c r="J107" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="K99" s="45" t="s">
+      <c r="K107" s="45" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="B100" s="42"/>
-      <c r="C100" s="42"/>
-      <c r="D100" s="42"/>
-      <c r="E100" s="42"/>
-      <c r="F100" s="42"/>
-      <c r="G100" s="42"/>
-      <c r="H100" s="42"/>
-      <c r="I100" s="42"/>
-      <c r="J100" s="42"/>
-      <c r="K100" s="42"/>
-    </row>
-    <row r="101" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F101" s="29" t="n">
+    <row r="108" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="B108" s="42"/>
+      <c r="C108" s="42"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="42"/>
+      <c r="F108" s="42"/>
+      <c r="G108" s="42"/>
+      <c r="H108" s="42"/>
+      <c r="I108" s="42"/>
+      <c r="J108" s="42"/>
+      <c r="K108" s="42"/>
+    </row>
+    <row r="109" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F109" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G101" s="30" t="n">
+      <c r="G109" s="30" t="n">
         <v>131</v>
-      </c>
-      <c r="H101" s="30" t="n">
-        <f aca="false">IF(K101="No",0,F101*G101)</f>
-        <v>131</v>
-      </c>
-      <c r="I101" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="J101" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K101" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="B102" s="42"/>
-      <c r="C102" s="42"/>
-      <c r="D102" s="42"/>
-      <c r="E102" s="42"/>
-      <c r="F102" s="42"/>
-      <c r="G102" s="42"/>
-      <c r="H102" s="42"/>
-      <c r="I102" s="42"/>
-      <c r="J102" s="42"/>
-      <c r="K102" s="42"/>
-    </row>
-    <row r="103" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="F103" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="30" t="n">
-        <v>35</v>
-      </c>
-      <c r="H103" s="30" t="n">
-        <f aca="false">IF(K103="No",0,F103*G103)</f>
-        <v>35</v>
-      </c>
-      <c r="I103" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J103" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K103" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="F104" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="H104" s="30" t="n">
-        <f aca="false">IF(K104="No",0,F104*G104)</f>
-        <v>15</v>
-      </c>
-      <c r="I104" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J104" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K104" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="F105" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="H105" s="30" t="n">
-        <f aca="false">IF(K105="No",0,F105*G105)</f>
-        <v>25</v>
-      </c>
-      <c r="I105" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J105" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K105" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E106" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F106" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H106" s="30" t="n">
-        <f aca="false">IF(K106="No",0,F106*G106)</f>
-        <v>10</v>
-      </c>
-      <c r="I106" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J106" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K106" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="F107" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H107" s="30" t="n">
-        <f aca="false">IF(K107="No",0,F107*G107)</f>
-        <v>10</v>
-      </c>
-      <c r="I107" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J107" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K107" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="F108" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H108" s="30" t="n">
-        <f aca="false">IF(K108="No",0,F108*G108)</f>
-        <v>12</v>
-      </c>
-      <c r="I108" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J108" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K108" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="F109" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" s="30" t="n">
-        <v>3</v>
       </c>
       <c r="H109" s="30" t="n">
         <f aca="false">IF(K109="No",0,F109*G109)</f>
-        <v>6</v>
-      </c>
-      <c r="I109" s="33" t="s">
-        <v>98</v>
+        <v>131</v>
+      </c>
+      <c r="I109" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="J109" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
+        <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
       <c r="K109" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="F110" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H110" s="30" t="n">
-        <f aca="false">IF(K110="No",0,F110*G110)</f>
-        <v>8</v>
-      </c>
-      <c r="I110" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J110" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K110" s="32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="B110" s="42"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="42"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="42"/>
+      <c r="H110" s="42"/>
+      <c r="I110" s="42"/>
+      <c r="J110" s="42"/>
+      <c r="K110" s="42"/>
+    </row>
+    <row r="111" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F111" s="29" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G111" s="30" t="n">
-        <v>0.5</v>
+        <v>35</v>
       </c>
       <c r="H111" s="30" t="n">
         <f aca="false">IF(K111="No",0,F111*G111)</f>
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I111" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J111" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Macor+machinable+ceramic+rod","Open")</f>
         <v>Open</v>
       </c>
       <c r="K111" s="32" t="s">
@@ -5364,250 +5466,294 @@
     </row>
     <row r="112" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F112" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H112" s="30" t="n">
         <f aca="false">IF(K112="No",0,F112*G112)</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I112" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J112" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Loctite+EA+E-30CL+epoxy","Open")</f>
         <v>Open</v>
       </c>
       <c r="K112" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F113" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="30" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H113" s="30" t="n">
         <f aca="false">IF(K113="No",0,F113*G113)</f>
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I113" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J113" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+conductive+silver+epoxy","Open")</f>
         <v>Open</v>
       </c>
       <c r="K113" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="46" t="s">
-        <v>337</v>
-      </c>
-      <c r="B114" s="42"/>
-      <c r="C114" s="42"/>
-      <c r="D114" s="42"/>
-      <c r="E114" s="42"/>
-      <c r="F114" s="42"/>
-      <c r="G114" s="42"/>
-      <c r="H114" s="42"/>
-      <c r="I114" s="42"/>
-      <c r="J114" s="42"/>
-      <c r="K114" s="42"/>
-    </row>
-    <row r="115" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="F114" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H114" s="30" t="n">
+        <f aca="false">IF(K114="No",0,F114*G114)</f>
+        <v>10</v>
+      </c>
+      <c r="I114" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J114" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=23+gauge+stainless+steel+hypodermic+tubing","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K114" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>341</v>
+        <v>90</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F115" s="29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G115" s="30" t="n">
-        <v>6.725</v>
+        <v>10</v>
       </c>
       <c r="H115" s="30" t="n">
         <f aca="false">IF(K115="No",0,F115*G115)</f>
-        <v>33.625</v>
-      </c>
-      <c r="I115" s="29" t="s">
-        <v>105</v>
+        <v>10</v>
+      </c>
+      <c r="I115" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J115" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=micro+coax+cable+1mm","Open")</f>
         <v>Open</v>
       </c>
       <c r="K115" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>341</v>
+        <v>90</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F116" s="29" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="30" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H116" s="30" t="n">
         <f aca="false">IF(K116="No",0,F116*G116)</f>
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I116" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J116" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Hammond+1590B+diecast+aluminum+enclosure","Open")</f>
         <v>Open</v>
       </c>
       <c r="K116" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>146</v>
+        <v>353</v>
       </c>
       <c r="F117" s="29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G117" s="30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H117" s="30" t="n">
         <f aca="false">IF(K117="No",0,F117*G117)</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I117" s="33" t="s">
         <v>98</v>
       </c>
       <c r="J117" s="31" t="str">
-        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=DB9+connector+with+backshell","Open")</f>
         <v>Open</v>
       </c>
       <c r="K117" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="46" t="s">
-        <v>349</v>
-      </c>
-      <c r="B118" s="42"/>
-      <c r="C118" s="42"/>
-      <c r="D118" s="42"/>
-      <c r="E118" s="42"/>
-      <c r="F118" s="42"/>
-      <c r="G118" s="42"/>
-      <c r="H118" s="42"/>
-      <c r="I118" s="42"/>
-      <c r="J118" s="42"/>
-      <c r="K118" s="42"/>
+    <row r="118" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F118" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="H118" s="30" t="n">
+        <f aca="false">IF(K118="No",0,F118*G118)</f>
+        <v>8</v>
+      </c>
+      <c r="I118" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J118" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=5+core+shielded+cable+300V","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K118" s="32" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>261</v>
+        <v>361</v>
       </c>
       <c r="F119" s="29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G119" s="30" t="n">
-        <v>21.39</v>
+        <v>0.5</v>
       </c>
       <c r="H119" s="30" t="n">
         <f aca="false">IF(K119="No",0,F119*G119)</f>
-        <v>21.39</v>
-      </c>
-      <c r="I119" s="29" t="s">
-        <v>105</v>
+        <v>4</v>
+      </c>
+      <c r="I119" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J119" s="31" t="str">
-        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2.2nF+100V+film+capacitor","Open")</f>
         <v>Open</v>
       </c>
       <c r="K119" s="32" t="s">
@@ -5616,540 +5762,512 @@
     </row>
     <row r="120" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>264</v>
+        <v>364</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>149</v>
+        <v>90</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>265</v>
+        <v>365</v>
       </c>
       <c r="F120" s="29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G120" s="30" t="n">
-        <v>0.61</v>
+        <v>5</v>
       </c>
       <c r="H120" s="30" t="n">
         <f aca="false">IF(K120="No",0,F120*G120)</f>
-        <v>6.1</v>
-      </c>
-      <c r="I120" s="29" t="s">
-        <v>105</v>
+        <v>5</v>
+      </c>
+      <c r="I120" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J120" s="31" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M3+heat+set+inserts+kit","Open")</f>
         <v>Open</v>
       </c>
       <c r="K120" s="32" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="46" t="s">
-        <v>355</v>
-      </c>
-      <c r="B121" s="42"/>
-      <c r="C121" s="42"/>
-      <c r="D121" s="42"/>
-      <c r="E121" s="42"/>
-      <c r="F121" s="42"/>
-      <c r="G121" s="42"/>
-      <c r="H121" s="42"/>
-      <c r="I121" s="42"/>
-      <c r="J121" s="42"/>
-      <c r="K121" s="42"/>
-    </row>
-    <row r="122" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="F122" s="37" t="n">
+    <row r="121" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F121" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="G122" s="30" t="n">
+      <c r="G121" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="H121" s="30" t="n">
+        <f aca="false">IF(K121="No",0,F121*G121)</f>
+        <v>40</v>
+      </c>
+      <c r="I121" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J121" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=handheld+LCR+meter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K121" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="46" t="s">
+        <v>370</v>
+      </c>
+      <c r="B122" s="42"/>
+      <c r="C122" s="42"/>
+      <c r="D122" s="42"/>
+      <c r="E122" s="42"/>
+      <c r="F122" s="42"/>
+      <c r="G122" s="42"/>
+      <c r="H122" s="42"/>
+      <c r="I122" s="42"/>
+      <c r="J122" s="42"/>
+      <c r="K122" s="42"/>
+    </row>
+    <row r="123" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="F123" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G123" s="30" t="n">
+        <v>6.725</v>
+      </c>
+      <c r="H123" s="30" t="n">
+        <f aca="false">IF(K123="No",0,F123*G123)</f>
+        <v>33.625</v>
+      </c>
+      <c r="I123" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J123" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/product-detail/C50636.html","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K123" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F124" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="H124" s="30" t="n">
+        <f aca="false">IF(K124="No",0,F124*G124)</f>
+        <v>40</v>
+      </c>
+      <c r="I124" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J124" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.lcsc.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K124" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F125" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="G125" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H125" s="30" t="n">
+        <f aca="false">IF(K125="No",0,F125*G125)</f>
+        <v>10</v>
+      </c>
+      <c r="I125" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="J125" s="31" t="str">
+        <f aca="false">HYPERLINK("https://jlcpcb.com/","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K125" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="B126" s="42"/>
+      <c r="C126" s="42"/>
+      <c r="D126" s="42"/>
+      <c r="E126" s="42"/>
+      <c r="F126" s="42"/>
+      <c r="G126" s="42"/>
+      <c r="H126" s="42"/>
+      <c r="I126" s="42"/>
+      <c r="J126" s="42"/>
+      <c r="K126" s="42"/>
+    </row>
+    <row r="127" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A127" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="F127" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="30" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="H127" s="30" t="n">
+        <f aca="false">IF(K127="No",0,F127*G127)</f>
+        <v>21.39</v>
+      </c>
+      <c r="I127" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J127" s="31" t="str">
+        <f aca="false">HYPERLINK("https://www.batteryjunction.com/products/energizer-ind-9v-en22-12pk","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K127" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="F128" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="30" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H128" s="30" t="n">
+        <f aca="false">IF(K128="No",0,F128*G128)</f>
+        <v>6.1</v>
+      </c>
+      <c r="I128" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="J128" s="31" t="str">
+        <f aca="false">HYPERLINK("https://octopart.com/part/keystone/232","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K128" s="32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="46" t="s">
+        <v>388</v>
+      </c>
+      <c r="B129" s="42"/>
+      <c r="C129" s="42"/>
+      <c r="D129" s="42"/>
+      <c r="E129" s="42"/>
+      <c r="F129" s="42"/>
+      <c r="G129" s="42"/>
+      <c r="H129" s="42"/>
+      <c r="I129" s="42"/>
+      <c r="J129" s="42"/>
+      <c r="K129" s="42"/>
+    </row>
+    <row r="130" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F130" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="30" t="n">
         <v>131</v>
       </c>
-      <c r="H122" s="30" t="n">
-        <f aca="false">IF(K122="Yes",F122*G122,0)</f>
+      <c r="H130" s="30" t="n">
+        <f aca="false">IF(K130="Yes",F130*G130,0)</f>
         <v>0</v>
       </c>
-      <c r="I122" s="37" t="s">
+      <c r="I130" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="J122" s="47" t="str">
+      <c r="J130" s="47" t="str">
         <f aca="false">HYPERLINK("https://www.piezodrive.com/product/tb3006-n-29um-range-piezo-tube-scanner/","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K122" s="32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="10" t="n">
-        <f aca="false">SUM(H100:H122)</f>
+      <c r="K130" s="32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="B131" s="9"/>
+      <c r="C131" s="9"/>
+      <c r="D131" s="9"/>
+      <c r="E131" s="9"/>
+      <c r="F131" s="9"/>
+      <c r="G131" s="9"/>
+      <c r="H131" s="10" t="n">
+        <f aca="false">SUM(H108:H130)</f>
         <v>412.115</v>
       </c>
-      <c r="I123" s="9"/>
-      <c r="J123" s="9"/>
-      <c r="K123" s="9"/>
-    </row>
-    <row r="125" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="46" t="s">
-        <v>360</v>
-      </c>
-      <c r="B125" s="42"/>
-      <c r="C125" s="42"/>
-      <c r="D125" s="42"/>
-      <c r="E125" s="42"/>
-      <c r="F125" s="42"/>
-      <c r="G125" s="42"/>
-      <c r="H125" s="42"/>
-      <c r="I125" s="42"/>
-      <c r="J125" s="42"/>
-      <c r="K125" s="42"/>
-    </row>
-    <row r="126" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="37" t="s">
+      <c r="I131" s="9"/>
+      <c r="J131" s="9"/>
+      <c r="K131" s="9"/>
+    </row>
+    <row r="133" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A133" s="46" t="s">
+        <v>393</v>
+      </c>
+      <c r="B133" s="42"/>
+      <c r="C133" s="42"/>
+      <c r="D133" s="42"/>
+      <c r="E133" s="42"/>
+      <c r="F133" s="42"/>
+      <c r="G133" s="42"/>
+      <c r="H133" s="42"/>
+      <c r="I133" s="42"/>
+      <c r="J133" s="42"/>
+      <c r="K133" s="42"/>
+    </row>
+    <row r="134" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B126" s="28" t="s">
-        <v>361</v>
-      </c>
-      <c r="C126" s="28"/>
-      <c r="D126" s="28"/>
-      <c r="E126" s="28"/>
-      <c r="H126" s="30" t="n">
-        <f aca="false">IF(SUM(H101+H122)&gt;0,60,0)</f>
+      <c r="B134" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" s="28"/>
+      <c r="D134" s="28"/>
+      <c r="E134" s="28"/>
+      <c r="H134" s="30" t="n">
+        <f aca="false">IF(SUM(H109+H130)&gt;0,60,0)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="37" t="s">
-        <v>277</v>
-      </c>
-      <c r="B127" s="28" t="s">
-        <v>362</v>
-      </c>
-      <c r="C127" s="28"/>
-      <c r="D127" s="28"/>
-      <c r="E127" s="28"/>
-      <c r="H127" s="30" t="n">
-        <f aca="false">ROUND(0.35*(H115+H116+H117),2)</f>
+    <row r="135" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="37" t="s">
+        <v>310</v>
+      </c>
+      <c r="B135" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="C135" s="28"/>
+      <c r="D135" s="28"/>
+      <c r="E135" s="28"/>
+      <c r="H135" s="30" t="n">
+        <f aca="false">ROUND(0.35*(H123+H124+H125),2)</f>
         <v>29.27</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B128" s="28" t="s">
-        <v>363</v>
-      </c>
-      <c r="C128" s="28"/>
-      <c r="D128" s="28"/>
-      <c r="E128" s="28"/>
-      <c r="H128" s="30" t="n">
-        <f aca="false">ROUND(0.1*(H101+H122)+0.08*(H120),2)+IF(SUM(H101+H122)&gt;0,65,0)</f>
+    <row r="136" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B136" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="C136" s="28"/>
+      <c r="D136" s="28"/>
+      <c r="E136" s="28"/>
+      <c r="H136" s="30" t="n">
+        <f aca="false">ROUND(0.1*(H109+H130)+0.08*(H128),2)+IF(SUM(H109+H130)&gt;0,65,0)</f>
         <v>78.59</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="10" t="n">
-        <f aca="false">SUM(H126:H128)</f>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B137" s="9"/>
+      <c r="C137" s="9"/>
+      <c r="D137" s="9"/>
+      <c r="E137" s="9"/>
+      <c r="F137" s="9"/>
+      <c r="G137" s="9"/>
+      <c r="H137" s="10" t="n">
+        <f aca="false">SUM(H134:H136)</f>
         <v>167.86</v>
       </c>
-      <c r="I129" s="9"/>
-      <c r="J129" s="9"/>
-      <c r="K129" s="9"/>
-    </row>
-    <row r="130" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="48" t="s">
-        <v>365</v>
-      </c>
-      <c r="B130" s="49" t="s">
-        <v>366</v>
-      </c>
-      <c r="C130" s="50"/>
-      <c r="D130" s="50"/>
-      <c r="E130" s="50"/>
-      <c r="F130" s="50"/>
-      <c r="G130" s="50"/>
-      <c r="H130" s="51" t="n">
-        <f aca="false">IF(K98="Yes",H123+H129,0)</f>
+      <c r="I137" s="9"/>
+      <c r="J137" s="9"/>
+      <c r="K137" s="9"/>
+    </row>
+    <row r="138" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="48" t="s">
+        <v>398</v>
+      </c>
+      <c r="B138" s="49" t="s">
+        <v>399</v>
+      </c>
+      <c r="C138" s="50"/>
+      <c r="D138" s="50"/>
+      <c r="E138" s="50"/>
+      <c r="F138" s="50"/>
+      <c r="G138" s="50"/>
+      <c r="H138" s="51" t="n">
+        <f aca="false">IF(K106="Yes",H131+H137,0)</f>
         <v>0</v>
       </c>
-      <c r="I130" s="50"/>
-      <c r="J130" s="50"/>
-      <c r="K130" s="50"/>
-    </row>
-    <row r="132" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="52" t="s">
-        <v>367</v>
-      </c>
-      <c r="B132" s="53"/>
-      <c r="C132" s="53"/>
-      <c r="D132" s="53"/>
-      <c r="E132" s="53"/>
-      <c r="F132" s="53"/>
-      <c r="G132" s="53"/>
-      <c r="H132" s="53"/>
-      <c r="I132" s="53"/>
-      <c r="J132" s="53"/>
-      <c r="K132" s="53"/>
-    </row>
-    <row r="133" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="54" t="s">
+      <c r="I138" s="50"/>
+      <c r="J138" s="50"/>
+      <c r="K138" s="50"/>
+    </row>
+    <row r="140" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A140" s="52" t="s">
+        <v>400</v>
+      </c>
+      <c r="B140" s="53"/>
+      <c r="C140" s="53"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="53"/>
+      <c r="F140" s="53"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="53"/>
+      <c r="I140" s="53"/>
+      <c r="J140" s="53"/>
+      <c r="K140" s="53"/>
+    </row>
+    <row r="141" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B133" s="54" t="s">
+      <c r="B141" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="C133" s="54" t="s">
+      <c r="C141" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="D133" s="54" t="s">
+      <c r="D141" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="E133" s="54" t="s">
+      <c r="E141" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="F133" s="54" t="s">
+      <c r="F141" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G133" s="54" t="s">
+      <c r="G141" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="H133" s="54" t="s">
+      <c r="H141" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="I133" s="54" t="s">
+      <c r="I141" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="J133" s="54" t="s">
+      <c r="J141" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="K133" s="54" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="F134" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="30" t="n">
-        <v>297</v>
-      </c>
-      <c r="H134" s="30" t="n">
-        <f aca="false">IF(OR(K134="Yes",K134=TRUE()),0,F134*G134)</f>
-        <v>297</v>
-      </c>
-      <c r="I134" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J134" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.advent-rm.com/en-GB/Products/Alloys/Platinum-Iridium/Form/Wire/Line/PT6710","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K134" s="55"/>
-    </row>
-    <row r="135" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="F135" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="30" t="n">
-        <v>77</v>
-      </c>
-      <c r="H135" s="30" t="n">
-        <f aca="false">IF(OR(K135="Yes",K135=TRUE()),0,F135*G135)</f>
-        <v>77</v>
-      </c>
-      <c r="I135" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J135" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K135" s="55"/>
-    </row>
-    <row r="136" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="F136" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="30" t="n">
-        <v>133.13</v>
-      </c>
-      <c r="H136" s="30" t="n">
-        <f aca="false">IF(OR(K136="Yes",K136=TRUE()),0,F136*G136)</f>
-        <v>133.13</v>
-      </c>
-      <c r="I136" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J136" s="47" t="str">
-        <f aca="false">HYPERLINK("https://octopart.com/search?q=8331D-14G","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K136" s="55"/>
-    </row>
-    <row r="137" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F137" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="H137" s="30" t="n">
-        <f aca="false">IF(OR(K137="Yes",K137=TRUE()),0,F137*G137)</f>
-        <v>25</v>
-      </c>
-      <c r="I137" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J137" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=USB+microscope+with+calibration+slide","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K137" s="55"/>
-    </row>
-    <row r="138" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="F138" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="30" t="n">
-        <v>57.99</v>
-      </c>
-      <c r="H138" s="30" t="n">
-        <f aca="false">IF(OR(K138="Yes",K138=TRUE()),0,F138*G138)</f>
-        <v>57.99</v>
-      </c>
-      <c r="I138" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J138" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K138" s="55"/>
-    </row>
-    <row r="139" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="F139" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="30" t="n">
-        <v>60</v>
-      </c>
-      <c r="H139" s="30" t="n">
-        <f aca="false">IF(OR(K139="Yes",K139=TRUE()),0,F139*G139)</f>
-        <v>60</v>
-      </c>
-      <c r="I139" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="J139" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Michelson+interferometer+kit+beamsplitter+cube+laser+diode","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K139" s="55"/>
-    </row>
-    <row r="140" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>396</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="F140" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="30" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="H140" s="30" t="n">
-        <f aca="false">IF(OR(K140="Yes",K140=TRUE()),0,F140*G140)</f>
-        <v>25.99</v>
-      </c>
-      <c r="I140" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="J140" s="47" t="str">
-        <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K140" s="55"/>
-    </row>
-    <row r="141" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E141" s="6" t="s">
+      <c r="K141" s="54" t="s">
         <v>401</v>
       </c>
-      <c r="F141" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="30" t="n">
-        <v>24.97</v>
-      </c>
-      <c r="H141" s="30" t="n">
-        <f aca="false">IF(OR(K141="Yes",K141=TRUE()),0,F141*G141)</f>
-        <v>24.97</v>
-      </c>
-      <c r="I141" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="J141" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
-        <v>Open</v>
-      </c>
-      <c r="K141" s="55"/>
-    </row>
-    <row r="142" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="142" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
         <v>402</v>
       </c>
@@ -6157,509 +6275,789 @@
         <v>403</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>90</v>
+        <v>405</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="F142" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G142" s="30" t="n">
-        <v>11.99</v>
+        <v>297</v>
       </c>
       <c r="H142" s="30" t="n">
         <f aca="false">IF(OR(K142="Yes",K142=TRUE()),0,F142*G142)</f>
-        <v>11.99</v>
+        <v>297</v>
       </c>
       <c r="I142" s="37" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J142" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://www.advent-rm.com/en-GB/Products/Alloys/Platinum-Iridium/Form/Wire/Line/PT6710","Open")</f>
         <v>Open</v>
       </c>
       <c r="K142" s="55"/>
     </row>
-    <row r="143" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>90</v>
+        <v>410</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="F143" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G143" s="30" t="n">
-        <v>25.26</v>
+        <v>77</v>
       </c>
       <c r="H143" s="30" t="n">
         <f aca="false">IF(OR(K143="Yes",K143=TRUE()),0,F143*G143)</f>
-        <v>25.26</v>
+        <v>77</v>
       </c>
       <c r="I143" s="37" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J143" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
+        <f aca="false">HYPERLINK("https://www.nanoandmore.com/AFM-Accessories-HOPG-ZYH","Open")</f>
         <v>Open</v>
       </c>
       <c r="K143" s="55"/>
     </row>
-    <row r="144" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="F144" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G144" s="30" t="n">
-        <v>32.12</v>
+        <v>30</v>
       </c>
       <c r="H144" s="30" t="n">
         <f aca="false">IF(OR(K144="Yes",K144=TRUE()),0,F144*G144)</f>
-        <v>32.12</v>
-      </c>
-      <c r="I144" s="37" t="s">
-        <v>92</v>
+        <v>30</v>
+      </c>
+      <c r="I144" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J144" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=CW2400+silver+conductive+epoxy","Open")</f>
         <v>Open</v>
       </c>
       <c r="K144" s="55"/>
     </row>
-    <row r="145" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>90</v>
+        <v>419</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>401</v>
+        <v>420</v>
       </c>
       <c r="F145" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G145" s="30" t="n">
-        <v>16.98</v>
+        <v>59.95</v>
       </c>
       <c r="H145" s="30" t="n">
         <f aca="false">IF(OR(K145="Yes",K145=TRUE()),0,F145*G145)</f>
-        <v>16.98</v>
+        <v>59.95</v>
       </c>
       <c r="I145" s="37" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="J145" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://plugable.com/products/usb2-micro-250x","Open")</f>
         <v>Open</v>
       </c>
       <c r="K145" s="55"/>
     </row>
-    <row r="146" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>389</v>
+        <v>423</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>90</v>
+        <v>424</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="F146" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G146" s="30" t="n">
-        <v>22.31</v>
+        <v>10.96</v>
       </c>
       <c r="H146" s="30" t="n">
         <f aca="false">IF(OR(K146="Yes",K146=TRUE()),0,F146*G146)</f>
-        <v>22.31</v>
-      </c>
-      <c r="I146" s="37" t="s">
-        <v>92</v>
+        <v>10.96</v>
+      </c>
+      <c r="I146" s="33" t="s">
+        <v>98</v>
       </c>
       <c r="J146" s="47" t="str">
-        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
+        <f aca="false">HYPERLINK("https://www.ebay.de/itm/273445014429","Open")</f>
         <v>Open</v>
       </c>
       <c r="K146" s="55"/>
     </row>
-    <row r="147" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="s">
-        <v>412</v>
+        <v>41</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="F147" s="37" t="n">
         <v>1</v>
       </c>
       <c r="G147" s="30" t="n">
-        <v>12.17</v>
+        <v>57.99</v>
       </c>
       <c r="H147" s="30" t="n">
         <f aca="false">IF(OR(K147="Yes",K147=TRUE()),0,F147*G147)</f>
+        <v>57.99</v>
+      </c>
+      <c r="I147" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J147" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=FNIRSI+DST-201+oscilloscope+multimeter","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K147" s="55"/>
+    </row>
+    <row r="148" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A148" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="F148" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="30" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="H148" s="30" t="n">
+        <f aca="false">IF(OR(K148="Yes",K148=TRUE()),0,F148*G148)</f>
+        <v>25.99</v>
+      </c>
+      <c r="I148" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="J148" s="47" t="str">
+        <f aca="false">HYPERLINK("https://pine64.com/?p=158078","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K148" s="55"/>
+    </row>
+    <row r="149" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A149" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F149" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="30" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="H149" s="30" t="n">
+        <f aca="false">IF(OR(K149="Yes",K149=TRUE()),0,F149*G149)</f>
+        <v>24.97</v>
+      </c>
+      <c r="I149" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J149" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=Sn42Bi58+solder+paste","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K149" s="55"/>
+    </row>
+    <row r="150" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A150" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F150" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="30" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="H150" s="30" t="n">
+        <f aca="false">IF(OR(K150="Yes",K150=TRUE()),0,F150*G150)</f>
+        <v>11.99</v>
+      </c>
+      <c r="I150" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J150" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=heat+shrink+tubing+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K150" s="55"/>
+    </row>
+    <row r="151" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A151" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F151" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="30" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H151" s="30" t="n">
+        <f aca="false">IF(OR(K151="Yes",K151=TRUE()),0,F151*G151)</f>
+        <v>25.26</v>
+      </c>
+      <c r="I151" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J151" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=RG178+coax+cable","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K151" s="55"/>
+    </row>
+    <row r="152" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A152" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F152" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="30" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="H152" s="30" t="n">
+        <f aca="false">IF(OR(K152="Yes",K152=TRUE()),0,F152*G152)</f>
+        <v>32.12</v>
+      </c>
+      <c r="I152" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J152" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=2x13+IDC+ribbon+cable","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K152" s="55"/>
+    </row>
+    <row r="153" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A153" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F153" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="30" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="H153" s="30" t="n">
+        <f aca="false">IF(OR(K153="Yes",K153=TRUE()),0,F153*G153)</f>
+        <v>16.98</v>
+      </c>
+      <c r="I153" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J153" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=pin+header+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K153" s="55"/>
+    </row>
+    <row r="154" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A154" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F154" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="30" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="H154" s="30" t="n">
+        <f aca="false">IF(OR(K154="Yes",K154=TRUE()),0,F154*G154)</f>
+        <v>22.31</v>
+      </c>
+      <c r="I154" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="J154" s="47" t="str">
+        <f aca="false">HYPERLINK("https://www.amazon.com/s?k=M2+M2.5+M3+screw+kit","Open")</f>
+        <v>Open</v>
+      </c>
+      <c r="K154" s="55"/>
+    </row>
+    <row r="155" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A155" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F155" s="37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="30" t="n">
         <v>12.17</v>
       </c>
-      <c r="I147" s="37" t="s">
+      <c r="H155" s="30" t="n">
+        <f aca="false">IF(OR(K155="Yes",K155=TRUE()),0,F155*G155)</f>
+        <v>12.17</v>
+      </c>
+      <c r="I155" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="J147" s="47" t="str">
+      <c r="J155" s="47" t="str">
         <f aca="false">HYPERLINK("https://www.amazon.com/s?k=precision+tweezers+set","Open")</f>
         <v>Open</v>
       </c>
-      <c r="K147" s="55"/>
-    </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="56" t="s">
-        <v>414</v>
-      </c>
-      <c r="B148" s="57"/>
-      <c r="C148" s="57"/>
-      <c r="D148" s="57"/>
-      <c r="E148" s="57"/>
-      <c r="F148" s="57"/>
-      <c r="G148" s="57"/>
-      <c r="H148" s="58" t="n">
-        <f aca="false">SUM(H134:H147)</f>
-        <v>821.91</v>
-      </c>
-      <c r="I148" s="57"/>
-      <c r="J148" s="57"/>
-      <c r="K148" s="57"/>
-    </row>
-    <row r="150" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B150" s="17"/>
-      <c r="C150" s="17"/>
-      <c r="D150" s="17"/>
-      <c r="E150" s="17"/>
-      <c r="F150" s="17"/>
-      <c r="G150" s="17"/>
-      <c r="H150" s="17"/>
-      <c r="I150" s="17"/>
-      <c r="J150" s="17"/>
-      <c r="K150" s="17"/>
-    </row>
-    <row r="151" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="59" t="s">
-        <v>416</v>
-      </c>
-      <c r="B151" s="60" t="s">
-        <v>417</v>
-      </c>
-      <c r="C151" s="61"/>
-      <c r="D151" s="61"/>
-      <c r="E151" s="61"/>
-      <c r="F151" s="61"/>
-      <c r="G151" s="61"/>
-      <c r="H151" s="62" t="n">
-        <f aca="false">H87+IF((K98="Yes"),H123,0)+H148</f>
-        <v>1956.55</v>
-      </c>
-      <c r="I151" s="61"/>
-      <c r="J151" s="61"/>
-      <c r="K151" s="61"/>
-    </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="59" t="s">
-        <v>281</v>
-      </c>
-      <c r="B152" s="60"/>
-      <c r="C152" s="61"/>
-      <c r="D152" s="61"/>
-      <c r="E152" s="61"/>
-      <c r="F152" s="61"/>
-      <c r="G152" s="61"/>
-      <c r="H152" s="62" t="n">
-        <f aca="false">H93+IF((K98="Yes"),H129,0)</f>
-        <v>272.8</v>
-      </c>
-      <c r="I152" s="61"/>
-      <c r="J152" s="61"/>
-      <c r="K152" s="61"/>
-    </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="59" t="s">
-        <v>418</v>
-      </c>
-      <c r="B153" s="60" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="61"/>
-      <c r="D153" s="61"/>
-      <c r="E153" s="61"/>
-      <c r="F153" s="61"/>
-      <c r="G153" s="61"/>
-      <c r="H153" s="62" t="n">
-        <f aca="false">ROUND(H151*0.0775,2)</f>
-        <v>151.63</v>
-      </c>
-      <c r="I153" s="61"/>
-      <c r="J153" s="61"/>
-      <c r="K153" s="61"/>
-    </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="59" t="s">
-        <v>420</v>
-      </c>
-      <c r="B154" s="60" t="s">
-        <v>421</v>
-      </c>
-      <c r="C154" s="61"/>
-      <c r="D154" s="61"/>
-      <c r="E154" s="61"/>
-      <c r="F154" s="61"/>
-      <c r="G154" s="61"/>
-      <c r="H154" s="62" t="n">
-        <f aca="false">ROUND((H151+H152+H153)*0.1,2)</f>
-        <v>238.1</v>
-      </c>
-      <c r="I154" s="61"/>
-      <c r="J154" s="61"/>
-      <c r="K154" s="61"/>
-    </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="B155" s="63"/>
-      <c r="C155" s="13"/>
-      <c r="D155" s="13"/>
-      <c r="E155" s="13"/>
-      <c r="F155" s="13"/>
-      <c r="G155" s="13"/>
-      <c r="H155" s="14" t="n">
-        <f aca="false">H151+H152+H153+H154</f>
-        <v>2619.08</v>
-      </c>
-      <c r="I155" s="13"/>
-      <c r="J155" s="13"/>
-      <c r="K155" s="13"/>
+      <c r="K155" s="55"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="59" t="s">
-        <v>423</v>
-      </c>
-      <c r="B156" s="60" t="s">
-        <v>424</v>
-      </c>
-      <c r="C156" s="61"/>
-      <c r="D156" s="61"/>
-      <c r="E156" s="61"/>
-      <c r="F156" s="61"/>
-      <c r="G156" s="61"/>
-      <c r="H156" s="62" t="n">
-        <f aca="false">2000-H155</f>
-        <v>-619.08</v>
-      </c>
-      <c r="I156" s="61"/>
-      <c r="J156" s="61"/>
-      <c r="K156" s="61"/>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="64" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B159" s="17"/>
-      <c r="C159" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E159" s="65" t="s">
-        <v>428</v>
-      </c>
-      <c r="F159" s="65"/>
-      <c r="G159" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="H159" s="3" t="s">
+      <c r="A156" s="56" t="s">
+        <v>448</v>
+      </c>
+      <c r="B156" s="57"/>
+      <c r="C156" s="57"/>
+      <c r="D156" s="57"/>
+      <c r="E156" s="57"/>
+      <c r="F156" s="57"/>
+      <c r="G156" s="57"/>
+      <c r="H156" s="58" t="n">
+        <f aca="false">SUM(H142:H155)</f>
+        <v>704.69</v>
+      </c>
+      <c r="I156" s="57"/>
+      <c r="J156" s="57"/>
+      <c r="K156" s="57"/>
+    </row>
+    <row r="158" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A158" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B158" s="17"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
+      <c r="F158" s="17"/>
+      <c r="G158" s="17"/>
+      <c r="H158" s="17"/>
+      <c r="I158" s="17"/>
+      <c r="J158" s="17"/>
+      <c r="K158" s="17"/>
+    </row>
+    <row r="159" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="59" t="s">
+        <v>450</v>
+      </c>
+      <c r="B159" s="60" t="s">
+        <v>451</v>
+      </c>
+      <c r="C159" s="61"/>
+      <c r="D159" s="61"/>
+      <c r="E159" s="61"/>
+      <c r="F159" s="61"/>
+      <c r="G159" s="61"/>
+      <c r="H159" s="62" t="n">
+        <f aca="false">H95+IF((K106="Yes"),H131,0)+H156</f>
+        <v>1922.44</v>
+      </c>
+      <c r="I159" s="61"/>
+      <c r="J159" s="61"/>
+      <c r="K159" s="61"/>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="B160" s="60"/>
+      <c r="C160" s="61"/>
+      <c r="D160" s="61"/>
+      <c r="E160" s="61"/>
+      <c r="F160" s="61"/>
+      <c r="G160" s="61"/>
+      <c r="H160" s="62" t="n">
+        <f aca="false">H101+IF((K106="Yes"),H137,0)</f>
+        <v>281.68</v>
+      </c>
+      <c r="I160" s="61"/>
+      <c r="J160" s="61"/>
+      <c r="K160" s="61"/>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="59" t="s">
+        <v>452</v>
+      </c>
+      <c r="B161" s="60" t="s">
+        <v>453</v>
+      </c>
+      <c r="C161" s="61"/>
+      <c r="D161" s="61"/>
+      <c r="E161" s="61"/>
+      <c r="F161" s="61"/>
+      <c r="G161" s="61"/>
+      <c r="H161" s="62" t="n">
+        <f aca="false">ROUND(H159*0.0775,2)</f>
+        <v>148.99</v>
+      </c>
+      <c r="I161" s="61"/>
+      <c r="J161" s="61"/>
+      <c r="K161" s="61"/>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="59" t="s">
+        <v>454</v>
+      </c>
+      <c r="B162" s="60" t="s">
+        <v>455</v>
+      </c>
+      <c r="C162" s="61"/>
+      <c r="D162" s="61"/>
+      <c r="E162" s="61"/>
+      <c r="F162" s="61"/>
+      <c r="G162" s="61"/>
+      <c r="H162" s="62" t="n">
+        <f aca="false">ROUND((H159+H160+H161)*0.1,2)</f>
+        <v>235.31</v>
+      </c>
+      <c r="I162" s="61"/>
+      <c r="J162" s="61"/>
+      <c r="K162" s="61"/>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="12" t="s">
+        <v>456</v>
+      </c>
+      <c r="B163" s="63"/>
+      <c r="C163" s="13"/>
+      <c r="D163" s="13"/>
+      <c r="E163" s="13"/>
+      <c r="F163" s="13"/>
+      <c r="G163" s="13"/>
+      <c r="H163" s="14" t="n">
+        <f aca="false">H159+H160+H161+H162</f>
+        <v>2588.42</v>
+      </c>
+      <c r="I163" s="13"/>
+      <c r="J163" s="13"/>
+      <c r="K163" s="13"/>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="59" t="s">
+        <v>457</v>
+      </c>
+      <c r="B164" s="60" t="s">
+        <v>458</v>
+      </c>
+      <c r="C164" s="61"/>
+      <c r="D164" s="61"/>
+      <c r="E164" s="61"/>
+      <c r="F164" s="61"/>
+      <c r="G164" s="61"/>
+      <c r="H164" s="62" t="n">
+        <f aca="false">2000-H163</f>
+        <v>-588.42</v>
+      </c>
+      <c r="I164" s="61"/>
+      <c r="J164" s="61"/>
+      <c r="K164" s="61"/>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="64" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B167" s="17"/>
+      <c r="C167" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="E167" s="65" t="s">
+        <v>462</v>
+      </c>
+      <c r="F167" s="65"/>
+      <c r="G167" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H167" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
-      <c r="K159" s="17"/>
-    </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="66" t="s">
-        <v>430</v>
-      </c>
-      <c r="B160" s="66"/>
-      <c r="C160" s="7" t="n">
-        <f aca="false">H87+SUMPRODUCT(F134:F147,G134:G147)</f>
-        <v>1956.55</v>
-      </c>
-      <c r="D160" s="7" t="n">
-        <f aca="false">H93</f>
-        <v>272.8</v>
-      </c>
-      <c r="E160" s="67" t="n">
-        <f aca="false">ROUND(C160*0.0775,2)</f>
-        <v>151.63</v>
-      </c>
-      <c r="F160" s="67"/>
-      <c r="G160" s="7" t="n">
-        <f aca="false">ROUND((C160+D160+E160)*0.1,2)</f>
-        <v>238.1</v>
-      </c>
-      <c r="H160" s="68" t="n">
-        <f aca="false">C160+D160+E160+G160</f>
-        <v>2619.08</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="66" t="s">
-        <v>431</v>
-      </c>
-      <c r="B161" s="66"/>
-      <c r="C161" s="7" t="n">
-        <f aca="false">H87</f>
-        <v>1134.64</v>
-      </c>
-      <c r="D161" s="7" t="n">
-        <f aca="false">H93</f>
-        <v>272.8</v>
-      </c>
-      <c r="E161" s="67" t="n">
-        <f aca="false">ROUND(C161*0.0775,2)</f>
-        <v>87.93</v>
-      </c>
-      <c r="F161" s="67"/>
-      <c r="G161" s="7" t="n">
-        <f aca="false">ROUND((C161+D161+E161)*0.1,2)</f>
-        <v>149.54</v>
-      </c>
-      <c r="H161" s="68" t="n">
-        <f aca="false">C161+D161+E161+G161</f>
-        <v>1644.91</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="66" t="s">
-        <v>432</v>
-      </c>
-      <c r="B162" s="66"/>
-      <c r="C162" s="7" t="n">
-        <f aca="false">H87+H123+SUMPRODUCT(F134:F147,G134:G147)</f>
-        <v>2368.665</v>
-      </c>
-      <c r="D162" s="7" t="n">
-        <f aca="false">H93+H129</f>
-        <v>440.66</v>
-      </c>
-      <c r="E162" s="67" t="n">
-        <f aca="false">ROUND(C162*0.0775,2)</f>
-        <v>183.57</v>
-      </c>
-      <c r="F162" s="67"/>
-      <c r="G162" s="7" t="n">
-        <f aca="false">ROUND((C162+D162+E162)*0.1,2)</f>
-        <v>299.29</v>
-      </c>
-      <c r="H162" s="68" t="n">
-        <f aca="false">C162+D162+E162+G162</f>
-        <v>3292.185</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="66" t="s">
-        <v>433</v>
-      </c>
-      <c r="B163" s="66"/>
-      <c r="C163" s="7" t="n">
-        <f aca="false">H87+H123</f>
-        <v>1546.755</v>
-      </c>
-      <c r="D163" s="7" t="n">
-        <f aca="false">H93+H129</f>
-        <v>440.66</v>
-      </c>
-      <c r="E163" s="67" t="n">
-        <f aca="false">ROUND(C163*0.0775,2)</f>
-        <v>119.87</v>
-      </c>
-      <c r="F163" s="67"/>
-      <c r="G163" s="7" t="n">
-        <f aca="false">ROUND((C163+D163+E163)*0.1,2)</f>
-        <v>210.73</v>
-      </c>
-      <c r="H163" s="68" t="n">
-        <f aca="false">C163+D163+E163+G163</f>
-        <v>2318.015</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="38" t="s">
-        <v>434</v>
-      </c>
-      <c r="B164" s="38"/>
-      <c r="C164" s="38"/>
-      <c r="D164" s="38"/>
-      <c r="E164" s="38"/>
-      <c r="F164" s="38"/>
-      <c r="G164" s="38"/>
-      <c r="H164" s="38"/>
-      <c r="I164" s="38"/>
-      <c r="J164" s="38"/>
-      <c r="K164" s="38"/>
+      <c r="I167" s="17"/>
+      <c r="J167" s="17"/>
+      <c r="K167" s="17"/>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="66" t="s">
+        <v>464</v>
+      </c>
+      <c r="B168" s="66"/>
+      <c r="C168" s="7" t="n">
+        <f aca="false">H95+SUMPRODUCT(F142:F155,G142:G155)</f>
+        <v>1922.44</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <f aca="false">H101</f>
+        <v>281.68</v>
+      </c>
+      <c r="E168" s="67" t="n">
+        <f aca="false">ROUND(C168*0.0775,2)</f>
+        <v>148.99</v>
+      </c>
+      <c r="F168" s="67"/>
+      <c r="G168" s="7" t="n">
+        <f aca="false">ROUND((C168+D168+E168)*0.1,2)</f>
+        <v>235.31</v>
+      </c>
+      <c r="H168" s="68" t="n">
+        <f aca="false">C168+D168+E168+G168</f>
+        <v>2588.42</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="66" t="s">
+        <v>465</v>
+      </c>
+      <c r="B169" s="66"/>
+      <c r="C169" s="7" t="n">
+        <f aca="false">H95</f>
+        <v>1217.75</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <f aca="false">H101</f>
+        <v>281.68</v>
+      </c>
+      <c r="E169" s="67" t="n">
+        <f aca="false">ROUND(C169*0.0775,2)</f>
+        <v>94.38</v>
+      </c>
+      <c r="F169" s="67"/>
+      <c r="G169" s="7" t="n">
+        <f aca="false">ROUND((C169+D169+E169)*0.1,2)</f>
+        <v>159.38</v>
+      </c>
+      <c r="H169" s="68" t="n">
+        <f aca="false">C169+D169+E169+G169</f>
+        <v>1753.19</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="66" t="s">
+        <v>466</v>
+      </c>
+      <c r="B170" s="66"/>
+      <c r="C170" s="7" t="n">
+        <f aca="false">H95+H131+SUMPRODUCT(F142:F155,G142:G155)</f>
+        <v>2334.555</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <f aca="false">H101+H137</f>
+        <v>449.54</v>
+      </c>
+      <c r="E170" s="67" t="n">
+        <f aca="false">ROUND(C170*0.0775,2)</f>
+        <v>180.93</v>
+      </c>
+      <c r="F170" s="67"/>
+      <c r="G170" s="7" t="n">
+        <f aca="false">ROUND((C170+D170+E170)*0.1,2)</f>
+        <v>296.5</v>
+      </c>
+      <c r="H170" s="68" t="n">
+        <f aca="false">C170+D170+E170+G170</f>
+        <v>3261.525</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B171" s="66"/>
+      <c r="C171" s="7" t="n">
+        <f aca="false">H95+H131</f>
+        <v>1629.865</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <f aca="false">H101+H137</f>
+        <v>449.54</v>
+      </c>
+      <c r="E171" s="67" t="n">
+        <f aca="false">ROUND(C171*0.0775,2)</f>
+        <v>126.31</v>
+      </c>
+      <c r="F171" s="67"/>
+      <c r="G171" s="7" t="n">
+        <f aca="false">ROUND((C171+D171+E171)*0.1,2)</f>
+        <v>220.57</v>
+      </c>
+      <c r="H171" s="68" t="n">
+        <f aca="false">C171+D171+E171+G171</f>
+        <v>2426.285</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A172" s="38" t="s">
+        <v>468</v>
+      </c>
+      <c r="B172" s="38"/>
+      <c r="C172" s="38"/>
+      <c r="D172" s="38"/>
+      <c r="E172" s="38"/>
+      <c r="F172" s="38"/>
+      <c r="G172" s="38"/>
+      <c r="H172" s="38"/>
+      <c r="I172" s="38"/>
+      <c r="J172" s="38"/>
+      <c r="K172" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -6681,24 +7079,24 @@
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B19:K19"/>
     <mergeCell ref="B20:K20"/>
-    <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B94:K94"/>
-    <mergeCell ref="A97:K97"/>
-    <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="A160:B160"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="A161:B161"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="A162:B162"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="A163:B163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="A164:K164"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B102:K102"/>
+    <mergeCell ref="A105:K105"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B136:E136"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="A168:B168"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="A169:B169"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="A170:B170"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="A171:B171"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="A172:K172"/>
   </mergeCells>
   <conditionalFormatting sqref="A24:J24">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6750,19 +7148,19 @@
       <formula>$K36="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A40:J40">
+  <conditionalFormatting sqref="A37:J37">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K40="No"</formula>
+      <formula>$K37="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41:J41">
+  <conditionalFormatting sqref="A38:J38">
     <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K41="No"</formula>
+      <formula>$K38="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A42:J42">
+  <conditionalFormatting sqref="A39:J39">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K42="No"</formula>
+      <formula>$K39="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:J43">
@@ -6775,24 +7173,24 @@
       <formula>$K44="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48:J48">
+  <conditionalFormatting sqref="A45:J45">
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K48="No"</formula>
+      <formula>$K45="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:J49">
+  <conditionalFormatting sqref="A46:J46">
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K49="No"</formula>
+      <formula>$K46="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50:J50">
+  <conditionalFormatting sqref="A47:J47">
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K50="No"</formula>
+      <formula>$K47="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A51:J51">
+  <conditionalFormatting sqref="A48:J48">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K51="No"</formula>
+      <formula>$K48="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:J52">
@@ -6805,29 +7203,29 @@
       <formula>$K53="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A54:J54">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K54="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55:J55">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K55="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56:J56">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K56="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A57:J57">
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K57="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58:J58">
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K58="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59:J59">
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K59="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A60:J60">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K60="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A61:J61">
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K61="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A62:J62">
@@ -6880,84 +7278,84 @@
       <formula>$K71="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A72:J72">
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K72="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A73:J73">
+    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K73="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74:J74">
+    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K74="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A75:J75">
-    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K75="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A76:J76">
-    <cfRule type="expression" priority="39" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K76="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A77:J77">
-    <cfRule type="expression" priority="40" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K77="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A81:J81">
-    <cfRule type="expression" priority="41" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K81="No"</formula>
+  <conditionalFormatting sqref="A78:J78">
+    <cfRule type="expression" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K78="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A82:J82">
-    <cfRule type="expression" priority="42" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K82="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A83:J83">
-    <cfRule type="expression" priority="43" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K83="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A84:J84">
-    <cfRule type="expression" priority="44" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K84="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A101:J101">
-    <cfRule type="expression" priority="45" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K101="No"</formula>
+  <conditionalFormatting sqref="A85:J85">
+    <cfRule type="expression" priority="48" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K85="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A103:J103">
-    <cfRule type="expression" priority="46" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K103="No"</formula>
+  <conditionalFormatting sqref="A89:J89">
+    <cfRule type="expression" priority="49" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K89="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A104:J104">
-    <cfRule type="expression" priority="47" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K104="No"</formula>
+  <conditionalFormatting sqref="A90:J90">
+    <cfRule type="expression" priority="50" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K90="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A105:J105">
-    <cfRule type="expression" priority="48" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K105="No"</formula>
+  <conditionalFormatting sqref="A91:J91">
+    <cfRule type="expression" priority="51" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K91="No"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A106:J106">
-    <cfRule type="expression" priority="49" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K106="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A107:J107">
-    <cfRule type="expression" priority="50" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K107="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A108:J108">
-    <cfRule type="expression" priority="51" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K108="No"</formula>
+  <conditionalFormatting sqref="A92:J92">
+    <cfRule type="expression" priority="52" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K92="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A109:J109">
-    <cfRule type="expression" priority="52" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="53" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K109="No"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A110:J110">
-    <cfRule type="expression" priority="53" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>$K110="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A111:J111">
@@ -6975,45 +7373,85 @@
       <formula>$K113="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A114:J114">
+    <cfRule type="expression" priority="57" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K114="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A115:J115">
-    <cfRule type="expression" priority="57" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="58" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K115="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A116:J116">
-    <cfRule type="expression" priority="58" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K116="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A117:J117">
-    <cfRule type="expression" priority="59" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="60" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K117="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A118:J118">
+    <cfRule type="expression" priority="61" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K118="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A119:J119">
-    <cfRule type="expression" priority="60" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="62" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K119="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A120:J120">
-    <cfRule type="expression" priority="61" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="63" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K120="No"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A121:J121">
+    <cfRule type="expression" priority="64" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K121="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A123:J123">
+    <cfRule type="expression" priority="65" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K123="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A124:J124">
+    <cfRule type="expression" priority="66" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K124="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A125:J125">
+    <cfRule type="expression" priority="67" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K125="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A127:J127">
+    <cfRule type="expression" priority="68" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K127="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A128:J128">
+    <cfRule type="expression" priority="69" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>$K128="No"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K98" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K106" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K122" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K130" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K134:K147" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K142:K155" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24:K25 K29:K36 K40:K44 K48:K53 K57:K71 K75:K77 K81:K84 K101 K103:K113 K115:K117 K119:K120" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K24:K25 K29:K39 K43:K48 K52:K58 K62:K78 K82:K85 K89:K92 K109 K111:K121 K123:K125 K127:K128" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
